--- a/接口序号图.xlsx
+++ b/接口序号图.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\~Terminal's SSD~\Tewlet\CubeMX program\engineer_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6420FCD3-EAB9-4800-8C8B-7C345F99CBEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B722BA02-2D40-478C-95F0-BBD3D97D2522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -128,13 +128,13 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -217,8 +217,8 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>133158</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="10" name="墨迹 9">
@@ -237,7 +237,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="10" name="墨迹 9">
@@ -282,8 +282,8 @@
       <xdr:row>5</xdr:row>
       <xdr:rowOff>77113</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="17" name="墨迹 16">
@@ -302,7 +302,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="17" name="墨迹 16">
@@ -347,8 +347,8 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>18376</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="18" name="墨迹 17">
@@ -367,7 +367,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="18" name="墨迹 17">
@@ -412,8 +412,8 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>177240</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="23" name="墨迹 22">
@@ -432,7 +432,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="23" name="墨迹 22">
@@ -477,8 +477,8 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>44656</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="28" name="墨迹 27">
@@ -497,7 +497,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="28" name="墨迹 27">
@@ -542,8 +542,8 @@
       <xdr:row>59</xdr:row>
       <xdr:rowOff>45511</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="29" name="墨迹 28">
@@ -562,7 +562,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="29" name="墨迹 28">
@@ -607,8 +607,8 @@
       <xdr:row>62</xdr:row>
       <xdr:rowOff>70539</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="34" name="墨迹 33">
@@ -627,7 +627,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="34" name="墨迹 33">
@@ -672,8 +672,8 @@
       <xdr:row>62</xdr:row>
       <xdr:rowOff>158019</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="39" name="墨迹 38">
@@ -692,7 +692,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="39" name="墨迹 38">
@@ -728,14 +728,14 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>560945</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>143719</xdr:rowOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>36159</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>238312</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>19346</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>624305</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>165759</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
@@ -752,8 +752,8 @@
           </xdr14:nvContentPartPr>
           <xdr14:nvPr macro=""/>
           <xdr14:xfrm>
-            <a:off x="9497880" y="7796849"/>
-            <a:ext cx="1052280" cy="422280"/>
+            <a:off x="9146145" y="7859359"/>
+            <a:ext cx="63360" cy="129600"/>
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
@@ -777,73 +777,8 @@
           </xdr:blipFill>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9491758" y="7790724"/>
-              <a:ext cx="1064524" cy="434530"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>451072</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123199</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>246736</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>124466</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId20">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="60" name="墨迹 59">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4371E681-9AC0-8A53-1AD1-228B4D09004B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="10762920" y="7776329"/>
-            <a:ext cx="483120" cy="547920"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="60" name="墨迹 59">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4371E681-9AC0-8A53-1AD1-228B4D09004B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="10756800" y="7770209"/>
-              <a:ext cx="495360" cy="560160"/>
+              <a:off x="9140025" y="7853239"/>
+              <a:ext cx="75600" cy="141840"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -857,19 +792,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>288136</xdr:colOff>
+      <xdr:colOff>516016</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>51559</xdr:rowOff>
+      <xdr:rowOff>158479</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>40023</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>99626</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>617016</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>141999</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId22">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId20">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="89" name="墨迹 88">
               <a:extLst>
@@ -882,8 +817,8 @@
           </xdr14:nvContentPartPr>
           <xdr14:nvPr macro=""/>
           <xdr14:xfrm>
-            <a:off x="11287440" y="7704689"/>
-            <a:ext cx="1126800" cy="594720"/>
+            <a:off x="11082416" y="7626079"/>
+            <a:ext cx="761400" cy="339120"/>
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
@@ -900,15 +835,15 @@
             <xdr:cNvPicPr/>
           </xdr:nvPicPr>
           <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
             <a:stretch>
               <a:fillRect/>
             </a:stretch>
           </xdr:blipFill>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11281320" y="7698569"/>
-              <a:ext cx="1139040" cy="606960"/>
+              <a:off x="11076296" y="7619959"/>
+              <a:ext cx="773640" cy="351360"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -932,9 +867,9 @@
       <xdr:row>48</xdr:row>
       <xdr:rowOff>4362</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId24">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId22">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="136" name="墨迹 135">
               <a:extLst>
@@ -952,7 +887,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="136" name="墨迹 135">
@@ -997,8 +932,8 @@
       <xdr:row>53</xdr:row>
       <xdr:rowOff>101132</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId26">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="144" name="墨迹 143">
@@ -1017,7 +952,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="144" name="墨迹 143">
@@ -1062,8 +997,8 @@
       <xdr:row>53</xdr:row>
       <xdr:rowOff>79892</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId28">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="149" name="墨迹 148">
@@ -1082,7 +1017,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="149" name="墨迹 148">
@@ -1127,8 +1062,8 @@
       <xdr:row>58</xdr:row>
       <xdr:rowOff>171981</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId30">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="164" name="墨迹 163">
@@ -1147,7 +1082,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="164" name="墨迹 163">
@@ -1192,8 +1127,8 @@
       <xdr:row>63</xdr:row>
       <xdr:rowOff>70391</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId32">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="184" name="墨迹 183">
@@ -1212,7 +1147,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="184" name="墨迹 183">
@@ -1332,6 +1267,981 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>32810</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>6155</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>249015</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>47054</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId36">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="3" name="墨迹 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74E40F73-F01E-C622-64EE-C51F332E3FBB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="5292104" y="8432979"/>
+            <a:ext cx="2188440" cy="1833840"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="3" name="墨迹 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74E40F73-F01E-C622-64EE-C51F332E3FBB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId37"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5286009" y="8426809"/>
+              <a:ext cx="2200630" cy="1846179"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>637815</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>60875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>352179</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>112299</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId38">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="27" name="墨迹 26">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{280FA13B-BBE1-2160-0193-D0FF0B42C9B8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="7869344" y="8487699"/>
+            <a:ext cx="1686600" cy="768600"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="27" name="墨迹 26">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{280FA13B-BBE1-2160-0193-D0FF0B42C9B8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId39"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7863224" y="8481579"/>
+              <a:ext cx="1698840" cy="780840"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>285579</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>159169</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>623928</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>74499</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId40">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="30" name="墨迹 29">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D03B5B8-CF20-AD71-FCA7-97B5C1BD57BF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="9489344" y="10558228"/>
+            <a:ext cx="995760" cy="811800"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="30" name="墨迹 29">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D03B5B8-CF20-AD71-FCA7-97B5C1BD57BF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId41"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9483224" y="10552108"/>
+              <a:ext cx="1008000" cy="824040"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>583351</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>175369</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>279252</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>84522</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId42">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="90" name="墨迹 89">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3630B016-8585-F8B7-B044-1563E95418A9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="9129704" y="11650193"/>
+            <a:ext cx="2982960" cy="1522800"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="90" name="墨迹 89">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3630B016-8585-F8B7-B044-1563E95418A9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId43"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9123615" y="11644019"/>
+              <a:ext cx="2995138" cy="1535148"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>250906</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>49209</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>308866</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>121209</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId44">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="95" name="墨迹 94">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99D93957-55C0-B082-40C5-C5F297117CA7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="10142252" y="8665671"/>
+            <a:ext cx="57960" cy="72000"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="95" name="墨迹 94">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99D93957-55C0-B082-40C5-C5F297117CA7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId45"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10136132" y="8659551"/>
+              <a:ext cx="70200" cy="84240"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>596866</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>55689</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>383317</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>152225</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId46">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="112" name="墨迹 111">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9594175-C110-F91D-44F9-3B61257F142D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="10488212" y="8672151"/>
+            <a:ext cx="1764720" cy="799920"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="112" name="墨迹 111">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9594175-C110-F91D-44F9-3B61257F142D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10482072" y="8666137"/>
+              <a:ext cx="1777000" cy="811949"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>457874</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>162213</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>342</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>174516</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId48">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="152" name="墨迹 151">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE194354-DFD1-6E40-6BD5-3241FDF206A4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="7061874" y="3540413"/>
+            <a:ext cx="2184068" cy="545703"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="152" name="墨迹 151">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE194354-DFD1-6E40-6BD5-3241FDF206A4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId49"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7055744" y="3534224"/>
+              <a:ext cx="2196328" cy="558081"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>16470</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>145550</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>97394</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId50">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="163" name="墨迹 162">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D51B8B8-7016-8C17-E1F0-0ED83FCAE912}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="9262070" y="3378200"/>
+            <a:ext cx="789480" cy="630794"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="163" name="墨迹 162">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D51B8B8-7016-8C17-E1F0-0ED83FCAE912}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId51"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9255950" y="3372079"/>
+              <a:ext cx="801720" cy="643035"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>151470</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>36690</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>39710</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>124370</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId52">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="190" name="墨迹 189">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F22AFCC0-90C2-0970-50AF-E0F8A47ABD17}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="9397070" y="4126090"/>
+            <a:ext cx="548640" cy="1332280"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="190" name="墨迹 189">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F22AFCC0-90C2-0970-50AF-E0F8A47ABD17}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId53"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9390950" y="4119969"/>
+              <a:ext cx="560880" cy="1344523"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>649160</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>58720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>237200</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>66760</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId54">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="208" name="墨迹 207">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D476F122-3573-82BF-84A3-9405CB18CEB5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="9234360" y="7704120"/>
+            <a:ext cx="1569240" cy="541440"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="208" name="墨迹 207">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D476F122-3573-82BF-84A3-9405CB18CEB5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId55"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9228240" y="7698004"/>
+              <a:ext cx="1581480" cy="553672"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>506800</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>107280</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>560080</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>126720</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId56">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="209" name="墨迹 208">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0E0D8F3-47C1-1A90-EBD3-596E7EBA4068}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="3808800" y="7041480"/>
+            <a:ext cx="53280" cy="19440"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="209" name="墨迹 208">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0E0D8F3-47C1-1A90-EBD3-596E7EBA4068}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId57"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3802680" y="7035360"/>
+              <a:ext cx="65520" cy="31680"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>319680</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>107080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>438160</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>42080</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId58">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="224" name="墨迹 223">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{994F4147-3D6F-25F4-C325-09BD4946E415}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="319680" y="9352680"/>
+            <a:ext cx="1439280" cy="2246400"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="224" name="墨迹 223">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{994F4147-3D6F-25F4-C325-09BD4946E415}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId59"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="313560" y="9346560"/>
+              <a:ext cx="1451520" cy="2258640"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>659560</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>3840</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>195920</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>154400</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId60">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="236" name="墨迹 235">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9A083EA-939D-8454-031E-73B01F452F4D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="1980360" y="11205240"/>
+            <a:ext cx="857160" cy="506160"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="236" name="墨迹 235">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9A083EA-939D-8454-031E-73B01F452F4D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId61"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1974240" y="11199116"/>
+              <a:ext cx="869400" cy="518409"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>505440</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>163160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>116320</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>68480</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId62">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="237" name="墨迹 236">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B1AED56-2A8B-C04A-A2F9-2598F8445772}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="505440" y="518760"/>
+            <a:ext cx="931680" cy="1505520"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="237" name="墨迹 236">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B1AED56-2A8B-C04A-A2F9-2598F8445772}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId63"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="499320" y="512640"/>
+              <a:ext cx="943920" cy="1517760"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>504720</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>153120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>402200</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>27320</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId64">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="273" name="墨迹 272">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27829E0E-9FDB-0919-E145-1C7951064F91}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="504720" y="2286720"/>
+            <a:ext cx="2539080" cy="763200"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="273" name="墨迹 272">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27829E0E-9FDB-0919-E145-1C7951064F91}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId65"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="498600" y="2280600"/>
+              <a:ext cx="2551320" cy="775440"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1394,8 +2304,8 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>83070</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="5" name="墨迹 4">
@@ -1414,7 +2324,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="5" name="墨迹 4">
@@ -1459,8 +2369,8 @@
       <xdr:row>5</xdr:row>
       <xdr:rowOff>144885</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="14" name="墨迹 13">
@@ -1479,7 +2389,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="14" name="墨迹 13">
@@ -1524,8 +2434,8 @@
       <xdr:row>3</xdr:row>
       <xdr:rowOff>132075</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="22" name="墨迹 21">
@@ -1544,7 +2454,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="22" name="墨迹 21">
@@ -1589,8 +2499,8 @@
       <xdr:row>3</xdr:row>
       <xdr:rowOff>132795</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="30" name="墨迹 29">
@@ -1609,7 +2519,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="30" name="墨迹 29">
@@ -1716,13 +2626,13 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">2780 623 160 0 0,'-14'-28'7785'0'0,"-29"33"-2993"0"0,-122 1-1193 0 0,-81 24-2605 0 0,34-8-159 0 0,143-17-494 0 0,-277 18 1248 0 0,-315 0-181 0 0,635-23-1356 0 0,-1 1 1 0 0,0 1-1 0 0,0 1 1 0 0,1 2 0 0 0,0 0-1 0 0,-32 11 1 0 0,40-8-59 0 0,1 1 0 0 0,-1 1 0 0 0,2 0 0 0 0,-1 1 0 0 0,1 1 0 0 0,1 0 0 0 0,-18 19 0 0 0,-90 111 67 0 0,65-71 141 0 0,24-32-75 0 0,12-16-56 0 0,2 1 0 0 0,0 1 1 0 0,-24 42-1 0 0,18-17-84 0 0,-100 207 45 0 0,56-116-28 0 0,38-67-9 0 0,16-38 0 0 0,-15 47 1 0 0,22-51 0 0 0,1 0 0 0 0,2 1-1 0 0,1 0 1 0 0,-1 50 0 0 0,6-60 0 0 0,1-1 0 0 0,2 1 0 0 0,0-1 0 0 0,2 1 0 0 0,0-1 0 0 0,1-1 0 0 0,15 35 0 0 0,-1-17 27 0 0,0 0 1 0 0,3-2-1 0 0,1 0 0 0 0,57 65 1 0 0,-70-91-18 0 0,-1-1-1 0 0,1-1 1 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,21 9-1 0 0,-2-2 17 0 0,53 17-1 0 0,545 142 437 0 0,-246-74-67 0 0,596 150 320 0 0,65-43 149 0 0,-656-154-563 0 0,216 35 102 0 0,-233-32-257 0 0,543 39 64 0 0,-100-72-21 0 0,-301-1-50 0 0,557 11 109 0 0,-362-5-107 0 0,-38-17-113 0 0,-413-13-13 0 0,-96 1 0 0 0,363 16-21 0 0,-315 0 88 0 0,336-17 0 0 0,-193-29 123 0 0,-161 12-58 0 0,189-22 113 0 0,616-56 139 0 0,-68-57-187 0 0,-534 80-155 0 0,-41 25-51 0 0,-50 8 0 0 0,-202 23 27 0 0,177-54 1 0 0,-223 53-18 0 0,0-3 0 0 0,-1-3 0 0 0,-1-1 0 0 0,77-54 1 0 0,-74 42-7 0 0,203-157 52 0 0,-223 164-60 0 0,60-58 3 0 0,-85 77 12 0 0,-1 0 0 0 0,0-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,8-18 0 0 0,-13 23 3 0 0,0-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-5-18 0 0 0,-5-10 8 0 0,-26-62 0 0 0,10 30 8 0 0,-83-210 599 0 0,87 231-462 0 0,-2 2 0 0 0,-2 1 0 0 0,-55-70 0 0 0,-14-6-58 0 0,-70-81 47 0 0,99 132-39 0 0,-119-99 0 0 0,101 108-72 0 0,-137-75-1 0 0,115 74-29 0 0,-202-106 26 0 0,300 165-42 0 0,-491-220 23 0 0,429 197-31 0 0,-84-28 6 0 0,-546-102-23 0 0,168 57 56 0 0,333 61-29 0 0,-98-13-31 0 0,224 44 14 0 0,-671-43-20 0 0,354 37 15 0 0,-389 14-48 0 0,327 14 98 0 0,-838 4-79 0 0,706-9 92 0 0,-445-4-88 0 0,537 4 76 0 0,303-7-50 0 0,1 9 1 0 0,-214 39 0 0 0,-93 27-43 0 0,419-67 39 0 0,-537 92-86 0 0,470-63 98 0 0,66-16-5 0 0,-158 25 0 0 0,-179 16-77 0 0,384-58 104 0 0,0-1 0 0 0,-52 1 0 0 0,42-3-34 0 0,1 1 0 0 0,0 2 0 0 0,0 2 0 0 0,-69 23 0 0 0,-2-1 3 0 0,22-3 22 0 0,53-14-2 0 0,-40 7-1 0 0,-187 43-72 0 0,-60 11-2653 0 0,296-70 1597 0 0,-1-2 0 0 0,-41-1-1 0 0,-13-9-6025 0 0,80 8 6684 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-3 0 0 0,1-25-2407 0 0,4 17 2239 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1139.62">16243 1783 28 0 0,'-6'-2'568'0'0,"1"0"0"0"0,0 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,-1 0 1 0 0,-10-1 0 0 0,-17 2 14244 0 0,41 2-11164 0 0,43 8-2214 0 0,381-24 2683 0 0,-198 3-3519 0 0,237 18 0 0 0,303 96 29 0 0,-395-46 393 0 0,-368-55-986 0 0,717 115 1842 0 0,-592-85-1876 0 0,136 51 0 0 0,-235-70 0 0 0,298 96 0 0 0,-256-87 0 0 0,0-4 0 0 0,109 10 0 0 0,114-13-1007 0 0,-301-15 332 0 0,-9-28-10033 0 0,2 14 7491 0 0,0 0 1 0 0,-1 0-1 0 0,-16-25 1 0 0,-34-36-3862 0 0,47 62 6645 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1472.61">20655 1751 428 0 0,'-8'-2'1621'0'0,"0"-1"1"0"0,0 1-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 1 0 0,-14 0-1 0 0,21 1 68 0 0,-3 9 6988 0 0,125 88-3346 0 0,-23-20-3196 0 0,14 14-317 0 0,57 51-478 0 0,-163-137-1340 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,2 6 0 0 0,-4-10 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-3 1 0 0 0,0 2 0 0 0,-16 9 0 0 0,0 0 0 0 0,-1-1 0 0 0,-25 9 0 0 0,-31 16 0 0 0,-58 35-251 0 0,-107 62-4092 0 0,131-52-1850 0 0,83-57 1061 0 0,-44 50-1 0 0,61-62 2204 0 0,13-17-802 0 0,17-23-1000 0 0,-14 21 5229 0 0,12-15-1220 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2270.02">22702 2245 152 0 0,'18'-26'1287'0'0,"-8"14"646"0"0,-1-1-1 0 0,0-1 1 0 0,-1 0-1 0 0,-1 0 1 0 0,0-1-1 0 0,9-28 1 0 0,-16 40-1653 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 1 0 0 0,-1-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,-5-2-1 0 0,-3-1 209 0 0,1 0-1 0 0,-1 0 1 0 0,0 1-1 0 0,0 1 0 0 0,0 0 1 0 0,-1 0-1 0 0,-12 1 0 0 0,0 2-114 0 0,-1 1 0 0 0,1 1 0 0 0,0 1-1 0 0,-1 1 1 0 0,2 2 0 0 0,-1 0 0 0 0,1 1 0 0 0,0 2-1 0 0,1 0 1 0 0,0 1 0 0 0,-28 19 0 0 0,4 3-268 0 0,1 2 0 0 0,1 2 0 0 0,-67 75 0 0 0,79-77-106 0 0,3 2 0 0 0,0 0 0 0 0,3 2 0 0 0,1 1 0 0 0,2 1 0 0 0,-18 46 0 0 0,30-59 0 0 0,1 0 0 0 0,1 1 0 0 0,1 0 0 0 0,2 0 0 0 0,1 1 0 0 0,1 0 0 0 0,2 0 0 0 0,1 0 0 0 0,1 0 0 0 0,6 41 0 0 0,-5-63-4 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,1 0 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 1 1 0 0,2-1-1 0 0,-1-1 1 0 0,0 1-1 0 0,1 0 0 0 0,0-1 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1-1 1 0 0,1 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,14 2 1 0 0,-1-1-309 0 0,1-1 1 0 0,-1-1-1 0 0,1-1 1 0 0,0 0-1 0 0,-1-2 1 0 0,1 0-1 0 0,-1-2 1 0 0,33-9-1 0 0,28-14-4200 0 0,111-54 0 0 0,-47 17-3911 0 0,-132 59 7473 0 0,1 1-1 0 0,0 0 1 0 0,0 1-1 0 0,1 0 0 0 0,-1 1 1 0 0,0 1-1 0 0,1 0 1 0 0,0 1-1 0 0,-1 0 1 0 0,1 1-1 0 0,14 4 1 0 0,-9 2 265 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2969.03">23836 2218 120 0 0,'-12'-24'2716'0'0,"10"7"4721"0"0,1 15-7073 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-4 0 0 0 0,-4 0 151 0 0,0 1-1 0 0,0 1 0 0 0,1-1 0 0 0,-1 2 0 0 0,0-1 1 0 0,1 1-1 0 0,0 0 0 0 0,-13 7 0 0 0,-63 41 269 0 0,61-36-420 0 0,-17 12 83 0 0,2 2 1 0 0,0 1-1 0 0,2 2 0 0 0,2 1 0 0 0,-53 65 0 0 0,70-75-274 0 0,1 0-1 0 0,1 0 1 0 0,1 1-1 0 0,1 1 1 0 0,1 0-1 0 0,1 1 0 0 0,2 1 1 0 0,0-1-1 0 0,2 1 1 0 0,1 0-1 0 0,-3 33 1 0 0,8-45-131 0 0,1 1 1 0 0,1-1-1 0 0,0 0 0 0 0,1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,1-1 1 0 0,0 1-1 0 0,12 20 0 0 0,-14-28-28 0 0,1-1-1 0 0,-1 1 1 0 0,2-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,1-1 1 0 0,-1 0-1 0 0,12 1 1 0 0,-2-4-55 0 0,0 0 0 0 0,0 0 0 0 0,0-2 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1-2 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-2 0 0 0,-1 0 0 0 0,1 0 0 0 0,-2-1 0 0 0,1-1 0 0 0,22-24 0 0 0,6-10-572 0 0,-3-1 0 0 0,-1-2 0 0 0,34-59 0 0 0,-36 51-27 0 0,-2-2 0 0 0,-3 0 0 0 0,-3-3 0 0 0,-2 0 1 0 0,20-71-1 0 0,-43 117 598 0 0,1 3 68 0 0,0-1 1 0 0,-1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,-2-17 0 0 0,2 30 15 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 2 20 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 3 0 0 0,-4 4 143 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-4 11 0 0 0,9-19-198 0 0,-40 131 1224 0 0,37-116-1113 0 0,0 0 1 0 0,1 0 0 0 0,1 1-1 0 0,0-1 1 0 0,1 1 0 0 0,4 22-1 0 0,3 5 117 0 0,24 81-1 0 0,-26-109-351 0 0,1-1 0 0 0,0 0-1 0 0,1-1 1 0 0,1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,1-1 0 0 0,19 21-1 0 0,-26-31-124 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,5-1 0 0 0,-4-1-579 0 0,1 0 0 0 0,-1 0-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,5-7-1 0 0,86-106-9093 0 0,-85 99 9198 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3641.12">24871 2117 100 0 0,'-8'-5'10078'0'0,"14"17"-3321"0"0,-4-1-7872 0 0,-2 10 2297 0 0,1 3-327 0 0,-2 0-1 0 0,0 0 0 0 0,-2 0 1 0 0,-7 34-1 0 0,-6-1-108 0 0,-84 273 854 0 0,66-229-1334 0 0,58-133-287 0 0,149-211-322 0 0,-169 238 336 0 0,66-86-81 0 0,5 3-1 0 0,99-92 1 0 0,-165 172 88 0 0,1-1 0 0 0,0 2 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1 2 0 0 0,21-9 0 0 0,-30 13 19 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,4 2 0 0 0,-3-1 32 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,-1 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,1 4 1 0 0,3 16 375 0 0,-1 0 0 0 0,-1 0 0 0 0,-1 1 0 0 0,-2 0 0 0 0,-3 37 0 0 0,-25 125 1152 0 0,16-119-1206 0 0,-7 34-34 0 0,-21 164-877 0 0,34-142-4301 0 0,6-124 4652 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,1 0 0 0 0,18-11-4277 0 0,23-29 1468 0 0,-36 34 1741 0 0,78-87-3155 0 0,-60 69 3718 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4141.92">26515 1985 124 0 0,'5'-19'2009'0'0,"9"18"383"0"0,23 26 2376 0 0,-13-8-2620 0 0,97 45 4412 0 0,-71-35-4406 0 0,73 53 0 0 0,-113-73-1960 0 0,0 1 0 0 0,-1 0 0 0 0,0 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,12 21 0 0 0,-16-25-115 0 0,-1 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,-4 11 0 0 0,-10 17 142 0 0,-1-1 1 0 0,-1-1-1 0 0,-41 55 1 0 0,-82 81-47 0 0,106-129-167 0 0,4-5 15 0 0,-1-1 1 0 0,-2-1-1 0 0,-1-2 1 0 0,-1-2 0 0 0,-48 29-1 0 0,80-55 81 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-7 0 1494 0 0,54 12-351 0 0,81 7 400 0 0,113 11-1095 0 0,-32-12-541 0 0,-125-9-364 0 0,0-4 1 0 0,125-5-1 0 0,-194-2-460 0 0,1-1 1 0 0,-1 0 0 0 0,0 0 0 0 0,15-5 0 0 0,3-10-3866 0 0,-8-10-3527 0 0,-25 11 2309 0 0,-15-5 2039 0 0,-24 2 95 0 0,21 14 2953 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">2689 618 160 0 0,'-14'-27'7785'0'0,"-27"31"-2993"0"0,-119 2-1193 0 0,-78 24-2605 0 0,33-8-159 0 0,139-17-494 0 0,-269 18 1248 0 0,-304 0-181 0 0,613-23-1356 0 0,0 1 1 0 0,0 1-1 0 0,0 1 1 0 0,1 2 0 0 0,0 0-1 0 0,-31 10 1 0 0,38-7-59 0 0,2 1 0 0 0,-2 1 0 0 0,3 0 0 0 0,-2 1 0 0 0,2 1 0 0 0,0 0 0 0 0,-16 19 0 0 0,-88 110 67 0 0,62-71 141 0 0,25-31-75 0 0,10-16-56 0 0,3 0 0 0 0,0 2 1 0 0,-24 42-1 0 0,18-18-84 0 0,-97 206 45 0 0,54-115-28 0 0,37-66-9 0 0,16-39 0 0 0,-15 48 1 0 0,21-51 0 0 0,1-1 0 0 0,3 2-1 0 0,0 0 1 0 0,-1 49 0 0 0,6-59 0 0 0,1-1 0 0 0,2 1 0 0 0,0-1 0 0 0,2 0 0 0 0,-1 0 0 0 0,2-1 0 0 0,15 35 0 0 0,-2-18 27 0 0,0 1 1 0 0,3-2-1 0 0,2-1 0 0 0,54 66 1 0 0,-67-91-18 0 0,-2-1-1 0 0,2-2 1 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,20 9-1 0 0,-2-2 17 0 0,51 17-1 0 0,527 141 437 0 0,-237-74-67 0 0,576 149 320 0 0,63-43 149 0 0,-635-152-563 0 0,209 34 102 0 0,-225-31-257 0 0,525 38 64 0 0,-97-71-21 0 0,-290-1-50 0 0,538 11 109 0 0,-351-6-107 0 0,-36-16-113 0 0,-399-13-13 0 0,-93 1 0 0 0,351 16-21 0 0,-305 0 88 0 0,325-17 0 0 0,-187-29 123 0 0,-155 12-58 0 0,183-21 113 0 0,595-57 139 0 0,-65-55-187 0 0,-517 78-155 0 0,-40 26-51 0 0,-48 7 0 0 0,-195 23 27 0 0,171-53 1 0 0,-216 52-18 0 0,0-3 0 0 0,0-3 0 0 0,-2-1 0 0 0,75-53 1 0 0,-72 41-7 0 0,196-155 52 0 0,-215 162-60 0 0,58-58 3 0 0,-82 78 12 0 0,-2-1 0 0 0,1-1 1 0 0,-1 0-1 0 0,-1 0 1 0 0,0-1-1 0 0,8-18 0 0 0,-14 23 3 0 0,1-1 0 0 0,-1 2 0 0 0,0-2 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-5-18 0 0 0,-4-9 8 0 0,-26-63 0 0 0,10 31 8 0 0,-81-209 599 0 0,85 229-462 0 0,-2 3 0 0 0,-2 0 0 0 0,-53-69 0 0 0,-14-6-58 0 0,-68-81 47 0 0,96 132-39 0 0,-115-99 0 0 0,98 108-72 0 0,-133-75-1 0 0,112 73-29 0 0,-196-105 26 0 0,290 165-42 0 0,-474-220 23 0 0,414 196-31 0 0,-81-27 6 0 0,-528-102-23 0 0,163 57 56 0 0,321 60-29 0 0,-94-13-31 0 0,216 45 14 0 0,-648-44-20 0 0,342 37 15 0 0,-377 14-48 0 0,317 14 98 0 0,-811 4-79 0 0,683-9 92 0 0,-430-4-88 0 0,519 4 76 0 0,293-7-50 0 0,2 8 1 0 0,-208 40 0 0 0,-90 27-43 0 0,406-68 39 0 0,-520 93-86 0 0,454-64 98 0 0,65-15-5 0 0,-153 25 0 0 0,-174 15-77 0 0,372-57 104 0 0,0-1 0 0 0,-50 1 0 0 0,40-3-34 0 0,2 1 0 0 0,-1 2 0 0 0,0 2 0 0 0,-66 23 0 0 0,-3-1 3 0 0,22-4 22 0 0,52-13-2 0 0,-40 7-1 0 0,-180 43-72 0 0,-59 10-2653 0 0,287-69 1597 0 0,-1-2 0 0 0,-40-1-1 0 0,-12-9-6025 0 0,77 8 6684 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-3 0 0 0,1-24-2407 0 0,4 16 2239 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1139.61">15711 1770 28 0 0,'-6'-2'568'0'0,"2"0"0"0"0,-1 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,-1 0 1 0 0,-9-1 0 0 0,-17 2 14244 0 0,40 2-11164 0 0,41 8-2214 0 0,369-24 2683 0 0,-192 3-3519 0 0,230 18 0 0 0,292 95 29 0 0,-381-46 393 0 0,-356-54-986 0 0,693 115 1842 0 0,-573-86-1876 0 0,132 52 0 0 0,-227-70 0 0 0,288 95 0 0 0,-247-86 0 0 0,-1-5 0 0 0,106 11 0 0 0,110-13-1007 0 0,-291-15 332 0 0,-9-28-10033 0 0,2 14 7491 0 0,1 1 1 0 0,-2-1-1 0 0,-15-25 1 0 0,-33-35-3862 0 0,45 61 6645 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1472.61">19979 1738 428 0 0,'-8'-2'1621'0'0,"0"-1"1"0"0,1 1-1 0 0,-2 0 0 0 0,1 0 0 0 0,-1 1 1 0 0,-13 0-1 0 0,20 1 68 0 0,-3 9 6988 0 0,121 87-3346 0 0,-22-19-3196 0 0,14 13-317 0 0,54 51-478 0 0,-157-136-1340 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-2 1 0 0 0,2-1 0 0 0,-1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,2 6 0 0 0,-4-10 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-3 1 0 0 0,0 2 0 0 0,-15 9 0 0 0,-1 0 0 0 0,0-1 0 0 0,-24 9 0 0 0,-31 15 0 0 0,-55 36-251 0 0,-104 61-4092 0 0,126-52-1850 0 0,81-56 1061 0 0,-43 49-1 0 0,60-61 2204 0 0,12-17-802 0 0,16-22-1000 0 0,-13 20 5229 0 0,11-15-1220 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2270.02">21959 2228 152 0 0,'17'-26'1287'0'0,"-7"14"646"0"0,-1-1-1 0 0,-1 0 1 0 0,0-1-1 0 0,-1 0 1 0 0,0-1-1 0 0,8-28 1 0 0,-15 40-1653 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 2 1 0 0,-1-2 0 0 0,1 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 1 0 0 0,-1-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,-4-2-1 0 0,-4-1 209 0 0,1 0-1 0 0,0 0 1 0 0,-1 1-1 0 0,0 1 0 0 0,1 0 1 0 0,-2 0-1 0 0,-11 1 0 0 0,0 2-114 0 0,-1 1 0 0 0,0 1 0 0 0,1 1-1 0 0,-1 1 1 0 0,2 2 0 0 0,-2 0 0 0 0,2 1 0 0 0,0 2-1 0 0,1 0 1 0 0,-1 0 0 0 0,-26 20 0 0 0,4 3-268 0 0,0 2 0 0 0,1 1 0 0 0,-64 76 0 0 0,76-78-106 0 0,3 3 0 0 0,0 0 0 0 0,3 1 0 0 0,1 2 0 0 0,1 1 0 0 0,-16 45 0 0 0,28-58 0 0 0,1 0 0 0 0,2 1 0 0 0,0-1 0 0 0,2 1 0 0 0,1 1 0 0 0,2 0 0 0 0,1-1 0 0 0,1 1 0 0 0,1 0 0 0 0,5 40 0 0 0,-4-62-4 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,1 0 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,0-1 1 0 0,0 1-1 0 0,1 0 0 0 0,0-1 1 0 0,0 0-1 0 0,1-1 0 0 0,-2 1 1 0 0,2-1-1 0 0,0 0 1 0 0,0 0-1 0 0,1-1 0 0 0,-2 0 1 0 0,2 0-1 0 0,0-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,15 2 1 0 0,-2-1-309 0 0,1-1 1 0 0,0-1-1 0 0,0-1 1 0 0,0 0-1 0 0,0-2 1 0 0,0 0-1 0 0,-1-2 1 0 0,33-9-1 0 0,26-13-4200 0 0,108-55 0 0 0,-46 18-3911 0 0,-127 58 7473 0 0,0 1-1 0 0,1 0 1 0 0,-1 1-1 0 0,2 0 0 0 0,-2 1 1 0 0,1 1-1 0 0,0 0 1 0 0,1 1-1 0 0,-2 0 1 0 0,2 1-1 0 0,13 4 1 0 0,-9 2 265 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2969.03">23056 2201 120 0 0,'-12'-24'2716'0'0,"10"8"4721"0"0,1 14-7073 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,2 1 0 0 0,-2 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-4 0 0 0 0,-3 0 151 0 0,-1 1-1 0 0,0 1 0 0 0,1-1 0 0 0,0 2 0 0 0,-1-1 1 0 0,1 1-1 0 0,1 0 0 0 0,-14 7 0 0 0,-60 40 269 0 0,59-35-420 0 0,-17 12 83 0 0,2 2 1 0 0,1 0-1 0 0,1 3 0 0 0,2 1 0 0 0,-51 64 0 0 0,67-74-274 0 0,2 0-1 0 0,0 0 1 0 0,2 0-1 0 0,0 2 1 0 0,2 0-1 0 0,0 1 0 0 0,2 1 1 0 0,0-1-1 0 0,3 0 1 0 0,0 1-1 0 0,-3 33 1 0 0,8-45-131 0 0,1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,13 19 0 0 0,-14-27-28 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 1 0 0,1 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,0-1 1 0 0,0-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,1-1 1 0 0,-1 0-1 0 0,11 1 1 0 0,-2-4-55 0 0,1 0 0 0 0,-1 0 0 0 0,1-2 0 0 0,-1 0-1 0 0,0-1 1 0 0,0 0 0 0 0,0-2 0 0 0,-2 0 0 0 0,2 0 0 0 0,-2-2 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,0-1 0 0 0,22-24 0 0 0,6-9-572 0 0,-4-2 0 0 0,0-1 0 0 0,33-60 0 0 0,-35 52-27 0 0,-3-3 0 0 0,-2 1 0 0 0,-2-4 0 0 0,-3 1 1 0 0,19-71-1 0 0,-41 116 598 0 0,1 3 68 0 0,0-1 1 0 0,-1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,-2-16 0 0 0,2 29 15 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 2 20 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 3 0 0 0,-4 4 143 0 0,1 0 0 0 0,0-1 0 0 0,0 2 0 0 0,-3 11 0 0 0,8-19-198 0 0,-39 130 1224 0 0,36-115-1113 0 0,0 0 1 0 0,1 0 0 0 0,1 1-1 0 0,0-1 1 0 0,1 1 0 0 0,4 21-1 0 0,3 6 117 0 0,23 80-1 0 0,-25-108-351 0 0,1-1 0 0 0,-1 0-1 0 0,2-2 1 0 0,1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,2-1 0 0 0,18 21-1 0 0,-25-31-124 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,1 0-1 0 0,-2 0 0 0 0,2 0 0 0 0,5-1 0 0 0,-4-1-579 0 0,1 0 0 0 0,-2 0-1 0 0,1-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-2 0 1 0 0,2-1 0 0 0,-1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,4-7-1 0 0,84-105-9093 0 0,-82 98 9198 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3641.12">24057 2101 100 0 0,'-8'-5'10078'0'0,"14"17"-3321"0"0,-4-1-7872 0 0,-2 10 2297 0 0,1 3-327 0 0,-2-1-1 0 0,0 1 0 0 0,-2 0 1 0 0,-7 34-1 0 0,-5-2-108 0 0,-82 272 854 0 0,64-228-1334 0 0,56-132-287 0 0,145-209-322 0 0,-164 236 336 0 0,63-85-81 0 0,6 2-1 0 0,95-90 1 0 0,-159 170 88 0 0,0-1 0 0 0,1 2 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,1 2 0 0 0,20-9 0 0 0,-30 13 19 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,4 2 0 0 0,-3-1 32 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,-2 1 1 0 0,1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,1 4 1 0 0,3 16 375 0 0,-2-1 0 0 0,0 1 0 0 0,-1 1 0 0 0,-2 0 0 0 0,-3 36 0 0 0,-24 125 1152 0 0,16-119-1206 0 0,-8 35-34 0 0,-19 162-877 0 0,32-141-4301 0 0,6-123 4652 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,1 0 0 0 0,17-11-4277 0 0,23-29 1468 0 0,-36 34 1741 0 0,77-86-3155 0 0,-59 68 3718 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4141.92">25647 1970 124 0 0,'5'-19'2009'0'0,"8"18"383"0"0,23 26 2376 0 0,-13-8-2620 0 0,94 44 4412 0 0,-68-34-4406 0 0,70 53 0 0 0,-110-73-1960 0 0,1 0 0 0 0,-1 1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,-2 1 0 0 0,13 21 0 0 0,-16-25-115 0 0,-1 1 0 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-5 11 0 0 0,-10 17 142 0 0,0-2 1 0 0,-2 0-1 0 0,-39 54 1 0 0,-79 81-47 0 0,102-128-167 0 0,4-5 15 0 0,-1-2 1 0 0,-2 0-1 0 0,-1-2 1 0 0,0-2 0 0 0,-48 28-1 0 0,78-54 81 0 0,2 0 0 0 0,-2 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-8 0 1494 0 0,52 12-351 0 0,79 7 400 0 0,110 11-1095 0 0,-32-12-541 0 0,-121-10-364 0 0,1-3 1 0 0,120-5-1 0 0,-187-2-460 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,14-4 0 0 0,3-11-3866 0 0,-8-10-3527 0 0,-24 11 2309 0 0,-14-5 2039 0 0,-24 2 95 0 0,21 14 2953 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -1746,7 +2656,7 @@
           <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2025-04-17T13:14:55.830"/>
+      <inkml:timestamp xml:id="ts0" timeString="2025-04-17T13:15:02.199"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -1754,73 +2664,12 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">148 631 68 0 0,'-25'5'2234'0'0,"12"-2"1483"0"0,-1-1 8258 0 0,42-12-9064 0 0,17 8-1590 0 0,0-3-1 0 0,66-15 0 0 0,-2 0-505 0 0,-82 15-913 0 0,45-16-1 0 0,-116 49-11594 0 0,-54 51 4476 0 0,49-38 4433 0 0,-28 24-45 0 0,54-42 2196 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="188.8">39 1049 292 0 0,'-1'2'376'0'0,"-1"-1"-1"0"0,1 1 1 0 0,-1 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,-4 1 0 0 0,-5 1 4405 0 0,20-11 4398 0 0,22-13-7513 0 0,128-77 1902 0 0,-133 84-3653 0 0,0 2 0 0 0,1 1 1 0 0,0 0-1 0 0,40-8 1 0 0,36-1-3799 0 0,1 12-6807 0 0,-101 8 10335 0 0,0 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,-1-2 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,1-5 0 0 0,5-3-261 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="418.17">1000 103 28 0 0,'9'-18'804'0'0,"16"-31"2678"0"0,-23 45-2749 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,7-4 11655 0 0,-28 45-9315 0 0,-104 221-682 0 0,-20-8-5066 0 0,112-201 1024 0 0,-11 19-2194 0 0,32-56 1067 0 0,0 0 0 0 0,-21 21 0 0 0,30-34 2682 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-2-1 0 0,0 1 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1-1 0 0,0-22-2293 0 0,7-24 819 0 0,3 15 710 0 0,3 0 148 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="600.69">915 103 192 0 0,'1'-1'157'0'0,"0"0"-1"0"0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,1 1 0 0 0,-1-1-1 0 0,0 1 1 0 0,1 0 0 0 0,2 2 827 0 0,0 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,3 8 0 0 0,-2-5-451 0 0,14 19 2435 0 0,1 0 0 0 0,26 24 0 0 0,105 85 658 0 0,-141-126-3422 0 0,25 17 109 0 0,-27-21-481 0 0,0 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,10 14 0 0 0,-16-20-24 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-2 1 0 0 0,-25 14-4195 0 0,-36-2-1472 0 0,51-14 5237 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,1-1 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 0 1 0 0,0-1-1 0 0,-12-8 0 0 0,-5-1-76 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="775.48">864 256 296 0 0,'-15'76'7827'0'0,"26"198"5170"0"0,31 141-6663 0 0,-14-157-5291 0 0,-9-65-4487 0 0,-10-146-1408 0 0,-9-44 2875 0 0,-18-27-7976 0 0,-40-102 2831 0 0,40 90 6337 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">660 298 88 0 0,'2'5'8782'0'0,"5"17"-6418"0"0,-4-13-3559 0 0,-3-5-2658 0 0,-18-3 1325 0 0,1-2-571 0 0,13-3 2712 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="13370.16">2742 1184 160 0 0,'1'3'405'0'0,"0"-1"0"0"0,0 1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,-2 6 4552 0 0,1-23-12594 0 0,0 10 8078 0 0,-25-20-3824 0 0,23 20 2953 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
 <file path=xl/ink/ink11.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
-          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
-          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2025-04-17T13:15:00.772"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.035" units="cm"/>
-      <inkml:brushProperty name="height" value="0.035" units="cm"/>
-      <inkml:brushProperty name="color" value="#E71224"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">28 1239 60 0 0,'2'2'5449'0'0,"6"10"9131"0"0,-5-9-12840 0 0,-2-1-3384 0 0,3 2 1993 0 0,0 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 10 0 0 0,4 6 216 0 0,-1-8-389 0 0,-1 1 0 0 0,-1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 18 0 0 0,-2-31-275 0 0,-9-34-11182 0 0,10-30 3523 0 0,0 42 5824 0 0,1 0-1 0 0,8-31 0 0 0,-6 33 1246 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-261.66">90 571 4 0 0,'-1'0'89'0'0,"1"-1"1"0"0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 1 1 0 0,-4 18 4097 0 0,5 21 1687 0 0,31 119 1244 0 0,-31-131-6512 0 0,-30-28-11653 0 0,25-1 10555 0 0,1 1-1 0 0,-1 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,-3 4 0 0 0,1 2-98 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1138.49">509 668 240 0 0,'-29'9'28685'0'0,"53"-11"-28404"0"0,0-1 0 0 0,0-2 0 0 0,-1 0 0 0 0,0-1 0 0 0,0-2 0 0 0,0 0 0 0 0,27-15 0 0 0,-11 6-396 0 0,42-12 0 0 0,-33 11-501 0 0,-38 14 12 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,1 1 0 0 0,18-2-1 0 0,-18 3-8437 0 0,-39-10-2354 0 0,-45 0 7240 0 0,59 10 3480 0 0,0-3 125 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1427.9">697 302 88 0 0,'2'5'8782'0'0,"6"18"-6418"0"0,-5-14-3559 0 0,-3-5-2658 0 0,-19-3 1325 0 0,1-2-571 0 0,14-3 2712 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="14798.06">2897 1201 160 0 0,'1'3'405'0'0,"0"0"0"0"0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,-2 6 4552 0 0,0-23-12594 0 0,1 10 8078 0 0,-26-20-3824 0 0,23 20 2953 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="16272.72">636 311 248 0 0,'0'-5'481'0'0,"1"1"0"0"0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,5-5 0 0 0,-7 7-250 0 0,1 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,4 1 0 0 0,-5-2-27 0 0,1 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,0 1 1 0 0,-9 39 160 0 0,-2 0 1 0 0,-1-2-1 0 0,-2 1 1 0 0,-2-2-1 0 0,-1 0 1 0 0,-47 71-1 0 0,43-77-620 0 0,-27 54 0 0 0,36-60 65 0 0,8-17-390 0 0,8-15-1682 0 0,-8 10-3068 0 0,-3 7 3041 0 0,0-1 0 0 0,0-1 0 0 0,-1 0 0 0 0,-19 16 0 0 0,8-12-1334 0 0,13-14 3218 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="16860.81">400 895 412 0 0,'0'0'2024'0'0,"19"37"7745"0"0,-17-33-9455 0 0,0 0-1 0 0,-1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,-1 6 1 0 0,1 13 676 0 0,7 61 1418 0 0,-4 94 0 0 0,-4-107-2150 0 0,-13 18-663 0 0,14-89 343 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,-13-13-1467 0 0,8-1 335 0 0,1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,0 0 0 0 0,0-29 1 0 0,7-84-3235 0 0,-4 124 4270 0 0,0 3 114 0 0,20-204-4505 0 0,-15 172 5588 0 0,21-65 0 0 0,-25 97-537 0 0,0-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,5-2 0 0 0,54-15 4444 0 0,-11 5-2182 0 0,-34 8-1726 0 0,-1 1-1 0 0,1 0 1 0 0,19-1-1 0 0,14-4 1298 0 0,-42 7-2008 0 0,0 1 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1 1-1 0 0,10 7 1 0 0,-14-7-322 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,-2 8 0 0 0,0 6 3 0 0,0 106-8 0 0,-1-60 0 0 0,3 1 0 0 0,2-1 0 0 0,15 82 0 0 0,-12-92-43 0 0,-5-54-215 0 0,-3-3-1467 0 0,1-1 1098 0 0,-1 1-1 0 0,1-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,0 0-1 0 0,-2-4 1 0 0,-2-2-1457 0 0,-42-66-8384 0 0,5-5 3630 0 0,-20-34 1284 0 0,53 95 4985 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17118.11">537 886 44 0 0,'-1'0'207'0'0,"0"0"0"0"0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,-7 11 12512 0 0,45 2-8421 0 0,-23-9-3976 0 0,0 0-1 0 0,0-1 1 0 0,0 0-1 0 0,1-1 1 0 0,-1-1-1 0 0,24 1 1 0 0,42 8 301 0 0,-75-11-712 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,5-3-1 0 0,-9 4-419 0 0,-25-22-7828 0 0,19 21 7676 0 0,0 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,1 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-7 2 0 0 0,2-1 18 0 0,-1 0 0 0 0,1 1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 2 0 0 0,-12 6-1 0 0,8-1 200 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17317.01">466 1062 564 0 0,'0'0'11275'0'0,"34"0"-5398"0"0,143 5-1128 0 0,-148-11-5423 0 0,-15-1-3081 0 0,-56-9-7344 0 0,31 14 9903 0 0,1-1-10 0 0,-1 0-1 0 0,0 1 1 0 0,-21-1 0 0 0,22 3 614 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17516.75">476 1095 28 0 0,'8'19'8847'0'0,"26"-1"-2779"0"0,32-3-3247 0 0,-53-12-2261 0 0,18 1-399 0 0,0-1 1 0 0,49 0-1 0 0,-80-3-613 0 0,-12 3-7856 0 0,-42 12 3666 0 0,-63 22-289 0 0,98-32 4492 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17804.81">236 1405 72 0 0,'-13'23'13603'0'0,"36"-21"-8557"0"0,22-14-2096 0 0,-20 4-1826 0 0,30-5 371 0 0,1 2 0 0 0,0 3 0 0 0,0 2 0 0 0,93 2-1 0 0,-36 8-500 0 0,-49-2-793 0 0,70 10-1 0 0,-111-10 382 0 0,-6-4-3381 0 0,-17 2 2719 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,-19-11-3189 0 0,-49-17-4104 0 0,-49-17-1315 0 0,94 37 7431 0 0,0 2 1 0 0,-1 0-1 0 0,-28-2 0 0 0,28 7 614 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17965.53">565 1373 160 0 0,'3'10'1384'0'0,"-3"-8"-650"0"0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-6 7 7856 0 0,-6 4-5114 0 0,4-9-3301 0 0,2 1-1 0 0,-1 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,2 1 1 0 0,-1-1 0 0 0,0 1-1 0 0,-4 6 1 0 0,-30 27-560 0 0,-1 0-1915 0 0,26-24-1462 0 0,5-26-8994 0 0,10 4 12217 0 0,1 0 1 0 0,-1 1-1 0 0,2-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,0-1 0 0 0,1 1 1 0 0,4-9-1 0 0,2-6-131 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="18116.44">598 1364 436 0 0,'16'7'1126'0'0,"0"1"0"0"0,-1 1 1 0 0,0 0-1 0 0,-1 1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 1 0 0 0,0 0 1 0 0,16 22-1 0 0,-10-13 824 0 0,0-1 1 0 0,39 30-1 0 0,18-2-372 0 0,-69-44-1859 0 0,0-1 1 0 0,1 1 0 0 0,-1-1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,14 0 0 0 0,-21-2-687 0 0,1-2 227 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,0 0 1 0 0,2-6 0 0 0,-14-54-5180 0 0,1 19 3931 0 0,9 24 1297 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="18371.28">1625 0 556 0 0,'1'2'426'0'0,"0"-1"0"0"0,-1 0 0 0 0,1 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 59 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,0 4-1 0 0,24 37 6731 0 0,-18-31-7266 0 0,2 0 0 0 0,0-1-1 0 0,12 13 1 0 0,-20-24-168 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,-22 15-5185 0 0,-48 5-17 0 0,55-16 4055 0 0,-2 2 598 0 0,-1 2 163 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="18541.04">1239 492 172 0 0,'-1'2'144'0'0,"-10"41"4492"0"0,-28 75 0 0 0,26-89-1516 0 0,-12 45 1 0 0,22-61-3015 0 0,1-1 1 0 0,0 1 0 0 0,-1 21-1 0 0,9-8-2737 0 0,0-24-854 0 0,0-16 1281 0 0,7-38-1463 0 0,26-68 1 0 0,-29 93 3200 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="18796.69">1328 483 68 0 0,'79'5'12653'0'0,"-55"-2"-10074"0"0,0-1 1 0 0,42-2-1 0 0,25-8 481 0 0,73-8 1029 0 0,112-39 981 0 0,-271 54-5055 0 0,-1 1 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,8 3 1 0 0,-13-3-23 0 0,1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0-1 0 0,0-1 1 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,-9 19-1134 0 0,9-16 912 0 0,0-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-4 3 1 0 0,-38 40-3999 0 0,22-22 460 0 0,-1-2 0 0 0,-47 38 0 0 0,29-33 23 0 0,0-1 1 0 0,-60 27 0 0 0,53-30 2031 0 0,24-17 1130 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="18991.82">1554 603 160 0 0,'-8'-4'10546'0'0,"-7"40"970"0"0,4 6-7512 0 0,7-26-3797 0 0,-1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,-14 27 0 0 0,-2-8-99 0 0,-37 53-853 0 0,53-80-189 0 0,-1 0 1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,-19 10 0 0 0,26-15 651 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,-1-2 1 0 0,1 1-47 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0-3 1 0 0,1-4-318 0 0,1-1-1 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,6-13 1 0 0,4-1-179 0 0,1-3 160 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="19153.16">1597 622 544 0 0,'12'5'1020'0'0,"0"1"-1"0"0,0 1 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 1-1 0 0,-1 1 1 0 0,1 0-1 0 0,8 10 1 0 0,42 34 5019 0 0,109 63-304 0 0,-160-105-6539 0 0,-10-10 610 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,-1-1 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,-4 3-812 0 0,1-1 1 0 0,-1 1 0 0 0,0-1-1 0 0,0-1 1 0 0,0 1-1 0 0,-8 0 1 0 0,-95 14-6127 0 0,85-12 6427 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="19350.56">1484 1030 544 0 0,'-1'0'333'0'0,"1"0"-1"0"0,-1 0 1 0 0,1 1 0 0 0,0-1 0 0 0,-1 0-1 0 0,1 1 1 0 0,0-1 0 0 0,-1 0-1 0 0,1 1 1 0 0,0-1 0 0 0,-1 0-1 0 0,1 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,20 6 5563 0 0,45-7-3861 0 0,-52 0-1179 0 0,128-2 1026 0 0,-73 0-3279 0 0,-1 1-5235 0 0,-67 1 6236 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,-5-9-1851 0 0,4 9 2016 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,-3 0 0 0 0,-1 0-245 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="19496.67">1667 1058 328 0 0,'-2'3'357'0'0,"-1"0"0"0"0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 8 0 0 0,4 72 4948 0 0,0-35-2436 0 0,-2-17-2365 0 0,2 0 0 0 0,10 46 0 0 0,-11-63-748 0 0,-3-12-22 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,-2 1 0 0 0,1 0-177 0 0,1-1 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-8-2 1 0 0,2-2-87 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="19729.56">1352 1507 148 0 0,'-13'6'1362'0'0,"-12"7"12839"0"0,38-13-8697 0 0,7 0-3558 0 0,14-2 424 0 0,0-1-1 0 0,44-11 0 0 0,-3 1-202 0 0,128-25-1836 0 0,-133 21-331 0 0,66-11 0 0 0,-121 25 0 0 0,1 2 0 0 0,0 0 0 0 0,-1 1 0 0 0,1 1 0 0 0,0 0 0 0 0,23 5 0 0 0,-21-5-2587 0 0,-18-1 2266 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-2-1 0 0,-10-37-17436 0 0,5 23 14758 0 0,3 4 5073 0 0,1-3-3005 0 0,-3-3 220 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="20210.78">2204 330 64 0 0,'0'0'129'0'0,"-1"0"-1"0"0,1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 1-1 0 0,1 0 534 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,2 0 1 0 0,48-18 5372 0 0,27-15-3523 0 0,9-8-1282 0 0,-6 3-3960 0 0,-93 44-7406 0 0,-3 2 3735 0 0,-9 8 2176 0 0,-2 2 4220 0 0,-19 12 2637 0 0,37-25-1703 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,0 1 1 0 0,1 0-1 0 0,-9 13 1 0 0,-27 59 3183 0 0,14-25-2577 0 0,2-5-519 0 0,-16 26 39 0 0,-1-14-608 0 0,25-33-856 0 0,-2-2-1 0 0,0 0 1 0 0,-2-1-1 0 0,-1-1 1 0 0,-36 32-1 0 0,52-52-235 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0-1 0 0 0,-8 2 1 0 0,13-3 483 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1-2-1 0 0,1-8-429 0 0,1-1 1 0 0,0 1-1 0 0,1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,11-18-1 0 0,-2 6 123 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="20367.73">2143 603 204 0 0,'4'0'390'0'0,"0"1"0"0"0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 2 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,4 5 0 0 0,3 7 2118 0 0,1-1 0 0 0,15 29 0 0 0,-20-30-1366 0 0,1-1-1 0 0,1 1 0 0 0,13 15 0 0 0,27 14-609 0 0,-46-44-1250 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-7 0 0 0,-2-60-4112 0 0,1 5 1764 0 0,9 24 1726 0 0,-7 22 862 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="20720.17">2407 469 64 0 0,'0'0'40'0'0,"0"-1"0"0"0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,17 8 2540 0 0,11 12 2582 0 0,17 18 1422 0 0,28 12-2076 0 0,-45-31-3260 0 0,-26-19-1221 0 0,-1 1 1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,-2 2 0 0 0,-1 1-9 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,-8 6-1 0 0,-6 3-13 0 0,-1-1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-2-2-1 0 0,1-1 1 0 0,-1 0-1 0 0,-31 6 1 0 0,-18 6 326 0 0,71-17 692 0 0,10-1-408 0 0,31 5-229 0 0,47 1-316 0 0,103-13-693 0 0,-178 6 1340 0 0,0 4-6097 0 0,-14 0-851 0 0,-15 2 2451 0 0,-47 12-3961 0 0,36-10 5926 0 0,13-4 1233 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="21526.86">2360 886 12 0 0,'-9'-4'4944'0'0,"9"3"-4625"0"0,-1 1-1 0 0,1 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0-1 0 0,0-1 1 0 0,8-1 1312 0 0,1 2-1195 0 0,0 0 0 0 0,0 1 0 0 0,0 0 1 0 0,0 1-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 1-1 0 0,1 0 0 0 0,12 12 0 0 0,45 42 3232 0 0,-64-55-3457 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0-1-1 0 0,-2 6 0 0 0,2 2 210 0 0,-11 141 1636 0 0,6-109-1494 0 0,2 0-1 0 0,1 0 1 0 0,8 70-1 0 0,-4-82-114 0 0,5 22-169 0 0,-6-31-279 0 0,-1-22 0 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0-1 1 0 0,-24-16-173 0 0,12 8-850 0 0,-6-4-951 0 0,1-1 0 0 0,0-1-1 0 0,1 0 1 0 0,1-1 0 0 0,0-1-1 0 0,-16-25 1 0 0,1 4-1464 0 0,3 2-922 0 0,-33-63 0 0 0,-10-11-640 0 0,57 95 4484 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="21740.51">2120 1030 316 0 0,'0'0'2200'0'0,"9"19"3557"0"0,45 0 828 0 0,-43-17-5688 0 0,0 2-1 0 0,-1-1 0 0 0,20 10 0 0 0,-27-11-690 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 1 0 0,3 7-1 0 0,-2-4-79 0 0,-1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,0-1 0 0 0,-1 1 0 0 0,0 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,-4 10 1 0 0,2-7-250 0 0,-1 0 0 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-2-1 0 0 0,1-1 0 0 0,-1 1 0 0 0,-1-1 0 0 0,0-1 0 0 0,-9 9 0 0 0,5-7-891 0 0,-1 0 0 0 0,1-1-1 0 0,-1 0 1 0 0,-24 10-1 0 0,30-16-89 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1-1 1 0 0,1 0-1 0 0,-12 1 1 0 0,19-2 967 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,3-12-1509 0 0,10-10 468 0 0,-2 10 527 0 0,6-1 137 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="22076.21">2718 932 148 0 0,'14'-3'1454'0'0,"1"0"0"0"0,29-3 0 0 0,-8 11 3661 0 0,-32-4-4213 0 0,-1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,2 3 0 0 0,-4 3 6414 0 0,-7 4-3695 0 0,-15 16-2157 0 0,11-16-485 0 0,-67 111-249 0 0,55-97-731 0 0,18-22 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1 0 0 0 0,-3 5 0 0 0,6-6 0 0 0,3-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,5 0 0 0 0,59 15 0 0 0,-41-10 0 0 0,49 7 0 0 0,50 10 0 0 0,-94-16 0 0 0,12 1 0 0 0,-37-11-8186 0 0,-11-5 3282 0 0,-15-9-2184 0 0,15 13 2522 0 0,1-1 3750 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 1 0 0,-3-8-1 0 0,4 9 762 0 0,-8-18-555 0 0</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink12.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -1848,54 +2697,54 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">4671 304 200 0 0,'-1'-5'16389'0'0,"-20"-7"-11343"0"0,-33-10-2834 0 0,-75-27 823 0 0,28 19-1797 0 0,-141-34 819 0 0,-82-23-792 0 0,297 80-1222 0 0,-1 0 0 0 0,0 3 0 0 0,-29-3 0 0 0,-2 1 1 0 0,37 4-28 0 0,0 1 1 0 0,0 0-1 0 0,1 2 0 0 0,-39 7 0 0 0,-86 24 28 0 0,115-24-40 0 0,-52 7-3 0 0,0-2 0 0 0,0-5-1 0 0,-133-3 1 0 0,127 0-13 0 0,0 4-1 0 0,-104 23 0 0 0,131-21 4 0 0,-76 18 14 0 0,-82 12-14 0 0,-28-35 4 0 0,165-7-5 0 0,-62-5-10 0 0,59 2 9 0 0,54 2 6 0 0,0 1 1 0 0,0 1 0 0 0,-36 6 0 0 0,-105 13-17 0 0,158-16 19 0 0,3-1-3 0 0,-1 0 1 0 0,1 1-1 0 0,0 1 1 0 0,-18 8-1 0 0,-61 24-26 0 0,70-23 23 0 0,4-4 1 0 0,0 1 0 0 0,1 1-1 0 0,1 0 1 0 0,-19 18 0 0 0,-93 108-18 0 0,57-54 39 0 0,33-30-3 0 0,-43 68-16 0 0,54-79-1 0 0,-21 42 4 0 0,5-1-4 0 0,-8 23-6 0 0,-54 212 4 0 0,83-247 7 0 0,-43 176-10 0 0,0-30 11 0 0,23-43 9 0 0,24-92-11 0 0,7-24-9 0 0,2 0 0 0 0,3 0 0 0 0,3 63 0 0 0,3-98-1 0 0,2 0-1 0 0,1 0 1 0 0,1-1 0 0 0,14 42 0 0 0,-7-24 0 0 0,1-5-4 0 0,2 0 0 0 0,1-1 0 0 0,30 49 0 0 0,-34-63 14 0 0,31 49-12 0 0,3-2 0 0 0,89 99 1 0 0,-96-124 22 0 0,1-2 0 0 0,2-2 0 0 0,1-2 0 0 0,2-2 1 0 0,2-1-1 0 0,52 26 0 0 0,-40-24-2 0 0,22 11 3 0 0,356 131 95 0 0,-341-145-74 0 0,2-4 0 0 0,163 25 0 0 0,7-10 14 0 0,63 21 36 0 0,-215-39-35 0 0,364 88 93 0 0,-124-27-24 0 0,-246-60-78 0 0,181 37 12 0 0,20-13-37 0 0,-113-20 26 0 0,-85-19 29 0 0,1-6 0 0 0,0-5 0 0 0,0-4 1 0 0,-1-6-1 0 0,198-42 0 0 0,-264 41-51 0 0,0-2 0 0 0,82-36 0 0 0,-82 27 2 0 0,-14 7 15 0 0,48-31 0 0 0,-43 20-5 0 0,-2-3 0 0 0,54-54 0 0 0,-51 47-23 0 0,-3-2 0 0 0,-1-2 0 0 0,35-52 0 0 0,-49 60-5 0 0,84-144 0 0 0,-78 122 0 0 0,-3-2 0 0 0,-3-1 0 0 0,-2 0 0 0 0,-2-2 0 0 0,-3 0 0 0 0,10-94 0 0 0,-18 84 0 0 0,8-157 0 0 0,-14 184 0 0 0,-1 1 0 0 0,-2-1 0 0 0,-2 1 0 0 0,-17-69 0 0 0,6 54 0 0 0,9 28 0 0 0,-1 1 0 0 0,-1 0 0 0 0,-22-43 0 0 0,-21-22 0 0 0,-4 4 0 0 0,-4 1 0 0 0,-135-148 0 0 0,82 124 0 0 0,-4 5 0 0 0,-246-171 0 0 0,274 218-32 0 0,-2 3-1 0 0,-3 5 1 0 0,-1 4 0 0 0,-116-40 0 0 0,162 73-632 0 0,-2 1 1 0 0,-87-9 0 0 0,-25 8-3792 0 0,124 11 2780 0 0,-293-8-13269 0 0,250 7 12764 0 0,0-4 0 0 0,0-3 0 0 0,-113-30 0 0 0,102 17 1550 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2058.85">7953 630 388 0 0,'4'-3'279'0'0,"0"0"1"0"0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,-1-1 1 0 0,8 5-1 0 0,-3-2 570 0 0,-1 0-1 0 0,0 0 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1 0 1 0 0,-2 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,0 0-1 0 0,0 0 1 0 0,7 12-1 0 0,-12-16-536 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 3 0 0 0,-28 50 2612 0 0,15-31-2208 0 0,-14 25 98 0 0,-2-1-1 0 0,-49 58 0 0 0,73-97-771 0 0,-29 36 89 0 0,-1-1 1 0 0,-67 60-1 0 0,89-95-136 0 0,1 0 0 0 0,-1-2 0 0 0,-1 1 0 0 0,1-2 0 0 0,-1 0 0 0 0,-1-1 0 0 0,-32 7 0 0 0,47-12 4 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,-2-1-1 0 0,-32-4-21 0 0,35 5 21 0 0,2 2-74 0 0,0-1 73 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,3 0 0 0 0,-2 1 3 0 0,22 12 54 0 0,42 19-1 0 0,14 9 90 0 0,-52-27-95 0 0,1-1 1 0 0,38 13-1 0 0,-9-4-264 0 0,54 9-2925 0 0,-112-32 2949 0 0,0 1 1 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0-1 0 0 0,0-7-1160 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,-1 1 0 0 0,-2-10 0 0 0,1 4 435 0 0,-3-10-640 0 0,-1 1-1 0 0,-2 0 0 0 0,0 1 1 0 0,-21-38-1 0 0,25 51 1492 0 0,1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,-2-14 0 0 0,3 14 1096 0 0,0 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,-6-12 0 0 0,20 38 6083 0 0,3 0-3414 0 0,43 36-4999 0 0,-5-5-1920 0 0,-50-46 2980 0 0,0 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,5-3-1 0 0,7-7-733 0 0,0-1 1 0 0,0 0-1 0 0,21-26 0 0 0,-24 25 653 0 0,9-6-108 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2219.91">8463 1013 488 0 0,'8'-15'-1158'0'0,"6"-1"7329"0"0,-3 17 908 0 0,-1 17-3436 0 0,-7-7-3217 0 0,0 0 0 0 0,-1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,-3 12 0 0 0,-3 6-150 0 0,0-1 0 0 0,-15 37-1 0 0,15-52-522 0 0,1 0 0 0 0,-2-1 0 0 0,1 0-1 0 0,-2 0 1 0 0,0-1 0 0 0,0 0 0 0 0,-1 0-1 0 0,-1-1 1 0 0,0 0 0 0 0,0-1 0 0 0,-1-1-1 0 0,0 0 1 0 0,-24 14 0 0 0,-12 2-2325 0 0,-2-3-1 0 0,-79 27 1 0 0,80-32 668 0 0,-3-1-645 0 0,0-3 0 0 0,-104 13 0 0 0,131-25 2065 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3608.46">7711 1728 40 0 0,'0'0'1309'0'0,"7"-13"-248"0"0,-4 12-1139 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,2-4 0 0 0,10-19 1833 0 0,-13 20-1217 0 0,0 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,1 1-1 0 0,6-9 2472 0 0,11 25-98 0 0,-15 1-2412 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,-1 1 0 0 0,-5 22 0 0 0,4-13-324 0 0,-2-1-1 0 0,0 0 1 0 0,-15 37 0 0 0,15-47-324 0 0,-1-1 1 0 0,0 0-1 0 0,0-1 1 0 0,-13 16-1 0 0,15-21-287 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,0-1-1 0 0,-6 4 1 0 0,11-7 333 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,-2-16-2138 0 0,7-18 267 0 0,-5 32 1609 0 0,10-43-868 0 0,2 1 1 0 0,2 1 0 0 0,29-61 0 0 0,-15 37 2084 0 0,-26 63-530 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0-1 0 0,0 1 1 0 0,-1 0 0 0 0,2-1 0 0 0,-1 1 0 0 0,0 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,8 2-1 0 0,35 1 2219 0 0,-13-2-1123 0 0,-2 1-264 0 0,-1-3 0 0 0,0 0-1 0 0,0-2 1 0 0,50-9 0 0 0,-32 4-263 0 0,19 1 138 0 0,50-8 310 0 0,-31-9-1082 0 0,-66 15-908 0 0,-15 4-630 0 0,-13 2 8 0 0,2 2 852 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 2 0 0 0,1-1 0 0 0,1 1 0 0 0,-7 3 0 0 0,-48 37-2843 0 0,40-28 2361 0 0,-317 250-9468 0 0,319-252 10248 0 0,-110 80-125 0 0,111-84 1692 0 0,-1 1 0 0 0,0-2 0 0 0,-27 7 8525 0 0,51-23-7851 0 0,14-6-1562 0 0,42-11 1479 0 0,108-26 0 0 0,-133 45-1890 0 0,1 2 0 0 0,0 1 1 0 0,45 3-1 0 0,-42 1-596 0 0,2 6-499 0 0,-38-5 427 0 0,-1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1-1-1 0 0,5-1 1 0 0,-11 2 374 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,-19-17-1560 0 0,18 18 1304 0 0,-143-120-6160 0 0,129 108 6661 0 0,1-2 0 0 0,1 0 0 0 0,0 0 1 0 0,-20-29-1 0 0,-21-22 6198 0 0,54 66-6118 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 1 0 0 0,1 52 1608 0 0,0-37-1283 0 0,-1-15-493 0 0,1 69 887 0 0,-3 1 0 0 0,-3 0 0 0 0,-21 107 0 0 0,19-140-1079 0 0,7-32 109 0 0,-1 0 0 0 0,0-1 0 0 0,-1 0-1 0 0,1 1 1 0 0,-2-1 0 0 0,1 0 0 0 0,-1 0-1 0 0,-4 8 1 0 0,1-4 61 0 0,4-7-311 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,-5 6 1 0 0,7-9 208 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,-1-1 0 0 0,-59-70-2941 0 0,-6-6 2282 0 0,60 72 924 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 1 0 0,-13-6-1 0 0,19 9-44 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-4 1 0 0 0,3 0 41 0 0,-1 0 0 0 0,1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-2 7 1 0 0,-1 4 270 0 0,1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,1-1 0 0 0,1 1 0 0 0,2 19 0 0 0,-2-30-248 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,2 1 1 0 0,-1 0-1 0 0,0-1 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,5 4 0 0 0,-1-3 78 0 0,0 1 1 0 0,0-1-1 0 0,1-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,1-1 1 0 0,10 1-1 0 0,14 0 255 0 0,0-3 0 0 0,0 0 0 0 0,0-2 0 0 0,47-11 0 0 0,-17 0-258 0 0,-1-3 0 0 0,90-38 0 0 0,111-67-359 0 0,-255 118 114 0 0,-6 2-7 0 0,1 1 1 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 2 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,4 1 0 0 0,-5 0 7 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,-2 2 1 0 0,-68 248-357 0 0,44-151-788 0 0,-12-14-3907 0 0,38-85 4814 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,-1 0 0 0 0,-23-10-3440 0 0,-14-26-140 0 0,27 19 2770 0 0,1-1 1 0 0,0 1-1 0 0,-13-33 0 0 0,-2-5-35 0 0,6 12 526 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3871.63">7373 875 56 0 0,'14'12'5851'0'0,"-8"-3"-4326"0"0,-6-7-1316 0 0,1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 3-1 0 0,19 52 2181 0 0,24 30-4769 0 0,-42-84 1542 0 0,5 29-4888 0 0,-25 38 1988 0 0,13-56 3308 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4475.02">7310 1433 364 0 0,'0'0'659'0'0,"-7"18"5309"0"0,10-14-5494 0 0,0 0 0 0 0,-1 0 0 0 0,2-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,8 4 0 0 0,15 14-126 0 0,-15-8-182 0 0,0 0 0 0 0,0 1 0 0 0,17 26 0 0 0,-25-32-150 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,-1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 14 0 0 0,-2-7-6 0 0,0 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,-2 1 0 0 0,1-1 0 0 0,-2 1 0 0 0,0-1 1 0 0,-1-1-1 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0-1 1 0 0,-2 0-1 0 0,-10 11 0 0 0,14-17 16 0 0,4-2 8 0 0,-1-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,-1 1 0 0 0,1 0 1 0 0,0-1-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-7 2-1 0 0,9-4 866 0 0,46 18-585 0 0,-39-17-233 0 0,-1 1 1 0 0,0 0-1 0 0,1 1 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,0 0 0 0 0,1 10 1 0 0,-1 3 236 0 0,0 0 0 0 0,-1-1 0 0 0,0 1 1 0 0,-2 0-1 0 0,0 0 0 0 0,-2-1 0 0 0,-5 21 1 0 0,4-28-216 0 0,0 0 0 0 0,-1-1 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,-1 0-1 0 0,0-1 1 0 0,-17 14-1 0 0,7-4-4 0 0,-14 12-19 0 0,-1-2 0 0 0,-1-1 0 0 0,-2-1 1 0 0,-39 21-1 0 0,50-33-195 0 0,-1-1 1 0 0,0-2 0 0 0,-1 0-1 0 0,0-2 1 0 0,0-1 0 0 0,-1-1-1 0 0,-36 5 1 0 0,50-11-129 0 0,0 0 0 0 0,0-1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,-21-7 0 0 0,32 8 156 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,2-6-1 0 0,0-5-33 0 0,2 0 1 0 0,0 0-1 0 0,0 1 0 0 0,1-1 0 0 0,1 1 0 0 0,0 1 1 0 0,1-1-1 0 0,0 1 0 0 0,1 0 0 0 0,1 1 0 0 0,18-21 1 0 0,-19 24 261 0 0,0 1 0 0 0,1 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1 1 1 0 0,1-1-1 0 0,-1 2 0 0 0,0-1 0 0 0,1 2 0 0 0,0-1 1 0 0,0 1-1 0 0,0 1 0 0 0,12 0 0 0 0,42 3 1725 0 0,-1 3 0 0 0,82 16-1 0 0,126 42 3740 0 0,-184-40-4066 0 0,173 57 1117 0 0,552 196-2657 0 0,-523-169 0 0 0,3 9 0 0 0,13 5 0 0 0,-153-71 0 0 0,-91-38-791 0 0,-23-15-4057 0 0,-39 2 4583 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,-3-24-3572 0 0,-11-19-527 0 0,13 43 4112 0 0,-32-82-5925 0 0,-25-36 1773 0 0,34 76 3608 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5231.21">9470 837 548 0 0,'-2'-5'13892'0'0,"7"15"-6406"0"0,4-3-9563 0 0,101 50 4736 0 0,-9-18-1501 0 0,-101-39-892 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-7 30-712 0 0,3-16 879 0 0,-4 115-74 0 0,3-19-164 0 0,-9 313 579 0 0,15-316-555 0 0,2 94 373 0 0,32 220-1 0 0,-32-402-591 0 0,31 177 0 0 0,-34-198 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,-11-13-500 0 0,-12-24-1188 0 0,-11-51-3700 0 0,4-1 0 0 0,3-1 0 0 0,-24-150 0 0 0,27 111 1844 0 0,7 38 1060 0 0,-7-110 1 0 0,23 145 2004 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5617">9419 1383 132 0 0,'-3'5'411'0'0,"-1"3"601"0"0,0 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-3 12 0 0 0,5-17-497 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,1 4 0 0 0,3 1 119 0 0,0 0 1 0 0,1 0-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1-1 1 0 0,15 4-1 0 0,15 2 1072 0 0,72 9 1 0 0,-104-18-1508 0 0,78 5 1258 0 0,-57-5-959 0 0,52 8 0 0 0,-57-6-416 0 0,-20-2-93 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1 0-129 0 0,-10 23-1019 0 0,-47 44-1429 0 0,-79 77-1 0 0,71-86 1683 0 0,-92 66 0 0 0,134-110 1156 0 0,-1-1 1 0 0,-1-1 0 0 0,0-1 0 0 0,-1-2 0 0 0,-1 0-1 0 0,-28 8 1 0 0,28-13 2206 0 0,54-15 1142 0 0,11-4-2795 0 0,260-96 1810 0 0,-172 72-2826 0 0,-92 30-1463 0 0,1-3 0 0 0,-2-1 0 0 0,67-30 0 0 0,-91 35 670 0 0,-1-1 0 0 0,0 0 0 0 0,0 0-1 0 0,-1-2 1 0 0,1 1 0 0 0,-2-1 0 0 0,1 0 0 0 0,-2-1-1 0 0,1 0 1 0 0,6-12 0 0 0,10-18-3366 0 0,23-55 1 0 0,13-66-458 0 0,-42 122 4108 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5779.76">10757 843 48 0 0,'97'-12'8173'0'0,"-75"16"-1341"0"0,-15 8-4522 0 0,-8-10-2448 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,0-1 0 0 0,-3 3-1 0 0,-10 4-875 0 0,0-1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0-2 0 0 0,-1 1 0 0 0,1-2 0 0 0,-22 1 0 0 0,-100 4-2967 0 0,100-7 3299 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5952.45">10018 1289 188 0 0,'2'17'1179'0'0,"0"-1"-1"0"0,2 1 1 0 0,0-1-1 0 0,1 1 1 0 0,0-1-1 0 0,2-1 1 0 0,-1 1 0 0 0,2-1-1 0 0,18 27 1 0 0,-18-30-322 0 0,1-1 1 0 0,0 0 0 0 0,1 0-1 0 0,18 15 1 0 0,-2-2-184 0 0,-21-19-679 0 0,-1-1 0 0 0,1 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 0 0 0 0,1 1-1 0 0,0-2 1 0 0,0 1 0 0 0,11 3 0 0 0,-15-5-84 0 0,0-1 1 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-5 0 0 0,7-25-1525 0 0,-1-1-1 0 0,-2-1 1 0 0,-2 1-1 0 0,1-42 1 0 0,0-6-415 0 0,-2 42 1074 0 0,-1 17 271 0 0,1 1-1 0 0,7-33 1 0 0,-3 28 223 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6178.54">10362 1050 208 0 0,'0'0'623'0'0,"64"14"7227"0"0,-46-11-6365 0 0,1 0-1 0 0,1-2 0 0 0,-1 0 0 0 0,33-3 0 0 0,355-56 6906 0 0,-343 43-7534 0 0,119-19 1640 0 0,-155 30-1988 0 0,0 2-1 0 0,0 1 1 0 0,1 2-1 0 0,44 6 0 0 0,-63-5-392 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 2 0 0 0,1-1 0 0 0,13 13 0 0 0,-19-16-166 0 0,0 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,2 5 1 0 0,-3-7-77 0 0,1 0 1 0 0,-1 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,-2 2 1 0 0,-92 79-7291 0 0,71-62 5205 0 0,-1-2 1 0 0,-1 0 0 0 0,-41 21 0 0 0,-1-5-771 0 0,23-11 1328 0 0,-2-1 0 0 0,0-2 0 0 0,-52 14 0 0 0,9-5 131 0 0,47-16 980 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6389">10661 1308 28 0 0,'8'-20'1003'0'0,"-7"17"-646"0"0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,1 1-1 0 0,3-4 0 0 0,-4 5 880 0 0,0 19 4867 0 0,1 5-364 0 0,-4-6-4756 0 0,-58 200 3925 0 0,-66 97-4068 0 0,117-296-1251 0 0,-1-1 0 0 0,-18 25 0 0 0,11-19-873 0 0,9-14-2564 0 0,4-11 959 0 0,3-27-717 0 0,13-36 186 0 0,6 11 1561 0 0,2 1 0 0 0,3 1 0 0 0,49-83 0 0 0,-51 91 1324 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6560.86">10706 1383 4 0 0,'4'-3'229'0'0,"0"0"-1"0"0,1 0 1 0 0,0 1 0 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,5 0 1 0 0,-7 2-34 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,1 0-1 0 0,2 4 0 0 0,127 111 8756 0 0,14-16-4470 0 0,-103-77-3660 0 0,0-1-1 0 0,57 19 1 0 0,-93-39-936 0 0,20 9 556 0 0,-27-13-471 0 0,0 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 1 1 0 0,-7-6-530 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,-7 0-1 0 0,-17-4-1514 0 0,0 1 0 0 0,0 2 0 0 0,-48 0 0 0 0,30 5-47 0 0,-75 12 0 0 0,80-6 1500 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6880.94">10579 1878 508 0 0,'-1'2'615'0'0,"1"0"1"0"0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,2 2 0 0 0,-1-2-113 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,0-1 0 0 0,3 0 1 0 0,9 0 516 0 0,-1-1 1 0 0,1-1 0 0 0,-1 0 0 0 0,18-6 0 0 0,4 1-492 0 0,34-7 433 0 0,-47 9-1078 0 0,1 0 0 0 0,43-2 0 0 0,-16 1-3093 0 0,-49 6 2271 0 0,-40 11-9771 0 0,33-9 10616 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,0 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 1-1 0 0,-7 7 1 0 0,7-5 456 0 0,1 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 10 0 0 0,-2 4 287 0 0,2 0 0 0 0,0 0 0 0 0,1 0 0 0 0,1 1 0 0 0,2-1 0 0 0,0 1 0 0 0,1-1 0 0 0,4 23 0 0 0,-5-17-411 0 0,0-24-252 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,2 6 0 0 0,-3-9-52 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,-13 6-3264 0 0,-14-2-229 0 0,-2-4 1624 0 0,1 1 1 0 0,-1 2 0 0 0,0 0-1 0 0,-32 9 1 0 0,41-6 1438 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7115.84">10196 2449 104 0 0,'-7'1'535'0'0,"1"0"0"0"0,-1 0 0 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 2 0 0 0,-8 5 0 0 0,-29 25 19787 0 0,78-33-16423 0 0,46-3-1731 0 0,32-14-1965 0 0,197-54 0 0 0,-9 0-221 0 0,-210 54 18 0 0,0 4 0 0 0,1 3 0 0 0,0 5 0 0 0,173 14 0 0 0,-134 18 0 0 0,-64-12 0 0 0,-57-14-8 0 0,0 1 0 0 0,-1 1 1 0 0,1-1-1 0 0,17 11 0 0 0,-4 3-3439 0 0,-39-13-5308 0 0,-6-1 5327 0 0,-37-1-3842 0 0,36 0 5207 0 0,1-1-1 0 0,-1-2 1 0 0,-43-5 0 0 0,29-2 1161 0 0,-6 6 261 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7710.8">12140 442 248 0 0,'107'101'8896'0'0,"-57"-57"-4917"0"0,28 31-895 0 0,-33-25-2219 0 0,-37-39-1904 0 0,-20-14-2937 0 0,-24-19-1224 0 0,30 18 4823 0 0,-1-1-234 0 0,1 1-1 0 0,-1-2 1 0 0,1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,-7-14-1 0 0,6 7-17 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8061.06">12395 511 564 0 0,'4'1'669'0'0,"0"0"0"0"0,0 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,3 5 1 0 0,4 0 1135 0 0,1-1-789 0 0,-1-1 0 0 0,1 0-1 0 0,0 0 1 0 0,1-1 0 0 0,-1-1 0 0 0,1 0 0 0 0,20 1-1 0 0,-14-1-335 0 0,0 0-1 0 0,35 13 0 0 0,-49-15-632 0 0,-1 0 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,4 7-1 0 0,-6-8-38 0 0,-1 1-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,-2 3 0 0 0,-24 26-10 0 0,-1-1 0 0 0,-2-1 0 0 0,0-2 0 0 0,-2-1 0 0 0,-1-1-1 0 0,-61 32 1 0 0,14-14 265 0 0,67-37 2047 0 0,27-12-1590 0 0,31-13-378 0 0,27-11 117 0 0,120-30-480 0 0,-63 25-6986 0 0,-126 34 6490 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1-1-1 0 0,0 1 1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,1-4 1 0 0,0-1-269 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1-7 0 0 0,0-3 154 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8594.47">13019 536 172 0 0,'4'-4'601'0'0,"-1"1"-1"0"0,1 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1 0 0 0 0,8-4-1 0 0,-2 25 8189 0 0,3 25-4345 0 0,-10-27-3812 0 0,-2-1-1 0 0,0 1 1 0 0,-1 25-1 0 0,-2-28-543 0 0,2 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,6 17 0 0 0,10 30-1437 0 0,-18-61 1281 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,0 0 0 0 0,13-12-1679 0 0,9-23-696 0 0,-20 31 2027 0 0,9-18-576 0 0,-1 0 1 0 0,-1-1 0 0 0,-1-1-1 0 0,7-30 1 0 0,17-101-684 0 0,-28 134 1752 0 0,0 1 842 0 0,-3 5 3593 0 0,41 15-88 0 0,-20-2-3040 0 0,13 3 150 0 0,-19 3-867 0 0,-12-4-538 0 0,0 1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,5 4 1 0 0,-3 0-85 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-2 0 1 0 0,1 1-1 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,-2 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,-7 10-1 0 0,4-8-68 0 0,-1 1 0 0 0,0-2-1 0 0,0 1 1 0 0,-1-1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-2-2-1 0 0,1 1 1 0 0,-1-1 0 0 0,0-1-1 0 0,0 0 1 0 0,-18 6 0 0 0,1-1-31 0 0,-2-2-1 0 0,1-1 1 0 0,-1-1 0 0 0,-35 3-1 0 0,-75-3-101 0 0,286 12 643 0 0,-95-18-310 0 0,1-3 0 0 0,-1-1 0 0 0,89-19 0 0 0,-137 21-245 0 0,0 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,-1-1 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0-1 0 0,3-5 1 0 0,-43-19-3720 0 0,28 25 3100 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,-18 7 1 0 0,-10 6-1390 0 0,-48 27-1 0 0,51-25 1103 0 0,-82 43-2215 0 0,-178 120-1 0 0,242-137 2728 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8806.68">12363 1477 140 0 0,'-84'74'4614'0'0,"73"-67"-5529"0"0,-2-6 9344 0 0,11-9 97 0 0,17-4-5888 0 0,55-27 21 0 0,2 3 0 0 0,142-49-1 0 0,-117 56-2318 0 0,1 4 0 0 0,1 4-1 0 0,187-14 1 0 0,-246 32-567 0 0,183-9 475 0 0,-71 9-4607 0 0,-136 4 5527 0 0,1 4-8368 0 0,-40-6-5151 0 0,-183-29 3471 0 0,172 24 8162 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9159.14">12892 1000 88 0 0,'-5'0'1504'0'0,"-3"2"4718"0"0,3 44 2056 0 0,-12 25-3614 0 0,1-6-2810 0 0,-5 13-1201 0 0,-2-1 1 0 0,-4-2-1 0 0,-4-1 1 0 0,-60 108-1 0 0,49-113-1938 0 0,-3-3-1 0 0,-71 81 1 0 0,74-96-1285 0 0,32-37 1465 0 0,10-13 901 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,-2-1 0 0 0,1 0-1351 0 0,8-8-1531 0 0,17-38 59 0 0,0 0 1234 0 0,1 0 0 0 0,34-45 0 0 0,-40 66 1969 0 0,2 1 1 0 0,1 0-1 0 0,0 2 0 0 0,28-22 1 0 0,-38 35 436 0 0,1 0 1 0 0,1 1 0 0 0,-1 0-1 0 0,2 1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1 1 0 0 0,1 0-1 0 0,1 1 1 0 0,24-3-1 0 0,-25 6 107 0 0,-1 1-1 0 0,0 0 0 0 0,0 1 0 0 0,0 1 0 0 0,0 0 0 0 0,19 6 0 0 0,74 29 2898 0 0,33 26-711 0 0,-94-40-2224 0 0,2-2 0 0 0,92 29-1 0 0,-38-33-1971 0 0,-99-16 1123 0 0,1-1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,4-1-1 0 0,16-4-4043 0 0,-20-32-2075 0 0,-8-28 1091 0 0,3 52 4552 0 0,1-1 1 0 0,1 0 0 0 0,1-25-1 0 0,6 8 91 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9317.75">13599 1069 168 0 0,'-2'1'401'0'0,"0"1"0"0"0,-1-1 0 0 0,1 1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,-1 3 0 0 0,-13 22 5687 0 0,14-27-5056 0 0,-1 2-872 0 0,1 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 1 0 0,0-1-1 0 0,0 6 0 0 0,0-3-325 0 0,-2-1-301 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-7 4 1 0 0,-11 4-1201 0 0,-1-1 0 0 0,-34 10 0 0 0,-11 4-24 0 0,32-9 971 0 0,-1 2 131 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9564.01">12318 1973 424 0 0,'0'7'1090'0'0,"-1"1"1"0"0,-1-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,-1 0 1 0 0,-5 13-1 0 0,-4 8 2210 0 0,0 34 911 0 0,11 4-5333 0 0,-1-59-4246 0 0,-3-23 306 0 0,4 11 5766 0 0,-2-9-1615 0 0,-1 0-137 0 0,0 0-1 0 0,1 0 0 0 0,-1-29 1 0 0,4 29 543 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9832.54">12299 1954 252 0 0,'1'0'111'0'0,"0"-1"0"0"0,0 1 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,2-1 0 0 0,-2 1 36 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,2 0 0 0 0,34-2 3497 0 0,-25 0-2543 0 0,-1 1 1 0 0,1 1-1 0 0,0 0 0 0 0,19 4 1 0 0,-12-1-459 0 0,1 1 0 0 0,-1 1 0 0 0,0 1 0 0 0,-1 1 0 0 0,0 1-1 0 0,28 15 1 0 0,-35-17-408 0 0,30 20 478 0 0,-39-25-686 0 0,0 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,2 3 0 0 0,-3-2-16 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,-2 2 0 0 0,-47 35 11 0 0,36-29-24 0 0,-8 7-9 0 0,9-5-1 0 0,-1 0 1 0 0,0-2 0 0 0,-1 0-1 0 0,0-1 1 0 0,-1 0 0 0 0,-18 5 0 0 0,8-6 54 0 0,11-2 114 0 0,-1-1-1 0 0,1-1 1 0 0,-1-1 0 0 0,-36 2-1 0 0,104-23 741 0 0,-28 10-695 0 0,0 1 0 0 0,1 2 0 0 0,0 0 0 0 0,0 1 0 0 0,38 0 1 0 0,-13 3 35 0 0,81 11 1 0 0,-107-7-600 0 0,0 2 0 0 0,0 1 0 0 0,-1 0 0 0 0,30 14 0 0 0,32 19-6446 0 0,-83-39 6764 0 0,2 1-1612 0 0,0-1 1320 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,1-2 0 0 0,19-61-2339 0 0,-12 31 1554 0 0,5 3 444 0 0,4 0 155 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9984.24">13102 1935 524 0 0,'0'-1'103'0'0,"0"1"0"0"0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1-1 0 0,2-1 1 0 0,11 9 5672 0 0,-25 25 1957 0 0,12-14-5679 0 0,1 38 924 0 0,0-50-2958 0 0,-1 0 0 0 0,1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,7 11 0 0 0,-9-16-235 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,4 1-1 0 0,-4-2-149 0 0,1 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0-1 0 0 0,2-2-1 0 0,79-138-6977 0 0,-68 122 6662 0 0,4-3 115 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10304.66">13446 1797 260 0 0,'90'-6'8291'0'0,"-52"11"-1866"0"0,7 17-1870 0 0,-14-5-3076 0 0,-26-14-1374 0 0,1 0 0 0 0,-1 0 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 1 0 0,1 11-1 0 0,-3-13-102 0 0,1 1 2 0 0,-1 0-1 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,0 0 1 0 0,1 0-1 0 0,-2-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 1 0 0,-2 4-1 0 0,-13 26-27 0 0,8-16-11 0 0,0 0-1 0 0,-2-1 1 0 0,0 0 0 0 0,-16 20 0 0 0,13-22 3 0 0,0 0 1 0 0,-1-2-1 0 0,0 0 0 0 0,-1-1 1 0 0,-1 0-1 0 0,0-1 0 0 0,-25 12 1 0 0,30-18 151 0 0,0-2 0 0 0,0 1 0 0 0,0-2 0 0 0,0 1 0 0 0,-1-2 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-2 0 0 0,-14-2 0 0 0,4-4 711 0 0,-17-2 3956 0 0,41 11-4646 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,3 1-1 0 0,34 6 169 0 0,254 22-307 0 0,-250-25-2057 0 0,79 3 6345 0 0,-70-5-6127 0 0,-6-2-5888 0 0,-2 1-8363 0 0,-80 1 13435 0 0,0 2-1 0 0,-38 9 1 0 0,36-6 1927 0 0,-17 4 86 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="13090.57">7176 3823 344 0 0,'-25'-36'5993'0'0,"11"4"3419"0"0,15 33-9092 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,48 6-705 0 0,-9 0 601 0 0,-29-4-195 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 0 1 0 0,20-3-1 0 0,-26 2-8 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,5-6 1 0 0,-1 3 86 0 0,-9 6-80 0 0,1-1-1 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,2-3-239 0 0,1-4 4033 0 0,-14 11-1342 0 0,8 2-2397 0 0,-1 1-1 0 0,1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 0-1 0 0,1 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,0 6-1 0 0,-3 6-17 0 0,-15 71 102 0 0,3 1 0 0 0,-5 121 0 0 0,13 185 192 0 0,8-334-308 0 0,7 263 147 0 0,24 151 16 0 0,-18-343-204 0 0,-56-203-9 0 0,-24-71-2372 0 0,31 70-1476 0 0,-41-119 0 0 0,-8-42-6337 0 0,-7-18 263 0 0,78 183 8292 0 0,8 40 1032 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="13469.1">6965 4300 508 0 0,'0'-4'144'0'0,"3"-9"9052"0"0,4 13-3092 0 0,1 2-4877 0 0,0 0-2363 0 0,36 7 4463 0 0,81 8 0 0 0,-64-14-2003 0 0,-1-2 0 0 0,76-10-1 0 0,-108 6-1054 0 0,42-8 311 0 0,-35 5-389 0 0,-28 5-224 0 0,-1 1-1 0 0,1-1 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,0-1 1 0 0,7-4-1 0 0,-12 6-206 0 0,-15 1-1167 0 0,0 1 648 0 0,0 0 1 0 0,0 1-1 0 0,0 1 0 0 0,1 0 1 0 0,-1 1-1 0 0,1 0 1 0 0,0 1-1 0 0,0 1 1 0 0,-15 8-1 0 0,-21 14-787 0 0,-53 42 0 0 0,71-48 861 0 0,-94 67-671 0 0,-162 109 2067 0 0,223-170 1021 0 0,20-11 4144 0 0,78-24-4083 0 0,110-33 283 0 0,62-13-314 0 0,-163 44-1478 0 0,-1 2 1 0 0,81-2 0 0 0,94 3-2644 0 0,-205 5 1512 0 0,0 1 0 0 0,0-1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-2 0 0 0,-1 1 0 0 0,18-9 0 0 0,-23 9 334 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-2-1 0 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-2 0 0 0 0,1 0 0 0 0,2-7 0 0 0,84-293-7560 0 0,-75 255 7608 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="13626.88">8208 3497 348 0 0,'2'0'213'0'0,"-1"0"0"0"0,1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1 1 1 0 0,37 59 6425 0 0,-28-43-6030 0 0,-1 0 1 0 0,14 40 0 0 0,-23-56-819 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-5 3-1 0 0,-7 4-643 0 0,-1-1 0 0 0,0-1 0 0 0,0 0-1 0 0,-1-1 1 0 0,0-1 0 0 0,0 0 0 0 0,-1-1 0 0 0,-16 2 0 0 0,14-5 328 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="13825.95">7864 3798 96 0 0,'0'2'352'0'0,"0"1"-1"0"0,0-1 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,3 0 1 0 0,12-1 1056 0 0,0-1-1 0 0,0 0 0 0 0,30-9 1 0 0,-37 9-1184 0 0,174-42 2854 0 0,-111 27-2698 0 0,-44 9-914 0 0,1 2 0 0 0,0 0 0 0 0,43-1 1 0 0,-72 7 397 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,1 2 0 0 0,-13 16-3569 0 0,-36 17-957 0 0,46-33 4382 0 0,-131 69-5172 0 0,48-28 3526 0 0,54-26 1505 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="14214.13">7966 4043 120 0 0,'-7'3'402'0'0,"1"1"-1"0"0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,1 0 1 0 0,0 0-1 0 0,-7 11 1 0 0,10-14-226 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,4 4 0 0 0,-1-2-154 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-2 1 0 0,-1 1-1 0 0,7-2 1 0 0,18-6-62 0 0,0-1 0 0 0,44-22 0 0 0,-54 23 44 0 0,17-10-76 0 0,54-37-1 0 0,-42 24 17 0 0,-22 16 49 0 0,-10 7 202 0 0,-1-1 1 0 0,27-22 0 0 0,-42 31 613 0 0,-15 27 591 0 0,-82 67 39 0 0,-4-4 1 0 0,-173 117-1 0 0,255-195-1114 0 0,-1-1 0 0 0,-1-1 0 0 0,-31 10 0 0 0,0 0 543 0 0,41-16-498 0 0,1 0 0 0 0,-1 0-1 0 0,0-1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,-10-1 1 0 0,18 0-17 0 0,2-5 452 0 0,0 5-780 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1-1 1 0 0,0 1 0 0 0,39-22 578 0 0,1 2 0 0 0,1 2 0 0 0,74-22 1 0 0,-95 33-466 0 0,55-13 184 0 0,1 3-1 0 0,150-14 1 0 0,-123 19-580 0 0,-39 14-512 0 0,-23 1-311 0 0,-21 1-332 0 0,-6-2-5049 0 0,-24-8 2262 0 0,-1 2 2937 0 0,0 0 0 0 0,0 1 0 0 0,0 1 0 0 0,0-1-1 0 0,-18 0 1 0 0,4 1-77 0 0,1 1-1 0 0,-1 1 0 0 0,-32 4 1 0 0,32 2 726 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="14534.8">8253 4269 140 0 0,'0'0'5013'0'0,"-26"19"5197"0"0,10-3-8228 0 0,1 2 1 0 0,-22 32 0 0 0,-45 95-1144 0 0,47-80-340 0 0,-110 179-263 0 0,128-213-229 0 0,8-14-5 0 0,0 1 1 0 0,-2-2-1 0 0,0 1 1 0 0,-14 15-1 0 0,23-30 22 0 0,-3 1 1026 0 0,9-5-519 0 0,0 0-388 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,6 1 0 0 0,53 3 957 0 0,-63-4-1089 0 0,134 24 1376 0 0,-118-21-1288 0 0,0 2 1 0 0,-1 0 0 0 0,1 1-1 0 0,-1 0 1 0 0,-1 1 0 0 0,19 12-1 0 0,3 4 6 0 0,-25-16-161 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,-1 1 1 0 0,16 16-1 0 0,0-1-513 0 0,-23-21 282 0 0,1 0 0 0 0,0-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,2 5 0 0 0,-4-8-874 0 0,-2-14-6393 0 0,-7-12 4505 0 0,0-6 899 0 0,-5-49-2018 0 0,8 53 3109 0 0,2-1 0 0 0,0 0 1 0 0,2-1-1 0 0,2-42 1 0 0,5 40 463 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="14876.97">8342 4702 104 0 0,'-1'-11'4110'0'0,"-30"52"4475"0"0,14-12-6361 0 0,0 0 1 0 0,-13 37 0 0 0,-13 23-841 0 0,5-13-610 0 0,-7 13-304 0 0,26-54-370 0 0,15-27-101 0 0,-1 0 0 0 0,1 0 0 0 0,-2 0 0 0 0,1 0 0 0 0,-11 11 0 0 0,7-10-216 0 0,0 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,0-1-1 0 0,-1 0 1 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,-13 3 0 0 0,18-6-49 0 0,-1-1 0 0 0,1 1-1 0 0,-1-2 1 0 0,0 1 0 0 0,1-1 0 0 0,-1-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,-9-8 1 0 0,7 3-64 0 0,1 1-1 0 0,-1-2 1 0 0,2 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0-1 1 0 0,1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,1 0 1 0 0,-3-16-1 0 0,-2-11-299 0 0,1 0 0 0 0,-3-61-1 0 0,7-40 717 0 0,4 124 328 0 0,1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,2 0 0 0 0,8-19 0 0 0,-10 26-10 0 0,2 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,1 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,16-1 1 0 0,11 1 322 0 0,0 1 0 0 0,0 1 0 0 0,47 7 0 0 0,-62-5-461 0 0,243 36 1298 0 0,-91-19-2811 0 0,-108-18-2610 0 0,-38-1-1449 0 0,-24-1 5101 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0-2 1 0 0,3-31-3444 0 0,-3-41-331 0 0,0 51 3338 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="15187.4">8858 3924 16 0 0,'3'0'490'0'0,"0"1"0"0"0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1 0 0 0,-1 0-1 0 0,2 3 1 0 0,2 3 845 0 0,0 1 0 0 0,-1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,4 17 0 0 0,4 72 3177 0 0,-9-72-3992 0 0,-1 0 0 0 0,-1-1 0 0 0,-7 45 0 0 0,7-67-491 0 0,-56 255 1097 0 0,48-231-1081 0 0,5-14-24 0 0,-1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,-1 0-1 0 0,0-1 1 0 0,-1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,-12 13 0 0 0,11-19 226 0 0,13-16 463 0 0,14-16-72 0 0,11 2-546 0 0,0 1 0 0 0,1 1 0 0 0,1 1 0 0 0,1 2 0 0 0,38-15 0 0 0,-49 23-189 0 0,32-11-630 0 0,-41 17-180 0 0,0-1 0 0 0,0 0 0 0 0,19-12 0 0 0,-18 10-1026 0 0,-12 6 1573 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,-1-1-1 0 0,0-68-5414 0 0,-5-40 1803 0 0,0 75 3164 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="15413.18">9291 3692 260 0 0,'0'0'2906'0'0,"26"0"2779"0"0,-22 5-4816 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,-1 1 1 0 0,3 13-1 0 0,-1 4 880 0 0,0 49-1 0 0,-45 472 3829 0 0,14-294-4661 0 0,12-113-628 0 0,-6 126-164 0 0,20-210-406 0 0,-12 63 0 0 0,7-65-1199 0 0,-2 63-1 0 0,5-90-992 0 0,3-25 2300 0 0,1 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-105 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0-20-303 0 0,24-127-6075 0 0,27-72 2661 0 0,-32 153 3317 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="15718.61">9629 3955 76 0 0,'2'-8'443'0'0,"1"0"0"0"0,0 1 0 0 0,0-1 1 0 0,1 1-1 0 0,0 0 0 0 0,7-9 0 0 0,15-16 6221 0 0,-24 33-6199 0 0,0 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 4 1 0 0,3 10 752 0 0,-2 1 1 0 0,0-1-1 0 0,1 23 0 0 0,-13 90 402 0 0,3-64-1024 0 0,-8 27-240 0 0,10-65-86 0 0,0 1 0 0 0,-1 40 0 0 0,6-64 621 0 0,19-28 1139 0 0,65-5-243 0 0,-37 12-1348 0 0,-9 4-200 0 0,0-1 0 0 0,-1-2 0 0 0,62-39 0 0 0,17-32-1393 0 0,-104 81 1673 0 0,3-5-6786 0 0,-16 11 5868 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 1 0 0,-1 1-1 0 0,-51 6-4824 0 0,37-6 3120 0 0,-1 1 1 0 0,-28 7-1 0 0,36-4 1345 0 0,-2 2 173 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="15938.19">9954 4074 696 0 0,'-25'13'9119'0'0,"18"38"920"0"0,-2 53-5213 0 0,-22 56-1877 0 0,21-117-2313 0 0,-14 59 82 0 0,-4-1 0 0 0,-5-1 0 0 0,-48 100 0 0 0,73-184-740 0 0,-62 119-642 0 0,61-121 300 0 0,0-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,-1-1 0 0 0,-1 0 0 0 0,0-1 0 0 0,-15 11 0 0 0,19-16-291 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0-1 0 0 0,-14 4 0 0 0,21-6 428 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,0-1 0 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 1 0 0 0,1-3-1 0 0,-6-23-1352 0 0,1 0 0 0 0,2 0-1 0 0,1 0 1 0 0,3-50 0 0 0,21-112-2172 0 0,7 77 2275 0 0,-21 62 984 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="16092.42">9527 4432 220 0 0,'3'1'350'0'0,"-1"0"1"0"0,0 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,2 6-1 0 0,22 55 4726 0 0,-24-59-4746 0 0,13 30 1997 0 0,2 0 0 0 0,1-1-1 0 0,23 33 1 0 0,19 35 386 0 0,110 180 590 0 0,-140-236-3073 0 0,-9-16-371 0 0,1-1-1 0 0,30 31 1 0 0,-34-41-1385 0 0,39 30 1 0 0,-53-47 1092 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,3-3 0 0 0,10-8-1568 0 0,0 0 1 0 0,-1-2-1 0 0,22-24 0 0 0,-26 26 1605 0 0,11-9-627 0 0,1 2 0 0 0,45-32 0 0 0,-67 52 1017 0 0,48-36-555 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="16476.67">11407 3616 484 0 0,'0'0'2401'0'0,"18"27"7903"0"0,-16-25-10229 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 1 0 0,-1 4-1 0 0,1-4-260 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,-2 2 0 0 0,-5 4-596 0 0,-2 0-1 0 0,1 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,-1-1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 0 0 0 0,-17 5 0 0 0,1 2-349 0 0,-43 19-1030 0 0,51-20 1698 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17099.12">11012 3974 40 0 0,'-1'14'2488'0'0,"2"-1"6104"0"0,24-9-4575 0 0,-11-5-3223 0 0,-1 0 0 0 0,1-2 0 0 0,-1 1 0 0 0,16-6-1 0 0,35-7 554 0 0,26 0-121 0 0,-63 9-982 0 0,1 1 0 0 0,44-1 0 0 0,35-7-276 0 0,-106 13-60 0 0,-21 20-1110 0 0,-196 167-678 0 0,166-137 1760 0 0,-46 60 0 0 0,76-83 124 0 0,0 1 0 0 0,2 1 1 0 0,2 0-1 0 0,-19 44 0 0 0,33-67-6 0 0,-1 1-1 0 0,1-1 1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1-1 0 0,1 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,1 1 1 0 0,0-1 0 0 0,3 8 0 0 0,-3-13 2 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,5-1 0 0 0,44-6 13 0 0,-9-8 4 0 0,-1-2 1 0 0,-1-1-1 0 0,-1-2 0 0 0,0-2 1 0 0,45-35-1 0 0,-46 32-9 0 0,-20 19 225 0 0,-20 18 27 0 0,-23 31 183 0 0,21-36-371 0 0,-19 27 122 0 0,0-1 0 0 0,-3-2 0 0 0,-40 41 0 0 0,-99 78 25 0 0,88-82-113 0 0,-144 99 579 0 0,174-135-320 0 0,43-29-311 0 0,-3 3 188 0 0,-1 0-1 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,-1-2-1 0 0,-14 5 0 0 0,22-8 954 0 0,21-20-37 0 0,23-7-967 0 0,1 2-1 0 0,0 3 0 0 0,2 1 1 0 0,1 2-1 0 0,0 3 0 0 0,1 1 0 0 0,73-12 1 0 0,-88 24-151 0 0,-1 0 0 0 0,1 3 1 0 0,-1 1-1 0 0,51 7 0 0 0,132 35-902 0 0,-148-28-42 0 0,-44-10 325 0 0,-10-1-290 0 0,0-1 0 0 0,0 0 0 0 0,1-1 1 0 0,-1-1-1 0 0,0 0 0 0 0,1-1 0 0 0,17-2 0 0 0,-29 2 580 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,2-4 0 0 0,7-56-4311 0 0,-8 46 3902 0 0,19-203-5016 0 0,-9 162 5010 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17226.93">12133 3491 536 0 0,'0'-9'538'0'0,"0"7"-210"0"0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,5-6 8476 0 0,-12 26-5075 0 0,9 25-2923 0 0,0-30-1091 0 0,-2 1 0 0 0,0 0-1 0 0,-3 22 1 0 0,-1-8-491 0 0,4-21 364 0 0,0-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,-1 0-1 0 0,-4 4 1 0 0,-1-1-291 0 0,0-1-1 0 0,-1 0 1 0 0,0-1 0 0 0,0 0 0 0 0,-1-1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 0-1 0 0,-15 1 1 0 0,9-3 110 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17465.02">11757 3754 292 0 0,'0'0'2471'0'0,"13"14"2067"0"0,-16 82 4898 0 0,-1-56-7412 0 0,-12 60 1 0 0,10-76-1498 0 0,2-8-92 0 0,0 1-1 0 0,1-1 1 0 0,1 1 0 0 0,-1 26-1 0 0,7-43-368 0 0,-1 0 1 0 0,0-1-1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,0 0 0 0 0,5-4 0 0 0,-3 4 31 0 0,80-32 570 0 0,-43 14-472 0 0,19-6-419 0 0,1 3 0 0 0,0 2 0 0 0,2 3 0 0 0,95-13 1 0 0,-121 27-847 0 0,-7 1-2579 0 0,55-11-1 0 0,-83 12 3302 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,1-3 1 0 0,1-6-854 0 0,0-1 1 0 0,0 0-1 0 0,0-25 0 0 0,5-21-851 0 0,-2 35 1515 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17616.68">12567 3554 12 0 0,'0'0'1414'0'0,"-13"31"4423"0"0,9-20-4669 0 0,1 0 0 0 0,1-1 0 0 0,0 2 0 0 0,0-1 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,2 14 0 0 0,-2-1-271 0 0,3 77 878 0 0,1 0-3506 0 0,-5-94 1214 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 1 0 0,-8 4-1 0 0,-13 12-1577 0 0,-2-1 1 0 0,-44 25-1 0 0,26-18 733 0 0,16-10 609 0 0,3-4 129 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17851.83">11789 4238 40 0 0,'-12'5'1046'0'0,"-13"8"2390"0"0,18-1 2154 0 0,7-11-5100 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 1 0 0 0,26 10 3915 0 0,48-5-2928 0 0,-44-5-69 0 0,12-1-13 0 0,77-6 1 0 0,-87 2-937 0 0,130-21 1037 0 0,-56 6-848 0 0,36-14-470 0 0,-66 13-333 0 0,-58 15-324 0 0,0-1 0 0 0,26-11 1 0 0,-40 14-142 0 0,0-1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,7-7-1 0 0,-13 10 427 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1-2 1 0 0,-22-19-4794 0 0,-33-5-1117 0 0,44 22 5338 0 0,0 1 0 0 0,0 1 1 0 0,0 0-1 0 0,-1 1 0 0 0,1 0 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,-22 6 0 0 0,15 3 157 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="18667.48">12350 4206 308 0 0,'-5'6'861'0'0,"1"0"-1"0"0,-1 1 1 0 0,2 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,-1 9-1 0 0,-1-9 254 0 0,0-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,0-1-1 0 0,-14 9 1 0 0,15-9-591 0 0,-6 3 33 0 0,-95 69 1754 0 0,78-58-3073 0 0,-1 0 1 0 0,-1-2-1 0 0,-49 19 0 0 0,61-31-362 0 0,0-1 1 0 0,-36 4-1 0 0,41-6 578 0 0,0-2-236 0 0,1-1-1 0 0,-1 0 0 0 0,0-1 1 0 0,0 0-1 0 0,0-1 1 0 0,-17-6-1 0 0,26 8 493 0 0,1-1 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-5-6 0 0 0,6 7 331 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-5 2067 0 0,2 12-1629 0 0,1 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 8 0 0 0,1-3 110 0 0,7 27 734 0 0,-1 0 1 0 0,6 68 0 0 0,2 10-558 0 0,-8-56-677 0 0,-7-38-290 0 0,1-1 1 0 0,1 1-1 0 0,1-1 1 0 0,0 0-1 0 0,12 25 1 0 0,-17-43 144 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,12-20-1419 0 0,2-34-375 0 0,32-195 148 0 0,-45 236 2187 0 0,0-1 1 0 0,2 1-1 0 0,-1-1 1 0 0,2 1-1 0 0,0 0 1 0 0,0 0-1 0 0,1 1 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 1 1 0 0,12-12-1 0 0,-8 12 380 0 0,1 2 0 0 0,1-1-1 0 0,-1 2 1 0 0,2 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,0 1-1 0 0,31-8 1 0 0,14-7 720 0 0,-15 7-442 0 0,0 2 0 0 0,0 2 0 0 0,69-7 0 0 0,-43 8-156 0 0,-11 0 297 0 0,97-2 0 0 0,-132 12-972 0 0,-1 0-1 0 0,0 1 1 0 0,0 1-1 0 0,0 2 0 0 0,0 0 1 0 0,45 17-1 0 0,-65-20-273 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,-1 1 1 0 0,3 8 0 0 0,-1 4 16 0 0,0-1 1 0 0,-1 1-1 0 0,-1 1 0 0 0,-2 17 1 0 0,1-20-55 0 0,-2 4-122 0 0,0-1 1 0 0,-2 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,-9 18 0 0 0,7-17-231 0 0,4-11-10 0 0,-1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-2 0 0 0,-13 4 0 0 0,-5 0-783 0 0,-1-2 1 0 0,1-1-1 0 0,-1-1 1 0 0,0-1-1 0 0,-48-5 1 0 0,31-2-223 0 0,1-3 0 0 0,1-1 0 0 0,-1-1 0 0 0,2-3-1 0 0,-65-30 1 0 0,84 32 777 0 0,0-1 0 0 0,2-1 0 0 0,-1-1 0 0 0,-27-26 0 0 0,26 23 151 0 0,16 11 477 0 0,1 1-1 0 0,0-1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,0-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1-14 0 0 0,2 6 1395 0 0,-1 24 1475 0 0,5 35-414 0 0,2-25-2069 0 0,-2 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,-2 26-1 0 0,3 37 315 0 0,1-38-483 0 0,-3-26-356 0 0,1 0 0 0 0,1 1 0 0 0,6 24 0 0 0,-9-42 81 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,11-11-522 0 0,8-21 3 0 0,-18 32 484 0 0,30-69-698 0 0,27-85 1 0 0,-1 0 832 0 0,-6 15 2473 0 0,-51 141-2492 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,2 17 1370 0 0,-1 20-119 0 0,-19 325 5995 0 0,13-202-5720 0 0,18 154 441 0 0,-12-302-1967 0 0,7 65 174 0 0,4-1-1 0 0,31 108 0 0 0,-28-136-904 0 0,22 48-1 0 0,-26-73-2526 0 0,26 42 0 0 0,-31-89-8628 0 0,-6-21 8754 0 0,-7 9 1074 0 0,-1 0 1 0 0,-20-55-1 0 0,6 22 807 0 0,-1 1 479 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">4520 301 200 0 0,'-1'-5'16389'0'0,"-20"-6"-11343"0"0,-31-11-2834 0 0,-73-27 823 0 0,28 19-1797 0 0,-138-33 819 0 0,-78-23-792 0 0,287 79-1222 0 0,-1 0 0 0 0,0 3 0 0 0,-29-3 0 0 0,-1 1 1 0 0,36 4-28 0 0,0 1 1 0 0,0 0-1 0 0,0 2 0 0 0,-37 7 0 0 0,-83 24 28 0 0,111-24-40 0 0,-50 6-3 0 0,-1-1 0 0 0,1-5-1 0 0,-129-3 1 0 0,123 0-13 0 0,0 4-1 0 0,-101 23 0 0 0,127-21 4 0 0,-74 18 14 0 0,-78 11-14 0 0,-28-34 4 0 0,159-7-5 0 0,-59-5-10 0 0,57 2 9 0 0,52 2 6 0 0,0 1 1 0 0,0 1 0 0 0,-35 6 0 0 0,-101 13-17 0 0,152-16 19 0 0,4-1-3 0 0,-2 0 1 0 0,1 1-1 0 0,1 1 1 0 0,-18 8-1 0 0,-59 23-26 0 0,67-22 23 0 0,5-4 1 0 0,-1 1 0 0 0,2 1-1 0 0,0 0 1 0 0,-17 18 0 0 0,-91 107-18 0 0,55-54 39 0 0,32-30-3 0 0,-41 68-16 0 0,52-78-1 0 0,-21 41 4 0 0,5 0-4 0 0,-7 22-6 0 0,-53 210 4 0 0,81-245 7 0 0,-42 175-10 0 0,0-30 11 0 0,23-42 9 0 0,22-92-11 0 0,8-23-9 0 0,1-1 0 0 0,3 1 0 0 0,3 62 0 0 0,3-97-1 0 0,2-1-1 0 0,1 1 1 0 0,1-1 0 0 0,13 41 0 0 0,-6-23 0 0 0,0-5-4 0 0,3 0 0 0 0,0-2 0 0 0,30 50 0 0 0,-34-64 14 0 0,31 50-12 0 0,2-3 0 0 0,87 99 1 0 0,-93-124 22 0 0,0-1 0 0 0,3-2 0 0 0,1-3 0 0 0,1-1 1 0 0,3-1-1 0 0,50 25 0 0 0,-39-23-2 0 0,21 11 3 0 0,345 129 95 0 0,-330-143-74 0 0,2-4 0 0 0,157 24 0 0 0,7-9 14 0 0,62 20 36 0 0,-209-38-35 0 0,352 87 93 0 0,-119-27-24 0 0,-239-59-78 0 0,176 37 12 0 0,19-14-37 0 0,-110-19 26 0 0,-81-19 29 0 0,0-6 0 0 0,0-5 0 0 0,1-4 1 0 0,-2-6-1 0 0,192-42 0 0 0,-256 41-51 0 0,1-1 0 0 0,79-37 0 0 0,-80 27 2 0 0,-13 7 15 0 0,46-30 0 0 0,-41 19-5 0 0,-2-3 0 0 0,52-53 0 0 0,-49 46-23 0 0,-3-1 0 0 0,-1-3 0 0 0,33-51 0 0 0,-46 59-5 0 0,80-143 0 0 0,-75 122 0 0 0,-2-3 0 0 0,-4 0 0 0 0,-2-1 0 0 0,-1-1 0 0 0,-4-1 0 0 0,10-92 0 0 0,-17 82 0 0 0,8-155 0 0 0,-14 183 0 0 0,-1 0 0 0 0,-2-1 0 0 0,-2 2 0 0 0,-16-69 0 0 0,5 53 0 0 0,10 28 0 0 0,-2 1 0 0 0,-1 1 0 0 0,-21-44 0 0 0,-20-21 0 0 0,-4 4 0 0 0,-4 1 0 0 0,-131-147 0 0 0,80 122 0 0 0,-5 6 0 0 0,-237-169 0 0 0,265 215-32 0 0,-2 4-1 0 0,-3 4 1 0 0,-1 5 0 0 0,-112-41 0 0 0,156 73-632 0 0,-1 2 1 0 0,-84-10 0 0 0,-25 8-3792 0 0,120 11 2780 0 0,-283-8-13269 0 0,242 7 12764 0 0,-1-4 0 0 0,1-3 0 0 0,-110-29 0 0 0,99 16 1550 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2058.85">7695 625 388 0 0,'4'-3'279'0'0,"0"0"1"0"0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 0 0 0,2 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 1 1 0 0,-2-1-1 0 0,2 1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,-1-1 1 0 0,7 5-1 0 0,-2-2 570 0 0,-1 0-1 0 0,0 0 1 0 0,-2 1-1 0 0,2 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,-3 0 0 0 0,2 0-1 0 0,-1 1 1 0 0,0 0-1 0 0,0 0 1 0 0,6 12-1 0 0,-11-16-536 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 3 0 0 0,-27 49 2612 0 0,15-30-2208 0 0,-14 24 98 0 0,-2 0-1 0 0,-48 57 0 0 0,71-96-771 0 0,-27 36 89 0 0,-2-2 1 0 0,-65 60-1 0 0,87-94-136 0 0,0 0 0 0 0,0-2 0 0 0,-2 1 0 0 0,2-2 0 0 0,-2 0 0 0 0,0-1 0 0 0,-32 7 0 0 0,46-12 4 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,-2-1-1 0 0,-31-4-21 0 0,34 5 21 0 0,2 2-74 0 0,0-1 73 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,2 0 0 0 0,-1 1 3 0 0,22 11 54 0 0,39 20-1 0 0,15 9 90 0 0,-51-27-95 0 0,1-1 1 0 0,37 12-1 0 0,-9-3-264 0 0,52 9-2925 0 0,-108-32 2949 0 0,0 1 1 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0-1 0 0 0,0-7-1160 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-2 2 0 0 0,-2-11 0 0 0,1 4 435 0 0,-3-10-640 0 0,-1 1-1 0 0,-1 1 0 0 0,-1 0 1 0 0,-20-38-1 0 0,24 51 1492 0 0,1 1 0 0 0,1 0 1 0 0,0-1-1 0 0,-2-14 0 0 0,3 14 1096 0 0,1 1 0 0 0,-2-1 0 0 0,0 1 0 0 0,-6-12 0 0 0,20 38 6083 0 0,2 0-3414 0 0,42 36-4999 0 0,-4-6-1920 0 0,-49-45 2980 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,5-3-1 0 0,6-7-733 0 0,1-1 1 0 0,-1 1-1 0 0,21-27 0 0 0,-23 25 653 0 0,8-6-108 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2219.91">8189 1004 488 0 0,'8'-14'-1158'0'0,"5"-2"7329"0"0,-2 17 908 0 0,-2 16-3436 0 0,-6-6-3217 0 0,0 0 0 0 0,-1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,-3 11 0 0 0,-3 7-150 0 0,1-1 0 0 0,-16 36-1 0 0,16-51-522 0 0,0 0 0 0 0,-2-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,-1-1 0 0 0,0 0 0 0 0,0-1-1 0 0,-2 0 1 0 0,0 0 0 0 0,1-1 0 0 0,-2-1-1 0 0,0 0 1 0 0,-22 14 0 0 0,-13 2-2325 0 0,-1-4-1 0 0,-77 28 1 0 0,77-32 668 0 0,-2-1-645 0 0,0-3 0 0 0,-101 12 0 0 0,127-24 2065 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3608.46">7461 1713 40 0 0,'0'0'1309'0'0,"7"-13"-248"0"0,-4 12-1139 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,2-4 0 0 0,10-19 1833 0 0,-13 20-1217 0 0,0 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 1 0 0,1 1-1 0 0,6-9 2472 0 0,10 25-98 0 0,-14 1-2412 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,-1 1 0 0 0,0-2 0 0 0,-1 1 0 0 0,0 1 0 0 0,-1-1 0 0 0,-1 1 0 0 0,-5 22 0 0 0,4-13-324 0 0,-2-2-1 0 0,0 1 1 0 0,-14 37 0 0 0,14-47-324 0 0,-1-2 1 0 0,0 1-1 0 0,1-1 1 0 0,-14 16-1 0 0,15-21-287 0 0,1-1-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,0-1-1 0 0,-5 4 1 0 0,10-7 333 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,-2-16-2138 0 0,7-18 267 0 0,-5 32 1609 0 0,9-42-868 0 0,3 0 1 0 0,2 1 0 0 0,27-60 0 0 0,-14 37 2084 0 0,-25 62-530 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0-1 0 0,0 1 1 0 0,-1 0 0 0 0,2-1 0 0 0,-2 1 0 0 0,1 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,7 2-1 0 0,35 1 2219 0 0,-14-2-1123 0 0,-1 1-264 0 0,-1-3 0 0 0,0 0-1 0 0,0-2 1 0 0,49-9 0 0 0,-32 4-263 0 0,19 1 138 0 0,48-7 310 0 0,-30-10-1082 0 0,-63 15-908 0 0,-15 4-630 0 0,-13 2 8 0 0,2 2 852 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 2 0 0 0,1-1 0 0 0,1 1 0 0 0,-6 3 0 0 0,-47 36-2843 0 0,38-27 2361 0 0,-306 248-9468 0 0,309-250 10248 0 0,-107 79-125 0 0,107-83 1692 0 0,0 1 0 0 0,-1-2 0 0 0,-25 7 8525 0 0,49-23-7851 0 0,13-6-1562 0 0,41-11 1479 0 0,104-26 0 0 0,-128 46-1890 0 0,1 1 0 0 0,0 1 1 0 0,43 3-1 0 0,-40 1-596 0 0,1 6-499 0 0,-36-5 427 0 0,-1-2-1 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,-1 0 1 0 0,2-1-1 0 0,5-1 1 0 0,-11 2 374 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,-18-17-1560 0 0,17 18 1304 0 0,-139-119-6160 0 0,126 107 6661 0 0,0-2 0 0 0,2 0 0 0 0,-1 0 1 0 0,-19-28-1 0 0,-20-23 6198 0 0,52 66-6118 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 1 0 0 0,1 51 1608 0 0,0-36-1283 0 0,-1-15-493 0 0,1 69 887 0 0,-3 0 0 0 0,-3 0 0 0 0,-20 107 0 0 0,18-139-1079 0 0,7-33 109 0 0,-1 1 0 0 0,0-1 0 0 0,-1 0-1 0 0,1 1 1 0 0,-2-1 0 0 0,1 0 0 0 0,-1 0-1 0 0,-4 8 1 0 0,2-4 61 0 0,3-7-311 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,-4 5 1 0 0,6-8 208 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,-1-1 0 0 0,-57-70-2941 0 0,-6-5 2282 0 0,59 71 924 0 0,-1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,-1 0 1 0 0,0 0-1 0 0,-1 1 1 0 0,-12-6-1 0 0,18 9-44 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-4 1 0 0 0,3 0 41 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-2 7 1 0 0,0 4 270 0 0,0 0 0 0 0,1-1 0 0 0,0 1 0 0 0,1 1 0 0 0,1-1 0 0 0,1 1 0 0 0,2 19 0 0 0,-2-30-248 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,2 1 1 0 0,-1 0-1 0 0,0-1 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,5 4 0 0 0,-1-3 78 0 0,-1 1 1 0 0,1-1-1 0 0,1-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,1-1 1 0 0,9 1-1 0 0,14 0 255 0 0,0-3 0 0 0,0 0 0 0 0,0-2 0 0 0,45-11 0 0 0,-16 0-258 0 0,-1-3 0 0 0,87-37 0 0 0,108-67-359 0 0,-248 117 114 0 0,-5 2-7 0 0,1 1 1 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 2 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,4 1 0 0 0,-5 0 7 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,-2 2 1 0 0,-66 246-357 0 0,43-150-788 0 0,-12-13-3907 0 0,37-85 4814 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,-24-9-3440 0 0,-12-27-140 0 0,25 19 2770 0 0,1-1 1 0 0,1 1-1 0 0,-14-32 0 0 0,-1-6-35 0 0,6 13 526 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3871.63">7134 868 56 0 0,'14'11'5851'0'0,"-9"-2"-4326"0"0,-5-7-1316 0 0,1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 3-1 0 0,19 52 2181 0 0,22 29-4769 0 0,-40-83 1542 0 0,5 29-4888 0 0,-24 37 1988 0 0,12-55 3308 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4475.02">7073 1421 364 0 0,'0'0'659'0'0,"-7"18"5309"0"0,10-14-5494 0 0,0 0 0 0 0,-1 0 0 0 0,2-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,0-1 0 0 0,8 4 0 0 0,14 14-126 0 0,-14-8-182 0 0,-1 0 0 0 0,1 1 0 0 0,16 25 0 0 0,-24-31-150 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 14 0 0 0,-2-7-6 0 0,0-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,-2 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,-1-1 1 0 0,-1-1-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-2 0 0 0 0,0-1 1 0 0,-2 0-1 0 0,-9 11 0 0 0,13-17 16 0 0,4-2 8 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0-1-1 0 0,-1 0 0 0 0,1 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-6 2-1 0 0,8-4 866 0 0,44 18-585 0 0,-37-17-233 0 0,-1 1 1 0 0,0 0-1 0 0,1 1 0 0 0,-2 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,-2 0-1 0 0,1 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-2 1-1 0 0,1-2 0 0 0,0 2 1 0 0,0-1-1 0 0,-1 1 0 0 0,0 0 0 0 0,1 10 1 0 0,-1 3 236 0 0,0 0 0 0 0,-1-1 0 0 0,0 1 1 0 0,-2-1-1 0 0,0 1 0 0 0,-2-1 0 0 0,-4 21 1 0 0,3-28-216 0 0,0 0 0 0 0,-1-2 1 0 0,0 1-1 0 0,1 0 1 0 0,-2 0-1 0 0,0-1 1 0 0,-1 0-1 0 0,1-1 1 0 0,-18 14-1 0 0,8-4-4 0 0,-14 11-19 0 0,-1-1 0 0 0,-1-1 0 0 0,-2-1 1 0 0,-37 20-1 0 0,48-32-195 0 0,-2-1 1 0 0,1-2 0 0 0,-1 0-1 0 0,0-2 1 0 0,0-1 0 0 0,-1-1-1 0 0,-35 5 1 0 0,48-11-129 0 0,1 0 0 0 0,-1-1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-21-7 0 0 0,31 8 156 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,2 1-1 0 0,-2-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,2-6-1 0 0,-1-5-33 0 0,3 1 1 0 0,0-1-1 0 0,0 1 0 0 0,1-1 0 0 0,1 1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,1 0 0 0 0,1 2 0 0 0,17-22 1 0 0,-19 24 261 0 0,1 1 0 0 0,1 0 0 0 0,0 0 1 0 0,-1 1-1 0 0,1 0 0 0 0,1 0 0 0 0,-2 1 0 0 0,2 1 1 0 0,1-1-1 0 0,-2 2 0 0 0,1-1 0 0 0,1 2 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 1 0 0 0,11 0 0 0 0,41 3 1725 0 0,-1 3 0 0 0,79 16-1 0 0,122 42 3740 0 0,-178-40-4066 0 0,168 56 1117 0 0,533 194-2657 0 0,-505-166 0 0 0,3 8 0 0 0,12 5 0 0 0,-148-71 0 0 0,-88-37-791 0 0,-23-15-4057 0 0,-37 2 4583 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,-3-24-3572 0 0,-10-18-527 0 0,12 42 4112 0 0,-31-82-5925 0 0,-24-35 1773 0 0,33 76 3608 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5231.21">9163 830 548 0 0,'-2'-5'13892'0'0,"7"15"-6406"0"0,4-3-9563 0 0,97 49 4736 0 0,-8-17-1501 0 0,-98-39-892 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-7 30-712 0 0,3-17 879 0 0,-4 115-74 0 0,4-19-164 0 0,-10 311 579 0 0,15-314-555 0 0,2 93 373 0 0,31 218-1 0 0,-31-398-591 0 0,30 176 0 0 0,-33-197 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,-11-13-500 0 0,-11-24-1188 0 0,-11-50-3700 0 0,4-2 0 0 0,3 0 0 0 0,-23-149 0 0 0,25 110 1844 0 0,8 38 1060 0 0,-7-109 1 0 0,22 143 2004 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5617">9114 1371 132 0 0,'-3'5'411'0'0,"-1"3"601"0"0,0 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-2 12 0 0 0,4-17-497 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1-1 0 0 0,1 4 0 0 0,3 1 119 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-2-1 0 0 0,2-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,0-1 1 0 0,14 4-1 0 0,15 2 1072 0 0,70 8 1 0 0,-102-17-1508 0 0,77 5 1258 0 0,-56-5-959 0 0,50 8 0 0 0,-54-6-416 0 0,-21-2-93 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,2 1 0 0 0,-1 0-129 0 0,-9 23-1019 0 0,-47 43-1429 0 0,-75 77-1 0 0,68-85 1683 0 0,-89 65 0 0 0,129-110 1156 0 0,0 0 1 0 0,-1-1 0 0 0,0-1 0 0 0,-2-2 0 0 0,0 0-1 0 0,-27 8 1 0 0,27-13 2206 0 0,52-15 1142 0 0,11-4-2795 0 0,251-95 1810 0 0,-166 71-2826 0 0,-90 30-1463 0 0,2-3 0 0 0,-2-1 0 0 0,65-29 0 0 0,-89 34 670 0 0,0-1 0 0 0,0 0 0 0 0,0 0-1 0 0,-2-2 1 0 0,2 1 0 0 0,-2-1 0 0 0,0 0 0 0 0,-1-1-1 0 0,1 0 1 0 0,5-11 0 0 0,11-19-3366 0 0,21-54 1 0 0,13-66-458 0 0,-40 121 4108 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5779.76">10408 836 48 0 0,'94'-12'8173'0'0,"-72"16"-1341"0"0,-16 8-4522 0 0,-7-10-2448 0 0,0 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,0-1 0 0 0,-3 3-1 0 0,-9 3-875 0 0,-1 0 0 0 0,1 0 0 0 0,-2-1 0 0 0,2-1 0 0 0,-2 0 0 0 0,1-2 0 0 0,-2 1 0 0 0,2-2 0 0 0,-22 1 0 0 0,-96 4-2967 0 0,96-7 3299 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5952.45">9693 1278 188 0 0,'2'17'1179'0'0,"0"-1"-1"0"0,2 1 1 0 0,0-2-1 0 0,1 2 1 0 0,0-1-1 0 0,1-1 1 0 0,0 1 0 0 0,2-1-1 0 0,17 26 1 0 0,-17-29-322 0 0,1-1 1 0 0,-1 0 0 0 0,2 0-1 0 0,17 15 1 0 0,-2-2-184 0 0,-20-19-679 0 0,-1-1 0 0 0,1 0-1 0 0,1-1 1 0 0,-2 0 0 0 0,1 0 0 0 0,1 1-1 0 0,0-2 1 0 0,0 1 0 0 0,10 3 0 0 0,-14-5-84 0 0,0-1 1 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1-1 0 0,0 0 1 0 0,0-5 0 0 0,7-25-1525 0 0,-1-1-1 0 0,-2-1 1 0 0,-2 2-1 0 0,0-43 1 0 0,1-5-415 0 0,-2 41 1074 0 0,-1 17 271 0 0,1 2-1 0 0,7-34 1 0 0,-3 28 223 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6178.54">10026 1041 208 0 0,'0'0'623'0'0,"62"14"7227"0"0,-44-11-6365 0 0,0 0-1 0 0,1-2 0 0 0,0 0 0 0 0,31-3 0 0 0,344-56 6906 0 0,-332 44-7534 0 0,115-20 1640 0 0,-150 30-1988 0 0,0 2-1 0 0,0 1 1 0 0,1 2-1 0 0,43 6 0 0 0,-61-5-392 0 0,-1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-2 1 0 0 0,1 1 0 0 0,0-1 0 0 0,-2 2 0 0 0,2-2 0 0 0,12 14 0 0 0,-18-16-166 0 0,0 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,2 5 1 0 0,-3-7-77 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,-2 2 1 0 0,-89 78-7291 0 0,69-61 5205 0 0,-1-3 1 0 0,-1 1 0 0 0,-40 21 0 0 0,-1-5-771 0 0,23-12 1328 0 0,-3 0 0 0 0,1-2 0 0 0,-51 14 0 0 0,9-5 131 0 0,45-17 980 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6389">10316 1297 28 0 0,'7'-20'1003'0'0,"-6"17"-646"0"0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,1 1-1 0 0,3-4 0 0 0,-4 5 880 0 0,0 19 4867 0 0,1 5-364 0 0,-4-6-4756 0 0,-56 198 3925 0 0,-64 96-4068 0 0,113-293-1251 0 0,-1-1 0 0 0,-17 25 0 0 0,11-20-873 0 0,8-13-2564 0 0,4-11 959 0 0,3-26-717 0 0,13-37 186 0 0,5 12 1561 0 0,3 0 0 0 0,2 2 0 0 0,48-83 0 0 0,-50 90 1324 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6560.86">10359 1371 4 0 0,'4'-3'229'0'0,"0"0"-1"0"0,1 0 1 0 0,0 1 0 0 0,-2-1 0 0 0,2 1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,4 0 1 0 0,-6 2-34 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-2 0 1 0 0,2 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,1 0-1 0 0,2 4 0 0 0,122 110 8756 0 0,15-16-4470 0 0,-101-76-3660 0 0,1-1-1 0 0,55 19 1 0 0,-90-39-936 0 0,19 8 556 0 0,-26-12-471 0 0,0 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 1 1 0 0,-6-6-530 0 0,0 0 1 0 0,-1 0-1 0 0,0 1 1 0 0,0 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-2 1 1 0 0,1 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-8 0-1 0 0,-16-4-1514 0 0,0 1 0 0 0,0 2 0 0 0,-46 0 0 0 0,28 5-47 0 0,-72 12 0 0 0,78-6 1500 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6880.94">10236 1862 508 0 0,'-1'2'615'0'0,"1"0"1"0"0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,2 2 0 0 0,-1-2-113 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,0-1 0 0 0,3 0 1 0 0,8 0 516 0 0,0-1 1 0 0,0-1 0 0 0,0 0 0 0 0,17-6 0 0 0,4 1-492 0 0,33-7 433 0 0,-46 9-1078 0 0,1 0 0 0 0,42-2 0 0 0,-16 1-3093 0 0,-47 6 2271 0 0,-38 11-9771 0 0,31-9 10616 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,0 1 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 1-1 0 0,-6 7 1 0 0,6-5 456 0 0,1 0 0 0 0,0 0 0 0 0,0 1 1 0 0,1-2-1 0 0,0 2 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 10 0 0 0,-1 4 287 0 0,1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,1 1 0 0 0,2-1 0 0 0,0 1 0 0 0,1-2 0 0 0,4 24 0 0 0,-5-17-411 0 0,0-24-252 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,2 5 0 0 0,-3-8-52 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,-13 6-3264 0 0,-13-2-229 0 0,-2-4 1624 0 0,1 1 1 0 0,-1 2 0 0 0,0 0-1 0 0,-31 9 1 0 0,39-6 1438 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7115.84">9866 2428 104 0 0,'-7'1'535'0'0,"1"0"0"0"0,-1 0 0 0 0,2 1 0 0 0,-2 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 1 0 0 0,2-1 0 0 0,-1 2 0 0 0,-8 5 0 0 0,-27 25 19787 0 0,74-33-16423 0 0,46-3-1731 0 0,30-14-1965 0 0,191-54 0 0 0,-9 1-221 0 0,-203 53 18 0 0,0 4 0 0 0,1 3 0 0 0,1 5 0 0 0,166 14 0 0 0,-129 18 0 0 0,-62-12 0 0 0,-56-14-8 0 0,1 1 0 0 0,-1 1 1 0 0,0-1-1 0 0,17 11 0 0 0,-3 2-3439 0 0,-39-12-5308 0 0,-5-1 5327 0 0,-36-1-3842 0 0,35 0 5207 0 0,0-1-1 0 0,0-2 1 0 0,-42-5 0 0 0,28-1 1161 0 0,-5 5 261 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7710.8">11747 438 248 0 0,'103'100'8896'0'0,"-54"-56"-4917"0"0,26 30-895 0 0,-31-24-2219 0 0,-37-39-1904 0 0,-18-14-2937 0 0,-24-19-1224 0 0,29 18 4823 0 0,-1-1-234 0 0,2 1-1 0 0,-2-2 1 0 0,1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-8-13-1 0 0,6 6-17 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8061.06">11993 507 564 0 0,'4'1'669'0'0,"0"0"0"0"0,0 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,0-1 0 0 0,3 4 1 0 0,4 1 1135 0 0,0-1-789 0 0,0-1 0 0 0,0 0-1 0 0,1 0 1 0 0,1-1 0 0 0,-2-1 0 0 0,2 0 0 0 0,19 1-1 0 0,-14-1-335 0 0,0 0-1 0 0,35 13 0 0 0,-48-15-632 0 0,-2 0 0 0 0,1 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,-2 0 1 0 0,1 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,4 7-1 0 0,-6-8-38 0 0,-1 0-1 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,-2 3 0 0 0,-23 26-10 0 0,-1-2 0 0 0,-2 0 0 0 0,0-2 0 0 0,-2-1 0 0 0,-1-1-1 0 0,-59 31 1 0 0,14-13 265 0 0,65-37 2047 0 0,25-12-1590 0 0,31-13-378 0 0,25-11 117 0 0,117-29-480 0 0,-61 24-6986 0 0,-122 34 6490 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,1-4 1 0 0,0-1-269 0 0,0-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 2 0 0 0,0-2 0 0 0,-1-7 0 0 0,0-3 154 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8594.46">12597 531 172 0 0,'4'-4'601'0'0,"-1"1"-1"0"0,1 1 1 0 0,0-2 0 0 0,0 1 0 0 0,-1 1-1 0 0,2-1 1 0 0,-1 1 0 0 0,1 0 0 0 0,8-4-1 0 0,-3 25 8189 0 0,4 24-4345 0 0,-10-26-3812 0 0,-2-1-1 0 0,0 1 1 0 0,-2 24-1 0 0,0-27-543 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,6 17 0 0 0,9 29-1437 0 0,-17-60 1281 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,0 0 0 0 0,13-12-1679 0 0,8-23-696 0 0,-19 31 2027 0 0,8-17-576 0 0,0-1 1 0 0,-1-1 0 0 0,-2-1-1 0 0,8-29 1 0 0,16-101-684 0 0,-27 133 1752 0 0,0 1 842 0 0,-3 5 3593 0 0,39 15-88 0 0,-19-2-3040 0 0,13 3 150 0 0,-18 3-867 0 0,-13-4-538 0 0,1 1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,4 4 1 0 0,-2 0-85 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,-1 1 0 0 0,0 1 1 0 0,1-1-1 0 0,-2 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,0 0 1 0 0,-1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,-6 10-1 0 0,3-8-68 0 0,-1 1 0 0 0,0-2-1 0 0,1 1 1 0 0,-2-2-1 0 0,-1 0 1 0 0,1 1 0 0 0,-1-2-1 0 0,0 1 1 0 0,-1-1 0 0 0,1-1-1 0 0,-1 0 1 0 0,-17 6 0 0 0,1-1-31 0 0,-2-2-1 0 0,1-1 1 0 0,-1-1 0 0 0,-34 3-1 0 0,-72-4-101 0 0,276 13 643 0 0,-92-18-310 0 0,2-3 0 0 0,-2-1 0 0 0,86-18 0 0 0,-132 20-245 0 0,0 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,-1-1 0 0 0,-1 0-1 0 0,2-1 1 0 0,-1 1 0 0 0,0 0-1 0 0,3-5 1 0 0,-42-19-3720 0 0,28 25 3100 0 0,-1 0-1 0 0,0 0 1 0 0,1 1-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 1-1 0 0,-1 1 1 0 0,0 0-1 0 0,1 0 0 0 0,-19 7 1 0 0,-8 6-1390 0 0,-48 26-1 0 0,51-24 1103 0 0,-81 43-2215 0 0,-171 118-1 0 0,234-135 2728 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8806.68">11962 1464 140 0 0,'-81'74'4614'0'0,"71"-67"-5529"0"0,-3-6 9344 0 0,11-9 97 0 0,17-4-5888 0 0,52-27 21 0 0,3 4 0 0 0,137-50-1 0 0,-113 57-2318 0 0,1 3 0 0 0,0 4-1 0 0,182-14 1 0 0,-238 32-567 0 0,177-9 475 0 0,-69 9-4607 0 0,-132 4 5527 0 0,2 4-8368 0 0,-40-6-5151 0 0,-176-28 3471 0 0,166 23 8162 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9159.14">12474 991 88 0 0,'-5'0'1504'0'0,"-2"2"4718"0"0,2 44 2056 0 0,-12 24-3614 0 0,2-5-2810 0 0,-5 12-1201 0 0,-3 0 1 0 0,-3-3-1 0 0,-4-1 1 0 0,-58 108-1 0 0,48-113-1938 0 0,-4-2-1 0 0,-68 79 1 0 0,71-94-1285 0 0,31-37 1465 0 0,10-13 901 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,-2-1 0 0 0,1 0-1351 0 0,8-8-1531 0 0,16-38 59 0 0,1 1 1234 0 0,0-1 0 0 0,33-44 0 0 0,-39 65 1969 0 0,3 1 1 0 0,0 0-1 0 0,0 3 0 0 0,28-23 1 0 0,-38 35 436 0 0,2 0 1 0 0,1 1 0 0 0,-2 0-1 0 0,3 1 1 0 0,-2 1-1 0 0,2 0 1 0 0,-2 1 0 0 0,2 0-1 0 0,0 1 1 0 0,24-2-1 0 0,-24 5 107 0 0,-2 1-1 0 0,1 0 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 1 0 0 0,18 6 0 0 0,71 29 2898 0 0,33 26-711 0 0,-92-41-2224 0 0,3-1 0 0 0,88 29-1 0 0,-36-33-1971 0 0,-96-16 1123 0 0,1-1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,4-1-1 0 0,15-4-4043 0 0,-19-32-2075 0 0,-8-27 1091 0 0,3 51 4552 0 0,1-1 1 0 0,1 0 0 0 0,1-25-1 0 0,6 9 91 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9317.75">13158 1060 168 0 0,'-2'1'401'0'0,"1"1"0"0"0,-2-1 0 0 0,1 1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,-1 3 0 0 0,-12 21 5687 0 0,13-26-5056 0 0,-1 2-872 0 0,1 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 1 0 0,0-1-1 0 0,0 6 0 0 0,0-3-325 0 0,-2-1-301 0 0,1 1-1 0 0,0-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-2 1 0 0,0 0-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-6 4 1 0 0,-12 4-1201 0 0,0-1 0 0 0,-33 10 0 0 0,-11 4-24 0 0,31-9 971 0 0,0 1 131 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9564.01">11919 1956 424 0 0,'0'7'1090'0'0,"-1"1"1"0"0,-1-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,-1 0 1 0 0,-4 13-1 0 0,-5 7 2210 0 0,0 35 911 0 0,11 3-5333 0 0,-1-58-4246 0 0,-2-23 306 0 0,3 11 5766 0 0,-2-8-1615 0 0,-1-1-137 0 0,0 0-1 0 0,1 0 0 0 0,-1-29 1 0 0,4 29 543 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9832.54">11901 1937 252 0 0,'0'0'111'0'0,"1"-1"0"0"0,0 1 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,2-1 0 0 0,-2 1 36 0 0,1 0 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,1-1 0 0 0,-2 1 1 0 0,1-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,2 0 0 0 0,33-2 3497 0 0,-24 0-2543 0 0,-2 1 1 0 0,2 1-1 0 0,0 0 0 0 0,18 4 1 0 0,-12-1-459 0 0,1 1 0 0 0,0 0 0 0 0,-1 2 0 0 0,-1 1 0 0 0,1 1-1 0 0,26 15 1 0 0,-33-17-408 0 0,29 20 478 0 0,-38-25-686 0 0,0 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,2 3 0 0 0,-3-2-16 0 0,0 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0-1 0 0,-1 1 1 0 0,-1-1 0 0 0,-2 2 0 0 0,-45 35 11 0 0,34-29-24 0 0,-7 7-9 0 0,8-5-1 0 0,0-1 1 0 0,-1-1 0 0 0,0 0-1 0 0,-1-1 1 0 0,0 0 0 0 0,-18 5 0 0 0,8-6 54 0 0,11-2 114 0 0,-2-1-1 0 0,2-1 1 0 0,-2-1 0 0 0,-34 2-1 0 0,101-23 741 0 0,-28 10-695 0 0,0 1 0 0 0,1 2 0 0 0,1 0 0 0 0,-1 1 0 0 0,37 0 1 0 0,-13 3 35 0 0,79 11 1 0 0,-104-7-600 0 0,1 2 0 0 0,-1 1 0 0 0,-1 0 0 0 0,30 14 0 0 0,30 18-6446 0 0,-80-38 6764 0 0,2 1-1612 0 0,0-1 1320 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,-1 2-1 0 0,1-2 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,1-2 0 0 0,18-61-2339 0 0,-11 32 1554 0 0,4 2 444 0 0,5 0 155 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9984.24">12678 1919 524 0 0,'0'-1'103'0'0,"0"1"0"0"0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1-1 0 0,2-1 1 0 0,11 9 5672 0 0,-25 24 1957 0 0,12-13-5679 0 0,1 38 924 0 0,0-50-2958 0 0,-1 0 0 0 0,1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,6 11 0 0 0,-8-16-235 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 1 0 0,4 1-1 0 0,-4-2-149 0 0,1 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0-1 0 0 0,2-2-1 0 0,76-137-6977 0 0,-65 121 6662 0 0,3-2 115 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10304.66">13010 1782 260 0 0,'87'-6'8291'0'0,"-50"11"-1866"0"0,7 17-1870 0 0,-14-6-3076 0 0,-25-13-1374 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,-1 0 0 0 0,1 0 1 0 0,1 10-1 0 0,-3-12-102 0 0,1 1 2 0 0,-1 0-1 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,0 0 1 0 0,1 0-1 0 0,-2-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 1 0 0,-3 4-1 0 0,-13 26-27 0 0,8-17-11 0 0,1 1-1 0 0,-3-1 1 0 0,0 0 0 0 0,-15 20 0 0 0,13-22 3 0 0,-1-1 1 0 0,0-1-1 0 0,-1 0 0 0 0,0-1 1 0 0,-2 0-1 0 0,1-1 0 0 0,-25 12 1 0 0,30-18 151 0 0,-1-2 0 0 0,0 1 0 0 0,1-3 0 0 0,-1 2 0 0 0,0-2 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1-2 0 0 0,-13-2 0 0 0,4-3 711 0 0,-17-3 3956 0 0,40 11-4646 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,3 1-1 0 0,32 6 169 0 0,247 22-307 0 0,-243-25-2057 0 0,78 3 6345 0 0,-69-5-6127 0 0,-6-2-5888 0 0,-1 1-8363 0 0,-78 1 13435 0 0,0 2-1 0 0,-36 9 1 0 0,34-6 1927 0 0,-16 4 86 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="13090.57">6944 3790 344 0 0,'-25'-35'5993'0'0,"12"3"3419"0"0,14 33-9092 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0-1 1 0 0,1 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,46 6-705 0 0,-8 0 601 0 0,-28-4-195 0 0,-1 0-1 0 0,1 0 0 0 0,-1-1 0 0 0,1 0 1 0 0,19-3-1 0 0,-25 2-8 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-2-1 1 0 0,1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,4-6 1 0 0,0 3 86 0 0,-9 6-80 0 0,1-1-1 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,2-3-239 0 0,1-4 4033 0 0,-14 11-1342 0 0,8 2-2397 0 0,-1 1-1 0 0,1 0 1 0 0,0 0-1 0 0,2 0 1 0 0,-2 1-1 0 0,1-1 1 0 0,0 0-1 0 0,1 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,0 6-1 0 0,-3 6-17 0 0,-14 70 102 0 0,2 1 0 0 0,-4 120 0 0 0,12 184 192 0 0,8-332-308 0 0,7 262 147 0 0,23 149 16 0 0,-17-341-204 0 0,-55-200-9 0 0,-23-71-2372 0 0,30 70-1476 0 0,-39-119 0 0 0,-9-41-6337 0 0,-6-17 263 0 0,76 180 8292 0 0,7 40 1032 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="13469.1">6739 4263 508 0 0,'0'-4'144'0'0,"3"-8"9052"0"0,4 12-3092 0 0,1 2-4877 0 0,0 0-2363 0 0,34 6 4463 0 0,79 9 0 0 0,-62-14-2003 0 0,-1-2 0 0 0,74-10-1 0 0,-105 6-1054 0 0,41-8 311 0 0,-35 5-389 0 0,-26 6-224 0 0,-1 0-1 0 0,1-1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,-1-1 1 0 0,8-4-1 0 0,-12 6-206 0 0,-15 1-1167 0 0,1 1 648 0 0,-1 0 1 0 0,1 1-1 0 0,-1 1 0 0 0,2 0 1 0 0,-2 1-1 0 0,1 0 1 0 0,1 1-1 0 0,-1 0 1 0 0,-14 9-1 0 0,-20 14-787 0 0,-52 42 0 0 0,69-49 861 0 0,-91 68-671 0 0,-157 107 2067 0 0,217-168 1021 0 0,18-12 4144 0 0,76-22-4083 0 0,106-34 283 0 0,60-13-314 0 0,-157 44-1478 0 0,-1 2 1 0 0,78-1 0 0 0,91 2-2644 0 0,-199 5 1512 0 0,1 1 0 0 0,0-1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1-2 0 0 0,-1 1 0 0 0,17-9 0 0 0,-22 9 334 0 0,-2 0-1 0 0,2 0 1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-2-1 0 0 0,1 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 1 0 0 0,2-8 0 0 0,81-291-7560 0 0,-72 254 7608 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="13626.88">7942 3467 348 0 0,'2'0'213'0'0,"-1"0"0"0"0,1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1 1 1 0 0,35 58 6425 0 0,-26-42-6030 0 0,-1 0 1 0 0,13 40 0 0 0,-22-56-819 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-4 3-1 0 0,-8 4-643 0 0,0-1 0 0 0,-1-1 0 0 0,1 0-1 0 0,-2-1 1 0 0,1-1 0 0 0,-1-1 0 0 0,0 0 0 0 0,-16 2 0 0 0,13-5 328 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="13825.95">7609 3766 96 0 0,'0'2'352'0'0,"0"1"-1"0"0,0-1 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,0-1 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,2 0 1 0 0,13-1 1056 0 0,-1-1-1 0 0,1 0 0 0 0,28-9 1 0 0,-35 9-1184 0 0,168-41 2854 0 0,-107 26-2698 0 0,-43 9-914 0 0,1 2 0 0 0,0 0 0 0 0,41-1 1 0 0,-69 7 397 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,1 2 0 0 0,-13 16-3569 0 0,-34 17-957 0 0,44-33 4382 0 0,-127 68-5172 0 0,47-27 3526 0 0,52-27 1505 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="14214.13">7708 4009 120 0 0,'-7'3'402'0'0,"1"1"-1"0"0,1-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,1 0 1 0 0,1 0-1 0 0,-8 11 1 0 0,10-14-226 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,4 4 0 0 0,-1-3-154 0 0,0 1 1 0 0,1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,2-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,0 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,1-2 1 0 0,-1 1-1 0 0,7-2 1 0 0,17-6-62 0 0,0-1 0 0 0,42-21 0 0 0,-51 22 44 0 0,16-10-76 0 0,52-37-1 0 0,-41 25 17 0 0,-21 15 49 0 0,-9 7 202 0 0,-2-1 1 0 0,27-22 0 0 0,-41 31 613 0 0,-15 27 591 0 0,-79 66 39 0 0,-4-3 1 0 0,-167 115-1 0 0,247-193-1114 0 0,-2-1 0 0 0,0-1 0 0 0,-30 9 0 0 0,-1 1 543 0 0,41-16-498 0 0,0 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1-1-1 0 0,0 0 1 0 0,1 0-1 0 0,-11-1 1 0 0,18 0-17 0 0,2-5 452 0 0,0 5-780 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1-1 1 0 0,0 1 0 0 0,38-22 578 0 0,0 3 0 0 0,2 1 0 0 0,71-22 1 0 0,-91 33-466 0 0,52-13 184 0 0,2 3-1 0 0,144-13 1 0 0,-118 18-580 0 0,-38 14-512 0 0,-22 1-311 0 0,-21 1-332 0 0,-6-2-5049 0 0,-22-8 2262 0 0,-2 2 2937 0 0,0 0 0 0 0,1 1 0 0 0,-1 1 0 0 0,0-1-1 0 0,-17 0 1 0 0,4 1-77 0 0,1 1-1 0 0,-2 1 0 0 0,-30 4 1 0 0,31 2 726 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="14534.8">7986 4233 140 0 0,'0'0'5013'0'0,"-26"18"5197"0"0,11-2-8228 0 0,0 2 1 0 0,-20 32 0 0 0,-45 94-1144 0 0,46-80-340 0 0,-106 178-263 0 0,124-211-229 0 0,7-14-5 0 0,0 0 1 0 0,-1-1-1 0 0,-1 1 1 0 0,-13 15-1 0 0,22-30 22 0 0,-3 1 1026 0 0,9-5-519 0 0,0 0-388 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1-1 0 0,-2 1 1 0 0,7 1 0 0 0,51 3 957 0 0,-61-4-1089 0 0,130 24 1376 0 0,-115-21-1288 0 0,1 2 1 0 0,-2 0 0 0 0,2 0-1 0 0,-2 1 1 0 0,0 1 0 0 0,18 12-1 0 0,3 4 6 0 0,-25-16-161 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,-1 1 1 0 0,15 15-1 0 0,0 0-513 0 0,-22-21 282 0 0,1 0 0 0 0,0-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,2 5 0 0 0,-4-8-874 0 0,-2-14-6393 0 0,-7-12 4505 0 0,0-6 899 0 0,-4-48-2018 0 0,7 52 3109 0 0,2-1 0 0 0,0 1 1 0 0,2-2-1 0 0,2-41 1 0 0,5 39 463 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="14876.97">8072 4662 104 0 0,'-1'-11'4110'0'0,"-29"52"4475"0"0,13-13-6361 0 0,1 1 1 0 0,-13 37 0 0 0,-13 22-841 0 0,5-13-610 0 0,-6 13-304 0 0,25-53-370 0 0,14-27-101 0 0,-1 0 0 0 0,1 0 0 0 0,-2 0 0 0 0,1 0 0 0 0,-10 11 0 0 0,6-10-216 0 0,0 0 0 0 0,0-2 0 0 0,-1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,-1-1 0 0 0,-1 0 0 0 0,2 0 0 0 0,-2-1 0 0 0,-12 3 0 0 0,17-6-49 0 0,0-1 0 0 0,0 1-1 0 0,-1-2 1 0 0,0 1 0 0 0,2-1 0 0 0,-2-1-1 0 0,0 1 1 0 0,1-1 0 0 0,0 0-1 0 0,0-1 1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0-1 0 0 0,0 1-1 0 0,-8-8 1 0 0,6 3-64 0 0,1 1-1 0 0,0-2 1 0 0,1 2-1 0 0,-1-2 1 0 0,1 0-1 0 0,1-1 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,0 0 1 0 0,1-1-1 0 0,0 0 1 0 0,-3-15-1 0 0,-2-12-299 0 0,1 0 0 0 0,-2-60-1 0 0,6-40 717 0 0,4 123 328 0 0,1 1 0 0 0,1 1 0 0 0,0-1 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,9-19 0 0 0,-10 26-10 0 0,2 1-1 0 0,-1 1 1 0 0,0-1-1 0 0,1 0 1 0 0,0 0-1 0 0,0 1 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,1 1-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0 1 1 0 0,1 0-1 0 0,-2 0 1 0 0,1 0-1 0 0,15-1 1 0 0,11 1 322 0 0,0 1 0 0 0,0 1 0 0 0,45 7 0 0 0,-59-5-461 0 0,234 36 1298 0 0,-87-19-2811 0 0,-105-18-2610 0 0,-37-1-1449 0 0,-23-1 5101 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0-2 1 0 0,3-31-3444 0 0,-3-40-331 0 0,0 50 3338 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="15187.4">8571 3891 16 0 0,'3'0'490'0'0,"0"1"0"0"0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1-1 0 0,-2 0 1 0 0,2-1 0 0 0,0 1 0 0 0,-1 0-1 0 0,2 3 1 0 0,2 3 845 0 0,0 1 0 0 0,-1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,3 17 0 0 0,5 71 3177 0 0,-9-71-3992 0 0,-1-1 0 0 0,-1 0 0 0 0,-7 44 0 0 0,7-66-491 0 0,-54 253 1097 0 0,46-229-1081 0 0,5-14-24 0 0,-1 0-1 0 0,1 0 1 0 0,-2-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,1 0-1 0 0,-2 0 1 0 0,-12 13 0 0 0,12-19 226 0 0,12-16 463 0 0,13-16-72 0 0,11 2-546 0 0,0 1 0 0 0,1 2 0 0 0,1 0 0 0 0,1 2 0 0 0,37-15 0 0 0,-48 23-189 0 0,31-11-630 0 0,-39 17-180 0 0,0-1 0 0 0,-1 0 0 0 0,19-11 0 0 0,-17 9-1026 0 0,-12 6 1573 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,-1-1-1 0 0,0-67-5414 0 0,-5-40 1803 0 0,1 74 3164 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="15413.18">8990 3661 260 0 0,'0'0'2906'0'0,"25"0"2779"0"0,-21 5-4816 0 0,0-1 1 0 0,0 2-1 0 0,0-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,-1 1 1 0 0,3 13-1 0 0,-1 4 880 0 0,0 48-1 0 0,-44 468 3829 0 0,14-291-4661 0 0,12-112-628 0 0,-7 125-164 0 0,20-209-406 0 0,-11 63 0 0 0,6-64-1199 0 0,-2 62-1 0 0,5-89-992 0 0,3-25 2300 0 0,1 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-105 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0-20-303 0 0,23-126-6075 0 0,27-71 2661 0 0,-32 152 3317 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="15718.61">9317 3921 76 0 0,'2'-8'443'0'0,"1"0"0"0"0,0 2 0 0 0,0-2 1 0 0,1 1-1 0 0,-1 0 0 0 0,8-9 0 0 0,14-16 6221 0 0,-23 33-6199 0 0,0 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 4 1 0 0,2 10 752 0 0,-1 1 1 0 0,0-1-1 0 0,1 22 0 0 0,-12 90 402 0 0,2-63-1024 0 0,-8 26-240 0 0,10-64-86 0 0,1 0 0 0 0,-2 41 0 0 0,6-64 621 0 0,18-28 1139 0 0,63-5-243 0 0,-35 12-1348 0 0,-9 4-200 0 0,-1 0 0 0 0,0-3 0 0 0,60-39 0 0 0,16-31-1393 0 0,-100 80 1673 0 0,2-5-6786 0 0,-15 11 5868 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 1 0 0,-1 1-1 0 0,-49 6-4824 0 0,35-6 3120 0 0,0 1 1 0 0,-28 7-1 0 0,36-4 1345 0 0,-3 2 173 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="15938.19">9632 4039 696 0 0,'-25'13'9119'0'0,"19"38"920"0"0,-3 52-5213 0 0,-21 56-1877 0 0,20-117-2313 0 0,-13 59 82 0 0,-4-1 0 0 0,-5 0 0 0 0,-46 98 0 0 0,70-182-740 0 0,-60 118-642 0 0,59-121 300 0 0,1 0 1 0 0,-2 0-1 0 0,0 0 0 0 0,0-1 0 0 0,-2 0 0 0 0,0-1 0 0 0,-14 11 0 0 0,19-16-291 0 0,-1-1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,0-1 0 0 0,-13 4 0 0 0,20-6 428 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,1 0 0 0 0,-1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,0-1 0 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,2 1-1 0 0,-2-1 1 0 0,0 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 1 0 0 0,1-3-1 0 0,-6-23-1352 0 0,1 0 0 0 0,3 0-1 0 0,0 1 1 0 0,3-51 0 0 0,20-110-2172 0 0,7 76 2275 0 0,-20 61 984 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="16092.42">9218 4394 220 0 0,'3'1'350'0'0,"-1"0"1"0"0,0 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,2 6-1 0 0,21 54 4726 0 0,-23-58-4746 0 0,13 30 1997 0 0,1 0 0 0 0,2-2-1 0 0,21 34 1 0 0,19 34 386 0 0,107 179 590 0 0,-136-235-3073 0 0,-9-15-371 0 0,2-1-1 0 0,28 30 1 0 0,-32-40-1385 0 0,37 30 1 0 0,-51-47 1092 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-2 1 0 0 0,2-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,-1 0 0 0 0,2 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,3-3 0 0 0,9-8-1568 0 0,1 0 1 0 0,-2-2-1 0 0,22-24 0 0 0,-26 27 1605 0 0,12-10-627 0 0,0 2 0 0 0,44-32 0 0 0,-65 52 1017 0 0,46-35-555 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="16476.66">11037 3585 484 0 0,'0'0'2401'0'0,"18"27"7903"0"0,-16-25-10229 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 1 0 0,-1 4-1 0 0,1-4-260 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1-2-1 0 0,-1 2 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,-1-1 1 0 0,2 1-1 0 0,-3 2 0 0 0,-5 4-596 0 0,-2 0-1 0 0,1 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 0 0 0 0,-18 5 0 0 0,2 2-349 0 0,-41 18-1030 0 0,48-19 1698 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17099.12">10655 3940 40 0 0,'-1'14'2488'0'0,"2"-1"6104"0"0,23-9-4575 0 0,-10-5-3223 0 0,-1 0 0 0 0,0-2 0 0 0,0 1 0 0 0,15-6-1 0 0,34-7 554 0 0,25 0-121 0 0,-61 9-982 0 0,1 1 0 0 0,43-1 0 0 0,33-6-276 0 0,-102 12-60 0 0,-20 19-1110 0 0,-190 167-678 0 0,160-137 1760 0 0,-44 60 0 0 0,74-82 124 0 0,0 1 0 0 0,1 1 1 0 0,3-1-1 0 0,-19 45 0 0 0,32-67-6 0 0,-1 1-1 0 0,1-1 1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1-1 0 0,1 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,1 1 1 0 0,0-1 0 0 0,3 8 0 0 0,-3-13 2 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,5-1 0 0 0,42-6 13 0 0,-8-8 4 0 0,-2-2 1 0 0,0-1-1 0 0,-1-2 0 0 0,-1-1 1 0 0,45-36-1 0 0,-46 32-9 0 0,-18 19 225 0 0,-20 18 27 0 0,-22 31 183 0 0,20-36-371 0 0,-18 26 122 0 0,-1 0 0 0 0,-2-2 0 0 0,-39 40 0 0 0,-95 78 25 0 0,84-82-113 0 0,-139 99 579 0 0,169-134-320 0 0,41-29-311 0 0,-3 3 188 0 0,-1 0-1 0 0,1-1 0 0 0,-1 0 0 0 0,0-2 0 0 0,0 2 1 0 0,0-2-1 0 0,-14 5 0 0 0,21-8 954 0 0,20-19-37 0 0,23-8-967 0 0,0 2-1 0 0,1 3 0 0 0,1 1 1 0 0,2 2-1 0 0,-1 4 0 0 0,2 0 0 0 0,70-12 1 0 0,-85 24-151 0 0,-1 0 0 0 0,0 3 1 0 0,0 1-1 0 0,50 7 0 0 0,127 35-902 0 0,-143-29-42 0 0,-43-9 325 0 0,-10-1-290 0 0,1-1 0 0 0,0 0 0 0 0,0-1 1 0 0,0-1-1 0 0,-1 0 0 0 0,2-1 0 0 0,16-2 0 0 0,-28 2 580 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,2-4 0 0 0,6-56-4311 0 0,-7 46 3902 0 0,19-201-5016 0 0,-10 161 5010 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17226.93">11740 3461 536 0 0,'0'-9'538'0'0,"0"7"-210"0"0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,5-6 8476 0 0,-12 26-5075 0 0,9 24-2923 0 0,0-29-1091 0 0,-2 1 0 0 0,0 0-1 0 0,-3 21 1 0 0,-1-7-491 0 0,4-21 364 0 0,0-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-2 0 0 0,-1 1 1 0 0,-1 0-1 0 0,-3 4 1 0 0,-2-1-291 0 0,0-1-1 0 0,0 0 1 0 0,-1-1 0 0 0,0 0 0 0 0,0-1-1 0 0,-1 0 1 0 0,0-1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 0-1 0 0,-15 1 1 0 0,8-3 110 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17465.02">11376 3722 292 0 0,'0'0'2471'0'0,"13"14"2067"0"0,-16 81 4898 0 0,-1-55-7412 0 0,-12 59 1 0 0,11-75-1498 0 0,1-8-92 0 0,0 0-1 0 0,1 0 1 0 0,1 1 0 0 0,-1 26-1 0 0,7-43-368 0 0,-1 0 1 0 0,0-1-1 0 0,0 0 0 0 0,1 1 0 0 0,-2-1 1 0 0,1 0-1 0 0,0 0 0 0 0,5-4 0 0 0,-3 4 31 0 0,77-32 570 0 0,-41 14-472 0 0,18-5-419 0 0,1 2 0 0 0,0 2 0 0 0,2 3 0 0 0,92-13 1 0 0,-118 27-847 0 0,-6 1-2579 0 0,53-11-1 0 0,-80 12 3302 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,1-3 1 0 0,1-6-854 0 0,0-1 1 0 0,0 0-1 0 0,0-25 0 0 0,4-20-851 0 0,-1 34 1515 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17616.68">12160 3524 12 0 0,'0'0'1414'0'0,"-13"30"4423"0"0,9-19-4669 0 0,1 0 0 0 0,2-1 0 0 0,-1 2 0 0 0,0-1 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,2 14 0 0 0,-2-2-271 0 0,3 77 878 0 0,0 1-3506 0 0,-4-94 1214 0 0,1-1 0 0 0,-1 2 0 0 0,-1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 1 0 0,-7 4-1 0 0,-14 11-1577 0 0,-1 0 1 0 0,-42 25-1 0 0,24-18 733 0 0,16-11 609 0 0,3-3 129 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17851.82">11407 4202 40 0 0,'-12'5'1046'0'0,"-12"8"2390"0"0,17-1 2154 0 0,7-11-5100 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1 1 0 0 0,25 10 3915 0 0,47-5-2928 0 0,-43-5-69 0 0,11-1-13 0 0,75-6 1 0 0,-84 2-937 0 0,126-20 1037 0 0,-55 5-848 0 0,36-14-470 0 0,-65 13-333 0 0,-55 15-324 0 0,-1-1 0 0 0,25-11 1 0 0,-38 14-142 0 0,0-1 0 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,7-8-1 0 0,-13 10 427 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1-2 1 0 0,-21-19-4794 0 0,-33-5-1117 0 0,44 22 5338 0 0,-1 1 0 0 0,1 1 1 0 0,-1 0-1 0 0,-1 1 0 0 0,2 0 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1 0 0 0 0,-21 6 0 0 0,15 3 157 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="18667.48">11950 4170 308 0 0,'-5'6'861'0'0,"1"0"-1"0"0,-1 1 1 0 0,2 0 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,-1 9-1 0 0,-1-9 254 0 0,0-1-1 0 0,0 0 1 0 0,-1 0 0 0 0,0-1-1 0 0,-13 9 1 0 0,14-9-591 0 0,-6 3 33 0 0,-91 69 1754 0 0,75-59-3073 0 0,-1 1 1 0 0,-1-2-1 0 0,-48 19 0 0 0,60-31-362 0 0,-1-1 1 0 0,-34 4-1 0 0,40-6 578 0 0,-1-2-236 0 0,2-1-1 0 0,-2 0 0 0 0,0-1 1 0 0,1 0-1 0 0,-1-1 1 0 0,-16-6-1 0 0,26 8 493 0 0,0-1 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,2-1 0 0 0,-2 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-5-6 0 0 0,6 7 331 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-5 2067 0 0,1 12-1629 0 0,2 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 8 0 0 0,1-3 110 0 0,7 27 734 0 0,-2-1 1 0 0,7 68 0 0 0,1 10-558 0 0,-7-55-677 0 0,-7-38-290 0 0,1-1 1 0 0,1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,13 25 1 0 0,-17-43 144 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,12-20-1419 0 0,1-34-375 0 0,32-193 148 0 0,-44 235 2187 0 0,0-2 1 0 0,2 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,1 0 1 0 0,0 0-1 0 0,1 1 1 0 0,1 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,1 1 1 0 0,11-12-1 0 0,-7 12 380 0 0,0 2 0 0 0,2-1-1 0 0,-1 2 1 0 0,1 0-1 0 0,0 0 1 0 0,0 1 0 0 0,1 2-1 0 0,29-9 1 0 0,14-7 720 0 0,-14 7-442 0 0,-1 2 0 0 0,1 2 0 0 0,66-7 0 0 0,-41 8-156 0 0,-11 0 297 0 0,94-1 0 0 0,-128 10-972 0 0,-1 1-1 0 0,0 1 1 0 0,1 1-1 0 0,-1 2 0 0 0,0 0 1 0 0,44 17-1 0 0,-63-20-273 0 0,1 0 0 0 0,-2 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,-1 1 1 0 0,3 8 0 0 0,-1 3 16 0 0,0 0 1 0 0,-1 1-1 0 0,-1 1 0 0 0,-2 17 1 0 0,1-20-55 0 0,-2 3-122 0 0,0 0 1 0 0,-2 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,-8 17 0 0 0,6-16-231 0 0,4-11-10 0 0,-1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-2-1 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1-1 0 0 0,-1 1 0 0 0,-1-2 0 0 0,-12 4 0 0 0,-5 0-783 0 0,-1-2 1 0 0,0-1-1 0 0,0-1 1 0 0,0-1-1 0 0,-46-5 1 0 0,29-2-223 0 0,2-3 0 0 0,0-1 0 0 0,-1-1 0 0 0,3-3-1 0 0,-64-29 1 0 0,82 31 777 0 0,0-1 0 0 0,1-1 0 0 0,0-1 0 0 0,-26-25 0 0 0,25 22 151 0 0,15 11 477 0 0,1 1-1 0 0,0-1 0 0 0,0-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,0-1 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1-14 0 0 0,2 6 1395 0 0,-1 24 1475 0 0,5 35-414 0 0,2-25-2069 0 0,-2 0 0 0 0,-1 0-1 0 0,0 1 1 0 0,0 0 0 0 0,-2 26-1 0 0,3 36 315 0 0,1-37-483 0 0,-3-27-356 0 0,1 1 0 0 0,1 1 0 0 0,6 24 0 0 0,-9-42 81 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,11-11-522 0 0,7-21 3 0 0,-17 32 484 0 0,29-68-698 0 0,26-85 1 0 0,0 0 832 0 0,-7 16 2473 0 0,-49 139-2492 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,2 16 1370 0 0,-1 21-119 0 0,-19 322 5995 0 0,13-200-5720 0 0,18 152 441 0 0,-12-299-1967 0 0,7 64 174 0 0,3 0-1 0 0,31 106 0 0 0,-27-134-904 0 0,20 47-1 0 0,-24-72-2526 0 0,25 41 0 0 0,-30-88-8628 0 0,-6-20 8754 0 0,-7 8 1074 0 0,-1 0 1 0 0,-19-54-1 0 0,6 22 807 0 0,-2 0 479 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink12.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -1923,13 +2772,13 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">31 791 232 0 0,'-31'-12'13112'0'0,"110"18"-5321"0"0,9 0-5422 0 0,94 7 1465 0 0,162 6 1131 0 0,152-53-4542 0 0,-405 25-382 0 0,-64 7-322 0 0,0 0 0 0 0,0 2 1 0 0,1 1-1 0 0,-1 1 0 0 0,41 9 0 0 0,-61-9 1184 0 0,4 0-4895 0 0,-17-6-4091 0 0,-104-23-2726 0 0,49 14 7311 0 0,31 7 2126 0 0,-24-9-557 0 0,-4-4 394 0 0,28 13 984 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="306.23">171 1243 440 0 0,'-17'4'1717'0'0,"17"-4"-1574"0"0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-11-5 14652 0 0,26 0-11509 0 0,24-5-2528 0 0,134-32 3443 0 0,74 14-657 0 0,125 15-2954 0 0,-142 26-590 0 0,-5 1 0 0 0,-157-7-444 0 0,-7 0-3632 0 0,-55-6 1887 0 0,-20-6-11636 0 0,9 2 12702 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,-8-10 0 0 0,8 7 499 0 0,0 0 1 0 0,1 0-1 0 0,0 0 1 0 0,1-1-1 0 0,0 1 1 0 0,-4-15-1 0 0,1-1-104 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="594.91">1344 428 68 0 0,'-19'-10'-1178'0'0,"0"-7"17226"0"0,19 17-15918 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,26 5 4642 0 0,116 28-13 0 0,-89-17-3758 0 0,0 3-1 0 0,-1 1 1 0 0,-2 3-1 0 0,57 33 1 0 0,-103-53-919 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,0 1 1 0 0,1 0 0 0 0,-2-1-1 0 0,1 1 1 0 0,0 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-3 7 1 0 0,-9 23-82 0 0,-2 0 0 0 0,-1-1 0 0 0,-2 0 0 0 0,-42 58 0 0 0,31-52-32 0 0,-215 285-327 0 0,205-280-731 0 0,-93 101-5110 0 0,35-56-2398 0 0,93-87 8091 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-2 0 0 0,0 1 0 0 0,-7-2 0 0 0,5 0 65 0 0,-1 0-1 0 0,1-1 1 0 0,0 0 0 0 0,0 0 0 0 0,1-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0 0 0 0,0-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-9-10 0 0 0,-5-9-83 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">30 791 232 0 0,'-30'-12'13112'0'0,"106"18"-5321"0"0,9 0-5422 0 0,89 7 1465 0 0,157 6 1131 0 0,146-53-4542 0 0,-390 25-382 0 0,-61 7-322 0 0,0 0 0 0 0,0 2 1 0 0,1 1-1 0 0,-1 1 0 0 0,39 9 0 0 0,-58-9 1184 0 0,4 0-4895 0 0,-17-6-4091 0 0,-100-23-2726 0 0,48 14 7311 0 0,29 7 2126 0 0,-23-9-557 0 0,-4-4 394 0 0,27 13 984 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="306.22">164 1242 440 0 0,'-16'4'1717'0'0,"16"-4"-1574"0"0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-11-5 14652 0 0,26 0-11509 0 0,22-5-2528 0 0,130-32 3443 0 0,70 14-657 0 0,121 15-2954 0 0,-137 26-590 0 0,-5 1 0 0 0,-150-7-444 0 0,-8 0-3632 0 0,-52-6 1887 0 0,-19-6-11636 0 0,8 2 12702 0 0,0 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,-8-10 0 0 0,8 7 499 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1-1-1 0 0,0 1 1 0 0,-4-15-1 0 0,2-1-104 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="594.91">1292 428 68 0 0,'-18'-10'-1178'0'0,"-1"-7"17226"0"0,19 17-15918 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,25 5 4642 0 0,112 28-13 0 0,-86-17-3758 0 0,0 3-1 0 0,-1 1 1 0 0,-2 3-1 0 0,55 33 1 0 0,-100-53-919 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,-2 0 1 0 0,2 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,-1 0 0 0 0,1 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,0 1 1 0 0,1 0 0 0 0,-2-1-1 0 0,1 1 1 0 0,0 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-3 7 1 0 0,-8 23-82 0 0,-3 0 0 0 0,0-1 0 0 0,-2 0 0 0 0,-41 58 0 0 0,30-52-32 0 0,-206 284-327 0 0,196-279-731 0 0,-89 101-5110 0 0,34-56-2398 0 0,89-87 8091 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,2 0 0 0 0,-1-1 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-2 0 0 0,1 1 0 0 0,-8-2 0 0 0,5 0 65 0 0,0 0-1 0 0,0-1 1 0 0,0 0 0 0 0,1 0 0 0 0,0-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,2 0 0 0 0,-1-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-8-10 0 0 0,-6-9-83 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink13.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -1957,14 +2806,14 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">730 87 424 0 0,'0'0'771'0'0,"-19"-12"5779"0"0,3 12-4506 0 0,-1 1-1 0 0,1 1 0 0 0,0 0 1 0 0,-25 8-1 0 0,22-4-962 0 0,0 1 0 0 0,1 1 1 0 0,-21 12-1 0 0,-5 8-756 0 0,2 2-1 0 0,-40 36 1 0 0,18-14 668 0 0,59-49-911 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 1 0 0 0,0-1-1 0 0,-4 7 1 0 0,7-11 242 0 0,52 26-361 0 0,-36-23 49 0 0,-1 1 0 0 0,0 0 0 0 0,21 13 0 0 0,3 0 65 0 0,-20-10 43 0 0,0 1-1 0 0,-1 1 1 0 0,0 0 0 0 0,-1 2-1 0 0,0 0 1 0 0,-1 0-1 0 0,26 27 1 0 0,-32-28 14 0 0,-1 0-1 0 0,0 1 1 0 0,-1 0 0 0 0,0 1-1 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,-1 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,5 29 0 0 0,-5-19 44 0 0,-2 0 1 0 0,0 0 0 0 0,-3 41 0 0 0,-1-55-136 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-2 0 1 0 0,-8 11-1 0 0,5-8-20 0 0,-1-1 0 0 0,0 0-1 0 0,0-1 1 0 0,-1 0 0 0 0,-1 0 0 0 0,1-1-1 0 0,-1-1 1 0 0,-1 0 0 0 0,0 0 0 0 0,0-2 0 0 0,0 1-1 0 0,-1-2 1 0 0,0 0 0 0 0,-25 6 0 0 0,11-5-227 0 0,-1-2 0 0 0,1 0 0 0 0,-1-2 0 0 0,0-1 0 0 0,0-1 0 0 0,1-2 0 0 0,-35-6 0 0 0,52 6-182 0 0,-1 0 0 0 0,1-1 0 0 0,-1 0-1 0 0,1-1 1 0 0,-13-6 0 0 0,20 8 16 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 0 0 0 0,-3-8-1 0 0,5 7-152 0 0,0 0-1 0 0,0 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,2 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,2-1 0 0 0,-1 1 0 0 0,3-4 0 0 0,6-9-1197 0 0,1 0-1 0 0,27-27 0 0 0,-22 25 667 0 0,-5 6 396 0 0,2-1 0 0 0,-1 2-1 0 0,19-13 1 0 0,-1 1 32 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="516.21">1201 244 392 0 0,'1'-1'207'0'0,"-1"1"0"0"0,1-1 0 0 0,-1 0 0 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 2 1 0 0,16 66 8457 0 0,-10-39-8025 0 0,5 11 781 0 0,-2 1-1 0 0,6 58 0 0 0,5 21-46 0 0,-13-87-1052 0 0,45 178 702 0 0,-48-196-1010 0 0,1-2-1 0 0,0 1 1 0 0,1 0 0 0 0,0-1-1 0 0,1 0 1 0 0,1-1 0 0 0,0 1 0 0 0,19 21-1 0 0,-27-34-11 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,18-20 44 0 0,10-30 17 0 0,0-26-16 0 0,33-129 0 0 0,-40 127-42 0 0,64-279-48 0 0,-62 252 14 0 0,-21 91 24 0 0,12-33-21 0 0,-15 47 35 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 1-1 0 0,11 19 297 0 0,4 25 147 0 0,54 441 1762 0 0,-51-309-2026 0 0,4-39-129 0 0,-20-123-42 0 0,1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 1 0 0,1-1-1 0 0,12 16 0 0 0,-19-28-11 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 1-1 0 0,1-2 1 0 0,-1 1 0 0 0,0 0-1 0 0,3 0 1 0 0,-2-2 5 0 0,1 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,3-4 0 0 0,4-6 29 0 0,-1-1 1 0 0,0-1-1 0 0,12-26 0 0 0,26-83-29 0 0,29-131-1 0 0,-49 163-8 0 0,37-190-2 0 0,-56 251-776 0 0,-1 0 1 0 0,-2-1-1 0 0,0-54 0 0 0,-4 84-120 0 0,-18 45-9688 0 0,-1 31 3639 0 0,12-53 4804 0 0,1 1 0 0 0,1 0-1 0 0,1 1 1 0 0,-1 32 0 0 0,5-54 1660 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="749.25">2584 62 588 0 0,'0'0'4583'0'0,"19"20"1917"0"0,-15-13-5047 0 0,-1-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,1 1 0 0 0,1 13 0 0 0,3 4 873 0 0,5 82 2267 0 0,-8-83-3799 0 0,-1 0-1 0 0,0 38 1 0 0,-1 3 101 0 0,1 128 399 0 0,-5-105-1155 0 0,0-9-980 0 0,-16 99 0 0 0,0-116-3203 0 0,-1-86-1883 0 0,13 4 4440 0 0,2-1 1 0 0,0 0-1 0 0,1 1 1 0 0,1-1 0 0 0,1 0-1 0 0,2-26 1 0 0,-1 30 784 0 0,29-323-7507 0 0,-26 317 7911 0 0,3-27-273 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="995.38">2680 87 48 0 0,'0'-9'1074'0'0,"1"0"0"0"0,0 0 1 0 0,1 0-1 0 0,0 0 0 0 0,5-15 0 0 0,-5 23-657 0 0,-1-1 0 0 0,0 1-1 0 0,1-1 1 0 0,0 1 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,3 0-1 0 0,52 14 4931 0 0,2 12-2442 0 0,-2 3-1 0 0,98 67 1 0 0,-113-69-2376 0 0,13 16-211 0 0,-45-36-294 0 0,-1 1 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,-1 0 0 0 0,0 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,8 21-1 0 0,-10-21-12 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-3 20 0 0 0,-1 0 16 0 0,-15 61 0 0 0,5-53-78 0 0,-1 0 1 0 0,-2-1-1 0 0,-2 0 0 0 0,-1-1 1 0 0,-2-2-1 0 0,-1 0 0 0 0,-52 62 1 0 0,55-76-664 0 0,0 1 0 0 0,-2-2-1 0 0,-1-1 1 0 0,0 0 0 0 0,-44 27 0 0 0,44-34-1502 0 0,-1 0 1 0 0,0-1-1 0 0,-46 15 0 0 0,54-22 1017 0 0,2 1-289 0 0,-1-1 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 0-1 0 0,0-2 0 0 0,-1 1 1 0 0,0-2-1 0 0,-22-1 0 0 0,-20-1-2128 0 0,38-4 2940 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">714 87 424 0 0,'0'0'771'0'0,"-19"-12"5779"0"0,3 12-4506 0 0,0 1-1 0 0,0 1 0 0 0,1 0 1 0 0,-26 8-1 0 0,23-4-962 0 0,-1 1 0 0 0,2 1 1 0 0,-21 12-1 0 0,-5 8-756 0 0,2 2-1 0 0,-40 36 1 0 0,19-14 668 0 0,57-49-911 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,2 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 1 0 0 0,0-1-1 0 0,-4 7 1 0 0,7-11 242 0 0,51 26-361 0 0,-36-23 49 0 0,0 1 0 0 0,0 0 0 0 0,20 13 0 0 0,3 0 65 0 0,-19-10 43 0 0,-1 1-1 0 0,0 1 1 0 0,-1 0 0 0 0,0 2-1 0 0,0 0 1 0 0,-2 0-1 0 0,26 27 1 0 0,-31-28 14 0 0,-1 0-1 0 0,0 1 1 0 0,-1 0 0 0 0,-1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,-1 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,4 29 0 0 0,-4-19 44 0 0,-2 0 1 0 0,0 0 0 0 0,-3 41 0 0 0,-1-55-136 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-2 0 1 0 0,-8 11-1 0 0,6-8-20 0 0,-2-1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 0 0 0 0,-2 0 0 0 0,1-1-1 0 0,-1-1 1 0 0,0 0 0 0 0,-1 0 0 0 0,0-2 0 0 0,0 1-1 0 0,0-2 1 0 0,-1 0 0 0 0,-24 6 0 0 0,11-5-227 0 0,-2-2 0 0 0,2 0 0 0 0,-1-2 0 0 0,-1-1 0 0 0,1-1 0 0 0,0-2 0 0 0,-33-6 0 0 0,50 6-182 0 0,-1 0 0 0 0,2-1 0 0 0,-2 0-1 0 0,1-1 1 0 0,-12-6 0 0 0,19 8 16 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 0 0 0 0,-3-8-1 0 0,5 7-152 0 0,0 0-1 0 0,0 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,2 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,2-1 0 0 0,-1 1 0 0 0,3-4 0 0 0,5-9-1197 0 0,2 0-1 0 0,26-27 0 0 0,-21 25 667 0 0,-5 6 396 0 0,1-1 0 0 0,0 2-1 0 0,18-13 1 0 0,0 1 32 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="516.21">1174 244 392 0 0,'1'-1'207'0'0,"-1"1"0"0"0,1-1 0 0 0,-1 0 0 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 2 1 0 0,16 66 8457 0 0,-10-39-8025 0 0,5 11 781 0 0,-3 1-1 0 0,7 58 0 0 0,5 21-46 0 0,-13-87-1052 0 0,43 178 702 0 0,-46-196-1010 0 0,1-2-1 0 0,0 1 1 0 0,1 0 0 0 0,0-1-1 0 0,1 0 1 0 0,0-1 0 0 0,1 1 0 0 0,19 21-1 0 0,-27-34-11 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,18-20 44 0 0,9-30 17 0 0,1-26-16 0 0,31-129 0 0 0,-38 127-42 0 0,62-279-48 0 0,-61 252 14 0 0,-20 91 24 0 0,12-33-21 0 0,-15 47 35 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 1-1 0 0,10 19 297 0 0,5 25 147 0 0,52 441 1762 0 0,-49-309-2026 0 0,3-39-129 0 0,-19-123-42 0 0,1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 1 0 0,1-1-1 0 0,11 16 0 0 0,-18-28-11 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 1-1 0 0,1-2 1 0 0,-1 1 0 0 0,0 0-1 0 0,2 0 1 0 0,-1-2 5 0 0,1 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,3-4 0 0 0,4-6 29 0 0,-2-1 1 0 0,1-1-1 0 0,12-26 0 0 0,25-83-29 0 0,28-131-1 0 0,-48 163-8 0 0,37-190-2 0 0,-55 251-776 0 0,-1 0 1 0 0,-2-1-1 0 0,0-54 0 0 0,-4 84-120 0 0,-18 45-9688 0 0,-1 31 3639 0 0,13-53 4804 0 0,0 1 0 0 0,1 0-1 0 0,1 1 1 0 0,-1 32 0 0 0,5-54 1660 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="749.25">2526 62 588 0 0,'0'0'4583'0'0,"19"20"1917"0"0,-15-13-5047 0 0,-1-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,1 1 0 0 0,0 13 0 0 0,4 4 873 0 0,5 82 2267 0 0,-8-83-3799 0 0,-1 0-1 0 0,0 38 1 0 0,-1 3 101 0 0,1 128 399 0 0,-5-105-1155 0 0,0-9-980 0 0,-16 99 0 0 0,1-116-3203 0 0,-2-86-1883 0 0,13 4 4440 0 0,2-1 1 0 0,0 0-1 0 0,1 1 1 0 0,1-1 0 0 0,1 0-1 0 0,2-26 1 0 0,-1 30 784 0 0,29-323-7507 0 0,-26 317 7911 0 0,3-27-273 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="995.38">2620 87 48 0 0,'0'-9'1074'0'0,"1"0"0"0"0,0 0 1 0 0,1 0-1 0 0,0 0 0 0 0,5-15 0 0 0,-5 23-657 0 0,-1-1 0 0 0,0 1-1 0 0,1-1 1 0 0,0 1 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,3 0-1 0 0,50 14 4931 0 0,3 12-2442 0 0,-2 3-1 0 0,95 67 1 0 0,-109-69-2376 0 0,11 16-211 0 0,-43-36-294 0 0,-1 1 1 0 0,-1 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1 0 0 0 0,0 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,7 21-1 0 0,-9-21-12 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-3 20 0 0 0,-1 0 16 0 0,-14 61 0 0 0,4-53-78 0 0,-1 0 1 0 0,-2-1-1 0 0,-1 0 0 0 0,-2-1 1 0 0,-1-2-1 0 0,-2 0 0 0 0,-50 62 1 0 0,53-76-664 0 0,1 1 0 0 0,-3-2-1 0 0,0-1 1 0 0,-1 0 0 0 0,-42 27 0 0 0,42-34-1502 0 0,0 0 1 0 0,-1-1-1 0 0,-44 15 0 0 0,52-22 1017 0 0,2 1-289 0 0,0-1 1 0 0,-1 0-1 0 0,-1-1 1 0 0,2 0-1 0 0,-1-2 0 0 0,-1 1 1 0 0,1-2-1 0 0,-23-1 0 0 0,-18-1-2128 0 0,36-4 2940 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink14.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -1996,7 +2845,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink15.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -2024,39 +2873,787 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">2582 716 484 0 0,'0'-1'280'0'0,"0"0"-1"0"0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,-1 0-1 0 0,-43-21 6008 0 0,26 12-4095 0 0,2 1-1251 0 0,-40-21 1711 0 0,-2 3-1 0 0,-75-24 0 0 0,54 27-1121 0 0,-162-41 614 0 0,157 44-2091 0 0,-55-16-53 0 0,71 25 0 0 0,43 5 0 0 0,0 2 0 0 0,-37-1 0 0 0,-38 3 0 0 0,43-1 0 0 0,-96 9 0 0 0,114-1 0 0 0,1 1 0 0 0,-1 3 0 0 0,1 1 0 0 0,1 1 0 0 0,-46 21 0 0 0,1 0 0 0 0,56-19 0 0 0,-15 7 0 0 0,1 1 0 0 0,0 3 0 0 0,-58 44 0 0 0,71-46 0 0 0,0 0 0 0 0,1 1 0 0 0,-36 41 0 0 0,47-45 0 0 0,-20 22 0 0 0,2 2 0 0 0,-32 53 0 0 0,18-23 0 0 0,29-48 0 0 0,-21 42 0 0 0,12-14 0 0 0,9-19 0 0 0,1 1 0 0 0,1 1 0 0 0,3 0 0 0 0,-20 71 0 0 0,23-67 0 0 0,8-32 0 0 0,1-1 0 0 0,-1 1 0 0 0,2-1 0 0 0,-1 1 0 0 0,0 13 0 0 0,-11 68 0 0 0,7 67 0 0 0,7-129-4 0 0,2 0 0 0 0,1 1 0 0 0,1-1 0 0 0,2-1 0 0 0,0 1 1 0 0,17 37-1 0 0,27 61 31 0 0,-38-100-27 0 0,1-1 0 0 0,2-1 0 0 0,0 0 0 0 0,2-1 0 0 0,0 0 0 0 0,1-2 0 0 0,26 21 0 0 0,-18-15 0 0 0,21 18 0 0 0,88 63 0 0 0,-54-62 0 0 0,-63-35 0 0 0,0 1 0 0 0,30 9 0 0 0,25 14 0 0 0,-33-13 0 0 0,67 22 0 0 0,-17-7 0 0 0,57 21 0 0 0,-103-40 0 0 0,66 15 0 0 0,-45-13 0 0 0,107 17 0 0 0,-85-21 0 0 0,-17-5 0 0 0,110 2 0 0 0,-36-4 0 0 0,-94-6 0 0 0,100-12 0 0 0,-100 6 0 0 0,-4-2 0 0 0,46-12 0 0 0,2-1 0 0 0,-7 2 0 0 0,0-3 0 0 0,114-44 0 0 0,-147 44 0 0 0,-1-2 0 0 0,-1-3 0 0 0,-1-2 0 0 0,-2-3 0 0 0,93-70 0 0 0,-82 53 0 0 0,-42 33 0 0 0,-1 0 0 0 0,0-1 0 0 0,19-21 0 0 0,-3-2 0 0 0,-18 22 0 0 0,-1 0 0 0 0,0-2 0 0 0,-2 0 0 0 0,0 0 0 0 0,15-29 0 0 0,-13 14 0 0 0,-1 4 0 0 0,-1-1 0 0 0,-2 0 0 0 0,12-48 0 0 0,-9 10 0 0 0,-3 0 0 0 0,-3-1 0 0 0,-3 0 0 0 0,-6-114 0 0 0,-10 106 0 0 0,-3 0 0 0 0,-28-85 0 0 0,39 152 0 0 0,-8-22 0 0 0,-2 1 0 0 0,-2 0 0 0 0,0 1 0 0 0,-21-29 0 0 0,32 52 0 0 0,-99-136 0 0 0,89 128 0 0 0,0 0 0 0 0,-24-19 0 0 0,-4-3 0 0 0,1 1 0 0 0,-2 1 0 0 0,-1 3 0 0 0,-2 1 0 0 0,-1 3 0 0 0,-63-29 0 0 0,74 41 0 0 0,0 1 0 0 0,-2 2 0 0 0,1 2 0 0 0,-2 1 0 0 0,1 2 0 0 0,-1 1 0 0 0,0 3 0 0 0,-42-1 0 0 0,46 7 78 0 0,1 2 0 0 0,-45 9-1 0 0,46-6-1340 0 0,0-2 0 0 0,-44 2 0 0 0,-6 6-8532 0 0,29-12 1984 0 0,-19 0 836 0 0,62-2 6284 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-20-7 0 0 0,5 2-76 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1748.06">3907 1368 56 0 0,'-1'8'16144'0'0,"2"-8"-15833"0"0,16 3 5955 0 0,35-6-7035 0 0,-32 1 2925 0 0,21 0-218 0 0,62-11 1 0 0,-25 2-649 0 0,3-1-339 0 0,95-29 0 0 0,-113 25-784 0 0,77-16 50 0 0,273-28 0 0 0,-272 58-194 0 0,0 6-1 0 0,166 25 0 0 0,-204-17-8 0 0,154 19 24 0 0,228 21 39 0 0,-250-20-42 0 0,-170-20-26 0 0,-3 1-2 0 0,-49-9 0 0 0,1-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0-2 1 0 0,0 1-1 0 0,0-2 0 0 0,0 0 1 0 0,0-1-1 0 0,16-2 0 0 0,10-6-7 0 0,1 2 1 0 0,-1 2-1 0 0,67-1 0 0 0,-11 19 24 0 0,-37 0-29 0 0,3-7 6 0 0,29 0 54 0 0,86-25-6 0 0,-122 17-46 0 0,-38 0-3 0 0,0 1-1 0 0,0 1 1 0 0,0 0-1 0 0,21 4 1 0 0,51 4 10 0 0,-12-3-1 0 0,-62-4-5 0 0,0-1 0 0 0,1 0 0 0 0,17-3-1 0 0,21 0 6 0 0,156-4-383 0 0,-57 20-4868 0 0,-144-11 4849 0 0,4 0-6156 0 0,-12-2 6455 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-5-3-513 0 0,1 0 0 0 0,-1 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 1 1 0 0,0 0-1 0 0,-8-1 0 0 0,-17-5-1394 0 0,-36-14-1070 0 0,-73-14 0 0 0,102 29 2586 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2430.94">4232 1839 112 0 0,'-35'-5'183'0'0,"20"1"4236"0"0,1 0 10328 0 0,40-2-12319 0 0,39 2-367 0 0,0-3 1 0 0,99-22-1 0 0,-76 11-1113 0 0,473-70 1481 0 0,-313 52-2151 0 0,-73 8-172 0 0,377-39 82 0 0,-27 69-77 0 0,-204 3-34 0 0,-111-2-25 0 0,187-5 61 0 0,-363 0-104 0 0,97-4 44 0 0,174-30 0 0 0,-104 5-35 0 0,-63 12-11 0 0,-89 18 6 0 0,-47 1 41 0 0,-35 0-1171 0 0,-179 17-12958 0 0,208-16 13793 0 0,-6 0-770 0 0,1 0-1 0 0,-1-1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,-15-5-1 0 0,20 6 648 0 0,0-2 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,2 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-5-9 0 0 0,-4-4-336 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2832.87">7998 596 60 0 0,'0'0'13763'0'0,"9"5"-8432"0"0,13 4-1950 0 0,-15-6-2560 0 0,1 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,11 9 0 0 0,16 9 829 0 0,16 8-680 0 0,-1 2 0 0 0,-2 2 0 0 0,62 57 0 0 0,-88-72-937 0 0,31 29 32 0 0,-3 3 1 0 0,56 71 0 0 0,-101-117-59 0 0,-1-1-1 0 0,0 2 1 0 0,0-1 0 0 0,-1 0 0 0 0,1 1-1 0 0,-1 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,0 1 0 0 0,-1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-7 8 0 0 0,-47 61 40 0 0,-120 118 0 0 0,102-118-124 0 0,11-9-994 0 0,-3-3-1 0 0,-97 72 0 0 0,132-112-87 0 0,-29 20-3028 0 0,56-40 3428 0 0,0 0 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-12 1 0 0 0,14-3 293 0 0,1 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1-1 0 0,-2-3 1 0 0,-32-53-3913 0 0,20 31 3007 0 0,3 2 400 0 0,0-4 244 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5210.65">9642 94 376 0 0,'-8'-16'2460'0'0,"8"15"-2229"0"0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-2-1 0 0 0,1 0 386 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-2 2 0 0 0,1 0-180 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-2 5 0 0 0,-3 9-762 0 0,1 1-1 0 0,-7 34 1 0 0,8-31 1808 0 0,-10 52-1002 0 0,2 1 0 0 0,4 0 0 0 0,3 0-1 0 0,3 1 1 0 0,4 0 0 0 0,20 139 0 0 0,-14-171-384 0 0,-4-11-34 0 0,2-1 1 0 0,1 0 0 0 0,1 0-1 0 0,2 0 1 0 0,16 34-1 0 0,-20-54-62 0 0,0-1 1 0 0,1 1-1 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,1-1 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,2 0 0 0 0,-1 0 0 0 0,0-1 1 0 0,1-1-1 0 0,0 0 0 0 0,14 3 0 0 0,-7-1 0 0 0,0-2 0 0 0,1 0 0 0 0,-1-1 0 0 0,0-1 0 0 0,1 0 0 0 0,0-2 0 0 0,-1 0 0 0 0,1-1 0 0 0,35-7 0 0 0,-29 2 0 0 0,1-1 0 0 0,-1-2 0 0 0,-1 0 0 0 0,0-1 0 0 0,0-2 0 0 0,34-22 0 0 0,-26 12 0 0 0,-1-1 0 0 0,-1-2 0 0 0,-2-1 0 0 0,0-1 0 0 0,-2-2 0 0 0,-1 0 0 0 0,-1-2 0 0 0,-1 0 0 0 0,30-59 0 0 0,-26 30 0 0 0,-3-1 0 0 0,-3-1 0 0 0,21-99 0 0 0,-32 110 0 0 0,4-92 0 0 0,-6 43 0 0 0,-6 81 0 0 0,-1 1 0 0 0,-1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-2 0 0 0 0,-5-25 0 0 0,8 43 9 0 0,-1-3-134 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,-1 1 0 0 0,-2-6 0 0 0,2 8-122 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-2 2 0 0 0,-4 0-767 0 0,1 2 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-6 12 0 0 0,0 2-867 0 0,1 1 1 0 0,1 0-1 0 0,-10 36 1 0 0,16-8-106 0 0,2-29 1253 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5564.63">11216 201 32 0 0,'0'0'24220'0'0,"-6"13"-21739"0"0,-2 9-509 0 0,6-19-1819 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-2 4-1 0 0,0 9 171 0 0,-1 0 0 0 0,-1 0-1 0 0,-1-1 1 0 0,-1 0 0 0 0,0 0-1 0 0,-13 24 1 0 0,1 2 9 0 0,-80 169-228 0 0,53-120-109 0 0,-48 141 1 0 0,18-27-1068 0 0,71-192 277 0 0,0-1 0 0 0,-1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 1 0 0,-9 11-1 0 0,16-37-9969 0 0,9-60 5986 0 0,7 3 1838 0 0,4 1 1 0 0,51-119 0 0 0,-48 135 2299 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5831.9">11210 163 280 0 0,'10'-19'448'0'0,"13"-8"7803"0"0,-22 26-7884 0 0,0 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,0 1 0 0 0,18 27 2955 0 0,27 57 0 0 0,28 103-1592 0 0,-47-114-1743 0 0,0 9 13 0 0,-16-47 0 0 0,22 52 0 0 0,46 111 0 0 0,-59-147 0 0 0,27 60 0 0 0,-28-72 0 0 0,-2 0 0 0 0,22 82 0 0 0,-38-120-65 0 0,0-1 1 0 0,-1 0-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,-1 5 0 0 0,1-7-136 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,-1-1 1 0 0,0 0-1 0 0,-8-3-1158 0 0,-3 1-287 0 0,0-1 1 0 0,0-1-1 0 0,1 0 0 0 0,0-1 1 0 0,0 0-1 0 0,1-1 1 0 0,-13-10-1 0 0,-14-16-2587 0 0,-57-67 1 0 0,69 70 3366 0 0,0 4 242 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6032.72">11082 728 152 0 0,'-25'-15'2758'0'0,"24"15"-2609"0"0,1 0 1 0 0,0-1-1 0 0,-1 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,0 1 1612 0 0,30-1 11189 0 0,49-5-9246 0 0,18 0-2843 0 0,-70 4-1251 0 0,-1 2 0 0 0,0 0 0 0 0,0 2 0 0 0,0 0 0 0 0,24 9-1 0 0,6 8-4203 0 0,-2 9-3303 0 0,-51-29 7482 0 0,1 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,3-1 0 0 0,1-1-55 0 0,0 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,-1-1-1 0 0,10-9 1 0 0,-1-4-88 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6313.92">12019 258 112 0 0,'10'-23'3292'0'0,"-10"21"-2956"0"0,0 1-1 0 0,0-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,1 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,2 0 3550 0 0,2 7 857 0 0,-5-6-4516 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0 0 0 0 0,7 95 5008 0 0,-29 241-4092 0 0,6-158-1145 0 0,12-91 3 0 0,8 124 0 0 0,4-141 0 0 0,2 74-37 0 0,-6-121-252 0 0,-1-4-4577 0 0,-10-54-1950 0 0,-3-49 353 0 0,0 14 2853 0 0,-9-118-2759 0 0,7-11 2642 0 0,12 148 3213 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6683.33">12044 370 328 0 0,'1'-6'498'0'0,"0"0"1"0"0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,2 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,0 1 0 0 0,0-1 1 0 0,1 1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 1 1 0 0,9-8-1 0 0,-9 8 80 0 0,-1 1 1 0 0,0 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 1-1 0 0,1 0 1 0 0,6 2-1 0 0,13 6 834 0 0,-18-7-1043 0 0,1 0 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 2 0 0 0,0-1 0 0 0,-1 1 0 0 0,8 6 0 0 0,9 11 596 0 0,12 13 679 0 0,46 55 1 0 0,-73-78-1510 0 0,1-1 1 0 0,-1 2-1 0 0,-1-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,0 1 0 0 0,-1-1 1 0 0,-1 1-1 0 0,5 23 0 0 0,-8-23-130 0 0,0 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,-1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,0 0-1 0 0,-2-1 1 0 0,1 1-1 0 0,-2-1 1 0 0,1 0 0 0 0,-2 0-1 0 0,-15 23 1 0 0,11-21-46 0 0,0 0-1 0 0,-1-1 1 0 0,-1 0 0 0 0,0-1-1 0 0,-1-1 1 0 0,0 0 0 0 0,-1 0 0 0 0,0-2-1 0 0,-1 0 1 0 0,0-1 0 0 0,-18 8-1 0 0,21-12-32 0 0,0-1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-2 0 0 0,-1 0-1 0 0,0 0 1 0 0,0-1 0 0 0,1-1 0 0 0,-1 0-1 0 0,-22-3 1 0 0,6 0-11 0 0,23 2 75 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,-9-5 1 0 0,4 4 227 0 0,15 10 338 0 0,18 12 29 0 0,-8-12-574 0 0,0 1 0 0 0,0 1 0 0 0,-2-1 0 0 0,1 2 0 0 0,10 12 0 0 0,15 13-10 0 0,97 97-1 0 0,-51-46 0 0 0,-55-58-162 0 0,0-3 1 0 0,2 0-1 0 0,1-2 1 0 0,1-1-1 0 0,1-1 0 0 0,1-2 1 0 0,42 17-1 0 0,-42-29-2293 0 0,-34-8 2219 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1-1 0 0 0,7-160-14124 0 0,-7 134 13080 0 0,1 0 0 0 0,1 0 0 0 0,9-37 0 0 0,0 22 545 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6932.97">13064 195 332 0 0,'-1'2'568'0'0,"1"1"0"0"0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,-2 2-1 0 0,4-3-120 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,1 0-1 0 0,119-40 10206 0 0,5-1-8430 0 0,-111 37-2222 0 0,0 1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,0 2 0 0 0,0-1 0 0 0,0 2 0 0 0,0 0 0 0 0,24 9 0 0 0,34 19-3884 0 0,-72-31 3711 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,-10 16-13522 0 0,9-14 13517 0 0,-8 0-1589 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,-13 1 0 0 0,-26 3-1870 0 0,37 1 3008 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7148.94">13293 308 172 0 0,'-33'44'2650'0'0,"24"-32"-885"0"0,0-1 0 0 0,0 2 0 0 0,1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-6 19 0 0 0,9-19-208 0 0,1-1 0 0 0,0 1 0 0 0,-1 18 0 0 0,4 77 2825 0 0,1-53-3023 0 0,15 173 1990 0 0,-6-118-2490 0 0,8 34-182 0 0,-2-20-1556 0 0,-12-41-2706 0 0,-4-81 2393 0 0,-18-41-11733 0 0,3-66 4908 0 0,9-53 3139 0 0,6 121 4375 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17987.54">9859 1782 44 0 0,'-15'-21'2070'0'0,"-3"-3"1715"0"0,11 7-900 0 0,5 12-1387 0 0,0 0 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 1 0 0,0-12-1 0 0,5 14-1174 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 2 0 0 0,-1-1 0 0 0,1 0 1 0 0,6-2-1 0 0,26-9 114 0 0,1 2 0 0 0,0 1 0 0 0,43-6-1 0 0,-65 14-349 0 0,0 1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1 1 0 0 0,-1 1-1 0 0,1 1 1 0 0,-1 0 0 0 0,0 1-1 0 0,0 1 1 0 0,20 6 0 0 0,57 35 264 0 0,-84-39-286 0 0,-1-1 0 0 0,1 1-1 0 0,-1 1 1 0 0,0-1 0 0 0,-1 1 0 0 0,1 1 0 0 0,11 15-1 0 0,-17-19 3 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-3 7-1 0 0,-3 3 125 0 0,-1 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,-14 18 1 0 0,-3 5-75 0 0,4-8-11 0 0,-1-1 0 0 0,-46 45 0 0 0,18-20-50 0 0,11-14-39 0 0,-2-2-1 0 0,-2-1 1 0 0,-1-3-1 0 0,-83 49 1 0 0,106-72-339 0 0,0-1 0 0 0,-1 0 1 0 0,0-2-1 0 0,-1-1 0 0 0,1 0 0 0 0,-30 3 1 0 0,45-9-235 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,-13-2 0 0 0,19 1 272 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-2-4 0 0 0,-2-28-1265 0 0,1 0 1 0 0,2 0-1 0 0,2 0 0 0 0,7-58 1 0 0,-3 39 683 0 0,34-249 1982 0 0,-28 233 8427 0 0,-9 72-9317 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1 1 1 0 0,-2 4 0 0 0,2-3 140 0 0,4 51 959 0 0,-2 0 0 0 0,-2 1 0 0 0,-10 84 0 0 0,2-49-399 0 0,-31 491 1882 0 0,33-507-2771 0 0,3-18-450 0 0,-3-1 0 0 0,-17 79 0 0 0,15-113-2293 0 0,2-36-6272 0 0,8-16 6988 0 0,1 0 1 0 0,1 1-1 0 0,1 0 1 0 0,16-42-1 0 0,-9 24 538 0 0,-2 12 542 0 0,2 1-1 0 0,1 1 1 0 0,29-51-1 0 0,-17 39 387 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="18356.22">11076 1901 76 0 0,'9'-13'3436'0'0,"-16"-11"23188"0"0,0 24-23148 0 0,0 1-3499 0 0,-1 4-3462 0 0,-36 15 5096 0 0,-8 5-1106 0 0,6 5-347 0 0,20-13-89 0 0,-36 29 0 0 0,13-5 7 0 0,23-20-47 0 0,2 0 0 0 0,0 1 0 0 0,1 2 1 0 0,1 0-1 0 0,-25 37 0 0 0,43-55-29 0 0,-30 45 0 0 0,3 2 0 0 0,1 2 0 0 0,4 0 0 0 0,-22 62 0 0 0,39-86 0 0 0,0 0 0 0 0,2 0 0 0 0,1 1 0 0 0,2 0 0 0 0,1 0 0 0 0,1 42 0 0 0,2-64 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 0 0 0 0,0-1 0 0 0,1 0 0 0 0,13 7 0 0 0,1-4 26 0 0,0 0 0 0 0,1-1 1 0 0,-1-1-1 0 0,1-2 0 0 0,0 0 0 0 0,1-1 0 0 0,34-2 1 0 0,-26-1-585 0 0,-1-3 0 0 0,1-1 0 0 0,0-1 0 0 0,-1-1 0 0 0,33-12 0 0 0,-5-3-3224 0 0,31-20-6292 0 0,-75 32 8201 0 0,-1 0-1 0 0,0-1 0 0 0,0 0 0 0 0,-1-2 1 0 0,0 1-1 0 0,-1-2 0 0 0,13-14 0 0 0,-13 9 1171 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="19806.51">12210 1619 512 0 0,'-13'0'16964'0'0,"29"4"-12821"0"0,75 16-3567 0 0,-40-15-172 0 0,-1-3 1 0 0,62-5 0 0 0,-12 0-34 0 0,-93 3-355 0 0,1-1-1 0 0,-1 2 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,9 7-1 0 0,-13-9-10 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 0 0 0 0,-2 4 0 0 0,-6 8 10 0 0,0 0-1 0 0,0-1 1 0 0,-15 17 0 0 0,21-27-11 0 0,-11 12-3 0 0,0 0 1 0 0,-1-2-1 0 0,0 1 1 0 0,-1-2 0 0 0,-1 0-1 0 0,0-1 1 0 0,0-1-1 0 0,-1-1 1 0 0,0 0 0 0 0,-32 10-1 0 0,16-10-5 0 0,0 0-1 0 0,0-2 0 0 0,-1-2 0 0 0,1-1 1 0 0,-49-1-1 0 0,73-5 40 0 0,21-2 37 0 0,28-3 24 0 0,215-5 350 0 0,-70 24-894 0 0,-171-8-1928 0 0,-18 4 329 0 0,-24 10-1288 0 0,24-15 2544 0 0,-23 11-2147 0 0,0-1 0 0 0,-59 18-1 0 0,6-2-336 0 0,-52 15-73 0 0,102-32 2915 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="19983.32">12012 2372 252 0 0,'0'21'1169'0'0,"-1"-19"-885"0"0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,2 2 0 0 0,6 12 1451 0 0,0 1 1 0 0,-1 1-1 0 0,-1 0 0 0 0,-1 0 0 0 0,5 22 1 0 0,10 26-96 0 0,-16-48-1341 0 0,-1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,-2 1-1 0 0,0 29 1 0 0,2 19 93 0 0,2 23-38 0 0,-2-28-1756 0 0,1-19-2752 0 0,-22-63 86 0 0,0-81-1674 0 0,15 78 4964 0 0,0 0 0 0 0,2-1-1 0 0,1 1 1 0 0,5-39 0 0 0,9-33-683 0 0,-3 45 930 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="20310.93">12274 2209 128 0 0,'4'-5'477'0'0,"1"1"1"0"0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,1 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,9 3 0 0 0,81 13 6403 0 0,18 5-2217 0 0,-86-17-3424 0 0,1 0 0 0 0,0-2 0 0 0,1-1 0 0 0,46-4 0 0 0,-21 1 388 0 0,-30 2-1185 0 0,-16 0-313 0 0,0-1 0 0 0,0 0 1 0 0,0-1-1 0 0,-1 0 0 0 0,19-4 0 0 0,-26 4-127 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 3 0 0 0,-2 55 79 0 0,-16 97-1 0 0,2-40-64 0 0,3-30-37 0 0,8-50-72 0 0,0 1-1 0 0,1 38 0 0 0,-8 36-1652 0 0,13-111 1588 0 0,0-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,-24-4-5405 0 0,-31-28-2792 0 0,46 26 7461 0 0,0-2-205 0 0,-1 0 1 0 0,1-1-1 0 0,1 0 0 0 0,-11-13 0 0 0,-4-3-360 0 0,-34-31-967 0 0,34 37 1947 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="20533.89">12235 2447 280 0 0,'-67'3'17185'0'0,"124"12"-14262"0"0,55-3 1011 0 0,200-4-1 0 0,-230-8-3563 0 0,-55-2 492 0 0,-8-2-3910 0 0,-19 4 2966 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-27-2-4069 0 0,-26 2-438 0 0,-59 0-2144 0 0,86 1 5635 0 0,-1 2 0 0 0,1 0 0 0 0,1 1 0 0 0,-36 11 0 0 0,35-3 564 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="20720.95">12210 2629 244 0 0,'-1'0'344'0'0,"0"1"1"0"0,-1-1-1 0 0,1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 3-1 0 0,0-3 7 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,2-1 1 0 0,16 7 2096 0 0,-1-2 0 0 0,28 5 0 0 0,-30-7-2453 0 0,331 41 6710 0 0,-295-39-6246 0 0,-45-4-427 0 0,30 3-200 0 0,0-1 1 0 0,0-2-1 0 0,0-2 0 0 0,52-7 0 0 0,-87 8 32 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,1-3 0 0 0,-1 1-288 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,-1-4-1 0 0,-3-5-979 0 0,0-1 0 0 0,-1 1 0 0 0,-1-1 0 0 0,0 2 0 0 0,-11-16 0 0 0,-62-76-5563 0 0,-46-44 1730 0 0,102 123 4725 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="20891.65">12592 2077 492 0 0,'3'4'402'0'0,"0"-1"-1"0"0,-1 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 6 0 0 0,2 56 3457 0 0,-3-64-3759 0 0,-3 171 6901 0 0,5 160-2552 0 0,3-213-3999 0 0,-4-56-821 0 0,19 123-1 0 0,-16-162-836 0 0,-2 0 0 0 0,-1 42 1 0 0,-1-42-2008 0 0,-26-36-1235 0 0,21 6 3993 0 0,1 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,-3-7 0 0 0,-14-20-956 0 0,6 11 649 0 0,1 0-1 0 0,0-1 1 0 0,-14-38 0 0 0,12 26 219 0 0,-5-14-70 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="21083.38">11898 1744 76 0 0,'-31'-24'3869'0'0,"30"23"-2980"0"0,-11 21 5217 0 0,32 15-4938 0 0,3 3-1263 0 0,-20-34-147 0 0,0-1 1 0 0,1 0-1 0 0,-1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 9 0 0 0,-3-3-582 0 0,0 0 0 0 0,0-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,0-1 0 0 0,-6 10-1 0 0,4-7 320 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="21629.62">11796 2152 136 0 0,'-15'11'866'0'0,"14"-9"-687"0"0,0-1 1 0 0,-1 0 0 0 0,1 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,1-1-1 0 0,-3 1 1 0 0,3 0-12 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1 1 0 0 0,-1 47 1141 0 0,1-37-1168 0 0,0 1-45 0 0,-1-10-90 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,-3 5-1 0 0,1 2 26 0 0,0 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,1 1-1 0 0,0-1 0 0 0,0 0 0 0 0,1 1 1 0 0,1-1-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,0 0-1 0 0,1-1 0 0 0,1 1 0 0 0,-1-1 1 0 0,2 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,0-1 0 0 0,15 14 0 0 0,32 40 1144 0 0,-53-61-1086 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,0 0 0 0 0,-2 2 0 0 0,-17 43 880 0 0,7-21-399 0 0,3-5-209 0 0,-1 0 0 0 0,-21 33 1 0 0,10-20-159 0 0,6-7-195 0 0,-1-2 0 0 0,-1 0 0 0 0,-2-1 0 0 0,0-1 1 0 0,-1-1-1 0 0,-2 0 0 0 0,0-2 0 0 0,-1 0 0 0 0,-37 23 1 0 0,55-40-96 0 0,0 0 1 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,-5-2-1 0 0,9 1 41 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,1-3-1 0 0,0-6 97 0 0,0 1 0 0 0,1-1-1 0 0,0 1 1 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1-1 0 0,0 0 1 0 0,10-6 0 0 0,-10 10 212 0 0,-1 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 2 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,-1 1 1 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0 0-1 0 0,8 2 1 0 0,6 1 555 0 0,0 2-1 0 0,-1 0 0 0 0,33 14 1 0 0,103 47 2943 0 0,158 91 897 0 0,-183-93-3856 0 0,264 90 0 0 0,-113-73-684 0 0,-266-78-112 0 0,194 34-687 0 0,-163-32-289 0 0,-39-6 166 0 0,0 0-1 0 0,1 0 0 0 0,-1-1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-2 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 0 1 0 0,15-10-1 0 0,-10 3-1088 0 0,1-1 1 0 0,-2-1-1 0 0,0-1 0 0 0,0 0 1 0 0,10-16-1 0 0,44-82-3843 0 0,-26 40 3474 0 0,-16 31 1682 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="22622.96">14179 1563 56 0 0,'1'0'173'0'0,"0"0"0"0"0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,1 35 5380 0 0,-4-20-2489 0 0,-1-1 0 0 0,-10 28 0 0 0,4-19-1178 0 0,-1-1 1 0 0,-14 25 0 0 0,-64 87 1255 0 0,23-36-2456 0 0,-52 71-442 0 0,43-66-399 0 0,30-47-852 0 0,-2-3 1 0 0,-76 71-1 0 0,99-104-211 0 0,-1-2 0 0 0,-28 18 0 0 0,-20 5-4583 0 0,72-43 5591 0 0,-1 0-1 0 0,1 1 1 0 0,0-1 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1-1-1 0 0,0 0 1 0 0,0-23-3301 0 0,14-24 1382 0 0,-8 37 1742 0 0,1 0 0 0 0,0-1 0 0 0,1 2 1 0 0,0-1-1 0 0,1 1 0 0 0,0 0 0 0 0,17-16 0 0 0,6-4-91 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="22803.66">13809 2228 156 0 0,'20'-9'278'0'0,"-11"5"118"0"0,1 0-1 0 0,-1 1 1 0 0,1 0 0 0 0,17-3 0 0 0,-24 6-218 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,4 3 0 0 0,1 2 481 0 0,-1 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,-1 1 0 0 0,0-1 1 0 0,5 17-1 0 0,1 5 790 0 0,-1 1 0 0 0,-2-1 0 0 0,-1 1 0 0 0,3 63 0 0 0,-14 130 1603 0 0,-51 202-1304 0 0,49-396-1858 0 0,-1 0 0 0 0,-13 31 0 0 0,6-19-456 0 0,13-37 337 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,-5 5 0 0 0,-10 0-1847 0 0,19-10 1951 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,-5-21-1117 0 0,2-1 1 0 0,0 1-1 0 0,2 0 0 0 0,0-1 0 0 0,2 0 1 0 0,0 1-1 0 0,6-29 0 0 0,44-160-2048 0 0,-34 153 2452 0 0,35-115-560 0 0,-21 85 934 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="22964.52">14772 1581 92 0 0,'9'-3'230'0'0,"-1"0"374"0"0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,11 0-1 0 0,-16 2-310 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,1 4 1 0 0,41 47 6602 0 0,9 14-3370 0 0,-50-62-3445 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-2 0 0 0 0,1 6 0 0 0,1 6-356 0 0,-3 10-1056 0 0,-1-21 776 0 0,0-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-11 3 0 0 0,-12 5-1906 0 0,-1-2 1 0 0,-55 11 0 0 0,47-12 1213 0 0,13-3 573 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="23199.12">14478 2021 320 0 0,'-7'22'2066'0'0,"-3"9"4216"0"0,10-30-6110 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,2 0 0 0 0,51 3 5777 0 0,8 0-3136 0 0,201-15 2573 0 0,-93 0-3929 0 0,-101 6-1247 0 0,153-20-41 0 0,-164 13-2466 0 0,-98 7-3203 0 0,6 7 1564 0 0,-1 2 0 0 0,-38 7 0 0 0,-73 23-3003 0 0,77-17 4732 0 0,-56 21-420 0 0,87-25 2090 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="23564.28">14440 2290 292 0 0,'0'1'162'0'0,"-1"-1"-1"0"0,0 1 1 0 0,1 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 1 1 0 0,1 0 379 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,5 1-1 0 0,4 2 734 0 0,0 0-1 0 0,0-1 1 0 0,1-1 0 0 0,19 5-1 0 0,26-3 730 0 0,0-2-1 0 0,80-7 1 0 0,-55-4-1150 0 0,0-3 1 0 0,127-36 0 0 0,-193 43-898 0 0,-11 3-67 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 0 1 0 0,7-4-1 0 0,-11 5-266 0 0,-2 0-977 0 0,0 0 1231 0 0,0 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,-26 2-1442 0 0,-43 12-3297 0 0,-79 26 0 0 0,-66 34 1130 0 0,208-71 3683 0 0,-16 6 153 0 0,0 1 1 0 0,-29 19 0 0 0,43-24 303 0 0,0 2 0 0 0,0-1 1 0 0,1 1-1 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 1 0 0,-9 13-1 0 0,17-20-196 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 1 0 0 0,2 1 133 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,6 3 0 0 0,7 2 644 0 0,0-1-1 0 0,1-1 1 0 0,0-1-1 0 0,26 4 1 0 0,13-5 644 0 0,-1-1 0 0 0,63-7-1 0 0,11-1-261 0 0,-8 11-1736 0 0,-109-4-3563 0 0,-82-3-11364 0 0,43 0 13398 0 0,0 1 1 0 0,0 1-1 0 0,-38 6 1 0 0,42-3 1272 0 0,4 0 131 0 0,0 1 1 0 0,0 0-1 0 0,-20 8 0 0 0,0 6-19 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="23719.83">14478 3018 628 0 0,'0'19'1890'0'0,"1"1"0"0"0,1-1 1 0 0,7 36-1 0 0,5 9 1181 0 0,-11-43-1437 0 0,2-1 0 0 0,0 0 0 0 0,1 0 0 0 0,13 30 0 0 0,-18-48-1773 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 1 0 0,4 2-1 0 0,-5-3 5 0 0,1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1-1 0 0,2-1 1 0 0,4-6-697 0 0,0-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,-1-1-1 0 0,0 1 1 0 0,6-19 0 0 0,8-14-931 0 0,-6 15 73 0 0,14-49 0 0 0,-17 46 333 0 0,21-46-1 0 0,-18 52 922 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="24041.48">14803 2911 160 0 0,'5'-3'768'0'0,"0"-1"0"0"0,0 0 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 2 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,9 0 0 0 0,15-1 4255 0 0,47 4 1 0 0,-23 0-3514 0 0,-45-2-1174 0 0,1 0-1 0 0,-1 1 0 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 1 0 0,1 2-1 0 0,-1-1 1 0 0,0 2-1 0 0,-1-1 1 0 0,1 1-1 0 0,13 8 1 0 0,-18-9-273 0 0,0 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,0 0 0 0 0,0 1-1 0 0,0 0 1 0 0,-1-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-2 1 0 0 0,1-1 0 0 0,0 1-1 0 0,-2 6 1 0 0,-2 8-58 0 0,-1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,-1 0 0 0 0,-1 0-1 0 0,-1-1 1 0 0,0 0 0 0 0,-1 0 0 0 0,-1-1 0 0 0,0-1 0 0 0,-2 1 0 0 0,1-2-1 0 0,-25 22 1 0 0,24-24-21 0 0,-1 0-1 0 0,0 0 1 0 0,-1-1 0 0 0,0-1-1 0 0,-1-1 1 0 0,0 0-1 0 0,-1-1 1 0 0,0 0-1 0 0,0-2 1 0 0,0 0 0 0 0,-1-1-1 0 0,1-1 1 0 0,-1 0-1 0 0,-1-1 1 0 0,1-1-1 0 0,0-1 1 0 0,0-1 0 0 0,-34-3-1 0 0,21 0 230 0 0,20 2-53 0 0,0 0 0 0 0,1 0 0 0 0,-1-1-1 0 0,-11-4 1 0 0,-41-13 3347 0 0,128 16-3507 0 0,-1-4 1 0 0,67-15-1 0 0,14-2 41 0 0,50-12 9 0 0,-152 27-47 0 0,184-29-866 0 0,-211 35 3256 0 0,3-2-4200 0 0,17-2-10195 0 0,-53 22 2476 0 0,13-13 9102 0 0,1 0 0 0 0,-1-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-8-3 0 0 0,-60-21-2525 0 0,53 16 2432 0 0,-25-9-234 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">2496 710 484 0 0,'0'-1'280'0'0,"0"0"-1"0"0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,-1 0-1 0 0,-42-21 6008 0 0,26 12-4095 0 0,2 1-1251 0 0,-39-21 1711 0 0,-3 3-1 0 0,-71-23 0 0 0,52 26-1121 0 0,-157-41 614 0 0,151 44-2091 0 0,-52-15-53 0 0,68 24 0 0 0,42 5 0 0 0,0 2 0 0 0,-36-1 0 0 0,-37 3 0 0 0,42-1 0 0 0,-92 9 0 0 0,109-1 0 0 0,1 1 0 0 0,-1 3 0 0 0,2 1 0 0 0,0 1 0 0 0,-44 20 0 0 0,1 1 0 0 0,53-19 0 0 0,-13 7 0 0 0,0 1 0 0 0,1 3 0 0 0,-57 43 0 0 0,69-45 0 0 0,0 0 0 0 0,1 0 0 0 0,-35 42 0 0 0,45-45 0 0 0,-19 21 0 0 0,3 3 0 0 0,-32 52 0 0 0,17-22 0 0 0,29-48 0 0 0,-21 41 0 0 0,12-13 0 0 0,9-20 0 0 0,0 2 0 0 0,2 1 0 0 0,2 0 0 0 0,-18 70 0 0 0,21-67 0 0 0,8-31 0 0 0,1-1 0 0 0,-1 1 0 0 0,2-1 0 0 0,-1 1 0 0 0,0 13 0 0 0,-10 67 0 0 0,6 67 0 0 0,7-128-4 0 0,2 0 0 0 0,1 0 0 0 0,1 0 0 0 0,1-1 0 0 0,1 1 1 0 0,16 36-1 0 0,27 61 31 0 0,-38-99-27 0 0,2-1 0 0 0,1-1 0 0 0,1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,2-2 0 0 0,24 21 0 0 0,-17-16 0 0 0,21 19 0 0 0,84 62 0 0 0,-51-61 0 0 0,-62-35 0 0 0,0 1 0 0 0,30 9 0 0 0,23 13 0 0 0,-31-12 0 0 0,64 22 0 0 0,-16-8 0 0 0,55 22 0 0 0,-99-40 0 0 0,63 15 0 0 0,-43-13 0 0 0,103 16 0 0 0,-82-20 0 0 0,-16-5 0 0 0,106 2 0 0 0,-35-4 0 0 0,-90-6 0 0 0,96-12 0 0 0,-97 6 0 0 0,-4-2 0 0 0,45-12 0 0 0,2-1 0 0 0,-7 2 0 0 0,0-2 0 0 0,111-45 0 0 0,-143 44 0 0 0,-1-2 0 0 0,-1-2 0 0 0,-1-3 0 0 0,-1-3 0 0 0,89-69 0 0 0,-79 52 0 0 0,-41 33 0 0 0,0 0 0 0 0,-1 0 0 0 0,19-22 0 0 0,-3-2 0 0 0,-18 22 0 0 0,0 0 0 0 0,-1-1 0 0 0,-1-1 0 0 0,-1 0 0 0 0,16-29 0 0 0,-14 14 0 0 0,0 5 0 0 0,-2-2 0 0 0,-1 0 0 0 0,11-47 0 0 0,-8 9 0 0 0,-4 1 0 0 0,-2-2 0 0 0,-3 1 0 0 0,-6-114 0 0 0,-10 106 0 0 0,-2 0 0 0 0,-28-85 0 0 0,38 151 0 0 0,-8-22 0 0 0,-1 1 0 0 0,-3 1 0 0 0,1 0 0 0 0,-21-29 0 0 0,31 52 0 0 0,-95-134 0 0 0,85 126 0 0 0,1 0 0 0 0,-24-19 0 0 0,-4-3 0 0 0,2 2 0 0 0,-3 0 0 0 0,-1 3 0 0 0,-1 1 0 0 0,-1 4 0 0 0,-62-30 0 0 0,72 41 0 0 0,1 1 0 0 0,-3 2 0 0 0,1 3 0 0 0,-2 0 0 0 0,2 2 0 0 0,-2 1 0 0 0,0 3 0 0 0,-40-1 0 0 0,44 7 78 0 0,1 2 0 0 0,-43 9-1 0 0,44-6-1340 0 0,0-2 0 0 0,-42 2 0 0 0,-7 5-8532 0 0,29-11 1984 0 0,-18 0 836 0 0,59-2 6284 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-19-6 0 0 0,5 1-76 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1748.06">3777 1357 56 0 0,'0'8'16144'0'0,"0"-8"-15833"0"0,17 3 5955 0 0,33-6-7035 0 0,-30 1 2925 0 0,19 0-218 0 0,61-11 1 0 0,-25 2-649 0 0,4-1-339 0 0,91-28 0 0 0,-109 24-784 0 0,74-16 50 0 0,264-27 0 0 0,-262 57-194 0 0,-1 6-1 0 0,161 24 0 0 0,-198-16-8 0 0,150 19 24 0 0,220 21 39 0 0,-242-21-42 0 0,-164-19-26 0 0,-3 1-2 0 0,-48-9 0 0 0,2-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1-2 1 0 0,1 1-1 0 0,-1-2 0 0 0,1 0 1 0 0,0-1-1 0 0,15-2 0 0 0,9-6-7 0 0,2 2 1 0 0,-1 2-1 0 0,64-1 0 0 0,-10 19 24 0 0,-36 0-29 0 0,3-7 6 0 0,28 0 54 0 0,83-25-6 0 0,-118 17-46 0 0,-36 0-3 0 0,-1 1-1 0 0,0 1 1 0 0,1 0-1 0 0,20 4 1 0 0,49 4 10 0 0,-12-3-1 0 0,-59-4-5 0 0,-1-1 0 0 0,2 0 0 0 0,15-3-1 0 0,22 0 6 0 0,150-4-383 0 0,-55 20-4868 0 0,-140-11 4849 0 0,5 0-6156 0 0,-12-2 6455 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-5-3-513 0 0,1 0 0 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 1 1 0 0,1 0-1 0 0,-9-1 0 0 0,-16-5-1394 0 0,-35-14-1070 0 0,-70-13 0 0 0,98 28 2586 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2430.94">4092 1824 112 0 0,'-34'-4'183'0'0,"19"0"4236"0"0,2 0 10328 0 0,38-2-12319 0 0,38 2-367 0 0,0-3 1 0 0,95-22-1 0 0,-73 11-1113 0 0,458-69 1481 0 0,-304 51-2151 0 0,-69 8-172 0 0,363-38 82 0 0,-25 68-77 0 0,-198 3-34 0 0,-107-2-25 0 0,181-5 61 0 0,-351 0-104 0 0,94-4 44 0 0,168-30 0 0 0,-101 5-35 0 0,-61 12-11 0 0,-85 19 6 0 0,-46 0 41 0 0,-34 0-1171 0 0,-173 16-12958 0 0,201-15 13793 0 0,-6 0-770 0 0,2 0-1 0 0,-2-1 1 0 0,0 0-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 0-1 0 0,1-1 1 0 0,-16-5-1 0 0,21 6 648 0 0,-1-2 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,2 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-5-9 0 0 0,-4-4-336 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2832.87">7733 591 60 0 0,'0'0'13763'0'0,"9"5"-8432"0"0,12 4-1950 0 0,-14-6-2560 0 0,0 1 0 0 0,0 0-1 0 0,1 0 1 0 0,10 9 0 0 0,16 9 829 0 0,15 8-680 0 0,0 1 0 0 0,-3 3 0 0 0,60 56 0 0 0,-84-71-937 0 0,29 29 32 0 0,-3 2 1 0 0,55 71 0 0 0,-98-116-59 0 0,-1-1-1 0 0,-1 2 1 0 0,1-1 0 0 0,-1 0 0 0 0,1 1-1 0 0,-1 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,-1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 1 0 0 0,-2-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-7 8 0 0 0,-45 60 40 0 0,-116 118 0 0 0,99-118-124 0 0,10-8-994 0 0,-3-4-1 0 0,-94 72 0 0 0,128-111-87 0 0,-27 20-3028 0 0,53-40 3428 0 0,0 0 1 0 0,-1-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,2 0 0 0 0,-2-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-11 1 0 0 0,13-3 293 0 0,1 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1-1 0 0,-2-3 1 0 0,-30-53-3913 0 0,18 31 3007 0 0,4 3 400 0 0,-1-5 244 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5210.65">9322 93 376 0 0,'-7'-16'2460'0'0,"7"15"-2229"0"0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-2-1 0 0 0,1 0 386 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-2 2 0 0 0,1-1-180 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,2-1-1 0 0,-2 1 1 0 0,1-1 0 0 0,-2 5 0 0 0,-3 9-762 0 0,1 1-1 0 0,-7 34 1 0 0,9-32 1808 0 0,-11 53-1002 0 0,2 0 0 0 0,5 1 0 0 0,2-1-1 0 0,3 2 1 0 0,4-1 0 0 0,19 138 0 0 0,-13-169-384 0 0,-4-11-34 0 0,2-2 1 0 0,0 1 0 0 0,2 0-1 0 0,2 0 1 0 0,15 33-1 0 0,-19-53-62 0 0,-1-1 1 0 0,2 1-1 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 0 1 0 0,1-1-1 0 0,-1 0 0 0 0,2 0 0 0 0,-1-2 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 1 0 0,0-1-1 0 0,1 0 0 0 0,13 3 0 0 0,-6-1 0 0 0,-1-2 0 0 0,1 0 0 0 0,0-1 0 0 0,-1-1 0 0 0,1 0 0 0 0,1-2 0 0 0,-2 0 0 0 0,2-1 0 0 0,33-7 0 0 0,-28 2 0 0 0,1-1 0 0 0,-1-2 0 0 0,0 0 0 0 0,-1-1 0 0 0,0-1 0 0 0,33-23 0 0 0,-25 12 0 0 0,-1-1 0 0 0,-1-2 0 0 0,-2 0 0 0 0,0-2 0 0 0,-2-2 0 0 0,-1 0 0 0 0,0-1 0 0 0,-2-1 0 0 0,29-59 0 0 0,-25 31 0 0 0,-3-2 0 0 0,-2 0 0 0 0,19-99 0 0 0,-30 110 0 0 0,3-92 0 0 0,-5 43 0 0 0,-6 80 0 0 0,-1 1 0 0 0,-1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-2 0 0 0 0,-4-24 0 0 0,7 42 9 0 0,-1-3-134 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,-1 1 0 0 0,-2-6 0 0 0,2 8-122 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-2 2 0 0 0,-4 0-767 0 0,2 2 0 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,2 0 0 0 0,-1-1 0 0 0,-6 13 0 0 0,0 2-867 0 0,2 1 1 0 0,0 0-1 0 0,-10 35 1 0 0,17-7-106 0 0,1-29 1253 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5564.63">10844 199 32 0 0,'0'0'24220'0'0,"-6"13"-21739"0"0,-1 9-509 0 0,5-19-1819 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-2 4-1 0 0,0 9 171 0 0,-1 0 0 0 0,-1-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,-12 24 1 0 0,0 1 9 0 0,-77 169-228 0 0,52-120-109 0 0,-47 140 1 0 0,17-26-1068 0 0,70-192 277 0 0,-1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 1 0 0,-10 11-1 0 0,16-37-9969 0 0,9-60 5986 0 0,6 4 1838 0 0,4 1 1 0 0,50-119 0 0 0,-47 135 2299 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5831.9">10838 162 280 0 0,'10'-19'448'0'0,"12"-8"7803"0"0,-21 26-7884 0 0,0 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,0 1 0 0 0,17 27 2955 0 0,26 56 0 0 0,28 103-1592 0 0,-46-114-1743 0 0,0 9 13 0 0,-15-46 0 0 0,21 51 0 0 0,44 111 0 0 0,-56-147 0 0 0,25 60 0 0 0,-27-71 0 0 0,-1 0 0 0 0,20 81 0 0 0,-36-119-65 0 0,0-1 1 0 0,-1 0-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-2 1 0 0,-1 2-1 0 0,1-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,-1 5 0 0 0,2-7-136 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0-1 0 0,-1-1 1 0 0,0 0-1 0 0,-8-3-1158 0 0,-3 1-287 0 0,1-1 1 0 0,-1-1-1 0 0,2 0 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 1 0 0,-12-11-1 0 0,-14-16-2587 0 0,-55-66 1 0 0,67 69 3366 0 0,0 4 242 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6032.72">10715 722 152 0 0,'-25'-15'2758'0'0,"24"15"-2609"0"0,1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,0 1 1612 0 0,29-1 11189 0 0,48-5-9246 0 0,16 0-2843 0 0,-66 4-1251 0 0,-2 2 0 0 0,0 0 0 0 0,0 2 0 0 0,0 0 0 0 0,24 9-1 0 0,5 8-4203 0 0,-2 9-3303 0 0,-49-29 7482 0 0,1 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,3-1 0 0 0,1-1-55 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,-2-1-1 0 0,11-9 1 0 0,-2-4-88 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6313.92">11621 256 112 0 0,'9'-23'3292'0'0,"-9"21"-2956"0"0,0 1-1 0 0,0-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,1 0-1 0 0,-2 1 1 0 0,2-1-1 0 0,2 0 3550 0 0,2 7 857 0 0,-5-6-4516 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0 0 0 0 0,6 94 5008 0 0,-27 240-4092 0 0,6-158-1145 0 0,11-89 3 0 0,8 122 0 0 0,3-140 0 0 0,3 74-37 0 0,-6-120-252 0 0,-1-4-4577 0 0,-10-54-1950 0 0,-3-48 353 0 0,1 13 2853 0 0,-10-116-2759 0 0,8-12 2642 0 0,11 148 3213 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6683.33">11645 367 328 0 0,'1'-6'498'0'0,"0"0"1"0"0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,1 1-1 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,1 1 1 0 0,9-8-1 0 0,-9 8 80 0 0,-2 1 1 0 0,1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,-1 1-1 0 0,2 0 1 0 0,6 2-1 0 0,12 6 834 0 0,-17-7-1043 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 2 0 0 0,0-1 0 0 0,-1 1 0 0 0,7 6 0 0 0,10 11 596 0 0,10 12 679 0 0,46 56 1 0 0,-72-79-1510 0 0,2 0 1 0 0,-1 2-1 0 0,-1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,0 1 0 0 0,-1-1 1 0 0,-1 1-1 0 0,4 22 0 0 0,-7-22-130 0 0,0 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 1-1 0 0,-1-1 1 0 0,-1-1 0 0 0,0 1-1 0 0,-2-1 1 0 0,1 1-1 0 0,-2-1 1 0 0,1 0 0 0 0,-1 0-1 0 0,-16 23 1 0 0,12-22-46 0 0,-1 1-1 0 0,0-1 1 0 0,-2 0 0 0 0,0-1-1 0 0,0-1 1 0 0,-1 0 0 0 0,0 0 0 0 0,-1-2-1 0 0,0 0 1 0 0,-1-2 0 0 0,-17 9-1 0 0,21-12-32 0 0,-1-1 0 0 0,1 0-1 0 0,-2 0 1 0 0,2-2 0 0 0,-2 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,2-1 0 0 0,-2 0-1 0 0,-21-3 1 0 0,6 0-11 0 0,22 2 75 0 0,1 1 1 0 0,-1-1-1 0 0,-1 0 0 0 0,1-1 1 0 0,1 1-1 0 0,-10-5 1 0 0,5 4 227 0 0,13 10 338 0 0,19 12 29 0 0,-9-12-574 0 0,1 1 0 0 0,-1 1 0 0 0,-1-1 0 0 0,1 2 0 0 0,9 12 0 0 0,15 12-10 0 0,93 97-1 0 0,-48-46 0 0 0,-54-57-162 0 0,0-3 1 0 0,2 0-1 0 0,1-2 1 0 0,1-2-1 0 0,0 0 0 0 0,2-2 1 0 0,41 17-1 0 0,-41-29-2293 0 0,-33-8 2219 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1-1 0 0 0,7-159-14124 0 0,-7 133 13080 0 0,1 1 0 0 0,1-1 0 0 0,8-37 0 0 0,1 23 545 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6932.96">12631 193 332 0 0,'-1'2'568'0'0,"1"1"0"0"0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,-2 2-1 0 0,4-3-120 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,1 0-1 0 0,115-40 10206 0 0,5 0-8430 0 0,-108 36-2222 0 0,1 1 0 0 0,-2 0 0 0 0,2 1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 2 0 0 0,1-1 0 0 0,-1 2 0 0 0,1 0 0 0 0,22 9 0 0 0,34 18-3884 0 0,-70-30 3711 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,-10 16-13522 0 0,9-14 13517 0 0,-7 0-1589 0 0,-2 0 0 0 0,1 0 0 0 0,0-1 0 0 0,-14 1 0 0 0,-24 3-1870 0 0,35 1 3008 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7148.94">12852 306 172 0 0,'-32'43'2650'0'0,"24"-31"-885"0"0,-1-1 0 0 0,0 2 0 0 0,2-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-6 18 0 0 0,10-18-208 0 0,0-1 0 0 0,0 1 0 0 0,-1 18 0 0 0,4 76 2825 0 0,1-52-3023 0 0,14 171 1990 0 0,-5-117-2490 0 0,7 34-182 0 0,-1-20-1556 0 0,-12-41-2706 0 0,-4-80 2393 0 0,-18-41-11733 0 0,4-65 4908 0 0,8-53 3139 0 0,6 121 4375 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17987.54">9532 1768 44 0 0,'-14'-21'2070'0'0,"-4"-3"1715"0"0,11 7-900 0 0,6 12-1387 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 1 0 0,0-12-1 0 0,5 14-1174 0 0,0-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,1 2 0 0 0,-1-1 0 0 0,1 0 1 0 0,5-2-1 0 0,26-9 114 0 0,1 2 0 0 0,0 1 0 0 0,41-6-1 0 0,-62 14-349 0 0,-1 1 0 0 0,1 1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 2 1 0 0,0 0 0 0 0,-1 1-1 0 0,1 1 1 0 0,18 6 0 0 0,56 35 264 0 0,-81-39-286 0 0,-1-1 0 0 0,1 1-1 0 0,-2 1 1 0 0,1-1 0 0 0,-1 1 0 0 0,0 1 0 0 0,12 14-1 0 0,-17-18 3 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-3 7-1 0 0,-2 3 125 0 0,-2 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-15 18 1 0 0,-2 5-75 0 0,4-9-11 0 0,-1 0 0 0 0,-45 45 0 0 0,18-21-50 0 0,10-13-39 0 0,-2-3-1 0 0,-1 0 1 0 0,-2-3-1 0 0,-79 48 1 0 0,101-71-339 0 0,1-1 0 0 0,-1 0 1 0 0,0-2-1 0 0,-2-1 0 0 0,2 0 0 0 0,-29 3 1 0 0,43-9-235 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,-12-2 0 0 0,18 1 272 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,2 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,2 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-2-4 0 0 0,-2-28-1265 0 0,1 1 1 0 0,2-1-1 0 0,2 0 0 0 0,7-57 1 0 0,-4 38 683 0 0,34-246 1982 0 0,-27 230 8427 0 0,-9 72-9317 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1 1 1 0 0,-2 4 0 0 0,2-3 140 0 0,3 50 959 0 0,-1 1 0 0 0,-2 1 0 0 0,-9 82 0 0 0,1-47-399 0 0,-30 486 1882 0 0,32-503-2771 0 0,3-17-450 0 0,-3-1 0 0 0,-16 78 0 0 0,14-113-2293 0 0,3-35-6272 0 0,6-15 6988 0 0,2-1 1 0 0,1 1-1 0 0,1 0 1 0 0,15-41-1 0 0,-8 23 538 0 0,-3 13 542 0 0,3 0-1 0 0,1 1 1 0 0,27-50-1 0 0,-16 38 387 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="18356.22">10709 1886 76 0 0,'9'-13'3436'0'0,"-16"-11"23188"0"0,0 24-23148 0 0,0 1-3499 0 0,-1 4-3462 0 0,-34 15 5096 0 0,-8 5-1106 0 0,5 5-347 0 0,20-13-89 0 0,-35 28 0 0 0,13-4 7 0 0,22-20-47 0 0,1-1 0 0 0,1 2 0 0 0,1 2 1 0 0,1 0-1 0 0,-25 36 0 0 0,42-54-29 0 0,-29 45 0 0 0,4 2 0 0 0,0 1 0 0 0,3 1 0 0 0,-20 61 0 0 0,37-85 0 0 0,1-1 0 0 0,1 1 0 0 0,1 1 0 0 0,2 0 0 0 0,1-1 0 0 0,1 43 0 0 0,2-64 0 0 0,1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,2-1 0 0 0,0 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-2 0 0 0,1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,14 7 0 0 0,0-4 26 0 0,0 0 0 0 0,1-1 1 0 0,0-1-1 0 0,0-2 0 0 0,0 0 0 0 0,1-1 0 0 0,33-2 1 0 0,-25-1-585 0 0,-1-3 0 0 0,1-1 0 0 0,0-1 0 0 0,-1-1 0 0 0,32-12 0 0 0,-5-3-3224 0 0,30-19-6292 0 0,-73 31 8201 0 0,0 0-1 0 0,-1-1 0 0 0,1 0 0 0 0,-2-2 1 0 0,1 1-1 0 0,-2-2 0 0 0,13-14 0 0 0,-12 9 1171 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="19806.5">11805 1606 512 0 0,'-12'0'16964'0'0,"27"4"-12821"0"0,73 16-3567 0 0,-39-15-172 0 0,0-3 1 0 0,59-5 0 0 0,-11 0-34 0 0,-91 3-355 0 0,2-1-1 0 0,-1 2 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,9 7-1 0 0,-13-9-10 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,-1-1-1 0 0,2 1 1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0-1 0 0,-1-1 1 0 0,2 0 0 0 0,-3 4 0 0 0,-6 8 10 0 0,0 0-1 0 0,1-1 1 0 0,-16 17 0 0 0,21-27-11 0 0,-10 11-3 0 0,-1 1 1 0 0,0-2-1 0 0,-1 1 1 0 0,0-2 0 0 0,-2 0-1 0 0,1-1 1 0 0,0-1-1 0 0,-2-1 1 0 0,1 0 0 0 0,-32 9-1 0 0,17-9-5 0 0,-1 0-1 0 0,0-2 0 0 0,-1-2 0 0 0,1-1 1 0 0,-47-1-1 0 0,70-5 40 0 0,21-2 37 0 0,26-3 24 0 0,209-5 350 0 0,-68 24-894 0 0,-165-8-1928 0 0,-18 4 329 0 0,-23 10-1288 0 0,23-15 2544 0 0,-22 11-2147 0 0,0-1 0 0 0,-57 18-1 0 0,5-3-336 0 0,-49 16-73 0 0,98-32 2915 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="19983.32">11614 2353 252 0 0,'0'21'1169'0'0,"-1"-19"-885"0"0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 2 0 0 0,7 12 1451 0 0,0 1 1 0 0,-1 0-1 0 0,-2 1 0 0 0,0 0 0 0 0,5 22 1 0 0,9 25-96 0 0,-15-47-1341 0 0,-1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,-3 1-1 0 0,1 28 1 0 0,2 20 93 0 0,2 22-38 0 0,-2-28-1756 0 0,1-18-2752 0 0,-21-63 86 0 0,-1-80-1674 0 0,15 77 4964 0 0,0 0 0 0 0,2 0-1 0 0,1 0 1 0 0,5-39 0 0 0,9-32-683 0 0,-4 44 930 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="20310.93">11867 2192 128 0 0,'4'-5'477'0'0,"1"1"1"0"0,0 0-1 0 0,-1 0 0 0 0,2 0 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,1-1 1 0 0,-2 1-1 0 0,2 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,8 3 0 0 0,79 13 6403 0 0,17 5-2217 0 0,-83-17-3424 0 0,1-1 0 0 0,0-1 0 0 0,1-1 0 0 0,45-4 0 0 0,-21 1 388 0 0,-29 2-1185 0 0,-15 0-313 0 0,-1-1 0 0 0,1 0 1 0 0,0-1-1 0 0,-2 0 0 0 0,19-4 0 0 0,-25 5-127 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 3 0 0 0,-2 55 79 0 0,-15 95-1 0 0,2-39-64 0 0,2-29-37 0 0,8-51-72 0 0,0 2-1 0 0,2 38 0 0 0,-9 35-1652 0 0,13-110 1588 0 0,0-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,-23-4-5405 0 0,-30-28-2792 0 0,44 26 7461 0 0,1-2-205 0 0,-2 0 1 0 0,1-1-1 0 0,2 0 0 0 0,-12-13 0 0 0,-3-2-360 0 0,-33-32-967 0 0,33 37 1947 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="20533.89">11829 2428 280 0 0,'-64'3'17185'0'0,"119"12"-14262"0"0,53-4 1011 0 0,194-3-1 0 0,-223-8-3563 0 0,-53-2 492 0 0,-8-2-3910 0 0,-18 4 2966 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-26-2-4069 0 0,-25 2-438 0 0,-57 0-2144 0 0,83 1 5635 0 0,-1 2 0 0 0,0 0 0 0 0,2 1 0 0 0,-35 11 0 0 0,34-3 564 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="20720.95">11805 2608 244 0 0,'-1'0'344'0'0,"0"1"1"0"0,-1-1-1 0 0,1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 3-1 0 0,0-3 7 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,0 1 0 0 0,2-1 1 0 0,16 7 2096 0 0,-2-2 0 0 0,28 5 0 0 0,-30-7-2453 0 0,320 40 6710 0 0,-284-38-6246 0 0,-44-4-427 0 0,28 3-200 0 0,1-1 1 0 0,0-2-1 0 0,0-2 0 0 0,50-7 0 0 0,-84 8 32 0 0,0-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0-3 0 0 0,0 1-288 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0-4-1 0 0,-4-5-979 0 0,0-1 0 0 0,-1 1 0 0 0,-1-1 0 0 0,1 3 0 0 0,-12-17 0 0 0,-59-75-5563 0 0,-45-44 1730 0 0,99 122 4725 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="20891.64">12175 2061 492 0 0,'2'4'402'0'0,"1"-1"-1"0"0,-1 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 6 0 0 0,2 56 3457 0 0,-3-64-3759 0 0,-3 169 6901 0 0,5 160-2552 0 0,3-212-3999 0 0,-4-56-821 0 0,18 123-1 0 0,-15-162-836 0 0,-2 1 0 0 0,-1 42 1 0 0,-1-42-2008 0 0,-26-36-1235 0 0,22 6 3993 0 0,0 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,-2-7 0 0 0,-15-20-956 0 0,7 11 649 0 0,0 1-1 0 0,1-2 1 0 0,-14-38 0 0 0,11 27 219 0 0,-4-15-70 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="21083.38">11504 1730 76 0 0,'-30'-24'3869'0'0,"29"23"-2980"0"0,-11 21 5217 0 0,31 15-4938 0 0,4 3-1263 0 0,-21-34-147 0 0,1-1 1 0 0,1 0-1 0 0,-1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 9 0 0 0,-3-3-582 0 0,0 0 0 0 0,1-1 0 0 0,-2 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,0-2 0 0 0,-6 11-1 0 0,5-7 320 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="21629.62">11405 2135 136 0 0,'-15'11'866'0'0,"14"-9"-687"0"0,1-1 1 0 0,-2 0 0 0 0,1 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,1-1-1 0 0,-3 1 1 0 0,3 0-12 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1 1 0 0 0,-1 46 1141 0 0,1-36-1168 0 0,0 1-45 0 0,-1-10-90 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,-3 5-1 0 0,1 2 26 0 0,0-1 1 0 0,1 1-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,1 1-1 0 0,0-1 0 0 0,0 0 0 0 0,1 1 1 0 0,1-1-1 0 0,0 0 0 0 0,0-1 0 0 0,1 1 1 0 0,0 0-1 0 0,1-1 0 0 0,1 1 0 0 0,-2-1 1 0 0,3 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,1-1 0 0 0,14 13 0 0 0,32 41 1144 0 0,-52-61-1086 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,0 0 0 0 0,-2 2 0 0 0,-16 42 880 0 0,6-20-399 0 0,4-5-209 0 0,-2 0 0 0 0,-20 32 1 0 0,10-19-159 0 0,5-7-195 0 0,0-2 0 0 0,-2-1 0 0 0,-1 0 0 0 0,0-1 1 0 0,-2-1-1 0 0,-1 0 0 0 0,0-2 0 0 0,-1-1 0 0 0,-36 24 1 0 0,53-40-96 0 0,0 0 1 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,2 0 0 0 0,-1 0-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-6-2-1 0 0,9 1 41 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,1-3-1 0 0,0-6 97 0 0,0 1 0 0 0,1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0 0 0 0 0,1 0 0 0 0,1 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,11-6 0 0 0,-10 10 212 0 0,-2 0 0 0 0,2 1-1 0 0,-1-1 1 0 0,1 2 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0-1 0 0,-1 1 1 0 0,0 0 0 0 0,1 0 0 0 0,0 1 0 0 0,-1 0-1 0 0,9 2 1 0 0,5 1 555 0 0,0 2-1 0 0,0 0 0 0 0,31 14 1 0 0,100 46 2943 0 0,152 91 897 0 0,-176-93-3856 0 0,255 90 0 0 0,-110-73-684 0 0,-256-77-112 0 0,187 34-687 0 0,-158-32-289 0 0,-37-6 166 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0-1 1 0 0,-1 1-1 0 0,1-2 0 0 0,0 1 1 0 0,0-1-1 0 0,-2 0 0 0 0,2-1 0 0 0,-1 0 1 0 0,14-10-1 0 0,-9 3-1088 0 0,0-1 1 0 0,-1 0-1 0 0,-1-2 0 0 0,1 0 1 0 0,9-16-1 0 0,43-81-3843 0 0,-25 39 3474 0 0,-16 32 1682 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="22622.96">13709 1551 56 0 0,'1'0'173'0'0,"0"0"0"0"0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,1 34 5380 0 0,-4-19-2489 0 0,-1-1 0 0 0,-9 28 0 0 0,3-20-1178 0 0,-1 0 1 0 0,-13 25 0 0 0,-62 86 1255 0 0,22-36-2456 0 0,-50 71-442 0 0,42-66-399 0 0,28-47-852 0 0,-1-2 1 0 0,-74 70-1 0 0,95-103-211 0 0,0-2 0 0 0,-27 17 0 0 0,-20 6-4583 0 0,70-43 5591 0 0,-1 0-1 0 0,1 1 1 0 0,0-1 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1-1-1 0 0,0 0 1 0 0,0-23-3301 0 0,14-23 1382 0 0,-9 36 1742 0 0,2 0 0 0 0,0-1 0 0 0,1 2 1 0 0,-1-1-1 0 0,2 1 0 0 0,0 0 0 0 0,16-16 0 0 0,6-3-91 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="22803.66">13351 2210 156 0 0,'20'-9'278'0'0,"-12"6"118"0"0,2-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,17-3 0 0 0,-23 6-218 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,3 4 0 0 0,2 2 481 0 0,-1 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,-1 1 0 0 0,0-1 1 0 0,4 17-1 0 0,2 4 790 0 0,-1 2 0 0 0,-2-1 0 0 0,-2 1 0 0 0,4 62 0 0 0,-14 129 1603 0 0,-49 201-1304 0 0,47-393-1858 0 0,0-1 0 0 0,-14 32 0 0 0,7-19-456 0 0,12-37 337 0 0,-1 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,-4 5 0 0 0,-11 0-1847 0 0,19-10 1951 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,-5-21-1117 0 0,2 0 1 0 0,0 0-1 0 0,2 0 0 0 0,0-1 0 0 0,2 0 1 0 0,0 2-1 0 0,6-30 0 0 0,42-158-2048 0 0,-32 151 2452 0 0,33-114-560 0 0,-20 85 934 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="22964.52">14282 1569 92 0 0,'9'-3'230'0'0,"-1"0"374"0"0,-2 1 0 0 0,2 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,10 0-1 0 0,-15 2-310 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,-1 0 1 0 0,2 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 1 0 0 0,0 4 1 0 0,41 47 6602 0 0,8 13-3370 0 0,-48-61-3445 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-2 0 0 0 0,0 6 0 0 0,2 6-356 0 0,-3 10-1056 0 0,0-22 776 0 0,-1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,-1 1 0 0 0,2-1 0 0 0,-2-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,-10 3 0 0 0,-13 5-1906 0 0,0-2 1 0 0,-53 10 0 0 0,46-11 1213 0 0,11-3 573 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="23199.12">13998 2005 320 0 0,'-7'22'2066'0'0,"-2"9"4216"0"0,9-30-6110 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,2 0 0 0 0,49 3 5777 0 0,8 0-3136 0 0,194-14 2573 0 0,-89-1-3929 0 0,-98 6-1247 0 0,147-20-41 0 0,-158 13-2466 0 0,-94 7-3203 0 0,5 7 1564 0 0,-1 2 0 0 0,-36 7 0 0 0,-72 23-3003 0 0,76-17 4732 0 0,-55 20-420 0 0,84-24 2090 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="23564.28">13961 2272 292 0 0,'0'1'162'0'0,"-1"-1"-1"0"0,0 1 1 0 0,1 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 1 1 0 0,1 0 379 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,4 1-1 0 0,5 1 734 0 0,0 1-1 0 0,-1-1 1 0 0,2-1 0 0 0,18 5-1 0 0,25-3 730 0 0,0-2-1 0 0,78-7 1 0 0,-54-4-1150 0 0,0-3 1 0 0,123-35 0 0 0,-186 42-898 0 0,-11 3-67 0 0,-2 0 1 0 0,2 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 0 1 0 0,6-4-1 0 0,-10 5-266 0 0,-2 0-977 0 0,0 0 1231 0 0,0 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,-25 2-1442 0 0,-42 12-3297 0 0,-76 26 0 0 0,-64 33 1130 0 0,202-70 3683 0 0,-16 6 153 0 0,-1 1 1 0 0,-27 19 0 0 0,41-24 303 0 0,1 1 0 0 0,-1 0 1 0 0,1 1-1 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 1 0 0,-8 13-1 0 0,16-20-196 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 1 0 0 0,2 1 133 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,6 3 0 0 0,6 2 644 0 0,0-1-1 0 0,2-1 1 0 0,-1-1-1 0 0,26 4 1 0 0,12-5 644 0 0,-1-1 0 0 0,61-7-1 0 0,11-1-261 0 0,-8 11-1736 0 0,-106-4-3563 0 0,-78-3-11364 0 0,40 0 13398 0 0,1 1 1 0 0,0 1-1 0 0,-37 6 1 0 0,41-3 1272 0 0,4 0 131 0 0,-1 1 1 0 0,1 0-1 0 0,-20 8 0 0 0,0 6-19 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="23719.83">13998 2994 628 0 0,'0'19'1890'0'0,"1"1"0"0"0,1-1 1 0 0,7 35-1 0 0,4 10 1181 0 0,-10-43-1437 0 0,2-2 0 0 0,0 1 0 0 0,1 0 0 0 0,12 30 0 0 0,-17-48-1773 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 1 0 0,4 2-1 0 0,-5-3 5 0 0,1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1-1 0 0,2-1 1 0 0,4-6-697 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1-1-1 0 0,0 1 1 0 0,5-19 0 0 0,9-13-931 0 0,-7 14 73 0 0,14-48 0 0 0,-16 45 333 0 0,20-46-1 0 0,-17 53 922 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="24041.48">14312 2888 160 0 0,'5'-3'768'0'0,"0"-1"0"0"0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 1 0 0,0 0-1 0 0,-1-1 0 0 0,0 2 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,8 0 0 0 0,15-1 4255 0 0,46 4 1 0 0,-23 0-3514 0 0,-43-2-1174 0 0,0 0-1 0 0,0 1 0 0 0,1 0 1 0 0,-2 1-1 0 0,1-1 1 0 0,1 2-1 0 0,-1-1 1 0 0,-1 2-1 0 0,0-1 1 0 0,1 1-1 0 0,12 8 1 0 0,-17-9-273 0 0,0 0-1 0 0,-1 0 1 0 0,-1 0 0 0 0,2 0 0 0 0,-1 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,0-1 0 0 0,-1 2-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-2 1 0 0 0,1-1 0 0 0,0 1-1 0 0,-1 6 1 0 0,-3 8-58 0 0,-1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,-1-1 0 0 0,0 1-1 0 0,-2-1 1 0 0,0 0 0 0 0,0 0 0 0 0,-2-1 0 0 0,0-1 0 0 0,-1 0 0 0 0,0-1-1 0 0,-24 22 1 0 0,24-24-21 0 0,-2 0-1 0 0,1 0 1 0 0,-2-1 0 0 0,1-1-1 0 0,-2-1 1 0 0,1-1-1 0 0,-2 0 1 0 0,1 0-1 0 0,-1-2 1 0 0,1 0 0 0 0,-1-1-1 0 0,0-1 1 0 0,0 0-1 0 0,-2-1 1 0 0,2-1-1 0 0,0-1 1 0 0,-1-1 0 0 0,-32-3-1 0 0,20 0 230 0 0,19 2-53 0 0,1 0 0 0 0,0 0 0 0 0,-1-1-1 0 0,-10-4 1 0 0,-40-13 3347 0 0,124 16-3507 0 0,-1-4 1 0 0,65-14-1 0 0,13-3 41 0 0,48-12 9 0 0,-146 27-47 0 0,177-29-866 0 0,-203 36 3256 0 0,2-3-4200 0 0,17-2-10195 0 0,-51 21 2476 0 0,12-12 9102 0 0,1 0 0 0 0,-1-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0-1 0 0 0,-1 1 0 0 0,2 0 0 0 0,-9-3 0 0 0,-58-20-2525 0 0,52 15 2432 0 0,-25-9-234 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink16.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-07-18T14:18:21.188"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">4704 1196 476 0 0,'0'-2'835'0'0,"0"-1"1"0"0,-1 1-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,-3-1 0 0 0,-39-30 3780 0 0,22 18-3651 0 0,-74-59 1103 0 0,-126-73 1 0 0,151 109-1778 0 0,-1 3-1 0 0,-2 4 1 0 0,-121-36 0 0 0,108 43-12 0 0,-167-51 508 0 0,184 51-474 0 0,-103-51 1 0 0,85 30-123 0 0,-38-21 75 0 0,-165-61 0 0 0,-190-1-276 0 0,382 106 16 0 0,-345-86-29 0 0,405 100 20 0 0,0 1 0 0 0,0 2 0 0 0,-1 2 0 0 0,0 1-1 0 0,1 2 1 0 0,-1 2 0 0 0,-41 8 0 0 0,-11 8-24 0 0,-107 36 0 0 0,168-43 12 0 0,0 2 0 0 0,0 0 0 0 0,2 2 0 0 0,-49 33-1 0 0,26-10-9 0 0,-71 65-1 0 0,-109 150-62 0 0,220-239 89 0 0,-12 17 3 0 0,0 1 0 0 0,-36 68 1 0 0,-20 80-30 0 0,63-135 10 0 0,-106 257-44 0 0,78-205 3 0 0,4 2-1 0 0,-28 109 1 0 0,60-157 20 0 0,2 0 0 0 0,2 1 0 0 0,4 89 0 0 0,1-85 29 0 0,8 246 15 0 0,-7-234-17 0 0,2-1 1 0 0,4 1-1 0 0,2-2 0 0 0,4 1 1 0 0,2-1-1 0 0,45 116 0 0 0,95 140-22 0 0,-119-262 39 0 0,3-2 0 0 0,2-1 0 0 0,87 91 0 0 0,-62-86 7 0 0,3-3-1 0 0,99 66 0 0 0,-151-113-9 0 0,63 41 38 0 0,139 72 0 0 0,237 60 25 0 0,-203-90-45 0 0,-110-38-3 0 0,122 49 42 0 0,-139-54-22 0 0,3-6-1 0 0,145 31 1 0 0,-189-53 16 0 0,-2 5 1 0 0,122 58 0 0 0,-61-23 40 0 0,-51-27 25 0 0,2-4 1 0 0,0-4-1 0 0,2-4 1 0 0,1-4-1 0 0,135 11 1 0 0,167 2 161 0 0,-370-31-261 0 0,75 6 100 0 0,109-5-1 0 0,-155-9-77 0 0,0-1-1 0 0,-1-4 0 0 0,0-1 0 0 0,72-25 0 0 0,-94 24-30 0 0,-1-2-1 0 0,-1-1 1 0 0,37-22-1 0 0,-50 24 2 0 0,0-2-1 0 0,0 0 1 0 0,-2-1-1 0 0,0-1 1 0 0,26-29-1 0 0,-12 4-4 0 0,-2-1-1 0 0,-2-1 1 0 0,30-61 0 0 0,56-151 21 0 0,-6-50-7 0 0,-48 125-14 0 0,-5 43-2 0 0,6-21 10 0 0,-43 95 0 0 0,-2-1 0 0 0,13-116 1 0 0,-14 64-16 0 0,-5 48 11 0 0,2-98 1 0 0,-15 116 16 0 0,-15-95-1 0 0,-25-48 83 0 0,30 149 15 0 0,-3 0 1 0 0,-2 1 0 0 0,-25-48-1 0 0,-174-362 327 0 0,191 402-177 0 0,-52-77-1 0 0,-18-34-81 0 0,70 108-174 0 0,-3 3 0 0 0,-36-52 0 0 0,15 22 46 0 0,6 8 3 0 0,-29-45 107 0 0,57 95-52 0 0,-1 0 0 0 0,-1 1 0 0 0,-1 1 0 0 0,-1 1 0 0 0,-1 0 0 0 0,-42-33 0 0 0,16 22-125 0 0,-71-45 0 0 0,102 68 0 0 0,-2 1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 1 0 0 0,-32-6 0 0 0,-227-58-1709 0 0,254 64 105 0 0,-1 1 1 0 0,0 1 0 0 0,-30-2 0 0 0,14 5-4431 0 0,-46 4 1 0 0,74-2 5051 0 0,0-1 1 0 0,0 0 0 0 0,0-1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 0 0 0 0,-15-6-1 0 0,11 2 252 0 0,0 0 1 0 0,0-1-1 0 0,1-1 0 0 0,-21-14 0 0 0,2-1 8 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
 <file path=xl/ink/ink17.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-07-18T14:18:21.999"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">151 884 512 0 0,'1'-1'302'0'0,"-1"0"-1"0"0,1 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,2 0 1 0 0,-3 0-30 0 0,1 1 1 0 0,0-1-1 0 0,-1 0 0 0 0,1 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-1 1-1 0 0,2 6 1120 0 0,0 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,0 9 1 0 0,0-7-1629 0 0,1 43 1161 0 0,-3 0-1 0 0,-13 104 1 0 0,-42 105-1560 0 0,54-255 526 0 0,-5 22-992 0 0,-1-1 0 0 0,-2 0 0 0 0,0 0 0 0 0,-18 31 0 0 0,27-59 927 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,-2 0-1 0 0,2-1 33 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,0-1 1 0 0,-2-4-501 0 0,1 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1-1 0 0,-1-12 1 0 0,0-5-80 0 0,0-1 1 0 0,2 1-1 0 0,1-1 1 0 0,1 0-1 0 0,6-29 1 0 0,0 11 199 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="405.34">318 599 36 0 0,'13'-27'500'0'0,"-2"4"1198"0"0,1 1 0 0 0,18-28-1 0 0,-26 44-778 0 0,1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,10-4 1 0 0,-7 6-366 0 0,0-1 1 0 0,1 1 0 0 0,-1 0 0 0 0,0 1 0 0 0,0 0-1 0 0,18 3 1 0 0,11-1 281 0 0,50-2 408 0 0,131 16-1 0 0,-187-10-1141 0 0,0 1 0 0 0,-1 1 0 0 0,32 13 0 0 0,-57-18-27 0 0,0 0-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,2 10 1 0 0,2 11 152 0 0,-1 0 1 0 0,-1 1 0 0 0,0 36-1 0 0,-4-65-224 0 0,-1 155 318 0 0,-32 245 1 0 0,-48 144-260 0 0,53-368-52 0 0,25-159-67 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,-12 26-1 0 0,16-43 15 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,0 0-72 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0-1-1 0 0,1 1 0 0 0,-4-2 0 0 0,-2-4-527 0 0,0 1 1 0 0,0-2-1 0 0,0 1 0 0 0,-6-10 1 0 0,-8-16-2931 0 0,1 0 0 0 0,-25-60 0 0 0,-18-77-4100 0 0,28 50 4859 0 0,25 78 2155 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="607.2">734 581 60 0 0,'1'-4'435'0'0,"0"-1"1"0"0,-1 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,-1-8 2301 0 0,-17 28 3397 0 0,-24 73-2053 0 0,1-3-4250 0 0,20-46-502 0 0,-16 24-2101 0 0,7-25-2579 0 0,27-57-902 0 0,4 16 6157 0 0,0 1 1 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,1-1 1 0 0,5-12-318 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="995.32">616 672 396 0 0,'2'-5'325'0'0,"-1"1"-1"0"0,1-1 1 0 0,0 0-1 0 0,1 1 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,7-5-1 0 0,-8 7 27 0 0,1 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,4 1 0 0 0,-2 0 75 0 0,0 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 1 0 0 0,4 3-1 0 0,-7-5-286 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-2 4-1 0 0,-5 9 200 0 0,-1 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,-14 18 1 0 0,-50 54 5 0 0,52-62-243 0 0,9-12-176 0 0,0-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,-1-2-1 0 0,0 0 0 0 0,-1 0 1 0 0,-19 9-1 0 0,27-15-134 0 0,0-1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 0-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,1 0 0 0 0,-9-3-1 0 0,13 4 18 0 0,0-1 0 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,-2-5-1 0 0,1 3-42 0 0,1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,3-9 0 0 0,0 0 28 0 0,2 1 0 0 0,-1 0 0 0 0,2 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 1-1 0 0,10-13 0 0 0,-13 20 324 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,0 0 0 0 0,11-7-1 0 0,-13 10 67 0 0,1-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,5 2 0 0 0,-2 0 253 0 0,1 0 0 0 0,-1 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1 1 0 0 0,11 9 0 0 0,4 6 813 0 0,22 28 1 0 0,-31-34-877 0 0,120 160 1916 0 0,-55-49-5027 0 0,-77-124 2462 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,-1 1 1 0 0,0-1-264 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,-3-1-1 0 0,-17 0-688 0 0,-4-3-505 0 0,13 1 1064 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1146.47">567 1203 184 0 0,'-5'6'4437'0'0,"2"3"-2279"0"0,0 2 10685 0 0,4-10-12783 0 0,-1 0-1 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 2 0 0 0,1 2-298 0 0,0 1-506 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-2 8 0 0 0,2-11 137 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-5 1 0 0 0,1-1 48 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1312.99">425 1428 16 0 0,'1'0'494'0'0,"-1"1"0"0"0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,2 0 0 0 0,22 7 6905 0 0,-11-4-8569 0 0,-8-1 2038 0 0,6 1-1470 0 0,-2 3-4827 0 0,-9-5 5162 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-32 19-3452 0 0,23-14 3131 0 0,0 0 84 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1504.32">130 1587 280 0 0,'-15'4'2189'0'0,"13"-4"-1732"0"0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,1 1 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 0 0 0,1 8 8297 0 0,11-4-5715 0 0,18 4-3636 0 0,-20-6 1439 0 0,91 29-14 0 0,45 16-1284 0 0,-50-14-3202 0 0,-84-30 2845 0 0,0 0 0 0 0,1-1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-2 0 0 0,0 0 0 0 0,15-9 0 0 0,29-21-1359 0 0,-24 15 1432 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2217.89">1978 492 436 0 0,'3'-2'358'0'0,"0"0"0"0"0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 2 0 0 0,1-1 1 0 0,4 0-1 0 0,-8 1-171 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,-1 0 173 0 0,1 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,0 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,0 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,-1 1 0 0 0,1 2-1 0 0,-2 3 543 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,-4 6 0 0 0,-27 50 1046 0 0,13-29-1342 0 0,-35 61-375 0 0,-94 123 1 0 0,136-199-442 0 0,-120 152-3036 0 0,103-136 339 0 0,-39 33-1 0 0,66-66 2460 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,-3 1 0 0 0,6-4 273 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,1 0 0 0 0,0 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,1-5-153 0 0,1 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,7-10 1 0 0,-2 2-64 0 0,114-163 135 0 0,-115 168 639 0 0,-3 1 225 0 0,1 1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,10-5 1 0 0,-16 11-505 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,8 15 1977 0 0,0 19 313 0 0,-4 13-864 0 0,-3 1 1 0 0,-4 69-1 0 0,-20 100-708 0 0,12-142-685 0 0,-14 66-1021 0 0,3-25-2369 0 0,20-112 3042 0 0,1 0-411 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-3 6-1 0 0,4-10-702 0 0,-11-35-5282 0 0,12 30 6422 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,2-5 0 0 0,1-5-155 0 0,1-10-105 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2640.22">2276 607 176 0 0,'-12'23'3268'0'0,"3"-10"3497"0"0,28-10-1255 0 0,-18-4-5448 0 0,167-18 4853 0 0,2 10-6286 0 0,-144 14-445 0 0,-20-2-5551 0 0,-7-2 7098 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-3 0 0 0 0,-23 10-2316 0 0,13-6 1177 0 0,7-4 867 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2875.27">2566 291 144 0 0,'0'-1'144'0'0,"1"1"1"0"0,-1 0-1 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 0 0 0,-5 19 3696 0 0,0 30-939 0 0,-10 92-542 0 0,-25 70-3056 0 0,31-169-919 0 0,-1 0-1 0 0,-21 45 1 0 0,21-61 37 0 0,-2-1 1 0 0,0 0-1 0 0,-2-1 1 0 0,-24 29-1 0 0,-31 29-1929 0 0,59-67 3095 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3472.49">2138 973 52 0 0,'-11'18'1084'0'0,"9"-15"-601"0"0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,-1 6 0 0 0,-2 0 1332 0 0,3-5 2883 0 0,13-4-2146 0 0,7-3-1942 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,0-1 0 0 0,19-8 0 0 0,-2 1-167 0 0,123-33 187 0 0,-127 38-1355 0 0,0 2 0 0 0,1 1 0 0 0,36 0 0 0 0,-68 4 697 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,-7 11-94 0 0,-254 187-270 0 0,180-139 453 0 0,-86 53 699 0 0,138-97-455 0 0,10-4 139 0 0,17-9 1 0 0,10-4 218 0 0,34-9-401 0 0,0 2 0 0 0,67-7 0 0 0,0 0 86 0 0,-92 14-299 0 0,1-1 0 0 0,0 2 0 0 0,0 0 0 0 0,0 1 0 0 0,32 5 0 0 0,-48-5-45 0 0,0 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 1 0 0 0,-1-1-3 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-2 1-1 0 0,-4 7-31 0 0,0-1-1 0 0,-1-1 1 0 0,-12 11-1 0 0,13-12-20 0 0,-30 30-309 0 0,-1-3 0 0 0,-44 32 0 0 0,66-54 346 0 0,-1-1-1 0 0,0-1 0 0 0,0-1 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 0 1 0 0,-1-2-1 0 0,1 0 0 0 0,-20 3 1 0 0,16-7 616 0 0,16-2 245 0 0,15-1-337 0 0,3 2-326 0 0,0 0-1 0 0,0 1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,13 5 1 0 0,-3-2 5 0 0,6 3-136 0 0,-1 1-1 0 0,0 2 1 0 0,44 23-1 0 0,34 13-3875 0 0,-100-45 3341 0 0,0 0 1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,8-5 0 0 0,-1-1-628 0 0,0-1-1 0 0,0 0 1 0 0,-1-1 0 0 0,0-1-1 0 0,11-13 1 0 0,-9 9 570 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5012.21">3233 411 92 0 0,'0'-1'156'0'0,"-1"0"-1"0"0,0 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 0-1 0 0,0 1 1 0 0,0-1-1 0 0,1 0 1 0 0,-1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,1 0 1 0 0,-1 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,0 2 407 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-1 4 1 0 0,0 9 65 0 0,1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,6 25 1 0 0,-2-12-515 0 0,-1 2-276 0 0,-2-9-1215 0 0,9 35 0 0 0,-7-81-10361 0 0,6-33 9923 0 0,-7 39 1367 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5395.69">3340 332 96 0 0,'6'-13'467'0'0,"-5"10"53"0"0,0 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,4-1 0 0 0,9-1 1595 0 0,27-6 1224 0 0,55-5-1457 0 0,-78 13-1632 0 0,137-16 884 0 0,-151 16-1119 0 0,40-5 79 0 0,-43 6-97 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,2 2 1 0 0,-3-2-20 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,-1 1-1 0 0,-15 30-350 0 0,11-23 213 0 0,-24 42-385 0 0,-2-2-1 0 0,-3-1 1 0 0,-1-1-1 0 0,-3-3 0 0 0,-2-1 1 0 0,-67 57-1 0 0,83-81 529 0 0,0-1 0 0 0,-33 17 0 0 0,44-28 219 0 0,0-1 0 0 0,0 0 0 0 0,-1-1 1 0 0,0-1-1 0 0,0-1 0 0 0,-20 4 0 0 0,14-7 1154 0 0,22-5-123 0 0,9-5-682 0 0,-2 4-431 0 0,0 0 1 0 0,1 0-1 0 0,0 1 0 0 0,-1 1 0 0 0,12-4 1 0 0,9-3 44 0 0,69-28 382 0 0,-17 8-1435 0 0,-28 6-3184 0 0,-59 24-973 0 0,-1 1 3989 0 0,1 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,-10 6 1 0 0,-4 4-68 0 0,-22 17-1 0 0,20-13 230 0 0,-1 0 466 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5559.55">2948 1127 448 0 0,'-5'13'7332'0'0,"24"-16"3233"0"0,-10 2-9462 0 0,0 0-3705 0 0,4 1 2444 0 0,-7 1-552 0 0,1-1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0-1 0 0 0,8-3 0 0 0,8-7-1976 0 0,-11 6 1081 0 0,0 0 1 0 0,21-8-1 0 0,-20 10 1092 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5929.38">3272 1028 436 0 0,'14'-9'2595'0'0,"0"1"-1"0"0,0 1 1 0 0,27-10 0 0 0,-19 10-495 0 0,-1 1 1 0 0,26-3 0 0 0,6 3-446 0 0,79 2 0 0 0,-128 4-1662 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 2 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,6 2 0 0 0,-8-3-30 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 2-1 0 0,-6 8-445 0 0,1-1 1 0 0,-1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-16 14 1 0 0,-52 39-1694 0 0,42-36 1372 0 0,-154 120-1795 0 0,154-124 2919 0 0,-1-2 0 0 0,-1-1 0 0 0,-72 29-1 0 0,69-39 1170 0 0,36-10-1260 0 0,0 0-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 1 0 0,-1-2-1 0 0,3 3-175 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,13-7 342 0 0,-14 7-385 0 0,305-114 1839 0 0,-257 97-1819 0 0,116-32-1695 0 0,-130 40 410 0 0,13-5-1586 0 0,-43 13 2172 0 0,-1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,-1 0 1 0 0,6-4-1 0 0,-8 4 360 0 0,0 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 1 1 0 0,1-1 0 0 0,-3-2-1 0 0,1-2-520 0 0,-21-43-2306 0 0,8 20 2119 0 0,7 8 499 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6138.82">3544 113 176 0 0,'1'-56'1837'0'0,"1"-1"4990"0"0,-4 79-2522 0 0,-12 91 440 0 0,-14 54-2978 0 0,4-31-1164 0 0,-8 61-492 0 0,-61 404-1009 0 0,45-199-4659 0 0,45-372 4335 0 0,-4 54-2298 0 0,9-29-2807 0 0,9-74 4099 0 0,-3 6 1725 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6398.35">4023 620 396 0 0,'-1'20'2512'0'0,"1"-11"-1737"0"0,-1 0 0 0 0,1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,1-1 0 0 0,3 10-1 0 0,6 10-398 0 0,11 18-2084 0 0,-20-40 1217 0 0,-3-4-970 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6954.32">4135 623 124 0 0,'5'-6'595'0'0,"0"0"0"0"0,-1 0 0 0 0,1-1 0 0 0,4-9 0 0 0,-8 12-219 0 0,1 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0 1 0 0 0,5-3 1 0 0,21-3 749 0 0,0 1 0 0 0,0 2 0 0 0,1 1 0 0 0,0 1 1 0 0,-1 2-1 0 0,1 1 0 0 0,-1 1 0 0 0,45 9 0 0 0,-70-10-1052 0 0,0 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,3 7-1 0 0,-3-1-26 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 0 0 0,-2 19 0 0 0,-2 11-245 0 0,-1-1 1 0 0,-3 0-1 0 0,-1 0 0 0 0,-2 0 1 0 0,-1-1-1 0 0,-26 56 1 0 0,26-72-80 0 0,-2-2 0 0 0,-1 1 0 0 0,-1-2 0 0 0,-1 0 0 0 0,-26 27 0 0 0,3-10-170 0 0,-68 51 0 0 0,7-19 368 0 0,97-68 133 0 0,-4 3 218 0 0,0 0 1 0 0,0-1-1 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,1-1 1 0 0,-2 1-1 0 0,1-1 1 0 0,0-1-1 0 0,0 1 1 0 0,-9-1-1 0 0,16-1 41 0 0,2-13 912 0 0,6 9-1107 0 0,0-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,0 0-1 0 0,0 0 1 0 0,1 1 0 0 0,-1 0-1 0 0,12-1 1 0 0,3-2 50 0 0,30-4-96 0 0,1 1 0 0 0,58 0 0 0 0,34-3-8088 0 0,-141 10 7549 0 0,56-11-6314 0 0,-58 12 6231 0 0,0-1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,4-6 0 0 0,-6 7-215 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink18.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-07-18T14:18:45.949"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">2126 853 280 0 0,'19'-133'3810'0'0,"-17"112"-2117"0"0,9-33 1 0 0,-7 41-1331 0 0,-1-1 1 0 0,-1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,-1-26 0 0 0,-2 19 112 0 0,-1-1 0 0 0,-1 1 1 0 0,-1 0-1 0 0,-1 1 0 0 0,-1-1 0 0 0,-1 1 1 0 0,0 1-1 0 0,-2-1 0 0 0,0 2 0 0 0,-1-1 1 0 0,-1 1-1 0 0,-14-16 0 0 0,6 10 78 0 0,-2 0-1 0 0,0 2 1 0 0,-2 0 0 0 0,0 2 0 0 0,-1 0-1 0 0,-1 2 1 0 0,-1 1 0 0 0,-40-19-1 0 0,36 24-312 0 0,-1 1-1 0 0,0 2 0 0 0,-1 1 1 0 0,0 1-1 0 0,0 2 1 0 0,-62-1-1 0 0,49 7-68 0 0,-1 1 1 0 0,1 3-1 0 0,0 2 0 0 0,0 2 1 0 0,1 1-1 0 0,0 3 0 0 0,1 2 1 0 0,-74 35-1 0 0,17 3 129 0 0,3 3 1 0 0,-129 99 0 0 0,131-84 60 0 0,-112 109 1 0 0,175-148-260 0 0,2 1-1 0 0,2 1 0 0 0,1 2 0 0 0,2 1 1 0 0,1 1-1 0 0,-32 69 0 0 0,43-72-69 0 0,1 0 0 0 0,2 1 0 0 0,2 1 1 0 0,1 0-1 0 0,2 0 0 0 0,2 0 0 0 0,1 1 0 0 0,2 0 0 0 0,1-1 0 0 0,2 1 0 0 0,2-1 1 0 0,1 1-1 0 0,19 64 0 0 0,-13-65-6 0 0,1-2-1 0 0,2 1 1 0 0,2-2 0 0 0,1 0 0 0 0,2 0 0 0 0,1-2-1 0 0,1-1 1 0 0,2 0 0 0 0,1-2 0 0 0,1 0-1 0 0,2-2 1 0 0,0-1 0 0 0,51 37 0 0 0,-26-31-8 0 0,0-1-1 0 0,2-3 1 0 0,1-2 0 0 0,0-3 0 0 0,2-2-1 0 0,1-3 1 0 0,96 18 0 0 0,-62-21-157 0 0,0-4-1 0 0,1-5 1 0 0,0-3 0 0 0,119-13 0 0 0,-112 0-396 0 0,-1-6-1 0 0,192-54 0 0 0,-220 47 76 0 0,-2-4 0 0 0,0-2-1 0 0,-2-4 1 0 0,107-69 0 0 0,-149 84 382 0 0,0-1 0 0 0,-1-1 1 0 0,-1-2-1 0 0,-1 0 0 0 0,-1-1 0 0 0,-1-1 1 0 0,-1-1-1 0 0,-1 0 0 0 0,-1-2 0 0 0,-1 0 0 0 0,-2-1 1 0 0,-1 0-1 0 0,-1-1 0 0 0,-1-1 0 0 0,-2 0 1 0 0,11-57-1 0 0,-8 3 290 0 0,3-120-1 0 0,-15 146 47 0 0,-2 0 0 0 0,-3 0 0 0 0,-13-56 0 0 0,13 91-141 0 0,-1 2-1 0 0,-1-1 0 0 0,-1 1 1 0 0,-1 0-1 0 0,0 1 0 0 0,-2 0 1 0 0,0 0-1 0 0,-2 1 0 0 0,0 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,-35-29 1 0 0,24 26-123 0 0,-1 2 1 0 0,0 1-1 0 0,-2 1 1 0 0,0 1-1 0 0,-1 1 1 0 0,-1 2-1 0 0,0 1 1 0 0,-47-12-1 0 0,-183-32-2582 0 0,-5 15-3967 0 0,169 28 3631 0 0,-461-38-8642 0 0,481 50 10862 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink19.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-07-18T14:21:22.182"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">2245 765 396 0 0,'-7'0'772'0'0,"-7"1"5749"0"0,18 13-3195 0 0,-1-7-4612 0 0,-1-2 1144 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,5 3-1 0 0,-7-6 63 0 0,1-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,1-1 0 0 0,0 1-19 0 0,-1-1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,2-3-1 0 0,18-26-542 0 0,40-46 0 0 0,-48 63 987 0 0,0 0 0 0 0,1 1 0 0 0,0 0 0 0 0,1 1 1 0 0,21-11-1 0 0,8 4 989 0 0,-42 17-1225 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,2 2-1 0 0,-4-1-85 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,-1 2 1 0 0,-8 37 65 0 0,7-33-70 0 0,-5 14-93 0 0,0 0 0 0 0,-1-1 0 0 0,-1 0 0 0 0,-1 0 0 0 0,-1-1 0 0 0,-21 29 0 0 0,22-35 21 0 0,-1 0 1 0 0,-1-1-1 0 0,-1 0 0 0 0,0-1 1 0 0,0 0-1 0 0,-1-1 0 0 0,0 0 1 0 0,-31 16-1 0 0,30-22 180 0 0,15-5-116 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,1 0 53 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0-1 0 0,3-1 1 0 0,11-5 109 0 0,0 0-1 0 0,1 1 1 0 0,-1 0-1 0 0,1 2 1 0 0,1-1-1 0 0,-1 2 1 0 0,21-2-1 0 0,25-6-828 0 0,-57 10 404 0 0,-1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1-7 1 0 0,2-9-779 0 0,0 0 1 0 0,-2 0 0 0 0,2-32-1 0 0,-2 21 261 0 0,-1 8 249 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="346.63">2571 324 144 0 0,'-2'1'157'0'0,"0"0"-1"0"0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 4-1 0 0,-11 33 1034 0 0,8-19-587 0 0,-51 180 2414 0 0,27-89-2618 0 0,-46 207-173 0 0,-2 8-536 0 0,65-281 247 0 0,4-12-1 0 0,-1-2 1 0 0,-1 1-1 0 0,-30 58 0 0 0,40-89 64 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-2 1 0 0 0,1-1 1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,-1-2 10 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0-6-1 0 0,3-17 143 0 0,1 1 1 0 0,0-1-1 0 0,3 1 1 0 0,0 0-1 0 0,1 1 1 0 0,2 0-1 0 0,0 0 1 0 0,24-38-1 0 0,-31 58-63 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,7 4 0 0 0,121 76 387 0 0,-130-80-821 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 1 0 0,2 2-1 0 0,-4-3-567 0 0,6-26-5013 0 0,7-36 4233 0 0,-6 32 1290 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="545.09">3076 205 292 0 0,'10'-23'920'0'0,"3"-3"827"0"0,-10 10 2758 0 0,-14 34-466 0 0,6-4-3855 0 0,0 1-1 0 0,1-1 1 0 0,1 1 0 0 0,0 0-1 0 0,0 17 1 0 0,3-26-1335 0 0,0-16-7938 0 0,2-19 7209 0 0,1 14 1447 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="802.47">3231 26 268 0 0,'21'-1'3821'0'0,"0"-1"1"0"0,38-9-1 0 0,-13 2-1434 0 0,-43 8-2299 0 0,1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1 0 1 0 0,0-1-1 0 0,-1 2 1 0 0,1-1-1 0 0,0 0 0 0 0,-1 0 1 0 0,0 1-1 0 0,1 0 1 0 0,5 4-1 0 0,-5-3-52 0 0,0 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 1 0 0 0,2 7-1 0 0,1 11-70 0 0,-1-1 0 0 0,-1 1-1 0 0,-1-1 1 0 0,-1 37-1 0 0,-1-56 43 0 0,0 14-505 0 0,-1 0-1 0 0,-1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,-12 29 1 0 0,15-43 226 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-3 1 0 0 0,-2-2-233 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,-13-6 0 0 0,7 1 96 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1025.51">3131 212 356 0 0,'-1'2'252'0'0,"0"-1"0"0"0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0-1 0 0,1 2 1 0 0,0-2 79 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,3-1-1 0 0,50-12 1629 0 0,-44 11-2169 0 0,0 1 0 0 0,0 0 0 0 0,0 1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 2 0 0 0,0 0 1 0 0,18 5-1 0 0,-30-7 39 0 0,0 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,1-1 1 0 0,-2-8-5711 0 0,-1 1 4945 0 0,0 4 2426 0 0,2-6-1940 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1155.8">3309 80 232 0 0,'0'0'77'0'0,"0"0"0"0"0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,-5 16 1872 0 0,0 17 757 0 0,-4 24-1631 0 0,-23 79 0 0 0,29-124-1843 0 0,-1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0-1 1 0 0,-16 12-1 0 0,18-15 351 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1846.47">3039 505 396 0 0,'0'0'5365'0'0,"23"0"558"0"0,-10-3-5463 0 0,-1 0-1 0 0,1 0 0 0 0,0 2 1 0 0,-1-1-1 0 0,1 2 0 0 0,0 0 1 0 0,0 0-1 0 0,25 5 0 0 0,-8 2-759 0 0,-12-3-1257 0 0,0 0 0 0 0,1 0 0 0 0,24 0 0 0 0,-43-4 1010 0 0,-42 29-943 0 0,-4 4 1852 0 0,0 2 0 0 0,3 2 0 0 0,-55 59 0 0 0,51-48 173 0 0,-8 7 1195 0 0,54-54-1104 0 0,23-2-142 0 0,0-1 1 0 0,28-7-1 0 0,-2 1-208 0 0,-29 5-173 0 0,21-3 76 0 0,56-1-1 0 0,-96 7-168 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,-9 11 238 0 0,-26 11 16 0 0,33-22-247 0 0,-94 58 198 0 0,29-17-141 0 0,-2-2 0 0 0,-114 48 1 0 0,166-82 108 0 0,1 0 0 0 0,-1-1 0 0 0,0-1 0 0 0,0 0 0 0 0,-28 2 0 0 0,45-6-77 0 0,0-1-79 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,1-1-1 0 0,30-8-7 0 0,-21 6 33 0 0,287-81 273 0 0,-187 53-265 0 0,11-7-87 0 0,71-17-1100 0 0,-173 50 768 0 0,-16 4 230 0 0,1-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,4 2 1 0 0,-8-1 61 0 0,-1 0 1 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1 0 0 0,-2 2 0 0 0,-17 21-1340 0 0,12-17 1001 0 0,-9 7-1047 0 0,-1 0 0 0 0,0-2 0 0 0,-37 20 0 0 0,32-22 297 0 0,-2-1 1 0 0,-42 9-1 0 0,50-12 754 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2229.94">3099 1083 76 0 0,'0'0'907'0'0,"5"23"2778"0"0,-10 82 1406 0 0,0-2-4078 0 0,-3 172 1498 0 0,5-223-1331 0 0,-15-70-954 0 0,-6-15-137 0 0,18 22-91 0 0,-2 1 1 0 0,-15-17 0 0 0,-48-35-17 0 0,-8-7 21 0 0,70 60 27 0 0,1-1 1 0 0,0 0-1 0 0,0 0 0 0 0,1-1 0 0 0,0 0 0 0 0,-6-12 0 0 0,12 20-2 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,1-4-1 0 0,1 3 40 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,6-4 0 0 0,7-3 187 0 0,0 0-1 0 0,0 1 1 0 0,1 1 0 0 0,20-8 0 0 0,-1 2 145 0 0,2 1 0 0 0,-1 1 0 0 0,1 3 0 0 0,1 1 0 0 0,-1 1 0 0 0,56-1 0 0 0,-83 7-557 0 0,-1 2 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 2 1 0 0,-1-1 0 0 0,11 6-1 0 0,-13-4-960 0 0,0-1 1 0 0,-1 1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,11 12 1 0 0,-17-15 766 0 0,1-1 1 0 0,0 1 0 0 0,1-1 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,5-2 0 0 0,9-3-325 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2756.28">4255 101 80 0 0,'0'13'9528'0'0,"-2"19"-5738"0"0,-3 8-1152 0 0,-14 55 0 0 0,-42 103-1241 0 0,47-157-1723 0 0,-1-1 0 0 0,-2 0 0 0 0,-2-2 0 0 0,-2 0-1 0 0,-50 69 1 0 0,47-75-649 0 0,-17 20-1059 0 0,36-47 1574 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,-10 5-1 0 0,14-8 387 0 0,1 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,0 0 1 0 0,1 0-37 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,1-2 1 0 0,0-4-145 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,3-10 0 0 0,4-3 306 0 0,1-1 0 0 0,1 1-1 0 0,1 0 1 0 0,0 1 0 0 0,1 0 0 0 0,1 1-1 0 0,1 1 1 0 0,33-28 0 0 0,-47 43 30 0 0,1-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 2 0 0 0,4 5 294 0 0,-1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 1 0 0 0,-1-1 0 0 0,4 18 0 0 0,4 27 986 0 0,-3 1 1 0 0,0 104-1 0 0,-19 113-149 0 0,3-156-1563 0 0,6-91-784 0 0,-1 1 0 0 0,-8 25-1 0 0,11-50 940 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,-1 1 0 0 0,2-1 68 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,0-2-145 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-3 0 0 0,0-9-462 0 0,0 0 0 0 0,5-19-1 0 0,0 7 216 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3040.36">4967 352 340 0 0,'12'0'1314'0'0,"0"1"0"0"0,1 0 0 0 0,-2 1 0 0 0,14 3 0 0 0,-21-4-550 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,3 6 0 0 0,-4-6-583 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,-1 3 0 0 0,-3 10 201 0 0,-12 29-1 0 0,12-34-194 0 0,-24 52 265 0 0,-66 110 0 0 0,-55 51-545 0 0,138-208 72 0 0,-21 30-110 0 0,-117 159-610 0 0,123-173 265 0 0,-2-2-1 0 0,0-1 1 0 0,-2-2 0 0 0,-35 26 0 0 0,56-47 116 0 0,-1 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 0 0 0 0,-14 4 1 0 0,22-9 190 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,-4 0 1 0 0,5 0 25 0 0,0 1 1 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,1 0 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 1-1 0 0,-2-4 1 0 0,-1-5-417 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1-1 1 0 0,1-11-1 0 0,13-78-2208 0 0,-5 45 1489 0 0,6-33-916 0 0,43-144-1 0 0,-42 182 1803 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3213.49">4492 575 160 0 0,'2'-3'173'0'0,"0"-1"0"0"0,0 1 0 0 0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,7-3 0 0 0,-9 6-72 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,2 1 1 0 0,-1 0 72 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,3 4 1 0 0,12 21 1490 0 0,0 2 0 0 0,-3 0 1 0 0,0 1-1 0 0,13 49 1 0 0,3 3 241 0 0,28 78 504 0 0,-20-52-1149 0 0,84 170-1 0 0,-102-246-1190 0 0,0-1 1 0 0,2-1-1 0 0,35 40 0 0 0,-25-43-378 0 0,-30-26 184 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,2 0 0 0 0,-3 0-59 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,-5-24-2395 0 0,-25-70-3407 0 0,-21-46 1987 0 0,36 100 3308 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3363.11">4797 495 212 0 0,'0'0'4166'0'0,"-1"6"585"0"0,-1 11-2462 0 0,5 33 3449 0 0,7 3-3518 0 0,-8-45-2502 0 0,1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,8 12-1 0 0,-9-15-289 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,7 5-1 0 0,-9-7 326 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0-1 0 0,-1-1 0 0 0,2 0 1 0 0,1 0-137 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,2-2 1 0 0,4-6-488 0 0,0-1 0 0 0,0 0 0 0 0,7-14 0 0 0,-16 25 842 0 0,16-24-643 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4219.47">6667 275 40 0 0,'-1'-2'197'0'0,"0"0"0"0"0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-4 0 0 0 0,2 1 147 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-8 4 0 0 0,-2 2 535 0 0,0 0 0 0 0,1 1-1 0 0,0 1 1 0 0,1 0-1 0 0,-12 11 1 0 0,-5 8-57 0 0,2 2 0 0 0,1 0-1 0 0,1 2 1 0 0,2 1 0 0 0,1 0-1 0 0,-23 50 1 0 0,24-39-488 0 0,2 1 1 0 0,2 0-1 0 0,3 2 1 0 0,1 0-1 0 0,-11 85 1 0 0,18-76-281 0 0,3 1 0 0 0,2 0 0 0 0,3 0-1 0 0,14 91 1 0 0,-12-128-308 0 0,0 0-1 0 0,1 0 1 0 0,1 0-1 0 0,1-1 1 0 0,1 0-1 0 0,12 22 0 0 0,-16-35-104 0 0,-1 0 0 0 0,2 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,10 5 0 0 0,-10-8-79 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,9-3 0 0 0,0 0-198 0 0,-2-1-1 0 0,1-1 0 0 0,0-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,-1 0 1 0 0,0-1-1 0 0,0-1 1 0 0,-1 1-1 0 0,16-18 0 0 0,-2 0 44 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4439.45">7019 689 220 0 0,'-3'2'10950'0'0,"7"-8"-5325"0"0,1 2-6320 0 0,5-1 1232 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,21-2 0 0 0,-11 3-651 0 0,-1 1 0 0 0,1 0 0 0 0,19 3 0 0 0,-14 1-749 0 0,-19-1 165 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,0-1 0 0 0,0 1 0 0 0,7-2 0 0 0,-11 2 297 0 0,-1-1 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-3-1 0 0,-2 2 77 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1-3 1 0 0,-1-6-352 0 0,-1-1 130 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4835.79">7248 148 220 0 0,'0'0'111'0'0,"0"-1"-1"0"0,-1 1 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,-5 22 2322 0 0,3-14-1251 0 0,-5 21 2142 0 0,-6 55 0 0 0,6-32-2231 0 0,-29 236 1264 0 0,-1 4-1838 0 0,7-73-471 0 0,-38 195-163 0 0,67-410 92 0 0,0 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-5 7-1 0 0,5-10 18 0 0,1 0-1 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-2 1-1 0 0,1-2-3 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,-9-14-39 0 0,2 1 0 0 0,0-1 0 0 0,0 0-1 0 0,1 0 1 0 0,1-1 0 0 0,1 0-1 0 0,-5-25 1 0 0,-4-9 65 0 0,4 19 136 0 0,2 0 0 0 0,1-1 0 0 0,-5-52-1 0 0,11 66 30 0 0,1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,2 0-1 0 0,8-23 1 0 0,-8 28-65 0 0,1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1 0 0 0,1 0 0 0 0,0 1 1 0 0,1-1-1 0 0,0 2 0 0 0,0 0 0 0 0,1 0 0 0 0,22-14 0 0 0,-25 19-107 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 1 0 0 0,0 0 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 2 0 0 0,11 4 0 0 0,5 6-1304 0 0,0 1-1 0 0,-1 1 1 0 0,39 36-1 0 0,-21-17-4443 0 0,-40-34 5356 0 0,1 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,3-2 0 0 0,-3 1 153 0 0,1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,1-3-1 0 0,4-7-294 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5214.98">7892 435 140 0 0,'28'-74'9274'0'0,"-28"73"-8869"0"0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,-1-2-1 0 0,1 3-239 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,-3 2 166 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,-5 5 0 0 0,-14 16-290 0 0,1 1 1 0 0,1 1 0 0 0,1 1-1 0 0,2 1 1 0 0,-18 34-1 0 0,-8 8-149 0 0,-119 196-443 0 0,162-263 555 0 0,-1 1-11 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 6 0 0 0,2-7 3 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,3 1 1 0 0,1 2 8 0 0,0 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,-1 1-1 0 0,0-1 1 0 0,1 0-1 0 0,-2 0 1 0 0,1 0-1 0 0,-1 5 0 0 0,-2 16 6 0 0,-1-1-1 0 0,-2 0 0 0 0,-16 49 0 0 0,-40 68-64 0 0,45-110-327 0 0,-1-1-1 0 0,-38 48 1 0 0,39-58-885 0 0,-1-1 1 0 0,-24 20-1 0 0,41-39 1104 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-2 0 0 0 0,2 0 38 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-2 1 0 0,0-6-740 0 0,0-1 0 0 0,1 1 0 0 0,4-11 0 0 0,17-42-977 0 0,2 1-1 0 0,3 2 1 0 0,40-63 0 0 0,-42 80 1386 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5546.29">7595 956 228 0 0,'9'-10'694'0'0,"1"-1"1"0"0,0 2-1 0 0,1-1 1 0 0,0 1-1 0 0,1 1 1 0 0,0 0-1 0 0,0 1 1 0 0,1 0-1 0 0,19-7 1 0 0,-12 6 1069 0 0,2 1 0 0 0,-1 1 0 0 0,1 1 1 0 0,0 1-1 0 0,40-2 0 0 0,-50 6-1505 0 0,1 0 0 0 0,-1 1 1 0 0,0 0-1 0 0,0 1 0 0 0,0 0 0 0 0,0 1 1 0 0,0 0-1 0 0,0 1 0 0 0,0 1 0 0 0,-1 0 0 0 0,0 0 1 0 0,12 8-1 0 0,-22-12-231 0 0,1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 3 0 0 0,-2 5 54 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-11 17 0 0 0,0-1 2 0 0,-6 14-127 0 0,-2-2-1 0 0,-1-1 1 0 0,-2-1 0 0 0,-2-1-1 0 0,-1-1 1 0 0,-39 34 0 0 0,41-41-865 0 0,-1-2 1 0 0,-2-2-1 0 0,0 0 0 0 0,-59 30 1 0 0,88-52 767 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,-2 0 0 0 0,2-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0-2 0 0 0,1-7-391 0 0,0-1 1 0 0,1 0 0 0 0,0 1 0 0 0,6-17-1 0 0,-3 12 195 0 0,4-13-238 0 0,20-44-1 0 0,-26 66 684 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 2 0 0 0,1-1 0 0 0,0 0 0 0 0,9-5 0 0 0,-12 9 19 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,3 4 0 0 0,6 3 522 0 0,-1 2-1 0 0,-1-1 1 0 0,15 19 0 0 0,115 175 4183 0 0,-53-71-3364 0 0,-71-110-1417 0 0,105 142-471 0 0,-54-86-2619 0 0,6-8-3750 0 0,-61-61 4816 0 0,-30-25-5584 0 0,6 5 7320 0 0,-8-4-516 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-2555.73">409 168 96 0 0,'0'0'315'0'0,"0"-1"0"0"0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,8 0 784 0 0,-1 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0-1 1 0 0,12-4 0 0 0,13-3 102 0 0,12-4-97 0 0,-35 10-860 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,17 2 0 0 0,-26-1-185 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 0 0 0,1 3 1 0 0,-2 5 151 0 0,1 1-1 0 0,-1-1 1 0 0,-5 14 0 0 0,5-15-107 0 0,-12 33 204 0 0,-2-1 0 0 0,-21 40-1 0 0,-48 75-137 0 0,58-108-136 0 0,-84 129-1391 0 0,-204 251 0 0 0,295-401-164 0 0,-25 41 0 0 0,36-49-150 0 0,8-15 150 0 0,8-11 307 0 0,96-170-3684 0 0,-22 36 3803 0 0,-63 112 1000 0 0,-3 4 310 0 0,0 2-1 0 0,2 0 0 0 0,0 1 0 0 0,37-37 0 0 0,-53 59-139 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,2 1 0 0 0,-3 0 39 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 1 0 0 0,2 2 0 0 0,1 6 386 0 0,0 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 20-1 0 0,-1 48 1114 0 0,-14 141-1 0 0,-32 78-1385 0 0,37-253-239 0 0,-2 7-263 0 0,1-12-850 0 0,2 1 1 0 0,0 41-1 0 0,6-81 947 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,0-1 1 0 0,0 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,1 1 0 0 0,0 0-1 0 0,7-10-1992 0 0,7-22 434 0 0,51-171-2303 0 0,-48 156 3634 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-2413.91">1113 137 264 0 0,'0'11'260'0'0,"0"-4"-20"0"0,-3 4-72 0 0,1 2-92 0 0,2 0-44 0 0,-3 0-16 0 0,-2-3-8 0 0,2 3-4 0 0,0 0 0 0 0,1-3-4 0 0,-3 1-68 0 0,5-1-96 0 0,-6 0-60 0 0,6-2-40 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-1966.72">1168 277 256 0 0,'2'3'373'0'0,"0"0"0"0"0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,1-1 0 0 0,-1 4 0 0 0,0-4 279 0 0,0 0-1 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,1 0 1 0 0,0-1-1 0 0,4 6 1 0 0,-6-7-517 0 0,0-1-190 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,-7 12-1643 0 0,-19 15 134 0 0,21-21 862 0 0,-39 40-1681 0 0,35-35 1982 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-1628.99">858 604 376 0 0,'-32'93'4207'0'0,"21"-65"-2833"0"0,2-1 0 0 0,-7 34 0 0 0,11-39-1215 0 0,3-14-387 0 0,0 0 1 0 0,0 0 0 0 0,1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,2 10 1 0 0,-1-20 96 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,3-3 0 0 0,1-4-57 0 0,4-8 453 0 0,0 0 0 0 0,1 0 0 0 0,1 1 0 0 0,0 1 0 0 0,1 0 1 0 0,1 0-1 0 0,0 1 0 0 0,1 1 0 0 0,1 0 0 0 0,24-16 0 0 0,-11 11 568 0 0,1 1 0 0 0,39-15 0 0 0,-51 24-515 0 0,2 2 0 0 0,-1 0 0 0 0,0 1 0 0 0,1 1 1 0 0,27-3-1 0 0,-41 7-301 0 0,0-1 1 0 0,-1 1 0 0 0,1 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,0 1-1 0 0,1 4 1 0 0,2 6-542 0 0,-1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,-2 1-1 0 0,-2 29 1 0 0,2-40 138 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,-4 7 1 0 0,5-9 153 0 0,0-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,1 0 1 0 0,-4-1 0 0 0,-3 0-120 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-1024.01">976 816 280 0 0,'0'0'1854'0'0,"-10"24"1218"0"0,-34 118 1532 0 0,11-39-2404 0 0,-32 175 1 0 0,62-255-2039 0 0,0 1 1 0 0,1 0-1 0 0,2 0 1 0 0,0 0-1 0 0,2 0 1 0 0,0 0-1 0 0,2-1 1 0 0,12 41-1 0 0,-15-60-134 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,5 1-1 0 0,-3-2 9 0 0,1 0 0 0 0,-1 0 0 0 0,1-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1 0 0 0,-1 1-1 0 0,1-2 1 0 0,-1 1 0 0 0,0-1 0 0 0,14-5 0 0 0,-3 0-112 0 0,-1-1 0 0 0,0 0 1 0 0,0-2-1 0 0,-1 1 1 0 0,29-24-1 0 0,-35 24-132 0 0,-2 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,4-15 1 0 0,-8 20 112 0 0,8-31-830 0 0,-10 35 842 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,-1-4 0 0 0,-4-3-64 0 0,1 0-1 0 0,1 0 1 0 0,0-1 0 0 0,0 0-1 0 0,1 0 1 0 0,0-1 0 0 0,-3-15-1 0 0,4 17 153 0 0,1-1 0 0 0,-1 1 0 0 0,-7-13 0 0 0,9 21 23 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,-1 1-1 0 0,-3 0 7 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 1 0 0 0,-8 7 0 0 0,-31 49-1412 0 0,29-38-367 0 0,-26 31-1 0 0,35-48 1398 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1-1 0 0 0,-2 1-1 0 0,1-1 1 0 0,-10 3 0 0 0,13-5 196 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,-1-1 0 0 0,-3-1 0 0 0,-11-7-413 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6375.01">910 1827 88 0 0,'0'0'2106'0'0,"-18"16"3991"0"0,16-11-5436 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 5 0 0 0,2 8 240 0 0,4 33 0 0 0,-1-17-523 0 0,-3-23-376 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,7 16 0 0 0,-8-22-381 0 0,1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 1 0 0,8 6 0 0 0,-12-9 143 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,-1 1 0 0 0,1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,2-1 1 0 0,1-1-207 0 0,0-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-2 0 0 0 0,1-1 0 0 0,4-5 0 0 0,2-6-91 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6757.88">1326 1861 456 0 0,'96'5'8286'0'0,"-9"1"-2425"0"0,-29-9-4776 0 0,-48 2-888 0 0,24-2 200 0 0,-32 2-383 0 0,-1 1 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,3 1 0 0 0,-4-1-17 0 0,1 0 1 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,-1 0 1 0 0,-1 1 0 0 0,-14 18-104 0 0,16-20 104 0 0,-63 71-609 0 0,-69 74-775 0 0,98-111 1061 0 0,-2-3 1 0 0,-45 33-1 0 0,61-50 312 0 0,-34 18 0 0 0,46-28 151 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-13 0 0 0 0,20 0-88 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-2 0 0 0,1-1 98 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 1 0 0,2 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,4-2 0 0 0,3 1 31 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 1 0 0 0,1 0 0 0 0,18-1 0 0 0,-2 3-51 0 0,39 2 1 0 0,0 10-733 0 0,-37-6-425 0 0,-20-3-3436 0 0,-13-1 1588 0 0,-27-1 52 0 0,1 1 849 0 0,0 3 667 0 0,0 2 0 0 0,0 1-1 0 0,0 1 1 0 0,-51 24-1 0 0,52-17 904 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7276.16">866 2488 404 0 0,'-137'57'4478'0'0,"93"-38"-839"0"0,-1 4 2704 0 0,45-23-6316 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,1-1 0 0 0,0 1 1 0 0,10 12 84 0 0,-3-5-258 0 0,1 1 0 0 0,1-2 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1-1 0 0 0,0-1 0 0 0,0 1 0 0 0,17 4 0 0 0,-19-7-189 0 0,0-1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 0-1 0 0,12-5 0 0 0,38-19-1528 0 0,-46 19 1769 0 0,0 0 1 0 0,0 1-1 0 0,1 1 0 0 0,0 0 0 0 0,0 1 1 0 0,0 1-1 0 0,0 0 0 0 0,20-1 0 0 0,188 17 4265 0 0,-178-16-3715 0 0,-33 2-394 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,1 1 1 0 0,-1 0-1 0 0,21 4 0 0 0,-31-5-60 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 2-1 0 0,0 0 3 0 0,-1-1-1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-4 4 0 0 0,-7 7-36 0 0,0-1 0 0 0,-1-1-1 0 0,-1 0 1 0 0,-20 12 0 0 0,-69 36-236 0 0,58-34 207 0 0,-45 24 162 0 0,-2-4 0 0 0,-109 38 0 0 0,186-78 305 0 0,0-2 1 0 0,-22 5-1 0 0,33-8-178 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-6-2 1 0 0,10 4-176 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 0 1 0 0,18-15 820 0 0,4 3-670 0 0,1 1 0 0 0,0 1 0 0 0,1 1 0 0 0,0 1 0 0 0,0 1 0 0 0,1 1-1 0 0,48-6 1 0 0,6 6-793 0 0,100 3-1 0 0,-19 2-3019 0 0,-142 1 2090 0 0,-1-1 0 0 0,31-6-1 0 0,-44 7 1055 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,5-8 0 0 0,-7 7 138 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,-1-1 0 0 0,0-6 0 0 0,1 8 213 0 0,-3-16-344 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7472.26">1360 1869 500 0 0,'-1'-4'448'0'0,"0"1"-1"0"0,0-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0-1-1 0 0,1 1 1 0 0,-2 0 0 0 0,-2-4-1 0 0,3 8-153 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,-2 2 0 0 0,-4 6 431 0 0,1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,0 1-1 0 0,1 0 1 0 0,-6 17-1 0 0,-15 69 1202 0 0,19-71-1625 0 0,-82 462 1573 0 0,29 3-1963 0 0,57-468 55 0 0,-35 446-4329 0 0,29-155-6354 0 0,11-292 8373 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10059.39">4544 2149 52 0 0,'-2'-20'1089'0'0,"2"18"-911"0"0,-1 1-1 0 0,1-1 1 0 0,0 0 0 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,0 1 0 0 0,0-1 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,2-1 0 0 0,4-4 803 0 0,0 0 1 0 0,1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 1-1 0 0,11-2 1 0 0,-8 3-360 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1 1 0 0 0,1 0 0 0 0,18 3 0 0 0,-10 0-422 0 0,0 2 1 0 0,-1 0-1 0 0,0 1 0 0 0,0 1 0 0 0,0 1 0 0 0,-1 0 1 0 0,0 1-1 0 0,19 14 0 0 0,-33-21-192 0 0,0 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,6 8 0 0 0,-8-9-35 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 1 0 0,-1 3-1 0 0,-4 5-248 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 0 0 0 0,-11 7 0 0 0,-64 39-2155 0 0,65-43 1945 0 0,-16 9-6 0 0,-1-1 1 0 0,-1-2 0 0 0,0-1-1 0 0,-2-2 1 0 0,1-2 0 0 0,-2-1-1 0 0,-46 7 1 0 0,72-16 1577 0 0,16-3 1105 0 0,24-1-448 0 0,-10 5-1451 0 0,0 1 1 0 0,-1 1 0 0 0,1 1-1 0 0,22 9 1 0 0,-31-10-506 0 0,-1-1 0 0 0,-1 1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 1-1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,6 9 0 0 0,-11-14 18 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,0 3 0 0 0,0 0-172 0 0,-1-1-1 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,-2 3 0 0 0,-6 2-701 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,-21 8 0 0 0,-28 15-955 0 0,39-19 1546 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10223.36">4211 2929 420 0 0,'-4'14'930'0'0,"2"0"0"0"0,0 0 0 0 0,1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,1 0 1 0 0,0 1-1 0 0,4 13 0 0 0,0 22 1523 0 0,4 242-650 0 0,-9-283-2189 0 0,2 1 0 0 0,0-1 1 0 0,4 14-1 0 0,-6-22 311 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1-1 0 0 0,5-7-1388 0 0,2-15 42 0 0,32-161-3593 0 0,-32 148 4584 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10511.27">4479 2721 4 0 0,'1'0'199'0'0,"-1"-1"0"0"0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,2 0 0 0 0,24 11 6535 0 0,0 0-2139 0 0,-5-7-3573 0 0,0-1-1 0 0,0-2 1 0 0,1 0-1 0 0,-1-1 0 0 0,0-2 1 0 0,34-5-1 0 0,-35 3-877 0 0,1 2 0 0 0,-1 0 0 0 0,1 1 0 0 0,0 1-1 0 0,-1 1 1 0 0,1 1 0 0 0,21 5 0 0 0,-38-6-132 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,6 8 0 0 0,-5-5-1 0 0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,0 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,2 10 0 0 0,-2 9-6 0 0,0 0 0 0 0,-1 0 1 0 0,-2 0-1 0 0,-4 28 0 0 0,5-53-5 0 0,-32 217-556 0 0,-5-66-2483 0 0,37-149 2719 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-5 3-1 0 0,5-5 24 0 0,0 1 0 0 0,0 0 0 0 0,0-1-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-2-3 0 0 0,-12-7-866 0 0,1-1 1 0 0,1-1-1 0 0,0 0 1 0 0,1-1 0 0 0,-23-30-1 0 0,20 21 622 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10899.31">4471 2882 76 0 0,'-5'-3'336'0'0,"4"1"-83"0"0,-1 1 0 0 0,1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-3 1 2357 0 0,42 20 4161 0 0,2-4-4845 0 0,-28-11-1432 0 0,1-1 1 0 0,18 6 0 0 0,-19-7-416 0 0,0-1 1 0 0,1-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,1-1 1 0 0,0 1-1 0 0,-1-2 1 0 0,1 0-1 0 0,0 0 1 0 0,21-6-1 0 0,-30 5-390 0 0,1 0-1 0 0,0 1 0 0 0,0-1 0 0 0,-1-1 0 0 0,1 1 0 0 0,3-4 0 0 0,-25 11-4788 0 0,7 2 4165 0 0,1-1 0 0 0,0 1-1 0 0,-12 12 1 0 0,-4 2-64 0 0,-35 26 0 0 0,-59 40 3603 0 0,80-53 3095 0 0,43-33-5339 0 0,0 1 0 0 0,-1-1 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1-1 0 0,4 1 1 0 0,23 4 374 0 0,0-1-1 0 0,0-2 1 0 0,0-1 0 0 0,60-5-1 0 0,-56 0-807 0 0,-8 0-255 0 0,32-7 0 0 0,-51 9-449 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,8-8 1 0 0,-13 10 297 0 0,0-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,1-1 1 0 0,-3-3-1 0 0,-34-64-5346 0 0,29 57 5275 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="11062.61">4686 2763 240 0 0,'-1'1'215'0'0,"-1"0"0"0"0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 2 0 0 0,-5 34 3009 0 0,4-20-1918 0 0,-23 252 6565 0 0,19-166-9150 0 0,-23 121 0 0 0,28-221 888 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,-3 2 0 0 0,6-6 309 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,-11-9-837 0 0,10 9 727 0 0,-5-8-281 0 0,0 0 0 0 0,0-1-1 0 0,1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-2-18-1 0 0,-2-4-31 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="11285.7">4232 2037 108 0 0,'-3'-7'11074'0'0,"2"17"-5397"0"0,2-2-7545 0 0,2 13 1558 0 0,7 21-3735 0 0,-10-41 2969 0 0,-1 3 537 0 0,0-1 1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,-5 4 0 0 0,-3 5-385 0 0,4-6 460 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9223.19">2374 2543 220 0 0,'-11'74'2744'0'0,"6"-48"-1062"0"0,1 0 0 0 0,1 0 0 0 0,1 0 0 0 0,3 42 0 0 0,15 22 3157 0 0,-13-78-4570 0 0,1 1-1 0 0,0-1 1 0 0,1 0 0 0 0,12 23 0 0 0,-11-26-291 0 0,-3-3-208 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,1 0 1 0 0,7 6-1 0 0,-12-10 85 0 0,0 1 0 0 0,1-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,5-15-2554 0 0,-5-26 15 0 0,-1 33 2074 0 0,-2-139-3656 0 0,2 110 3784 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9603.37">2550 2353 8 0 0,'1'-2'286'0'0,"1"0"0"0"0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,3 1 0 0 0,76 0 6916 0 0,0 3-3578 0 0,161-1-605 0 0,-212-5-2693 0 0,55 4 0 0 0,-84-2-322 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 1 0 0,-1 2-1 0 0,-2 9-42 0 0,0-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,-7 14 0 0 0,7-16-16 0 0,-30 63-603 0 0,-3-1 0 0 0,-3-2-1 0 0,-64 84 1 0 0,68-105 400 0 0,-2-3 0 0 0,-2-1 0 0 0,-2-1 0 0 0,-60 47 1 0 0,87-80 414 0 0,0 0-1 0 0,-21 10 1 0 0,32-19 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,-8-1 1 0 0,12 1-106 0 0,0 0 1 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 1-1 0 0,1-2 1 0 0,0-1 22 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,3-3 0 0 0,2-2-19 0 0,2 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 1 1 0 0,0 0-1 0 0,1 0 1 0 0,0 1-1 0 0,0 0 0 0 0,0 1 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 1 1 0 0,14-2-1 0 0,-2 2-78 0 0,0 1 1 0 0,0 1 0 0 0,1 0-1 0 0,23 4 1 0 0,86 17-2902 0 0,16 0-8067 0 0,-125-19 8694 0 0,1-1 0 0 0,0-1-1 0 0,39-6 1 0 0,-42 2 1648 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="11780.39">4061 2382 292 0 0,'-18'57'6182'0'0,"-8"13"-5542"0"0,-13 41 163 0 0,37-104-804 0 0,1-1 1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 0 0 0 0,1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,3 7 0 0 0,5 8-3 0 0,19 36 1 0 0,-13-28 2 0 0,-13-25 1 0 0,14 26 425 0 0,21 60 1 0 0,-34-79-337 0 0,0 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-5 20 1 0 0,-3 0-23 0 0,-1 0 1 0 0,-1 0 0 0 0,-2-1 0 0 0,-1 0 0 0 0,-2-1 0 0 0,-1-1 0 0 0,-1 0 0 0 0,-1-1 0 0 0,-1-1 0 0 0,-25 25 0 0 0,37-43-217 0 0,-2 0 0 0 0,1-1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0-1 1 0 0,-14 7-1 0 0,16-9-61 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-2 1 0 0,-15-1-1 0 0,20 2 155 0 0,0 0 1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1-3 1 0 0,0 2 87 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,4-3 0 0 0,1 0 287 0 0,1 0 1 0 0,0 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 1-1 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,0 2-1 0 0,0-1 1 0 0,0 1-1 0 0,0 1 1 0 0,18 0-1 0 0,9 3 1051 0 0,0 2 0 0 0,41 10 1 0 0,-59-11-952 0 0,92 22 1812 0 0,0 6-1 0 0,106 46 0 0 0,203 108 38 0 0,-312-136-1993 0 0,96 31-735 0 0,-166-70-1171 0 0,65 11 0 0 0,-92-20 757 0 0,1-1-1 0 0,-1 0 0 0 0,0-1 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 0 1 0 0,0-1-1 0 0,-1 0 0 0 0,1-1 1 0 0,0 0-1 0 0,-1 0 0 0 0,0-1 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,14-15 1 0 0,-8 8-51 0 0,1-2 204 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="13170.63">6381 2105 272 0 0,'2'-1'346'0'0,"-1"-1"0"0"0,1 2 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,3 1 1 0 0,-1 6 2788 0 0,-8 9-1072 0 0,-7 11 2963 0 0,-30 48 1 0 0,-5 10-2906 0 0,-75 206-1395 0 0,37-85-1646 0 0,69-171-319 0 0,-1 0 0 0 0,-2-1 0 0 0,-1-1 0 0 0,-31 39 0 0 0,48-69 908 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0-1-1 0 0,1 0 1 0 0,-5 1-1 0 0,6-1 204 0 0,0-1-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0-1-1 0 0,0-12-389 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,2 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,7-14 0 0 0,1-4 133 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="13348.06">6116 2602 148 0 0,'5'-3'138'0'0,"1"-3"248"0"0,0 2-1 0 0,1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,13-4 1 0 0,-18 7-231 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,1 3-1 0 0,6 17 1042 0 0,0-1 1 0 0,-2 1-1 0 0,0 1 0 0 0,-2-1 0 0 0,-1 1 1 0 0,1 28-1 0 0,-1-25-534 0 0,5 115 1367 0 0,-14 173 0 0 0,1-189-1819 0 0,0-47-1186 0 0,-31 152-1 0 0,33-216 580 0 0,-17 67-4306 0 0,19-80 3537 0 0,-1-11-1368 0 0,1-9 1340 0 0,0 0 0 0 0,2 0 0 0 0,0 1 0 0 0,5-26 0 0 0,22-74-1043 0 0,-23 98 1836 0 0,47-146-1294 0 0,-30 107 1327 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="13509.91">6765 2322 12 0 0,'34'-60'1042'0'0,"-18"30"1491"0"0,2 0 0 0 0,37-46 0 0 0,-49 68-1247 0 0,-6 7-1039 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,2 1 1417 0 0,2 7 1856 0 0,3 6-2366 0 0,-4 0-859 0 0,-1-1-1 0 0,3 22 1 0 0,-4-18-1543 0 0,-1 0 0 0 0,-1 0 0 0 0,-1 0 0 0 0,-2 16 1 0 0,1-21 180 0 0,0 1 0 0 0,-1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,-2 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-10 11 0 0 0,-6 7-601 0 0,9-15 1067 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="13735.73">6628 2618 208 0 0,'0'0'117'0'0,"-19"22"4013"0"0,14-3 5935 0 0,13-19-5973 0 0,8-2-2778 0 0,59-18 614 0 0,-46 13-1560 0 0,37-13-1 0 0,60-26-96 0 0,-2 1-5151 0 0,-133 59-8321 0 0,-14 9 11476 0 0,-19 11-577 0 0,27-22 1746 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="13938">6649 2867 4 0 0,'0'0'86'0'0,"3"21"5903"0"0,-3-20-5713 0 0,1-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,113 0 7061 0 0,57 0-7962 0 0,-145-4-240 0 0,-1 0-4900 0 0,-28 5 5321 0 0,0 1 0 0 0,0-1 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 1-1 0 0,0-1 1 0 0,-3 4 0 0 0,-1 1-522 0 0,-107 96-6001 0 0,98-88 6492 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="14112.91">6641 3147 328 0 0,'-26'10'9312'0'0,"26"-10"-9095"0"0,0 1 0 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,-1-1 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,28 1 1428 0 0,-21 0-1051 0 0,109-10 1674 0 0,-30 2-2657 0 0,-68 7-1288 0 0,0 1 0 0 0,30 4 1 0 0,-49-4 1328 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 1 0 0 0,-4 11-3107 0 0,-20 12 2370 0 0,20-21 205 0 0,-7 6 341 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="14296.6">6504 3530 240 0 0,'-6'9'1628'0'0,"-1"0"0"0"0,2 0-1 0 0,-1 0 1 0 0,-4 12 0 0 0,10-20-1124 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,16 19 1397 0 0,27 13-4494 0 0,-42-33 2716 0 0,-1 0-386 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,1-4 0 0 0,5-4-889 0 0,-1-1-1 0 0,0 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,5-14-1 0 0,-8 16 940 0 0,3-5-335 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="14667.03">6757 3455 256 0 0,'6'3'1397'0'0,"0"-1"1"0"0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 0 0 0 0,9-1 1 0 0,56-6 4092 0 0,-4 1-3785 0 0,-55 4-1434 0 0,0 0 0 0 0,21-5 0 0 0,-22 3-121 0 0,1 1 0 0 0,20-1-1 0 0,-32 3-147 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 2-29 0 0,-1-1-1 0 0,0 0 1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-3 4 0 0 0,-2 6-299 0 0,-1 0-1 0 0,-14 18 1 0 0,-10 11-1018 0 0,-1-2-1 0 0,-2-1 1 0 0,-64 55 0 0 0,68-68 1296 0 0,0-3 0 0 0,-2 0 0 0 0,-1-2 0 0 0,0-1 0 0 0,-56 23 0 0 0,43-27 1295 0 0,43-14-1030 0 0,-1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,-3-1 0 0 0,6 2-141 0 0,-1 0-1 0 0,1 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,1 1-1 0 0,15-11-30 0 0,-11 8 364 0 0,11-7-119 0 0,0 2-1 0 0,0 0 1 0 0,26-9-1 0 0,-19 7-78 0 0,8-2 79 0 0,0 2 1 0 0,1 1 0 0 0,0 1-1 0 0,60-6 1 0 0,20 8-1429 0 0,1 12-4335 0 0,-57 1-3006 0 0,-34-1-640 0 0,-21-5 8321 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="14825.4">7298 4116 392 0 0,'-27'77'16038'0'0,"26"-81"-13836"0"0,-2-20-7033 0 0,2 16 5117 0 0,2-35-4102 0 0,-7-147-5862 0 0,4 162 9085 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink2.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-04-17T13:14:17.317"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 328 0 0,'7'15'3826'0'0,"0"2"1"0"0,-1-1-1 0 0,-1 2 1 0 0,4 19-1 0 0,9 78 6008 0 0,5 25-6361 0 0,8-15-3473 0 0,23 200 0 0 0,-49-298-192 0 0,1 22 565 0 0,-5-46-620 0 0,-1-2-1 0 0,-1 2 0 0 0,1-1 1 0 0,0 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-2-1 0 0,0 1 0 0 0,0 0 1 0 0,-3 2-1 0 0,3-3-168 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,-1-2 0 0 0,-27-28-7188 0 0,23 20 6181 0 0,1 0 0 0 0,0 0 0 0 0,-4-18 0 0 0,1 6 246 0 0,-1 2 499 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink20.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-07-18T14:22:41.440"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">155 199 364 0 0,'-4'-3'6016'0'0,"-4"-6"-2010"0"0,4-24-6336 0 0,-1-5-3524 0 0,4 26 4404 0 0,-1 6 1038 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="888.79">123 27 244 0 0,'-1'-4'7858'0'0,"-4"-10"335"0"0,4 13-7941 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-2 0-1 0 0,1 1-77 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,-3 2 1 0 0,0 0-68 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 1 0 0 0,0 0 0 0 0,-5 7 0 0 0,5-5-4 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,-2 11 1 0 0,5-16-88 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,1 0 1 0 0,0 1 0 0 0,2 6-1 0 0,-3-11-14 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,2 1 0 0 0,-1-1 2 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,2-2 0 0 0,1 0 5 0 0,1 0 0 0 0,-1 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,9-7 1 0 0,-6 2-4 0 0,1 0 1 0 0,-2 0 0 0 0,9-10-1 0 0,-15 15-1 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-2 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0-3 0 0 0,0 5 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-3 0 0 0 0,-3 0 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-13 7 1 0 0,14-6-2 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,-6 10-1 0 0,8-13-1 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1-1 0 0,1-1 1 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,3 4 0 0 0,-3-5 0 0 0,-1-1 0 0 0,1 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,0-1 0 0 0,0 1-1 0 0,1-2 1 0 0,28-15 26 0 0,-29 16-26 0 0,7-5 20 0 0,0-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,7-13 0 0 0,-13 22-16 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,-19-2 58 0 0,16 2-67 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,-1 5-1 0 0,3-9 4 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,9-2-9 0 0,8-5 34 0 0,15-19-31 0 0,-32 26 58 0 0,-1-1-49 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,-1 2 0 0 0,2-2-18 0 0,7 0-116 0 0,22-24-1251 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink21.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-07-18T14:22:43.443"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">69 129 452 0 0,'-2'-29'12390'0'0,"2"28"-12123"0"0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-18 10 1926 0 0,15-6-2076 0 0,0-1 1 0 0,0 1-1 0 0,1-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,-3 7 0 0 0,7-9-102 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,2 2 1 0 0,-3-3-16 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,2-1-1 0 0,-1 0 2 0 0,40-38-37 0 0,-39 36 33 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,4-10-1 0 0,-6 14 14 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,-2 0 1 0 0,0 0 13 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 2 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-4 3 0 0 0,3 0-6 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,1 0 0 0 0,0 1-1 0 0,-2 4 1 0 0,4-9-16 0 0,-1 0-1 0 0,1 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,1 1 0 0 0,1-1 2 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,1-1 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,4-5-1 0 0,0 1 18 0 0,0 0 0 0 0,-1-1 0 0 0,1 0 1 0 0,5-9-1 0 0,-11 15-16 0 0,0 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,-9-1 73 0 0,-11 7-42 0 0,16-3-41 0 0,1 0-1 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,1-1-1 0 0,0 1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,1 0 0 0 0,-2 10 1 0 0,3-15 9 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,11-7 151 0 0,-8 4-102 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0-6 1 0 0,-1 11-57 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,-29 6-1593 0 0,26-5 827 0 0,-2 0-2168 0 0,21-8-13412 0 0,3 0 13257 0 0,-10 5 2425 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1526.4">1110 31 284 0 0,'1'1'166'0'0,"0"0"1"0"0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 3 1 0 0,2 4 1949 0 0,-3-7-1601 0 0,0 1-36 0 0,-1 9 12738 0 0,0-8-11104 0 0,-5-3-2020 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-8 8 0 0 0,7-6-64 0 0,0 0 1 0 0,0 0-1 0 0,1 1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-3 9 1 0 0,6-15-30 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 1 1 0 0,0-1-1 0 0,2 1 1 0 0,3-1 11 0 0,-1 1 0 0 0,0 0 1 0 0,1-1-1 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,8-2-1 0 0,-3-1-1 0 0,-1 0-1 0 0,0-1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,10-10 1 0 0,-12 10-10 0 0,0 1 1 0 0,0-1-1 0 0,-1-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,-1 0 1 0 0,7-15-1 0 0,-10 21 8 0 0,1-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1 0-1 0 0,-3 1 1 0 0,-1-1 20 0 0,-1 0 1 0 0,0 0-1 0 0,1 1 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 1 1 0 0,-6 2-1 0 0,4-1-15 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1 0 0 0 0,-7 9 0 0 0,11-12-13 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,0 3 0 0 0,-1-6-2 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,1 1 0 0 0,0 0 3 0 0,0-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,1 1 0 0 0,2-1 0 0 0,3-1 9 0 0,-1 0 0 0 0,0-1 0 0 0,0 0-1 0 0,12-6 1 0 0,-11 5 2 0 0,-1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,0-1-1 0 0,0 1 1 0 0,9-14 0 0 0,-14 19-7 0 0,-1 1 1 0 0,0-1 0 0 0,0 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 1 7 0 0,-1-1 1 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-3 1 1 0 0,-42 13 99 0 0,38-9-120 0 0,-1 0-1 0 0,1 1 0 0 0,0 0 1 0 0,0 0-1 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,1 1 1 0 0,0 0-1 0 0,0 0 1 0 0,-10 18-1 0 0,16-26 2 0 0,1 1-7 0 0,0 0 13 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,2-1 0 0 0,26-6 99 0 0,-17 2-72 0 0,-1-1 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1-1-1 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,13-20-1 0 0,-21 29-22 0 0,-1 1 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,0-2-1 0 0,0 2 3 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-2 0 0 0 0,-6 1 6 0 0,1 0 1 0 0,0 0-1 0 0,-13 4 1 0 0,15-3-25 0 0,0 0 1 0 0,0 1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,1 0 1 0 0,-7 5 0 0 0,11-8 8 0 0,-1 0-1 0 0,1 1 1 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 4 0 0 0,0-5 6 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,16-11 89 0 0,-14 9-77 0 0,1 0 3 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,3-4 0 0 0,-5 8-16 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,0 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,0-1-1 0 0,-15-2 32 0 0,13 4-40 0 0,0-1 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-4 2 0 0 0,-36 42-542 0 0,42-45 376 0 0,-15-42-20266 0 0,23-3 17367 0 0,-6 39 2750 0 0,4-21-555 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="15827.31">1204 499 328 0 0,'-1'-2'1130'0'0,"0"0"-1"0"0,0-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-5 0 0 0,-1 5-695 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,2-2 1310 0 0,-2 4-1663 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 2-1 0 0,2 41 793 0 0,-2-36-603 0 0,-1 27 408 0 0,-2 0 0 0 0,-12 61 1 0 0,-26 66 72 0 0,34-139-698 0 0,-64 193-2103 0 0,71-216 1875 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,-5-15-5012 0 0,-1-36-1008 0 0,6 41 4657 0 0,-9-63-3252 0 0,8 59 4301 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="16080.58">911 925 104 0 0,'-8'23'1853'0'0,"1"-1"1"0"0,2 1-1 0 0,0 0 1 0 0,1 0-1 0 0,1 0 1 0 0,2 1-1 0 0,0-1 1 0 0,1 1-1 0 0,1-1 0 0 0,6 31 1 0 0,-6-49-1699 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 1-1 0 0,9 5 1 0 0,-8-7-85 0 0,-1 0-1 0 0,2 0 1 0 0,-1 0 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 0 0 0 0,1 1-1 0 0,7-4 1 0 0,3-2 59 0 0,0 0 1 0 0,-1 0-1 0 0,0-2 1 0 0,0 0 0 0 0,-1 0-1 0 0,0-1 1 0 0,23-21-1 0 0,-14 8-319 0 0,-1 0 0 0 0,-1-2-1 0 0,20-28 1 0 0,-12 4-1879 0 0,-26 45 1429 0 0,-1-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,-1-1 0 0 0,1 0-1 0 0,0-5 1 0 0,-1 8 252 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 0 0 0,-24-8-6915 0 0,25 9 6756 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="16834.57">318 1633 84 0 0,'-5'0'1189'0'0,"1"-1"1"0"0,-1 1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,-3 1 1 0 0,-5 2 1108 0 0,-1 1 1 0 0,-16 8-1 0 0,20-7-1809 0 0,-1 1-1 0 0,1-1 1 0 0,1 2-1 0 0,-1-1 1 0 0,-11 14-1 0 0,11-11-333 0 0,0 0 1 0 0,2 1-1 0 0,-1 0 0 0 0,1 1 1 0 0,1 0-1 0 0,0 0 1 0 0,0 1-1 0 0,-7 19 0 0 0,12-23-140 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,1-1 1 0 0,0 1-1 0 0,1-1 1 0 0,0 1 0 0 0,0-1-1 0 0,1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,1-1-1 0 0,0 0 1 0 0,1 1-1 0 0,4 9 1 0 0,-4-11-15 0 0,0 0 1 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 1 0 0,11 7-1 0 0,-13-9-2 0 0,0 0 0 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0-1 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,8-5 0 0 0,-1-2 4 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,0-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0-1 0 0 0,6-16 0 0 0,0-1 25 0 0,-2-1 0 0 0,-2 0 0 0 0,10-44 0 0 0,-18 66-22 0 0,-1 1 0 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,0 1-1 0 0,-3-16 1 0 0,2 20-11 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-2 0-1 0 0,-2-1 0 0 0,0 0-220 0 0,0 1-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 1-1 0 0,-1 0 0 0 0,-8-1 0 0 0,11 2-397 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,-4 3 1 0 0,8-5 424 0 0,-2 1-388 0 0,1 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,-1 4 1 0 0,7 9-3199 0 0,-3-8 3218 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17399.86">585 1638 56 0 0,'5'8'1587'0'0,"-1"0"1"0"0,0-1-1 0 0,0 1 0 0 0,-1 0 1 0 0,0 1-1 0 0,2 9 0 0 0,-3-4 167 0 0,0 0 0 0 0,0-1 0 0 0,-1 19 0 0 0,-2 8 571 0 0,-13 68 0 0 0,9-76-2595 0 0,3-13 333 0 0,-1 1-1 0 0,-2-1 1 0 0,0 0-1 0 0,-11 29 0 0 0,22-102 431 0 0,-1 40-486 0 0,29-87 1 0 0,-28 87-18 0 0,0 0 0 0 0,1 1 0 0 0,1 0 0 0 0,0 1-1 0 0,10-14 1 0 0,-16 25 12 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,3 0 1 0 0,6 1 20 0 0,0 2 1 0 0,19 7-1 0 0,-6-1 13 0 0,-6-3 10 0 0,0 0 0 0 0,21 13 1 0 0,-28-13-17 0 0,1-1 1 0 0,0 0-1 0 0,0-1 1 0 0,1 0-1 0 0,0-1 1 0 0,23 5-1 0 0,-32-9-27 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,2-5 1 0 0,-2 4-9 0 0,1-1 0 0 0,-1 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,-3-7 0 0 0,3 9 7 0 0,-1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,-6 2 0 0 0,1-1 37 0 0,1 0 1 0 0,0 1-1 0 0,0 0 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 1 1 0 0,0 1-1 0 0,-11 7 1 0 0,9-4 83 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1 0-1 0 0,0 1 1 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-3 16 0 0 0,6-22-98 0 0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,1 1-1 0 0,0-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 0 1 0 0,1 1-1 0 0,0-2 0 0 0,4 4 1 0 0,-1-3-90 0 0,-1 1 0 0 0,1-1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0-1-1 0 0,9 1 0 0 0,-9-1-776 0 0,0-1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0-1 0 0 0,13-3 1 0 0,-11 1-704 0 0,1-1 1 0 0,-1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0-2 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,11-15 1 0 0,2-1-505 0 0,-12 13 1324 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17826.41">1294 2237 184 0 0,'-6'14'11316'0'0,"28"-17"-1666"0"0,-9 0-10147 0 0,76-16 2714 0 0,-58 11-2101 0 0,0 2 0 0 0,34-4 0 0 0,-38 9-395 0 0,31-3-4564 0 0,-56 3 4358 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1-1 1 0 0,12-36-3999 0 0,-8 21 2966 0 0,1 3 655 0 0,1-1 158 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="18453.61">2199 1550 0 0 0,'27'44'4571'0'0,"-21"-33"-2870"0"0,1 0-1 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,8 9 1 0 0,5 1-83 0 0,-1 0 1 0 0,0 2 0 0 0,22 35 0 0 0,-33-44-1404 0 0,0 1 1 0 0,-2 1-1 0 0,0-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,-1 1 1 0 0,5 27-1 0 0,-9-35-180 0 0,0-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,-4 10 1 0 0,1-6-55 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,-15 19 0 0 0,6-12-84 0 0,-1 0 0 0 0,0-2 0 0 0,-1 0 0 0 0,-1-1 0 0 0,0-1 0 0 0,-30 16-1 0 0,38-24 98 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1-1 0 0 0,-21 2 0 0 0,33-3 22 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,7-8 412 0 0,14-7 164 0 0,-9 9-365 0 0,1 2 1 0 0,0-1 0 0 0,0 2 0 0 0,0-1 0 0 0,0 2 0 0 0,1 0 0 0 0,0 1 0 0 0,-1 0 0 0 0,15 0 0 0 0,10 3-250 0 0,72 11 0 0 0,-4 0-4130 0 0,-99-12 3215 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1-1 0 0 0,7-5-1 0 0,-4 1-173 0 0,0 0 0 0 0,0-1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-2 0 0 0,9-14-1 0 0,-4 4 326 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="20073.34">2221 75 304 0 0,'-7'21'5984'0'0,"-8"-1"-48"0"0,12-16-5342 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-3 6-1 0 0,5-9-578 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,1 2 1 0 0,-1-2-16 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,2 0 0 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,5-4 0 0 0,0-2-1 0 0,-1 1 0 0 0,0-1 0 0 0,0-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,6-13 0 0 0,-10 20-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,1 0 0 0 0,-4-2 0 0 0,2 2 25 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,-6 2-1 0 0,0 1 163 0 0,1 1 0 0 0,-1 0 0 0 0,1 0-1 0 0,1 0 1 0 0,-9 7 0 0 0,14-10-120 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,0 4 0 0 0,1-7-65 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,0 0 1 0 0,2 1-1 0 0,-1-2 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,2-2 0 0 0,2 0 3 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-2 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,8-8 1 0 0,-11 10 0 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1-3 0 0 0,-2 6-4 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,-1 1 6 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,-1 1 0 0 0,0 0 0 0 0,-1 0-1 0 0,0 1 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 1-1 0 0,-1 3 1 0 0,-1 2-10 0 0,0 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-6 20 0 0 0,10-27 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,2 2 0 0 0,-1-3 0 0 0,-1 0 1 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,2 1-1 0 0,0-1 6 0 0,0 0-1 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,1 0 0 0 0,3-3 0 0 0,-2 0 4 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,2-13 0 0 0,-3 17 10 0 0,-1 0 1 0 0,0-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 1 0 0 0,-4-1 0 0 0,1 0 14 0 0,-1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,1 2-1 0 0,-1-1 1 0 0,0 0 0 0 0,1 1-1 0 0,-9 3 1 0 0,12-4-32 0 0,0 0-1 0 0,1 0 1 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 4-1 0 0,-1-4 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,2 1 0 0 0,-1 0 5 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,5-1 0 0 0,-3 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,4-6-1 0 0,-7 8-27 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1-2-1 0 0,0 2-248 0 0,-8-5-4764 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="20964.03">2403 419 400 0 0,'1'7'593'0'0,"-1"-1"1"0"0,1 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 0 0 0,1-1 1 0 0,-1-1-1 0 0,1 1 0 0 0,4 6 1 0 0,7 10 1603 0 0,20 24 0 0 0,-15-22-952 0 0,191 237 4787 0 0,-151-196-4930 0 0,121 102 0 0 0,-62-83-2706 0 0,-132-93-10045 0 0,-20-12 6909 0 0,2 0 2602 0 0,20 15 1655 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="21271.72">2708 1023 12 0 0,'-1'1'298'0'0,"1"0"1"0"0,-1 1-1 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,2 2 1 0 0,5 4 1479 0 0,0 0 0 0 0,0-1 0 0 0,14 8 0 0 0,-10-6-1003 0 0,22 16 778 0 0,55 34 650 0 0,-76-50-2008 0 0,1-2 0 0 0,0 1 1 0 0,0-1-1 0 0,27 6 1 0 0,-37-11-176 0 0,-1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,4-2 0 0 0,-2 1-2 0 0,-1 0 1 0 0,0-1-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,3-7 1 0 0,0-2-18 0 0,-1-1-1 0 0,0 0 1 0 0,0 1 0 0 0,-1-2 0 0 0,-1 1 0 0 0,3-24 0 0 0,-3 0-782 0 0,-3-70-1 0 0,-1 91-1106 0 0,-1 0 0 0 0,-1 0 1 0 0,-8-27-1 0 0,11 43 1532 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-2-1 1 0 0,-5 5-4689 0 0,6 4 4984 0 0,1-7-462 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="21903.95">3069 1480 472 0 0,'-44'80'9443'0'0,"19"-33"-4509"0"0,23-42-4764 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,2 8 0 0 0,1-2-143 0 0,-1-1 0 0 0,1 0-1 0 0,0 0 1 0 0,1-1 0 0 0,0 1-1 0 0,11 13 1 0 0,-15-21-26 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,5-2 0 0 0,-3 1 10 0 0,-1-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,3-6 0 0 0,-1 2 167 0 0,-1 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,2-17 0 0 0,-4 21-54 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-5-3-1 0 0,-8-5-121 0 0,0 1 0 0 0,-1 1 0 0 0,0 0-1 0 0,0 1 1 0 0,-27-8 0 0 0,43 16-276 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0-2 0 0 0,6-15-4346 0 0,14-15-727 0 0,4 1 2281 0 0,-17 23 2594 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="22531.76">3422 1513 52 0 0,'7'37'4147'0'0,"-2"1"-1"0"0,-2 0 1 0 0,-1-1-1 0 0,-5 58 1 0 0,1-8-3653 0 0,-7-12-226 0 0,9-89-11 0 0,0 3-204 0 0,0 0 0 0 0,1-1 1 0 0,2-13-1 0 0,1 7 25 0 0,1 0 1 0 0,0 1-1 0 0,2-1 1 0 0,0 1-1 0 0,0 0 1 0 0,2 1-1 0 0,0 0 1 0 0,23-29-1 0 0,-32 44-66 0 0,1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,1 1 0 0 0,4 4 62 0 0,0 1 0 0 0,-1-1 0 0 0,10 16 1 0 0,1-1 10 0 0,-1-5-78 0 0,4 4 17 0 0,28 22 1 0 0,-41-37-22 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 1 0 0,12 3-1 0 0,-15-5-3 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 0-1 0 0,5-6 0 0 0,0-1 2 0 0,0 0 0 0 0,-1-1-1 0 0,0 0 1 0 0,10-21-1 0 0,-15 28-5 0 0,0-1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,-3-10 0 0 0,3 12 4 0 0,0 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-7 0 1 0 0,5 0-1 0 0,-1 1 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,-8 5 0 0 0,6-2 1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,1 1 1 0 0,0-1-1 0 0,-6 10 0 0 0,5-6 0 0 0,0 2 0 0 0,0-1 0 0 0,1 0 0 0 0,0 1 0 0 0,1 0 0 0 0,1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,1 1 0 0 0,0-1 0 0 0,1 23 0 0 0,2-28-5 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,0-1 0 0 0,7 7 0 0 0,-5-6-361 0 0,0 0-1 0 0,1-1 1 0 0,0 0 0 0 0,16 8-1 0 0,-14-9-745 0 0,0 0-1 0 0,0-1 0 0 0,0 0 0 0 0,12 2 0 0 0,-16-4 158 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,5-5-1 0 0,-4 2 371 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="22781.59">4107 2011 140 0 0,'1'26'1957'0'0,"-1"-22"-434"0"0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1-1 0 0,4 7 1 0 0,-5-10-829 0 0,1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0 0 0 0,3 2-1 0 0,21 5 2187 0 0,9-4-1936 0 0,-10-1-1138 0 0,0-1 0 0 0,0 0 1 0 0,47-5-1 0 0,-71 3-171 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1-1-761 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0-5 0 0 0,-1-5 295 0 0,0-39-3310 0 0,2 38 3538 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="23235.42">4797 1442 52 0 0,'0'0'648'0'0,"5"23"4985"0"0,16 104 8171 0 0,-12 4-9325 0 0,-10 129-2552 0 0,-7 14-2784 0 0,17-293-11303 0 0,3-30 7673 0 0,21-149-3644 0 0,-24 153 7471 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink22.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-07-18T14:23:45.355"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">6056 32 172 0 0,'-16'-3'1855'0'0,"-5"-10"5229"0"0,-2-1 373 0 0,21 13-7138 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-4 2 0 0 0,-31 21 642 0 0,31-18-909 0 0,0-1-1 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,1-1 1 0 0,1 1-1 0 0,-3 8 1 0 0,3-9-54 0 0,1-1 0 0 0,0 0-1 0 0,0 1 1 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,1-1 1 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,7 10 0 0 0,-8-14 3 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,3 1-1 0 0,-1-1 2 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,5-3 1 0 0,1-2 2 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,7-9 0 0 0,-7 8 1 0 0,-2-1-1 0 0,1 0 1 0 0,7-13-1 0 0,-13 19 10 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,-2-4-1 0 0,1 5 11 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,-3 0 0 0 0,-4 0 34 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-13 4 0 0 0,18-4-56 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,-2 5 0 0 0,4-6-6 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,2 2 0 0 0,-1-2 2 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,1-1 2 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1-1 0 0,3-4 1 0 0,4-2 17 0 0,-1-1-1 0 0,-1-1 1 0 0,15-16-1 0 0,-21 22-9 0 0,0 1 1 0 0,-1 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,1-3 0 0 0,-2 5-5 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-2 1 0 0 0,-2 0-5 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-7 6 1 0 0,8-6-7 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 7 0 0 0,1-9 6 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1-1 0 0,13-4 17 0 0,-11 3-6 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-4 0 0 0,-1 7-13 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-16 1-395 0 0,-13 12-1486 0 0,25-10 1053 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-5 7 0 0 0,-19 39-7023 0 0,21-36 6201 0 0,2-4 585 0 0,0-1-1 0 0,1 1 0 0 0,-4 18 0 0 0,4-11 447 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1229.97">5858 1351 364 0 0,'0'-3'250'0'0,"0"1"712"0"0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,0-1 1 0 0,0-2-1 0 0,0 4-643 0 0,1 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,-14 5-10 0 0,8-1-85 0 0,0-1 0 0 0,0 1 0 0 0,0 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 1 0 0 0,1 0 0 0 0,0-1 0 0 0,-8 12 0 0 0,12-15-215 0 0,-1 1 0 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,2 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 0 0 0 0,3 4-1 0 0,-3-4-5 0 0,-1 0 0 0 0,1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,2-1 1 0 0,8-6 128 0 0,-1-1-1 0 0,0-1 1 0 0,0 1 0 0 0,-1-2-1 0 0,-1 1 1 0 0,0-1 0 0 0,0-1-1 0 0,-2 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,7-19 0 0 0,-14 32-40 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1 0 1 0 0,0-1-1 0 0,-1 1 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,-1-2 1 0 0,1 1 39 0 0,-1 1 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,-3 0 0 0 0,-1 0 7 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 2 0 0 0,-6 1 0 0 0,6-1-110 0 0,-1 1 0 0 0,2 0 0 0 0,-1 0 0 0 0,0 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-6 7 0 0 0,10-10-35 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 0 1 0 0,1 1-1 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 1 1 0 0,2 0-1 0 0,-2-1-14 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,2 0-1 0 0,1-1-15 0 0,-1 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,5-5 1 0 0,-3 2 16 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,4-12-1 0 0,-7 18 28 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,-1-1 0 0 0,1 1 5 0 0,0 1 1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,-1 1 0 0 0,-3 0 20 0 0,0 0 0 0 0,-1 1 0 0 0,1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,-9 7 0 0 0,8-4-41 0 0,1 1 0 0 0,-1 1 0 0 0,2-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,1 1-1 0 0,-1 16 1 0 0,2-24 6 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,11-5-11 0 0,13-17 34 0 0,-23 19-26 0 0,8-7 6 0 0,-1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,0 0-1 0 0,-1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,9-24-1 0 0,-15 35 5 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-2 1 0 0,-1 1 2 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-5-1 1 0 0,0 0-74 0 0,-1 1 0 0 0,1 0 0 0 0,0 1 0 0 0,0 0 0 0 0,-10 0 0 0 0,-32 10-2505 0 0,47-9 1760 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,-2 2 0 0 0,-16 6-18168 0 0,19-6 18357 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1758.13">5735 1253 24 0 0,'-18'-1'6344'0'0,"15"2"-5363"0"0,0 0-1 0 0,0 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,-4-2 0 0 0,-39-12 3320 0 0,19 2-3498 0 0,-1 1-1 0 0,0 2 0 0 0,0 1 0 0 0,-57-9 0 0 0,-28 10-491 0 0,57 5-346 0 0,-100-17-1 0 0,116 7-461 0 0,37 11 154 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-2-4 0 0 0,4 3-626 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,4-5 1 0 0,0-4-1743 0 0,16-45-3724 0 0,-18 48 5987 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2094.3">5237 767 160 0 0,'0'0'153'0'0,"0"0"0"0"0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 1071 0 0,-1-1-1071 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-7 8 4792 0 0,-14 6 1300 0 0,19-13-5376 0 0,-56 38 1929 0 0,28-16-2634 0 0,2 1 0 0 0,-36 36 0 0 0,25-16-128 0 0,0 0 1 0 0,-44 71-1 0 0,81-113-30 0 0,1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,1 2-1 0 0,0-1-3 0 0,1 0 0 0 0,0 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,4 3 0 0 0,-5-5-5 0 0,71 74-412 0 0,-15-16-3321 0 0,-4 5-5661 0 0,-46-55 7619 0 0,-6-6 1092 0 0,1 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 0 1 0 0,2 3-1 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4191.66">248 378 52 0 0,'10'-27'3502'0'0,"-3"8"10269"0"0,0 20-11499 0 0,7 4-1184 0 0,-13-5-715 0 0,16 5 143 0 0,1-1 0 0 0,0-1-1 0 0,0 0 1 0 0,0-2 0 0 0,0 0 0 0 0,30-2 0 0 0,26 1-155 0 0,-43 0-563 0 0,21 3-1240 0 0,-21 6-4809 0 0,-52-20-6416 0 0,-9-14 8824 0 0,23 18 3294 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4402.65">470 292 108 0 0,'-17'31'8018'0'0,"-26"37"0"0"0,-3-5-1384 0 0,3-3-5946 0 0,-16 28-305 0 0,2-3-807 0 0,-70 78 0 0 0,109-141-152 0 0,11-13-291 0 0,0 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,-12 9 0 0 0,22-23-6378 0 0,15-29 3502 0 0,-2 13 2121 0 0,0 0 1 0 0,23-26-1 0 0,-23 30 1111 0 0,3-3 16 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4536.13">179 691 284 0 0,'5'-4'362'0'0,"1"-1"-1"0"0,-1 1 1 0 0,1 0-1 0 0,0 0 1 0 0,0 1-1 0 0,12-6 1 0 0,-16 8-172 0 0,-1 1 0 0 0,1-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 1-1 0 0,1 0 1 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,1 2-1 0 0,2 3 609 0 0,0 1-1 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 1 0 0 0,3 11 1 0 0,1 51 1218 0 0,-5-50-2291 0 0,7 40 1 0 0,1-30-4221 0 0,-6-55-3431 0 0,4-28 5003 0 0,-4 33 2452 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4855.95">367 745 292 0 0,'18'-31'1226'0'0,"-15"27"-204"0"0,0-1-1 0 0,1 1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,6-1 1 0 0,-6 2-503 0 0,1 0 1 0 0,0 0 0 0 0,0 1-1 0 0,-1 0 1 0 0,10 1-1 0 0,-13-1-471 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 1 0 0,0 1-1 0 0,-1 0-30 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 1 1 0 0,-2-1-1 0 0,1 0 0 0 0,-1 4 1 0 0,-1 6-103 0 0,-2 0 0 0 0,1-1 0 0 0,-2 1 0 0 0,0-1 0 0 0,-8 16 0 0 0,-10 13-485 0 0,-1-2 1 0 0,-45 56-1 0 0,61-86 544 0 0,0 0 0 0 0,0-1 0 0 0,-11 8 0 0 0,17-13 133 0 0,-1-1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,-1 0 0 0 0,-4 0 0 0 0,7 0-3 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,6-5 2290 0 0,19-3-60 0 0,-1 8-1803 0 0,0 1 1 0 0,-1 2-1 0 0,1 0 0 0 0,35 8 1 0 0,0-1-3191 0 0,1-4-3777 0 0,-53-6 5132 0 0,-1 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,5-4-1 0 0,-5 3 306 0 0,1-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,6-8 1 0 0,-2 3 403 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6384.83">1096 134 332 0 0,'3'15'1146'0'0,"0"1"0"0"0,-1 0 0 0 0,-1 0 0 0 0,-1 25 0 0 0,3 29 4857 0 0,-3-69-5894 0 0,0 0-68 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,0-1-625 0 0,-6-26-5207 0 0,3 21 5223 0 0,0 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 0-1 0 0,-5-4 1 0 0,2 3 87 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6610.38">865 397 96 0 0,'0'2'462'0'0,"0"-1"0"0"0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,3 0 0 0 0,8 2 1133 0 0,0-1 0 0 0,0-1 0 0 0,13 0 0 0 0,-11 0-1486 0 0,34-2 1150 0 0,58-8-1 0 0,-3-8-3295 0 0,-79 16-1706 0 0,-40 14-7055 0 0,11-10 10205 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,-8 0 0 0 0,1-3 7 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6824.15">866 414 8 0 0,'-2'10'1322'0'0,"-1"0"1"0"0,1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 1-1 0 0,2 18 0 0 0,0 7 2276 0 0,-4 23-1200 0 0,-2 0 0 0 0,-12 61 1 0 0,-2-37-3066 0 0,-2-1 0 0 0,-40 99-1 0 0,56-172 250 0 0,-16 40-2031 0 0,18-46 1932 0 0,1 0 0 0 0,-1-1 0 0 0,0 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-4 3-1 0 0,6-5 376 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,1 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 0 1 0 0,-6-17-1895 0 0,4 9 1487 0 0,1-1 0 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,0 0 0 0 0,3-14 0 0 0,0 4 86 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7105.56">1578 180 52 0 0,'13'-28'3251'0'0,"-6"3"13457"0"0,-25 55-15075 0 0,5 0-1432 0 0,-98 209 444 0 0,22-87-4809 0 0,61-118 1158 0 0,27-33 2780 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,0 0 0 0 0,-2-2-1 0 0,2 1-3 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-4 1 0 0,5-28-1383 0 0,-4 29 1331 0 0,13-43-1175 0 0,-4 18 924 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7252.98">1537 137 36 0 0,'4'0'446'0'0,"0"0"1"0"0,0 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,3 4-1 0 0,8 9 2691 0 0,-2 1 0 0 0,23 35 1 0 0,-18-24-1576 0 0,6 4-957 0 0,11 17-2113 0 0,-31-43 485 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,0-1 1 0 0,2 9-1 0 0,-4-11 498 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 0 0 0,-3 2 0 0 0,-3 2-49 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7652.25">1436 676 88 0 0,'1'1'360'0'0,"0"0"-1"0"0,1-1 1 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 0-1 0 0,1 1 1 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 1 0 0 0,3-2-1 0 0,34-16 4941 0 0,-35 16-4550 0 0,13-7 1547 0 0,-9 5-1579 0 0,1-1 0 0 0,-1 1 0 0 0,1 1 1 0 0,0 0-1 0 0,16-5 0 0 0,-22 8-693 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,1 2 0 0 0,0 2-87 0 0,0-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,1-1 1 0 0,-2 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-3 6 0 0 0,3-8-139 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-5 0 0 0 0,-26-10-1176 0 0,31 9 1302 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 2 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-8 2 0 0 0,10 0 136 0 0,1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 4 0 0 0,-17 49 1339 0 0,18-50-1254 0 0,-3 9 160 0 0,1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,1 1 0 0 0,0-1-1 0 0,1 1 1 0 0,0-1 0 0 0,1 0 0 0 0,1 1-1 0 0,0-1 1 0 0,1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,1-1 0 0 0,0 1 0 0 0,1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,2-1 0 0 0,0 0-1 0 0,1-1 1 0 0,0 1 0 0 0,12 11-1 0 0,-9-13-110 0 0,0-1-1 0 0,0 0 0 0 0,0-1 1 0 0,1 0-1 0 0,0-1 0 0 0,1 0 1 0 0,0-1-1 0 0,0-1 0 0 0,0 0 1 0 0,29 5-1 0 0,-28-7-309 0 0,-1-2 0 0 0,1 1 0 0 0,0-2 0 0 0,24-2 0 0 0,-27 1-566 0 0,-1-1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 1 0 0,10-6-1 0 0,-16 7-241 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 1 0 0,6-11-1 0 0,-1-1-1334 0 0,-1-1-1 0 0,9-35 1 0 0,-16 52 2246 0 0,5-22-633 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8140.29">2283 390 652 0 0,'5'3'1188'0'0,"0"0"0"0"0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,9 0 0 0 0,7-2 2279 0 0,41-9 1 0 0,5 0-2452 0 0,5 3-906 0 0,-65 7-755 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,10-7 0 0 0,-15 9 238 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,-1-2-1 0 0,-2-8-1602 0 0,-1 1 0 0 0,-12-22 1 0 0,15 31 1726 0 0,-6-11-429 0 0,1 1 195 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8518.28">2552 43 224 0 0,'3'4'1186'0'0,"-1"1"1"0"0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 6 0 0 0,-1-1 533 0 0,0 0-1 0 0,-1 0 1 0 0,-1 17-1 0 0,-4 4 745 0 0,-15 55 0 0 0,14-64-2596 0 0,-3 6-88 0 0,0 1-1 0 0,-2-2 1 0 0,-1 1 0 0 0,-22 36-1 0 0,23-47-703 0 0,0 0-1 0 0,-1-1 1 0 0,-1-1 0 0 0,-19 19-1 0 0,25-28 88 0 0,0 0-1 0 0,0 0 1 0 0,-1-1 0 0 0,0 0-1 0 0,0-1 1 0 0,-14 7 0 0 0,22-11 894 0 0,-1 1 1 0 0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 2 0 0 0,5 26 1636 0 0,-4-22-1285 0 0,13 105 3978 0 0,-12-74-3770 0 0,-2 0 1 0 0,-6 58 0 0 0,-3-43-1160 0 0,-2-20-3768 0 0,11-32 4187 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0-1-1 0 0,-9-11-2347 0 0,6 3 1694 0 0,0-1 1 0 0,1 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,1 0-1 0 0,0 1 0 0 0,0-1 0 0 0,3-14 1 0 0,2 1 197 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8787.84">2420 525 116 0 0,'5'-5'1638'0'0,"0"1"0"0"0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,7-2 0 0 0,31-6 7961 0 0,-16 5-6891 0 0,-19 3-2820 0 0,-7 2 145 0 0,-1-1-1 0 0,1 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,1 2-1 0 0,-1 0 72 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 4-1 0 0,1 9 418 0 0,0 0-1 0 0,-2 0 1 0 0,-2 30-1 0 0,2-34-451 0 0,-8 106-386 0 0,1-34-589 0 0,8 165 0 0 0,-1-248 781 0 0,1 19-1018 0 0,-3-8-2682 0 0,-10-33-3914 0 0,-13-42-2302 0 0,-5-35 3491 0 0,23 75 5779 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9011.42">2439 590 152 0 0,'-1'0'172'0'0,"0"0"201"0"0,0 0 1 0 0,0 0-1 0 0,-12 11 15956 0 0,23-1-13295 0 0,-3-7-2728 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 0 1 0 0,0 0 0 0 0,13 0-1 0 0,-16-2-919 0 0,0 1 0 0 0,1-1 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 1 0 0 0,11-4-1 0 0,-10 1-5281 0 0,-17 10-6282 0 0,6-3 12519 0 0,2 1-964 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9178.49">2461 743 196 0 0,'0'1'478'0'0,"0"-1"-1"0"0,0 1 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1 0 0 0,0-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,17 0 5744 0 0,2-7-5062 0 0,-4-1-4027 0 0,-32 21-13935 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9365.71">2422 860 192 0 0,'1'2'804'0'0,"0"1"0"0"0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,3 1 0 0 0,1 0 682 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,10-1 1 0 0,-6 0-1846 0 0,-5 0 113 0 0,0-1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0-1 0 0,8-2 1 0 0,1-1-5423 0 0,-33-6-1138 0 0,11 10 5629 0 0,0 0 1 0 0,0 1-1 0 0,-16 3 0 0 0,12-1 573 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9585.31">2126 1020 52 0 0,'-10'17'1671'0'0,"10"-16"-1160"0"0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 2 0 0 0,1-2 19 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,1 2 1 0 0,18 4 1564 0 0,41 4 958 0 0,109 3 0 0 0,-44-5-2338 0 0,-42-1-1165 0 0,27 3-1802 0 0,-38-1-2984 0 0,-56-3 1015 0 0,-17-6 4054 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,-18 5-6292 0 0,4-5 6332 0 0,5-2-650 0 0,-1-1 170 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9740.21">2436 1094 112 0 0,'-21'16'1449'0'0,"10"-8"-72"0"0,0 1 1 0 0,-13 13-1 0 0,-17 19 2274 0 0,25-26-3178 0 0,2 0 1 0 0,-19 23-1 0 0,30-34-812 0 0,1-1-46 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-5 2 0 0 0,7-4 298 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,1-1-1 0 0,4-15-1016 0 0,2 8 731 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9871.82">2285 1218 216 0 0,'3'-1'308'0'0,"0"1"0"0"0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,5 3 0 0 0,41 24 4920 0 0,-25-13-2872 0 0,95 41 3014 0 0,4-11-4869 0 0,-102-37-867 0 0,2-1-1997 0 0,33 8 1 0 0,-51-13 1672 0 0,0-1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1-1 0 0 0,0 1 1 0 0,5-3-1 0 0,-7 2 371 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,2-5 1 0 0,3-3-346 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10083.7">3254 297 136 0 0,'4'10'21459'0'0,"2"-4"-21052"0"0,-4 1-5706 0 0,-2-6 4927 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,-26 6-4143 0 0,24-6 3976 0 0,-5 0-338 0 0,-2-1 180 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10241.11">2979 499 36 0 0,'-7'33'1967'0'0,"-9"17"5290"0"0,0-1-82 0 0,9-16-5401 0 0,7-32-1923 0 0,0-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,7-9-4682 0 0,10-22-227 0 0,8-22 1461 0 0,-18 37 3042 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10434.46">3063 492 568 0 0,'42'17'8901'0'0,"-34"-13"-6748"0"0,0 0 1 0 0,0-1 0 0 0,17 5 0 0 0,16-2 1516 0 0,77 1 0 0 0,-72-5-2773 0 0,53 7 0 0 0,-95-8-918 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,7 4-1 0 0,-9-5-65 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,0 1 0 0 0,-1 1 0 0 0,-2 4-1200 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,0 0-1 0 0,-12 10 1 0 0,5-7-269 0 0,1-1 0 0 0,-1 0 0 0 0,-1-1 0 0 0,1-1 0 0 0,-18 6-1 0 0,16-7 887 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10677.86">3193 602 340 0 0,'-1'0'367'0'0,"0"0"1"0"0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0 1 0 0 0,-17 30 3460 0 0,13-22-2968 0 0,-37 66 1725 0 0,-35 57-1991 0 0,65-114-1251 0 0,9-12-594 0 0,-1 0-1 0 0,-1-1 0 0 0,-9 12 1 0 0,20-43-7486 0 0,14-12 6417 0 0,-15 28 1712 0 0,17-27-653 0 0,-8 17 804 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10814.92">3193 657 60 0 0,'2'-1'247'0'0,"0"0"1"0"0,0 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,2 3 1 0 0,5 5 1866 0 0,0 0 1 0 0,-1 1 0 0 0,13 19 0 0 0,-7-9 847 0 0,18 14-786 0 0,-24-27-3417 0 0,0 1 0 0 0,12 16-1 0 0,-22-17-6957 0 0,1-7 7957 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,-21 4-2705 0 0,14-3 2072 0 0,0 1 416 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="11209.12">3075 951 176 0 0,'0'2'433'0'0,"0"0"1"0"0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,1 0 1 0 0,0 1-1 0 0,1-1 92 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,3 0 1 0 0,1 0-56 0 0,0 0 0 0 0,0-1 0 0 0,14-3 0 0 0,13-9-2279 0 0,-30 11 1431 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1-1 0 0 0,7-7 0 0 0,-20 33 236 0 0,0 0 0 0 0,1 0 0 0 0,-11 45 0 0 0,17-55 144 0 0,-12 37 352 0 0,1-2 461 0 0,2 0-1 0 0,-8 61 1 0 0,21-90 803 0 0,0-17-1495 0 0,-1-1 0 0 0,0 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 1 0 0 0,3-2 242 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,5-3-1 0 0,-7 4-392 0 0,15-5 90 0 0,0 0 1 0 0,0 1-1 0 0,0 0 0 0 0,1 1 1 0 0,-1 2-1 0 0,1-1 1 0 0,20 2-1 0 0,-34 0-751 0 0,1 0-1 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-1 1 0 0,4-3-1 0 0,-3 1-149 0 0,0 1 0 0 0,-1-1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,3-6 0 0 0,20-50-2498 0 0,-15 37 2640 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="11614.44">3798 223 480 0 0,'0'9'3169'0'0,"-1"-8"-2453"0"0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,0 3 0 0 0,0-4-371 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1-1 1 0 0,57-12 3933 0 0,-18 3-2697 0 0,1 2 1 0 0,82-4 0 0 0,-109 10-1429 0 0,-13 2-120 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,3 1 0 0 0,-6-1 6 0 0,-5 18 157 0 0,-21 14-575 0 0,0-1 1 0 0,-36 33-1 0 0,-67 52-2316 0 0,32-31 418 0 0,45-39 725 0 0,-41 40-5284 0 0,92-87 6643 0 0,1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,0-13-3263 0 0,11-19 610 0 0,-6 24 2272 0 0,0 1 0 0 0,1 0 0 0 0,9-12 0 0 0,-2 6 44 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="11743.19">3777 512 328 0 0,'2'0'227'0'0,"0"-1"0"0"0,0 0-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 1 0 0 0,3-1-1 0 0,-4 1 57 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,1 4 0 0 0,15 49 5281 0 0,1 4-2333 0 0,-16-52-3271 0 0,1-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,4 5 0 0 0,-7-9-190 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 1 0 0,0 1-1 0 0,2-3 0 0 0,2-2-1023 0 0,1 0 1 0 0,-1-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,5-10 0 0 0,-1 3 849 0 0,-2 3-48 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="12101.37">4061 557 96 0 0,'4'-2'1155'0'0,"0"1"0"0"0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,5 2 0 0 0,26 6 4326 0 0,-8 4-5151 0 0,-25-11-317 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 4 0 0 0,-1-2-46 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,-2 6 0 0 0,-2 2-247 0 0,0 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,-13 17 0 0 0,11-18-28 0 0,-1-1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1-1 0 0 0,-20 15 1 0 0,23-20 373 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-2-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0-1-1 0 0,-11 0 1 0 0,4-2 1784 0 0,23-3 509 0 0,24-3-899 0 0,-9 5-1469 0 0,44 2 1 0 0,-57 1-1791 0 0,0 0-1 0 0,1 1 1 0 0,14 5 0 0 0,-31 9-15872 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="12750.15">3972 879 28 0 0,'-1'1'301'0'0,"0"-1"0"0"0,0 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,1 2 1 0 0,0 1 715 0 0,1 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,3 6 0 0 0,13 24 1305 0 0,-14-12-1505 0 0,-1-1 1 0 0,0 1 0 0 0,-2 0 0 0 0,0 33-1 0 0,1 0-119 0 0,11 173 777 0 0,-12-176-1230 0 0,-2-51-255 0 0,-19-12-1157 0 0,3 0-209 0 0,2-2 0 0 0,0 0 0 0 0,0-1 0 0 0,1 0 0 0 0,-15-22 0 0 0,-48-86-1862 0 0,0 0 6232 0 0,67 110-2194 0 0,1 2 517 0 0,1 0 0 0 0,0-1 1 0 0,0 0-1 0 0,-9-21 0 0 0,16 32-1285 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 9 201 0 0,2 12-508 0 0,3 16-39 0 0,-4-32-216 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,2 5 1 0 0,-2-8 269 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,3 0 0 0 0,5 0-263 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-2 1 0 0,0 1-1 0 0,-1-1 0 0 0,1-1 1 0 0,10-5-1 0 0,11-8 679 0 0,46-33-1 0 0,-13 7 1613 0 0,-32 21-223 0 0,-25 16-820 0 0,0 1 0 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,15-4 0 0 0,-22 7-623 0 0,1 0-1 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,1 0 42 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 2 0 0 0,-17 37 1287 0 0,16-37-1303 0 0,-5 9 70 0 0,1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,1 1-1 0 0,-3 20 1 0 0,6-27-59 0 0,-1 0 0 0 0,2 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,1 0 1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 1 0 0 0,5 3 0 0 0,30 19 364 0 0,9-5-3299 0 0,-37-19 792 0 0,-1 1 1 0 0,1-1 0 0 0,0-1-1 0 0,0 0 1 0 0,0-1-1 0 0,21 0 1 0 0,-26-1 1162 0 0,-1-1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0-1 0 0,7-3 1 0 0,-6 1 192 0 0,0 0-1 0 0,0-1 0 0 0,0 0 1 0 0,-1 1-1 0 0,9-10 0 0 0,1-3-70 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink23.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-07-18T14:24:26.682"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">32 566 292 0 0,'-1'2'540'0'0,"-22"25"4465"0"0,18-17-325 0 0,3 1 3794 0 0,7-12-4189 0 0,19-1-2202 0 0,-12 0-1429 0 0,69-6 3173 0 0,-72 8-3545 0 0,0 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,16 5 0 0 0,77 26-952 0 0,-99-32 255 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,3 0 1 0 0,11-4-6034 0 0,-10-16-3210 0 0,-4-24 2455 0 0,2-11 3448 0 0,-1 40 3174 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="282.49">381 233 172 0 0,'0'0'146'0'0,"0"0"1"0"0,-1 0-1 0 0,1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 1 0 0,9 9 4628 0 0,15 8 2157 0 0,40 21 210 0 0,-48-28-6394 0 0,-1 1 0 0 0,1 0 0 0 0,-2 1 0 0 0,0 0 1 0 0,0 1-1 0 0,21 29 0 0 0,-10-7-464 0 0,20 28 400 0 0,-41-56-631 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,3 17 0 0 0,-6-22-53 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,-3 4 0 0 0,-6 7 0 0 0,-24 19 0 0 0,23-20 0 0 0,-7 4-1689 0 0,-1-1 0 0 0,0-1 0 0 0,-43 23 1 0 0,-73 25-8384 0 0,93-43 8623 0 0,31-14 293 0 0,-50 19-4091 0 0,57-22 4774 0 0,1-1-1 0 0,-1 0 0 0 0,0 0 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,-6-1 0 0 0,-1-5-580 0 0,2-3 208 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1521.33">1350 161 460 0 0,'-25'7'13529'0'0,"33"-8"-8266"0"0,9-3-3428 0 0,21 0-459 0 0,47 2-1 0 0,17-1-1102 0 0,-63-5-568 0 0,-31 5-186 0 0,-1 1 0 0 0,1 1 0 0 0,15-2 0 0 0,-22 3 127 0 0,-11 20-2384 0 0,-3-5 2645 0 0,-2-2 1 0 0,1 0 0 0 0,-2 0 0 0 0,0-1-1 0 0,-17 9 1 0 0,-19 15 284 0 0,-35 30-669 0 0,3 4 0 0 0,3 3-1 0 0,-73 87 1 0 0,144-147-962 0 0,20-21-551 0 0,-5 2 1925 0 0,0 1 1 0 0,1-1-1 0 0,0 1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,1 1 1 0 0,-1 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,8 1 1 0 0,11 1 374 0 0,-20 0-172 0 0,-1-1-1 0 0,1 1 1 0 0,0-1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,0-1-1 0 0,-1 1 1 0 0,14-5-1 0 0,-10 0 231 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,9-10 0 0 0,-14 11-174 0 0,0 1 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 1 0 0,0 0 0 0 0,0 1-1 0 0,11-3 1 0 0,-15 5-115 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,4 2-1 0 0,-4 0 5 0 0,1-1-1 0 0,-1 0 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 1 0 0 0,2 5 1 0 0,-1-3 13 0 0,-1 1 1 0 0,1 0 0 0 0,-2 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,-2-1 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,-3 12-1 0 0,1-14-1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 0 1 0 0,-8 2-1 0 0,-11 3 207 0 0,-1-2 1 0 0,0-1-1 0 0,-36 2 0 0 0,58-6-286 0 0,-1 0-11 0 0,-48 2 191 0 0,49-2-251 0 0,-1 0-1 0 0,1-1 1 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,-7-3 0 0 0,11 5-14 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,13-28-1874 0 0,-10 24 1351 0 0,96-165-10798 0 0,9 5 4978 0 0,-61 100 4990 0 0,-26 31 934 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1681.32">1870 0 52 0 0,'7'6'1071'0'0,"0"0"1"0"0,0 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,5 9 1 0 0,-4-5 2405 0 0,-1 1 0 0 0,10 23 1 0 0,-2-6 583 0 0,0 1-3718 0 0,-14-26-984 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 4 0 0 0,-11 14-8170 0 0,9-19 8227 0 0,0 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,-2 1 0 0 0,1-1-11 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1875.61">1854 296 196 0 0,'-5'9'996'0'0,"-12"25"2746"0"0,17-33-3209 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 0 0 0,0 2 0 0 0,1-4-281 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,25-8 3123 0 0,-24 8-2936 0 0,11-3 1 0 0,-1 0 0 0 0,1 1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 2 0 0 0,19 2 0 0 0,-10 0-725 0 0,30 8-1 0 0,18 12-4000 0 0,-66-21 5174 0 0,6 2-1836 0 0,0-3-7877 0 0,-14-19-2574 0 0,0 12 10703 0 0,-5-1 133 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2052.53">1919 327 252 0 0,'-12'10'1347'0'0,"1"2"0"0"0,0-1-1 0 0,1 1 1 0 0,1 1 0 0 0,0-1 0 0 0,-13 26 0 0 0,-35 92 8497 0 0,18-37-7014 0 0,-27 61-1957 0 0,56-127-1566 0 0,8-10-3273 0 0,-18-22-12134 0 0,11-3 14421 0 0,5 2 1090 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2466.61">1361 765 216 0 0,'4'-3'-566'0'0,"5"-7"10621"0"0,-16 14-6515 0 0,-20 20-41 0 0,1 0 0 0 0,-37 46 0 0 0,-37 62-1957 0 0,58-74-2045 0 0,-75 81 0 0 0,83-108-427 0 0,31-29 666 0 0,0 0 1 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,-5 0 1 0 0,9-1 106 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1-1-1 0 0,6-33-3435 0 0,2 6 1543 0 0,2 1-1 0 0,16-32 1 0 0,-6 20 786 0 0,3 1 0 0 0,32-42 0 0 0,-31 48 794 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2611.25">1272 732 4 0 0,'4'0'290'0'0,"1"1"1"0"0,-1-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,-1 1 0 0 0,5 5 1 0 0,4 9 1457 0 0,-1-1 1 0 0,-1 2-1 0 0,10 25 1 0 0,-6-12 557 0 0,45 89 3608 0 0,-42-93-6132 0 0,1 0 0 0 0,23 28 0 0 0,-33-45-2626 0 0,-22-13-12483 0 0,5-4 12909 0 0,2 2 4207 0 0,-3-2-2589 0 0,2 1 127 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3045.58">1219 1132 232 0 0,'-1'1'258'0'0,"1"-1"0"0"0,0 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,0 0 159 0 0,0 0 1 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 1 0 0,2-1-1 0 0,42-3 5435 0 0,-36 1-4978 0 0,1 1-521 0 0,-1 1 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,15 6 0 0 0,-21-6-334 0 0,0 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 5-1 0 0,1 1-126 0 0,-2 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,-1 0 0 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,-1-1 0 0 0,0 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,0-1-1 0 0,0 0 1 0 0,-13 10 0 0 0,19-17-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,0-1-63 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,-1-2 0 0 0,-2-8-321 0 0,0 0 1 0 0,0 0-1 0 0,-4-23 0 0 0,8 33 467 0 0,-1-7 125 0 0,0 1 0 0 0,-1-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-11-16 0 0 0,14 24-36 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,0-1 1 0 0,0 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0-1 0 0,-2 2 1 0 0,-2 0 170 0 0,1 1-1 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 1 0 0,0-1 0 0 0,-4 7-1 0 0,0 2 63 0 0,2-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,1 1 1 0 0,1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,2 0 0 0 0,-1 1 0 0 0,2-1-1 0 0,0 24 1 0 0,1-29-157 0 0,1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,1-1-1 0 0,0 1 0 0 0,0-1 1 0 0,1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,0-1 1 0 0,1-1-1 0 0,-1 0 1 0 0,11 8-1 0 0,0-2 122 0 0,2-2 0 0 0,-1 0 0 0 0,1-1-1 0 0,1 0 1 0 0,0-2 0 0 0,0 0 0 0 0,41 7 0 0 0,-39-10-1459 0 0,1-2 0 0 0,0 0 1 0 0,0-2-1 0 0,24-1 0 0 0,-42 0-177 0 0,1 0 1 0 0,0 1-1 0 0,-1-2 1 0 0,1 1-1 0 0,5-3 0 0 0,-9 3 813 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,1-1 0 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1-2 0 0 0,3-8-1629 0 0,-4 6 1446 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink24.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-07-18T14:24:30.547"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">653 270 220 0 0,'-10'15'1556'0'0,"1"1"1"0"0,0 1-1 0 0,2-1 0 0 0,0 1 0 0 0,0 1 1 0 0,-6 30-1 0 0,9-31-334 0 0,-3 9 756 0 0,2 0 0 0 0,1 0 0 0 0,-1 30 0 0 0,4 82 469 0 0,2-76-2361 0 0,-1-52-190 0 0,-1-4-173 0 0,1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,5 11 0 0 0,-6-16 214 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,6-7-1684 0 0,1-12-741 0 0,22-140-6321 0 0,-6 19 5784 0 0,-14 101 2467 0 0,2 0 125 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="236.65">735 198 80 0 0,'0'0'416'0'0,"1"-1"0"0"0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,34 12 4830 0 0,-18-6-3363 0 0,96 14 1815 0 0,-90-18-3134 0 0,0 1 0 0 0,0 0 0 0 0,0 2 1 0 0,0 1-1 0 0,34 15 0 0 0,-49-18-399 0 0,0 1-1 0 0,0 0 1 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0-1 0 0,12 12 1 0 0,-17-14-159 0 0,0-1-1 0 0,-1 1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,-1 8 1 0 0,-1 0-412 0 0,0 0-1 0 0,-1-1 1 0 0,0 0 0 0 0,0 1 0 0 0,-2-1 0 0 0,1-1 0 0 0,-1 1-1 0 0,-1-1 1 0 0,-9 15 0 0 0,5-12-1019 0 0,1 0-1 0 0,-2-1 1 0 0,0-1 0 0 0,0 1-1 0 0,-1-2 1 0 0,-20 15-1 0 0,23-18 563 0 0,0-2 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,1-1-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-19-4 0 0 0,13 0 356 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="486.02">750 346 308 0 0,'-18'-5'3246'0'0,"18"5"-3014"0"0,-1 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 0 0 0,1 1 1 0 0,0 0-1 0 0,0 0 151 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,1 1-1 0 0,0 0 1 0 0,9 5-90 0 0,0-1 1 0 0,0 0-1 0 0,1-1 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 0-1 0 0,0-1 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 0-1 0 0,22-4 1 0 0,-21 1-1090 0 0,0 0 0 0 0,0-1 1 0 0,0 0-1 0 0,-1-1 1 0 0,0 0-1 0 0,0-1 1 0 0,19-12-1 0 0,-58 37-10985 0 0,-44 38 6781 0 0,58-45 4480 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="608.65">773 568 0 0 0,'-21'11'844'0'0,"-27"17"2036"0"0,44-25-2123 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,-2 5-1 0 0,5-8-526 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 1 0 0,0-1-1 0 0,-1 1 0 0 0,2 0 0 0 0,35 17 943 0 0,-27-14-605 0 0,5 3-562 0 0,0-1-1 0 0,0 0 1 0 0,1-2-1 0 0,0 0 1 0 0,-1 0-1 0 0,1-2 1 0 0,0 0 0 0 0,1 0-1 0 0,-1-2 1 0 0,20-1-1 0 0,-26 0-644 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,11-15 0 0 0,-5 0-630 0 0,-1 1 0 0 0,-1-1 0 0 0,-1-1 0 0 0,-1 0 0 0 0,-1 0 0 0 0,9-44 0 0 0,-11 37 800 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="835.97">1137 22 408 0 0,'-1'-2'217'0'0,"0"1"-1"0"0,1-1 1 0 0,-1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-3 1 1 0 0,0 1 290 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-3 5 1 0 0,-9 14 936 0 0,1 0 0 0 0,1 0 1 0 0,1 1-1 0 0,-13 41 1 0 0,-21 101 385 0 0,44-161-1780 0 0,-19 82 672 0 0,-12 108-1 0 0,29-159-629 0 0,1 1-1 0 0,2-1 0 0 0,1 0 1 0 0,2 0-1 0 0,1 0 1 0 0,9 36-1 0 0,-10-62-82 0 0,-1 0-1 0 0,1 0 1 0 0,1 0-1 0 0,0-1 1 0 0,0 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,12 12 1 0 0,-14-16-55 0 0,0-1 1 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,4-2-1 0 0,3-2-732 0 0,0-1 0 0 0,-1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,-1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1-1 0 0 0,0 0-1 0 0,0-1 1 0 0,10-15 0 0 0,-5 5-1342 0 0,-1-1-1 0 0,-1 0 1 0 0,-1-1 0 0 0,-1 0 0 0 0,8-26 0 0 0,-16 39 1506 0 0,-1 0 161 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1190.43">275 1228 200 0 0,'2'-4'1102'0'0,"0"1"0"0"0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,6-3 0 0 0,19-1 2668 0 0,16 5-1633 0 0,54 4 0 0 0,-56 0-2743 0 0,61-5 0 0 0,-54 0-4269 0 0,-48 2 3338 0 0,-21-23-13698 0 0,11 19 14639 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1378.53">475 1225 12 0 0,'-51'55'6542'0'0,"-63"87"-1"0"0,-31 71-2356 0 0,113-164-4533 0 0,28-44 313 0 0,-7 13-443 0 0,0-1-1 0 0,-1-1 0 0 0,-2 0 1 0 0,1 0-1 0 0,-18 14 0 0 0,30-29 326 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 0 0 0,-2 0 0 0 0,2 0 16 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-2-3-281 0 0,1 1-1 0 0,0-1 1 0 0,1 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,2-6-1 0 0,1-7-198 0 0,0 0-1 0 0,2 0 1 0 0,0 1-1 0 0,0-1 0 0 0,2 1 1 0 0,9-20-1 0 0,-3 11 212 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1789.91">213 1478 184 0 0,'4'5'258'0'0,"1"-1"0"0"0,-1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,2 7 0 0 0,2 11 1204 0 0,7 30 1 0 0,-8-26-192 0 0,14 87 3124 0 0,0-1-2791 0 0,-19-113-1618 0 0,-1 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,2 2 1 0 0,-2-2-9 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0-2 0 0 0,5-4-66 0 0,0-1 1 0 0,-1 0-1 0 0,0-1 1 0 0,6-16-1 0 0,3-13 81 0 0,-6 14 365 0 0,1 1-1 0 0,1 0 1 0 0,26-44-1 0 0,-36 66-265 0 0,1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,2-1 0 0 0,-3 2 26 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,1 2 0 0 0,1 3 116 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,2 13 0 0 0,-4-10-174 0 0,0-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-2 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,-7 11-1 0 0,-7 9 16 0 0,-44 50-1 0 0,17-23 30 0 0,28-34 247 0 0,-27 24 1 0 0,30-30 1256 0 0,38-15-1298 0 0,50-7-226 0 0,22-4-1273 0 0,-85 9 323 0 0,0 0-1 0 0,0-1 1 0 0,0 0-1 0 0,0-1 1 0 0,0-1 0 0 0,10-5-1 0 0,-13 4-46 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,5-9-1 0 0,5-12-1637 0 0,15-38 0 0 0,-17 36 1560 0 0,-3 2 360 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1955.88">908 1212 184 0 0,'0'0'1690'0'0,"-8"18"4238"0"0,6-10-4100 0 0,1-1-235 0 0,0 0-1 0 0,0 1 1 0 0,1 13-1 0 0,6-3-1363 0 0,-5-18-390 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,2 0-494 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,7-4 0 0 0,30-26-2717 0 0,-13 10 1856 0 0,-13 11 1016 0 0,-1-2 93 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2728.72">1228 1118 420 0 0,'2'1'404'0'0,"-1"1"-1"0"0,0-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 3 0 0 0,0-1 153 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,-2 2 0 0 0,-30 28 3976 0 0,-1-6-3386 0 0,25-20-1795 0 0,-30 18 651 0 0,0-1-1 0 0,-2-2 0 0 0,-68 25 0 0 0,-25 12 371 0 0,130-56-316 0 0,-2 0 121 0 0,1 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-10 10 0 0 0,16-13-140 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0-1 0 0,0-1 1 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 1 0 0 0,2-1 0 0 0,22 9 195 0 0,18 0-41 0 0,1-2 0 0 0,1-2 0 0 0,62 0 0 0 0,16 1-3092 0 0,-63 1-4858 0 0,-59-7 7634 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,-4-10-2214 0 0,-11-7 860 0 0,13 16 1524 0 0,0 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,-5 1 1 0 0,3 1 194 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 1 0 0 0,1 0 0 0 0,-6 3 0 0 0,-7 5 741 0 0,0 0 1 0 0,1 2-1 0 0,-19 15 0 0 0,33-24-882 0 0,-68 54 2487 0 0,-120 125 0 0 0,190-180-2569 0 0,-21 24 184 0 0,21-24-180 0 0,0-1 0 0 0,0 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,1 2 0 0 0,0-3 7 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,2-1 0 0 0,36-7 582 0 0,31-16 207 0 0,-46 15-641 0 0,0 1 0 0 0,33-6 0 0 0,-57 14-175 0 0,1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 0 0 0 0,0 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 1 0 0 0,0 0-1 0 0,0 0 9 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,-2 3 0 0 0,-33 32 118 0 0,-16 12-104 0 0,-71 58-47 0 0,70-58 35 0 0,50-46 29 0 0,5-2-13 0 0,8-5 0 0 0,16-9-13 0 0,13-12 4 0 0,39-22 12 0 0,-68 43-29 0 0,0 0 1 0 0,0 1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 2 0 0 0,16-3 0 0 0,-24 5-6 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,1 3-1 0 0,0 7-919 0 0,0 0-1 0 0,-1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,-2 15 1 0 0,1 5-4917 0 0,1-34 5690 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 1 1 0 0,0-2 2 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,1-1 0 0 0,5-7-244 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3241.56">1259 1586 164 0 0,'2'-6'614'0'0,"2"-16"2330"0"0,-4 21-2685 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,-3 4 3782 0 0,-11 8-482 0 0,7 1-2796 0 0,1-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-8 20-1 0 0,-16 55-620 0 0,29-81-47 0 0,-4 6-82 0 0,1 1-1 0 0,0 0 0 0 0,2-1 1 0 0,-1 2-1 0 0,1-1 1 0 0,1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,3 16 1 0 0,-1-28-15 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,2-1 1 0 0,4-1-2 0 0,1 0 0 0 0,-1-1 0 0 0,-1 1 0 0 0,9-5 0 0 0,1-2-1 0 0,0-2 0 0 0,17-12 1 0 0,2-2-38 0 0,-35 24 40 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,2 1 1 0 0,-1-1 0 0 0,-1 1 1 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 4 7 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,-3 5 0 0 0,-6 10-3 0 0,-1-2-1 0 0,0 0 1 0 0,-2 0 0 0 0,0-2 0 0 0,-1 1-1 0 0,-29 24 1 0 0,34-34 17 0 0,1 1 0 0 0,0 0-1 0 0,1 0 1 0 0,-11 13 0 0 0,18-19-12 0 0,-1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,-1 4 0 0 0,2-6-10 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,3 1 0 0 0,-3-2-26 0 0,1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 0 0 0 0,4 1 0 0 0,0-1-76 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,8-4 0 0 0,2-2-419 0 0,-1 0 0 0 0,0-1 1 0 0,20-14-1 0 0,65-62-3489 0 0,-27 20 1521 0 0,-71 63 2502 0 0,0 0 1 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,2 1-1 0 0,-2 0 24 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 1-1 0 0,0 1 1 0 0,1 5-92 0 0,0 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 0 0 0 0,-3 13 0 0 0,0-10-813 0 0,0 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,-10 12-1 0 0,2-5-486 0 0,0-1 0 0 0,-1 0 0 0 0,-28 22 0 0 0,26-25 950 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3573.38">448 2825 428 0 0,'0'0'89'0'0,"0"0"0"0"0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 1 0 0 0,2 11 2313 0 0,-1 18-231 0 0,-1-26-1501 0 0,0 93 7127 0 0,1 30-3170 0 0,-11 168-3273 0 0,8-260-1454 0 0,-11 103-588 0 0,-3-49-3009 0 0,16-87 3434 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,-1 0 0 0 0,2-1 8 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1-2 0 0 0,-3-11-406 0 0,0 0 0 0 0,1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,2 0 0 0 0,2-20 0 0 0,1-8 44 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3738.96">653 2414 76 0 0,'2'-11'451'0'0,"-1"6"39"0"0,-1 1 0 0 0,1-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,4-7 1 0 0,-1 42 4296 0 0,-3-16-3826 0 0,0 0 0 0 0,0 16 0 0 0,-2-23-1819 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 1 0 0,1 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,1-1-1 0 0,1 1 0 0 0,4 8 0 0 0,-4-9 448 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4058.48">917 2649 316 0 0,'20'-9'1290'0'0,"111"-38"10588"0"0,-122 46-11414 0 0,0-1 0 0 0,-1 2 1 0 0,1-1-1 0 0,-1 1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 1 1 0 0,8 6-1 0 0,3 3-29 0 0,0 0 1 0 0,-1 1-1 0 0,-1 1 0 0 0,-1 1 1 0 0,19 24-1 0 0,-26-28-76 0 0,-1 0 1 0 0,0 1-1 0 0,-1 0 0 0 0,0 0 0 0 0,-1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,-1 0 0 0 0,3 27 1 0 0,-1 9 372 0 0,-2 81 1 0 0,-4-124-692 0 0,-16 486 372 0 0,16-474-609 0 0,0-13-4 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,-5 10 1 0 0,5-16 21 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,-3-2 0 0 0,-36-15-3782 0 0,17 4 1767 0 0,0-2 0 0 0,1-1 0 0 0,1-1 0 0 0,1 0 0 0 0,-32-36 0 0 0,16 9-558 0 0,-52-80 0 0 0,66 88 2208 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4266.29">824 2646 44 0 0,'0'17'4061'0'0,"-7"90"5596"0"0,-13 0-3534 0 0,5-53-4552 0 0,-39 98 0 0 0,49-141-1786 0 0,0-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,-13 14 1 0 0,16-19-270 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-11 3 0 0 0,13-5-60 0 0,-1 0 1 0 0,0 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-5-2-1 0 0,6 2 267 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,1 1 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1-3 1 0 0,0 0-46 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,0 0-1 0 0,2-6 0 0 0,2-2-113 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4420.2">644 2991 448 0 0,'5'8'699'0'0,"-1"1"1"0"0,1 0-1 0 0,-2 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,2 12-1 0 0,8 61 3411 0 0,-9-54-2417 0 0,3 28 1462 0 0,-2 77 0 0 0,-6-85-3668 0 0,-14 91 1 0 0,4-94-4837 0 0,9-45 4888 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0-3 93 0 0,0 0-1 0 0,0 1 1 0 0,1-1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,1 0 1 0 0,0-10-1 0 0,0 7 111 0 0,-1-12-147 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4637.46">873 3101 72 0 0,'4'7'648'0'0,"13"17"4963"0"0,-17-24-5421 0 0,1 0 1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,4-6 1154 0 0,21-33 3545 0 0,3 2-3395 0 0,-24 33-1514 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,10-2 0 0 0,19-7-2258 0 0,-26 8-417 0 0,1-1 1 0 0,0 0-1 0 0,-1 0 0 0 0,0-1 1 0 0,14-11-1 0 0,-21 14 2260 0 0,1 1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,4-2 0 0 0,0 1-86 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4845.36">1297 2989 68 0 0,'-20'51'9132'0'0,"17"-44"-7711"0"0,0 0-1 0 0,0-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,-6 7-1 0 0,-32 33 2082 0 0,14-18-3346 0 0,16-15-221 0 0,0-1 0 0 0,-1-1-1 0 0,-1 0 1 0 0,0-1 0 0 0,-18 10 0 0 0,-1-2-2641 0 0,-46 17 0 0 0,74-33 2039 0 0,1 0 1 0 0,-1-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-7-2-1 0 0,9 2 304 0 0,0-1 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,-1-4 1 0 0,-5-21-919 0 0,5 9 840 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5062.11">921 2696 100 0 0,'10'46'5757'0'0,"5"95"-1"0"0,-4-22 472 0 0,21 64-2025 0 0,-18-120-3860 0 0,3 0 1 0 0,32 78-1 0 0,-39-116-478 0 0,-6-13-310 0 0,1 1-1 0 0,0-1 1 0 0,1 0-1 0 0,0-1 1 0 0,1 0 0 0 0,15 20-1 0 0,-22-31 305 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1-1 0 0 0,3-16-3142 0 0,-9-29 264 0 0,6 42 2480 0 0,-21-177-5313 0 0,17 143 5341 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5205.51">1157 2765 164 0 0,'-7'18'4819'0'0,"2"2"-1796"0"0,0 0 0 0 0,1 0 0 0 0,2 0 0 0 0,-2 27 0 0 0,15-60-12269 0 0,-6-7 7453 0 0,-1 0 0 0 0,-1 0 1 0 0,-1-1-1 0 0,0-24 0 0 0,0 5 740 0 0,0 7 442 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink25.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-07-18T14:25:50.837"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 631 340 0 0,'0'0'2019'0'0,"1"1"-2146"0"0,4 11 10684 0 0,-4-12-10319 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,1-1-1 0 0,-1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,16-7 7839 0 0,29 6-5292 0 0,-29 0-1863 0 0,0 2 0 0 0,22 1 0 0 0,-15 4-747 0 0,0 0 1 0 0,-1 1-1 0 0,41 17 1 0 0,-35-11 16 0 0,47 11 1 0 0,-3-10-690 0 0,-48-10 87 0 0,-1 1 0 0 0,0 1 0 0 0,-1 1 1 0 0,0 1-1 0 0,0 1 0 0 0,37 19 0 0 0,-47-22-2845 0 0,-15-32-12443 0 0,0 20 15945 0 0,-15-49-6980 0 0,8-3 3363 0 0,8 41 2856 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="278.28">651 331 220 0 0,'0'7'955'0'0,"0"0"0"0"0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,2 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-2 0 0 0,2 1 0 0 0,7 4 0 0 0,12 7 249 0 0,0 1 0 0 0,-2 2 1 0 0,0 1-1 0 0,-1 0 0 0 0,36 41 0 0 0,-55-56-1189 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,-2 10 0 0 0,-1-6-1 0 0,1 0 0 0 0,-2 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,-1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1-1 0 0 0,0 0 0 0 0,0 0-1 0 0,-14 11 1 0 0,-30 22-1916 0 0,-105 63-12598 0 0,88-63 10716 0 0,62-37 3671 0 0,3-2-259 0 0,-9 5-925 0 0,1-1 1 0 0,-1 0-1 0 0,-12 4 0 0 0,22-9 1050 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,-1-2-1 0 0,-5-8-547 0 0,4-8 235 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="941.98">1609 451 52 0 0,'-3'25'1634'0'0,"3"-22"-689"0"0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,1 6 0 0 0,0-7-612 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,2-1 0 0 0,16 5 665 0 0,-1-1 0 0 0,1-1 0 0 0,0-1 1 0 0,0 0-1 0 0,25-2 0 0 0,96-14-1113 0 0,-94 8 362 0 0,-23 4-793 0 0,36-11 0 0 0,-50 10-698 0 0,-1 0 0 0 0,1 0 1 0 0,14-9-1 0 0,-22 12 932 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,0-1-1 0 0,-16-28-2988 0 0,14 25 2348 0 0,-17-31-1457 0 0,16 23 1891 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1307.17">1925 124 492 0 0,'-2'11'2350'0'0,"0"-1"0"0"0,0 20 0 0 0,2-19-131 0 0,0-1 1 0 0,-1 0-1 0 0,-4 15 1 0 0,-23 66 3755 0 0,-28 40-5342 0 0,49-118-905 0 0,0 1 1 0 0,-1-1-1 0 0,-1-1 0 0 0,0 1 0 0 0,0-2 1 0 0,-20 19-1 0 0,21-23-418 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-2 0 0 0,0 1 0 0 0,-1-1 0 0 0,-19 4 0 0 0,0-3-1071 0 0,17-3 1002 0 0,0 0 0 0 0,0 1 1 0 0,-15 5-1 0 0,25-8 749 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-2 4 0 0 0,2 3 441 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,2 0 0 0 0,-1 0 0 0 0,2 0 0 0 0,2 9 0 0 0,5 25 1514 0 0,-6-9-623 0 0,-1-1 0 0 0,-3 37 1 0 0,-3-23-772 0 0,-2 0 1 0 0,-16 62-1 0 0,17-90-616 0 0,3-10-389 0 0,-1 0-1 0 0,0-1 1 0 0,-6 16-1 0 0,7-24-146 0 0,-10-18-3660 0 0,10 1 3028 0 0,1 1 1 0 0,0 0 0 0 0,1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,9-27-1 0 0,37-93-2242 0 0,-35 107 2940 0 0,0 2 72 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1515.61">1656 733 436 0 0,'5'-3'992'0'0,"0"0"-1"0"0,1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 1-1 0 0,0 0 1 0 0,8 1 0 0 0,-6 0-30 0 0,1 0 1 0 0,-1 1-1 0 0,0 0 0 0 0,0 0 1 0 0,9 6-1 0 0,-11-6-701 0 0,0 1-1 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,5 7-1 0 0,-7-7-84 0 0,0 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,-1 0 1 0 0,2 11-1 0 0,-1-6-176 0 0,-2 0 0 0 0,1 1 0 0 0,-2-1 0 0 0,1 0 1 0 0,-4 17-1 0 0,-1-7-1354 0 0,-1 0 1 0 0,0-1-1 0 0,-1 0 0 0 0,-1 0 1 0 0,-20 34-1 0 0,24-49 229 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,-11 7 0 0 0,13-10 845 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,1 0 1 0 0,-2-2-1 0 0,-4-5-223 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1713.73">1636 813 172 0 0,'0'0'143'0'0,"0"1"0"0"0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,1 1 505 0 0,0 0 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,2 0 0 0 0,33 7 2469 0 0,-22-5-3495 0 0,1 0 0 0 0,32 2 0 0 0,-34-5-3803 0 0,-35 1-11669 0 0,9 0 17290 0 0,4-1-1864 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1887.76">1620 849 60 0 0,'0'0'197'0'0,"-1"0"0"0"0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 235 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,2 1 0 0 0,23 26 6569 0 0,-19-23-6768 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1-1-1 0 0,0 1 1 0 0,11 2-1 0 0,-11-4-1392 0 0,1-1-1 0 0,0 1 0 0 0,-1-2 0 0 0,11 1 0 0 0,-46 8-12817 0 0,14-7 12728 0 0,3 0 806 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2079.03">1529 984 40 0 0,'0'0'105'0'0,"0"0"0"0"0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,5 7 2414 0 0,-4-7-2039 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,2 0 1 0 0,4 1 936 0 0,65 11 5009 0 0,-43-7-5705 0 0,46 16 0 0 0,-66-18-1156 0 0,0-1 0 0 0,1-1 0 0 0,-1 1-1 0 0,1-2 1 0 0,10 2 0 0 0,-59 3-13765 0 0,-28-8 9910 0 0,51 4 3776 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2446.6">1409 1100 12 0 0,'-1'0'179'0'0,"0"0"0"0"0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-2 72 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,1 1 0 0 0,4 3 1049 0 0,1 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,11 3 0 0 0,75 13 2616 0 0,49-6-2716 0 0,-120-13-1486 0 0,40-5 0 0 0,-37 3-71 0 0,-21 1 217 0 0,1 1 0 0 0,-1-1-1 0 0,0-1 1 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,4-3-1 0 0,-8 5-55 0 0,-2-1-57 0 0,0 1 179 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,-2 2 0 0 0,-40 10-754 0 0,1 1 0 0 0,1 3 0 0 0,-45 23 0 0 0,5-3 24 0 0,69-30 711 0 0,-11 4 117 0 0,0 0 0 0 0,0-2 0 0 0,-28 6 0 0 0,58-15 1676 0 0,13-3-31 0 0,35-2 0 0 0,-7 8-1024 0 0,0 2 0 0 0,0 3 0 0 0,0 1 0 0 0,-1 2 0 0 0,76 28 0 0 0,-2 15-1856 0 0,-81-34-2641 0 0,68 24-1 0 0,-99-41 3234 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,-1-2 0 0 0,1 1 0 0 0,0 0 1 0 0,0-1-1 0 0,0-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,12-3 0 0 0,-12 2 259 0 0,-1 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,-1-1 0 0 0,6-8 0 0 0,7-10-349 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2640.72">2631 0 92 0 0,'0'0'22806'0'0,"-22"19"-36339"0"0,17-13 12561 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1-1 1 0 0,-1 0-1 0 0,-7 4 0 0 0,5-4 433 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2940.38">2287 236 528 0 0,'-117'246'13675'0'0,"109"-231"-12550"0"0,1 0-1 0 0,1 0 1 0 0,1 1 0 0 0,0 0 0 0 0,-5 27 0 0 0,10-42-1102 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,1 2 0 0 0,-1-2-9 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,5-2 17 0 0,0 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,10-7 0 0 0,27-27 212 0 0,41-46-1 0 0,21-20 496 0 0,-88 89-390 0 0,1 0 0 0 0,0 2 0 0 0,1 0 0 0 0,28-13 0 0 0,-37 21-155 0 0,-1 1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 2 0 0 0,0-1 0 0 0,0 1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 2 0 0 0,1-1 0 0 0,-1 1 0 0 0,-1 0 0 0 0,12 9 0 0 0,-14-9-276 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 1 1 0 0,0 0-1 0 0,6 14 0 0 0,-7-14-348 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,0 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,-2 8 0 0 0,0-1-1420 0 0,0-1-1 0 0,-2 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-13 23 1 0 0,14-31 1219 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,-10 2 1 0 0,-11-3-848 0 0,12-2 1009 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3168.29">2542 404 604 0 0,'-11'31'1305'0'0,"-15"29"0"0"0,6-22 3135 0 0,-35 52 0 0 0,-36 27 4294 0 0,26-44-6452 0 0,56-64-2555 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,-1-1 0 0 0,-1 0 1 0 0,-13 6-1 0 0,25-13 142 0 0,-1 1 1 0 0,0-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0-1-130 0 0,1 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,1-1 1 0 0,0-1 0 0 0,1-8-1268 0 0,1 1 0 0 0,9-19 0 0 0,4-2 206 0 0,1 1-1 0 0,1 1 0 0 0,2 0 0 0 0,1 1 0 0 0,35-36 0 0 0,-29 37 907 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3302.18">2516 462 64 0 0,'4'0'326'0'0,"0"1"-1"0"0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1 0 0 0,-1 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,2 5 0 0 0,4 7 2027 0 0,0 1-1 0 0,-1 0 1 0 0,10 30 0 0 0,-1-2 2085 0 0,-10-27-3672 0 0,19 35 204 0 0,-24-49-1265 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,4 2 1 0 0,-56-12-19607 0 0,36 7 19367 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3603.26">2387 842 500 0 0,'2'4'753'0'0,"1"-1"-1"0"0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,6 1-1 0 0,-6-2 83 0 0,1-1-1 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,0 1-1 0 0,2 4 0 0 0,-3-5-617 0 0,-1 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,1 5-1 0 0,-2 7 0 0 0,0 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,-7 20 0 0 0,-32 64-69 0 0,23-55 70 0 0,17-39-143 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 0 0 0 0,1 1-1 0 0,1 6 1 0 0,-1-8-14 0 0,0 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 1 0 0,1-1-1 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,5 4 0 0 0,4 1-141 0 0,1-1 0 0 0,0 0 0 0 0,-1-1 0 0 0,2 0 1 0 0,-1-1-1 0 0,0-1 0 0 0,16 2 0 0 0,-21-4-537 0 0,1 0 0 0 0,-1 0-1 0 0,0-1 1 0 0,0 0 0 0 0,13-4 0 0 0,-16 4-241 0 0,1-1 0 0 0,-1 0-1 0 0,0-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,0-1-1 0 0,6-5 1 0 0,7-8-1759 0 0,-2-1-1 0 0,16-22 1 0 0,8-10 289 0 0,-22 29 1808 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4506.76">3582 22 412 0 0,'13'-7'1343'0'0,"-11"6"-760"0"0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,1 0 0 0 0,1 1-1 0 0,12 5 1221 0 0,0-2 0 0 0,0 1 0 0 0,0-2 0 0 0,20 3-1 0 0,-19-5-1291 0 0,-1 0-1 0 0,0-2 1 0 0,1 0-1 0 0,-1 0 0 0 0,1-2 1 0 0,-1 0-1 0 0,27-7 1 0 0,-20 6-418 0 0,-25 7-77 0 0,-12 4-18 0 0,-261 152-2764 0 0,83-44-634 0 0,161-99 2610 0 0,-105 56-5361 0 0,136-72 5443 0 0,9-17-2617 0 0,15-5 2695 0 0,0 0 0 0 0,1 2 0 0 0,1 1 0 0 0,1 1 0 0 0,51-24 0 0 0,-74 39 679 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,6 1 1 0 0,-8-1 28 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-2 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,3 4 0 0 0,0 6 223 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,-1 0-1 0 0,1 21 1 0 0,3 23-401 0 0,-5-55 34 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,1 1 0 0 0,-1-1 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 0-1 0 0,1 1 1 0 0,0-1 0 0 0,1 0-84 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1-1 0 0,1 0 1 0 0,30-29-3220 0 0,-28 27 2991 0 0,42-40-1880 0 0,-1 1 3444 0 0,-41 39-668 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,7 0 0 0 0,8-2 2601 0 0,29 1 0 0 0,-48 2-3049 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 2 0 0 0,-2-2-63 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 3-1 0 0,-3 2-253 0 0,1 1 0 0 0,-1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,-8 8 0 0 0,1-5-88 0 0,0-1 1 0 0,-1-1 0 0 0,0 0-1 0 0,-1-1 1 0 0,1-1 0 0 0,-1 0 0 0 0,-23 7-1 0 0,-10 5 127 0 0,16-5 1542 0 0,-53 16 3533 0 0,94-25-3875 0 0,15 1-784 0 0,-5-5-984 0 0,1-1 0 0 0,-1-1 0 0 0,24-6 0 0 0,-10-2-4371 0 0,-3-5-3694 0 0,-19 9 4776 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4995.28">3769 580 300 0 0,'-7'11'940'0'0,"1"1"0"0"0,0 0 0 0 0,0 0 0 0 0,2 1-1 0 0,-4 13 1 0 0,-14 69 5421 0 0,8-25-2282 0 0,5-24-1794 0 0,-6 86-1 0 0,11-80-1357 0 0,-13 61 1 0 0,17-111-912 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-2 3 0 0 0,1-5-32 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 1 0 0 0,-2-3 1 0 0,-5-3-205 0 0,0 0 0 0 0,0-1-1 0 0,1 0 1 0 0,0-1 0 0 0,-12-15 0 0 0,-26-48-749 0 0,3 6 378 0 0,-58-58 76 0 0,23 30 401 0 0,66 80 158 0 0,1-1 0 0 0,0-1 0 0 0,-13-27 0 0 0,23 41-28 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,1-3 0 0 0,-1 4-11 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,6 0 13 0 0,1 1 0 0 0,-1 0 1 0 0,0 1-1 0 0,8 4 0 0 0,6 1-13 0 0,63 19-48 0 0,-51-15-231 0 0,63 13 0 0 0,-74-22 49 0 0,1 0 0 0 0,-1-2 0 0 0,1-1 0 0 0,25-2-1 0 0,89-21-288 0 0,-135 23 618 0 0,0-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 1-1 0 0,0-1 1 0 0,1 0-1 0 0,2 1 1 0 0,-5-1-53 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,-6 15 1094 0 0,-1-4-609 0 0,-1-1 0 0 0,0-1 0 0 0,-11 11 1 0 0,-8 8 269 0 0,25-24-675 0 0,-1 0 0 0 0,0-1 1 0 0,1 1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,1 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 8 0 0 0,2-5 50 0 0,0-1 0 0 0,0 1 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,1 0-1 0 0,5 10 1 0 0,1-3-11 0 0,0 0 1 0 0,0 0-1 0 0,2-1 0 0 0,-1 0 0 0 0,2-1 0 0 0,0 0 0 0 0,22 17 1 0 0,-8-11-987 0 0,0-1 1 0 0,51 23 0 0 0,-61-33-797 0 0,0 0 1 0 0,1-1-1 0 0,0-1 1 0 0,1-1 0 0 0,-1 0-1 0 0,24 1 1 0 0,-34-5 906 0 0,0 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,0 0 1 0 0,0-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 1 0 0,-1-1 0 0 0,0 0-1 0 0,10-7 1 0 0,1-4-397 0 0,0 0 0 0 0,-2-2 0 0 0,21-25 0 0 0,-7 5 458 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink26.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-07-18T14:26:25.091"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">147 54 8 0 0,'-1'-1'473'0'0,"0"-1"0"0"0,0 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,-2 1 0 0 0,-16-4 3054 0 0,17 3-3372 0 0,0 0-1 0 0,0-1 1 0 0,0 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,-4-4 1 0 0,-9-3-7337 0 0,-14 4 2427 0 0,18 3 2695 0 0,5 2 1587 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink27.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-07-18T14:26:31.043"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">2144 94 368 0 0,'-23'-9'5476'0'0,"-27"-15"0"0"0,8 3 842 0 0,24 13-4776 0 0,0 1 0 0 0,-1 0 0 0 0,-37-7 0 0 0,45 12-1245 0 0,0 1-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 2 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-16 5 0 0 0,-21 9 284 0 0,0 1 1 0 0,2 3-1 0 0,0 2 1 0 0,-64 41-1 0 0,48-21-262 0 0,3 3-1 0 0,-78 74 1 0 0,78-60 18 0 0,2 2 0 0 0,3 2 0 0 0,-49 76 0 0 0,-247 477 290 0 0,277-458-564 0 0,-83 261 0 0 0,117-290-52 0 0,6 2 1 0 0,6 1-1 0 0,-17 218 0 0 0,41-250-42 0 0,16 160 1 0 0,40 96-1 0 0,-19-196 75 0 0,8-1 1 0 0,72 184-1 0 0,-92-293 62 0 0,48 80-1 0 0,-42-82-77 0 0,-17-30-28 0 0,1-1 0 0 0,0 0 0 0 0,2-1 0 0 0,0-1 0 0 0,0 0 0 0 0,33 25 0 0 0,-13-15 0 0 0,0-3 0 0 0,57 29 0 0 0,-49-31 0 0 0,0-3 0 0 0,2-1 0 0 0,0-2 0 0 0,1-2 0 0 0,0-2 0 0 0,1-3 0 0 0,-1-1 0 0 0,1-2 0 0 0,1-2 0 0 0,75-6 0 0 0,-59-4 0 0 0,0-2 0 0 0,-1-3 0 0 0,0-2 0 0 0,-1-4 0 0 0,-1-1 0 0 0,-1-4 0 0 0,67-37 0 0 0,-39 13 0 0 0,-1-4 0 0 0,-4-3 0 0 0,103-89 0 0 0,-133 96 0 0 0,-1-2 0 0 0,-2-2 0 0 0,-3-3 0 0 0,-3-1 0 0 0,54-91 0 0 0,-50 60 0 0 0,-5-1 0 0 0,42-126 0 0 0,38-194 0 0 0,2-182 0 0 0,-110 480 0 0 0,-5 0 0 0 0,-5-1 0 0 0,-15-160 0 0 0,1 199 0 0 0,-4 0 0 0 0,-2 0 0 0 0,-3 2 0 0 0,-48-114 0 0 0,2 43 0 0 0,-92-151 0 0 0,119 228 0 0 0,-2 2 0 0 0,-2 2 0 0 0,-65-69 0 0 0,94 116 0 0 0,0 0 0 0 0,-1 1 0 0 0,-1 0 0 0 0,0 2 0 0 0,0-1 0 0 0,-1 2 0 0 0,0 0 0 0 0,-21-8 0 0 0,23 13 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 2 0 0 0,-18 3 0 0 0,-65 22-2629 0 0,-43 26-7062 0 0,-50 15-172 0 0,179-64 9198 0 0,0-1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0-1-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 0-1 0 0,0-1 1 0 0,1 0-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,-11-5-1 0 0,-3-6-160 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2084.35">20 4980 16 0 0,'0'1'526'0'0,"0"1"0"0"0,-1-1 1 0 0,1 0-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 2 0 0 0,1-2-23 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 2 0 0 0,34 157 5742 0 0,43 74-5670 0 0,-52-161-1607 0 0,-17-46-1508 0 0,2 0-1 0 0,19 39 1 0 0,-29-66 2282 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0-1 0 0,0-1 9 0 0,0 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 1 0 0,11-47-1712 0 0,-10 38 1051 0 0,3-10 261 0 0,3-1 122 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2419.37">482 5071 540 0 0,'16'-18'2074'0'0,"-1"1"13447"0"0,-21 20-11466 0 0,-7 7-2684 0 0,-2 7-982 0 0,0 1 0 0 0,2 1-1 0 0,-16 27 1 0 0,-6 10-265 0 0,-201 263-613 0 0,196-272 104 0 0,40-47 362 0 0,5 24-80 0 0,3 6 201 0 0,0 1-1 0 0,-2-1 1 0 0,4 59 0 0 0,-8 96-1030 0 0,-3-107-138 0 0,2-17-428 0 0,1-25-2277 0 0,-6 57 0 0 0,2-82-5250 0 0,2-24 6247 0 0,1-26 1569 0 0,3 23 756 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2862.43">649 5538 148 0 0,'0'-1'416'0'0,"0"0"1"0"0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,0-1-1 0 0,-1 0 0 0 0,1 1 28 0 0,-1-1 0 0 0,0 1 0 0 0,1 0-1 0 0,-1 0 1 0 0,0-1 0 0 0,1 1-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,1-1 0 0 0,-3 1-1 0 0,-8 4 544 0 0,1 0 0 0 0,0 1 0 0 0,-12 8 0 0 0,16-10-699 0 0,-5 4-140 0 0,0 1 1 0 0,0 0-1 0 0,1 0 1 0 0,0 1 0 0 0,1 1-1 0 0,0 0 1 0 0,1 0 0 0 0,0 1-1 0 0,1 0 1 0 0,0 0-1 0 0,1 1 1 0 0,0 0 0 0 0,-5 16-1 0 0,6-14-141 0 0,1 0 0 0 0,1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,1 0-1 0 0,1 1 1 0 0,0-1 0 0 0,1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,6 25 0 0 0,-7-37-17 0 0,2 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,5 3-1 0 0,-5-5-6 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,3-2 0 0 0,4-3-44 0 0,0-1-1 0 0,-1-1 0 0 0,0 1 0 0 0,0-2 0 0 0,-1 1 1 0 0,0-1-1 0 0,-1 0 0 0 0,0-1 0 0 0,11-22 0 0 0,-4 5-67 0 0,-2-1-1 0 0,15-57 1 0 0,-25 79 117 0 0,4-15-19 0 0,-1 0 0 0 0,0-1-1 0 0,2-39 1 0 0,-5 51 48 0 0,3 23 16 0 0,2 21 16 0 0,9 125-892 0 0,-9-56 220 0 0,-1-44-971 0 0,2 28-2860 0 0,-4-62 529 0 0,10 37 0 0 0,-3-34-517 0 0,-3-30 2866 0 0,-1-1 969 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3275.67">902 5622 396 0 0,'7'-15'16870'0'0,"8"28"-12592"0"0,-8 2-3918 0 0,0 1 0 0 0,-1 0 0 0 0,-1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 19 0 0 0,9 43-336 0 0,-9-57-126 0 0,-3-17-14 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,6 7-1 0 0,-8-12 83 0 0,0 0-1 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,12-10-659 0 0,4-17-84 0 0,-5-2 468 0 0,-1-1 0 0 0,-1 0 1 0 0,6-48-1 0 0,-7 35 448 0 0,-6 36-4 0 0,2-13 177 0 0,-3 20-274 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,1 1 38 0 0,0 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 2-1 0 0,11 22 394 0 0,9 38 277 0 0,-16-45-555 0 0,1 0 0 0 0,1-1 0 0 0,0 0 0 0 0,2 0 0 0 0,12 20 0 0 0,-21-37-164 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,3 1 0 0 0,-3-2 10 0 0,1 1 1 0 0,0-1-1 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1-1 1 0 0,1-1-1 0 0,3-4 42 0 0,0-1-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,3-12-1 0 0,20-75-1240 0 0,-4 10-4691 0 0,-18 69 4074 0 0,-4 12 272 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,4-6 0 0 0,11-4-1480 0 0,-10 9 2356 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3606.71">2131 5129 24 0 0,'-3'-8'283'0'0,"-4"-3"5237"0"0,2 10 185 0 0,0 12-2623 0 0,2 42 363 0 0,12 30-3267 0 0,-4-39-283 0 0,13 64-2013 0 0,1-39-3759 0 0,-18-68 4622 0 0,-7-59-6137 0 0,1 19 6407 0 0,3 13 536 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3841.04">2175 5029 620 0 0,'4'-2'724'0'0,"-1"0"0"0"0,1 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,7 3-1 0 0,8 1 1833 0 0,-1 2 0 0 0,18 8 0 0 0,-12-5-1361 0 0,37 10 1071 0 0,33 13 191 0 0,-83-28-2200 0 0,-1 1 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 2 0 0 0,0-1 0 0 0,14 14 0 0 0,-16-12-233 0 0,-1 0 0 0 0,-1 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,-1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,2 13 0 0 0,-4-10-365 0 0,0-1 1 0 0,0 1 0 0 0,-1-1-1 0 0,-1 1 1 0 0,-3 15-1 0 0,-16 63-4326 0 0,15-73 3280 0 0,1 0-716 0 0,-2 0-1 0 0,0-1 1 0 0,-13 24-1 0 0,16-35 1497 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,-6 3 0 0 0,9-6 379 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,-4-1 1 0 0,-6 0-458 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4236.41">2262 5351 136 0 0,'-12'-13'1070'0'0,"-1"-8"4771"0"0,13 20-5540 0 0,0 1 0 0 0,0-1 0 0 0,-1 0-1 0 0,1 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 1-1 0 0,1-2 1 0 0,0 1-49 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,2 0-1 0 0,4-1 25 0 0,-1 1 1 0 0,1 0 0 0 0,0 0 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 1 0 0 0,9 4 0 0 0,-4-2-963 0 0,0 2 0 0 0,-1-1 0 0 0,0 1 0 0 0,-1 1 0 0 0,13 12 1 0 0,-19-17 227 0 0,0 1 1 0 0,0 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-2 1-1 0 0,1-1 1 0 0,0 1 0 0 0,-1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,-2 6 0 0 0,1-4 242 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-9 8-1 0 0,1-5 1316 0 0,-1 0-1 0 0,0-1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-2 0-1 0 0,1-2 1 0 0,-1 0-1 0 0,-17 4 1 0 0,-47 18 4791 0 0,66-23-5258 0 0,-3 3 1952 0 0,18-3-1567 0 0,10 1-812 0 0,18 1-49 0 0,-1-1 1 0 0,1-1-1 0 0,58-2 0 0 0,-17 1-610 0 0,-57-3 291 0 0,20 3-1677 0 0,47-4 0 0 0,-77 0 1504 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0-1-1 0 0,0-4 0 0 0,2-11-1014 0 0,-1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,-3-22-1 0 0,1 21 726 0 0,-8-104-2602 0 0,7 93 2730 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4492.44">2555 4807 80 0 0,'-3'-15'820'0'0,"-6"-17"2038"0"0,8 31-2410 0 0,1-1 1 0 0,-1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,-2-2-1 0 0,2 3-240 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,1 0 0 0 0,0 0-1 0 0,-12 26 2786 0 0,11-25-2700 0 0,-9 35 715 0 0,2 0 0 0 0,1 0 1 0 0,-4 57-1 0 0,6-39-521 0 0,-35 412 1537 0 0,29-311-1782 0 0,0 180-434 0 0,11-329 136 0 0,5 43-370 0 0,-4-47 349 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,4 2 0 0 0,-3-4 2 0 0,-1 0 1 0 0,0 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1-2 1 0 0,23-20-1313 0 0,0-7-1714 0 0,0-1-1 0 0,-2-2 1 0 0,34-64-1 0 0,37-116-5089 0 0,-83 180 7645 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4728.71">2849 5167 132 0 0,'0'-1'571'0'0,"0"0"-1"0"0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,2 0 1 0 0,38-3 6226 0 0,-25 3-6680 0 0,7-2 860 0 0,0 2 1 0 0,33 4-1 0 0,-34-2-947 0 0,0-1 0 0 0,32-3 1 0 0,-48 2-516 0 0,-1-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1-1 0 0,5-5 1 0 0,-8 6 39 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1-3 0 0 0,-5-16-1946 0 0,-1 0 0 0 0,0 0 0 0 0,-14-26 0 0 0,9 22 1285 0 0,5 8 614 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5061.92">3009 4631 308 0 0,'-1'0'86'0'0,"1"0"0"0"0,0-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,-1 1 0 0 0,-2 15 2361 0 0,8 25 1082 0 0,-5-39-3349 0 0,46 272 9858 0 0,8 142-7084 0 0,-40-271-2552 0 0,-4 170 0 0 0,-10-293-398 0 0,-1 1 0 0 0,-1 0 0 0 0,-1 0 1 0 0,-1-1-1 0 0,-1 1 0 0 0,-14 36 0 0 0,19-58-6 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,-1 0 0 0 0,1 0-2 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-1-3 0 0 0,-5-4-9 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-11-21 0 0 0,2-2 293 0 0,1 0 1 0 0,1-2-1 0 0,2 0 1 0 0,1 0-1 0 0,2-1 0 0 0,1 0 1 0 0,-5-59-1 0 0,13 87-119 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,1 0 0 0 0,7-6 0 0 0,-6 7-84 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,1 2 0 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0 0-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,11 2-1 0 0,13 4-1060 0 0,38 11 0 0 0,-42-9-2403 0 0,0-1 0 0 0,33 3 0 0 0,-59-9 3031 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0-4 0 0 0,1-6-630 0 0,-1 0 1 0 0,0-1 0 0 0,-1 1-1 0 0,-1-19 1 0 0,1 26 890 0 0,-2-17-456 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5283.09">3300 5018 520 0 0,'2'-11'5350'0'0,"4"14"-852"0"0,4 16 1572 0 0,-3 7-2663 0 0,5 47 1 0 0,-4 83-2174 0 0,-7-104-701 0 0,1 14-436 0 0,3 51-1457 0 0,-15 172 0 0 0,8-264 589 0 0,2-19 255 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 1 0 0,-3 11-1 0 0,4-17 451 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-3-15-1826 0 0,-2-19-148 0 0,4-216-6179 0 0,3 112 6154 0 0,-2 104 1732 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5584.43">3329 5275 28 0 0,'-1'-57'1256'0'0,"2"-85"4459"0"0,2 104-860 0 0,10-62 1 0 0,-11 89-3839 0 0,1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,7-14 0 0 0,-9 22-691 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,6-1 0 0 0,-6 3-198 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,1 4 0 0 0,6 4 678 0 0,-1 2-1 0 0,10 13 0 0 0,-18-23-804 0 0,11 17-1 0 0,-2 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-2 0 0 0 0,9 37 0 0 0,13 104 0 0 0,-26-137 0 0 0,21 220 0 0 0,-2-14 0 0 0,-14-175 0 0 0,2-2 0 0 0,22 65 0 0 0,-27-102 0 0 0,1 0 0 0 0,0-1 0 0 0,1 0 0 0 0,13 19 0 0 0,-16-27 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,10 4 0 0 0,-10-5-107 0 0,-1-1 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 1 0 0,9-3-1 0 0,-2 0-636 0 0,1-1 1 0 0,23-11 0 0 0,-34 14-186 0 0,1 0 1 0 0,-1 0-1 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 1 1 0 0,-1-2-1 0 0,0 1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,1-6-1 0 0,1-7-1785 0 0,0-1 0 0 0,-1-31 0 0 0,-1 19 1531 0 0,1-6 41 0 0,-1-4 296 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink28.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-07-18T14:26:37.614"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 201 64 0 0,'0'0'624'0'0,"7"20"4615"0"0,20 118 6517 0 0,-7 73-7008 0 0,6 28-4204 0 0,-11-111-2803 0 0,-14-121-362 0 0,-3-7 665 0 0,-5-11-494 0 0,-7-20-347 0 0,-21-86-3393 0 0,25 65 4134 0 0,-7-77 0 0 0,13 86 1558 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="261.65">82 85 412 0 0,'9'1'1679'0'0,"-1"0"0"0"0,1 1 1 0 0,-1-1-1 0 0,1 2 0 0 0,-1-1 0 0 0,10 6 0 0 0,22 6 3734 0 0,129 32 1477 0 0,-156-43-6758 0 0,0 0 0 0 0,0 1 1 0 0,0 1-1 0 0,0 0 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 0 0 0,0 2 0 0 0,-1-1 0 0 0,0 1 1 0 0,0 1-1 0 0,-1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,8 19 0 0 0,-4-7-433 0 0,-1 2-1 0 0,-1-1 0 0 0,-1 1 1 0 0,8 50-1 0 0,-13-55-1088 0 0,-1 1 1 0 0,-2 0-1 0 0,-3 37 0 0 0,1-36-904 0 0,-2 0 0 0 0,-7 22 0 0 0,9-35 1357 0 0,-2-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-2-1 0 0 0,-7 11 0 0 0,11-17 723 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-6-2 1 0 0,-7-4-324 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="511.8">149 354 188 0 0,'-1'1'263'0'0,"0"-1"1"0"0,0 1-1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,3 0 1 0 0,8 6 893 0 0,1-1 0 0 0,0-1 0 0 0,0 0 1 0 0,1-1-1 0 0,-1 0 0 0 0,27 3 0 0 0,-23-5-1002 0 0,1-1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1-1 0 0 0,0-1-1 0 0,1-1 1 0 0,-1 0 0 0 0,31-11-1 0 0,-35 9-412 0 0,0-1-1 0 0,17-11 0 0 0,1-7-3386 0 0,-46 34-3483 0 0,-39 36 124 0 0,-9 8 3158 0 0,47-41 3294 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="680.13">109 765 508 0 0,'-6'8'710'0'0,"-17"30"2872"0"0,22-35-2761 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 4 0 0 0,2-6-545 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 0 0 0,1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,1 0 1 0 0,32 3 1024 0 0,-28-2-684 0 0,31-1 88 0 0,-1-1 0 0 0,1-1 0 0 0,46-10 0 0 0,-2 0-981 0 0,-70 11 120 0 0,9 0-1050 0 0,-1-2-1 0 0,1 0 0 0 0,-1-1 1 0 0,0 0-1 0 0,32-14 1 0 0,-48 16 779 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-2-1-1 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-6 0 0 0,0-9-813 0 0,-1 0 0 0 0,0 0-1 0 0,-8-29 1 0 0,8 40 1078 0 0,-3-17-363 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="930.62">373 1 520 0 0,'-2'1'353'0'0,"0"0"0"0"0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-2 3 0 0 0,-10 35 2985 0 0,8-24-2157 0 0,-7 26 2349 0 0,-9 60-1 0 0,6 46-269 0 0,13 149-1295 0 0,3-275-1765 0 0,13 247 458 0 0,-6-205-608 0 0,2-1-1 0 0,21 74 1 0 0,-27-124-82 0 0,0 0 0 0 0,0 0 0 0 0,2 0 0 0 0,0-1 0 0 0,0 0 0 0 0,12 17 0 0 0,-16-26-49 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,1-1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,5-2 0 0 0,4-3-638 0 0,1-1 1 0 0,-1 0 0 0 0,0-1 0 0 0,-1 0-1 0 0,0 0 1 0 0,0-2 0 0 0,-1 1 0 0 0,0-1-1 0 0,-1-1 1 0 0,11-14 0 0 0,7-14-2801 0 0,36-71 0 0 0,-32 46 1115 0 0,25-76 1 0 0,-40 94 1862 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1070.23">1082 74 68 0 0,'6'10'1979'0'0,"-1"1"-1"0"0,-1 0 0 0 0,6 21 1 0 0,-7 0-2736 0 0,-10 4-5891 0 0,6-35 6171 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1211.64">1016 465 308 0 0,'-9'98'3516'0'0,"8"-55"-1033"0"0,1 21-2467 0 0,5 0-4828 0 0,-1-48 3764 0 0,-3-8 629 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1402.21">1024 1221 28 0 0,'5'8'16768'0'0,"-2"-19"-15453"0"0,0 0 0 0 0,1 1 0 0 0,9-17 0 0 0,21-28-3079 0 0,-21 35-1287 0 0,-1-1 0 0 0,13-28-1 0 0,39-123-7131 0 0,-53 144 9524 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1667.41">1500 138 280 0 0,'-7'24'2383'0'0,"5"-19"-1080"0"0,0-1-1 0 0,1 1 1 0 0,0-1 0 0 0,0 1-1 0 0,-1 8 1 0 0,2-13-774 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,2-1-1 0 0,13 8 3883 0 0,25 0-3903 0 0,-24-5 632 0 0,58 14 260 0 0,-11-2-1193 0 0,84 8-1 0 0,-84-22-3135 0 0,-35-1-2819 0 0,-50-11-7329 0 0,-11-15 9512 0 0,16 12 2213 0 0,-13-11-162 0 0,13 10 985 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1861.93">1407 205 116 0 0,'-31'345'11917'0'0,"15"-114"-6951"0"0,0-29-4078 0 0,-22 157-3004 0 0,37-348 1705 0 0,-1-3-487 0 0,1 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,-5 10 1 0 0,6-17-399 0 0,1-2 1121 0 0,-1 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,-1-1-1 0 0,-3-17-1339 0 0,1 3 790 0 0,1-1 0 0 0,1 1 0 0 0,1-1 0 0 0,1-17 0 0 0,1 6 266 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2642.01">1616 281 52 0 0,'1'1'319'0'0,"1"0"0"0"0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 4 0 0 0,-1 4 1097 0 0,0 0 1 0 0,0 0-1 0 0,-6 16 1 0 0,3-9 95 0 0,-21 89 1209 0 0,-15 50-3755 0 0,11-36-907 0 0,29-120 1933 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,9-12-60 0 0,9-17 155 0 0,16-41 257 0 0,-25 48-134 0 0,2 1-1 0 0,0 0 1 0 0,1 0 0 0 0,1 1 0 0 0,28-33 0 0 0,-40 51-165 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 0 0 0,-1 0 1 0 0,1 1-1 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0 1-1 0 0,2 0 0 0 0,-2 0 11 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,1 3 1 0 0,2 11 73 0 0,0 1 0 0 0,-1 0 0 0 0,-1 0 1 0 0,-1 0-1 0 0,0 27 0 0 0,-1-35-219 0 0,-1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-8 10 1 0 0,10-16 19 0 0,-1 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,-4 0 0 0 0,6 0 53 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0 0-1 0 0,1-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0-2-1 0 0,0 2 19 0 0,1 1-1 0 0,0 0 1 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,0 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 6 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,3-2 0 0 0,-1 1 9 0 0,1 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,10 3 0 0 0,-10-2-6 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 6 0 0 0,2 6 5 0 0,-2-1-1 0 0,0 1 0 0 0,0 0 1 0 0,-3 31-1 0 0,-10 45-3 0 0,-18 45 10 0 0,20-96-16 0 0,8-38 145 0 0,-3 11 2081 0 0,4-15-2185 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,-8-4 31 0 0,-1 0 1 0 0,0 1-1 0 0,-15-3 1 0 0,0 0-171 0 0,5 1 15 0 0,-1-2 0 0 0,1 0 0 0 0,-22-13 0 0 0,33 16 132 0 0,1-1 0 0 0,-1-1 1 0 0,1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 0 0 0 0,1 0 1 0 0,-8-11-1 0 0,13 16-1 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 1 0 0,1 1-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,3-3 1 0 0,3-5 190 0 0,0 0 0 0 0,1 1 0 0 0,10-10 0 0 0,-17 18-222 0 0,11-10 108 0 0,0 1-1 0 0,0 1 1 0 0,1 0-1 0 0,0 0 1 0 0,1 1-1 0 0,0 1 1 0 0,0 1-1 0 0,1 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0 1-1 0 0,0 1 1 0 0,1 0 0 0 0,17 0-1 0 0,-16 2-151 0 0,0 0 0 0 0,0 2 0 0 0,0 0-1 0 0,0 1 1 0 0,0 0 0 0 0,-1 2 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 2 1 0 0,0 0 0 0 0,-1 1 0 0 0,0 0 0 0 0,15 10 0 0 0,21 20-4015 0 0,51 48 0 0 0,-93-77 3066 0 0,-1-2 1 0 0,1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0-1-1 0 0,1 0 1 0 0,0-1 0 0 0,15 6-1 0 0,-19-9 590 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1-1 0 0 0,1 1-1 0 0,0-2 1 0 0,0 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 0-1 0 0,0-1 1 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,9-6-1 0 0,8-9-338 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink29.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-07-18T14:26:45.208"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">2446 432 364 0 0,'-20'-42'2684'0'0,"-2"0"1"0"0,-30-41-1 0 0,33 57-860 0 0,-1 0 1 0 0,-1 1-1 0 0,-1 2 0 0 0,-29-25 1 0 0,34 34-1224 0 0,-1 1 0 0 0,0 0 0 0 0,-1 1 1 0 0,-1 1-1 0 0,1 1 0 0 0,-43-15 0 0 0,41 20-376 0 0,0 0-1 0 0,0 1 0 0 0,0 2 1 0 0,0 0-1 0 0,0 1 0 0 0,-26 2 0 0 0,10 3-37 0 0,0 0 0 0 0,-60 17 0 0 0,59-9-122 0 0,1 2 1 0 0,0 1 0 0 0,1 1-1 0 0,-46 30 1 0 0,-127 96 267 0 0,186-125-278 0 0,-78 58 120 0 0,4 4 1 0 0,4 5 0 0 0,3 3 0 0 0,-107 135 0 0 0,102-96-192 0 0,5 4 0 0 0,6 4 1 0 0,6 4-1 0 0,7 3 0 0 0,-82 225 0 0 0,131-300-6 0 0,3 1 1 0 0,-20 129-1 0 0,33-149 11 0 0,3 0 1 0 0,2 0 0 0 0,2 1 0 0 0,1-1-1 0 0,12 54 1 0 0,6-8 16 0 0,35 97 0 0 0,46 85 41 0 0,-71-196-38 0 0,97 222 114 0 0,-91-232 114 0 0,2-1 0 0 0,56 76 0 0 0,77 66 1027 0 0,-149-187-1073 0 0,2 0 0 0 0,0-2-1 0 0,1 0 1 0 0,1-2 0 0 0,1-1-1 0 0,39 19 1 0 0,-42-27-109 0 0,0-1 0 0 0,0-2 0 0 0,1 0 0 0 0,0-1 1 0 0,0-2-1 0 0,0-1 0 0 0,27 1 0 0 0,179-11 278 0 0,-183 3-294 0 0,-1-2-1 0 0,0-1 0 0 0,65-21 0 0 0,-86 19-38 0 0,0 0-1 0 0,0-3 1 0 0,-1 0-1 0 0,0-1 1 0 0,-1-1-1 0 0,-1-2 1 0 0,27-21-1 0 0,-12 2 8 0 0,-2-2 0 0 0,-1-1 0 0 0,41-58 1 0 0,76-138 19 0 0,55-152-117 0 0,-165 287 49 0 0,-4-2-1 0 0,26-112 0 0 0,-44 127 312 0 0,-4-1-1 0 0,-3 0 1 0 0,-5-1-1 0 0,-3 0 1 0 0,-10-130 0 0 0,-35-121 100 0 0,27 272-331 0 0,-2 1 0 0 0,-4 1 0 0 0,-27-64 0 0 0,39 112-66 0 0,-1 0 0 0 0,-1 0 0 0 0,-1 1 0 0 0,0 0 0 0 0,-1 1 0 0 0,-24-26 0 0 0,25 31 0 0 0,-1 0 0 0 0,0 1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 2 0 0 0,-1-1 0 0 0,0 1 0 0 0,-22-6 0 0 0,-29-5-1685 0 0,4 5-3607 0 0,-1 2 0 0 0,-80-2 1 0 0,123 11 3488 0 0,1 0 1 0 0,0-1-1 0 0,0-1 1 0 0,-22-6-1 0 0,32 6 1405 0 0,1 1 0 0 0,-1-1 0 0 0,1 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0-1 0 0 0,-6-8-1 0 0,-4-10-208 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink3.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-04-17T13:14:16.081"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">401 61 328 0 0,'8'-29'2678'0'0,"-2"8"9263"0"0,-33 12-3443 0 0,0 8-5824 0 0,-21 1 466 0 0,37 4-2985 0 0,-1 0 0 0 0,2 0 0 0 0,-1 1 0 0 0,1 0 0 0 0,1 1 0 0 0,-2 0 0 0 0,2 0 0 0 0,-1 2 0 0 0,2-1 0 0 0,-1 1 0 0 0,1 1 0 0 0,0-1 0 0 0,-12 16-1 0 0,3 0-120 0 0,1 2-1 0 0,1-2 0 0 0,0 3 0 0 0,-13 34 0 0 0,24-53-31 0 0,-7 18 2 0 0,1 0 0 0 0,1 0-1 0 0,0 2 1 0 0,-8 55-1 0 0,11-19-17 0 0,2-46-1 0 0,2 2 0 0 0,0-1 0 0 0,1 0 0 0 0,1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,8 37 0 0 0,-4-41-2 0 0,0 0 0 0 0,1 0-1 0 0,0 0 1 0 0,1-2 0 0 0,0 1 0 0 0,2 0-1 0 0,0-1 1 0 0,-1 0 0 0 0,2-2 0 0 0,0 1 0 0 0,16 14-1 0 0,-21-21-170 0 0,1 0-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0-2-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,0 0 1 0 0,0-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,9-4 0 0 0,-7 1-541 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-2-1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,6-9 0 0 0,6-9-3748 0 0,24-48 0 0 0,-31 51 2147 0 0,0 3 0 0 0,0-2 0 0 0,31-32 0 0 0,-32 44 1682 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="586.76">973 121 268 0 0,'-2'-2'872'0'0,"0"-1"0"0"0,0 2 0 0 0,0-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-3 0 0 0 0,2 1-219 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,1 1 0 0 0,-2-1 0 0 0,-3 2 0 0 0,-8 6 98 0 0,0 1 1 0 0,1 0-1 0 0,-28 23 1 0 0,7-4 397 0 0,26-21-990 0 0,-1 1 0 0 0,2-1 0 0 0,-1 2 1 0 0,2 0-1 0 0,-1 1 0 0 0,1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,2 0 0 0 0,0 2 0 0 0,-7 20 1 0 0,2-5-54 0 0,4 0 0 0 0,-1-1 0 0 0,2 2 0 0 0,-4 42 0 0 0,9-56-104 0 0,1 0 0 0 0,0 1 1 0 0,1 0-1 0 0,0-2 0 0 0,1 2 0 0 0,1-1 0 0 0,0 0 1 0 0,9 21-1 0 0,-9-27-27 0 0,0 0 0 0 0,1-1 0 0 0,1 1 0 0 0,-1-2 0 0 0,1 1 0 0 0,0 0 0 0 0,1-1 1 0 0,1 0-1 0 0,-2 0 0 0 0,2 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,2-1 0 0 0,-1 0 0 0 0,9 6 0 0 0,-10-9-46 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-2 1 0 0 0,2-1 0 0 0,6-6 0 0 0,1 1-174 0 0,-1-1 0 0 0,0-2 1 0 0,0 1-1 0 0,-1-2 0 0 0,0 0 1 0 0,16-22-1 0 0,-12 11-139 0 0,0-1 0 0 0,-3-1 0 0 0,0 0 0 0 0,-1-1 0 0 0,-1-1 0 0 0,11-45 0 0 0,-12 28-82 0 0,-3 0 0 0 0,0 1-1 0 0,-1-69 1 0 0,-15 52 3230 0 0,9 62-2657 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,1 5 0 0 0,0 46 159 0 0,4 3-172 0 0,4 0 0 0 0,1 0-1 0 0,3-2 1 0 0,20 57 0 0 0,-32-108-136 0 0,25 57-255 0 0,-25-56 123 0 0,1-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 0 0 0,3 2 1 0 0,-4-4-86 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0-2-1 0 0,5-9-1126 0 0,-1 1 0 0 0,0-1 0 0 0,4-16 1 0 0,-7 20 850 0 0,29-119-4728 0 0,-22 101 4546 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="998.24">1394 71 564 0 0,'-2'5'913'0'0,"0"1"0"0"0,1-1-1 0 0,0 1 1 0 0,1-2 0 0 0,-1 2 0 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1 0 0 0,2 7 0 0 0,9 42 3103 0 0,24 217 1249 0 0,-27-197-4840 0 0,-6-46-196 0 0,4 47 1 0 0,-8-74-214 0 0,1 0 4 0 0,7-7-10 0 0,3-12 0 0 0,1-27-55 0 0,14-41 0 0 0,5-10-65 0 0,-12 10 4 0 0,11-37-93 0 0,-4 63 121 0 0,-25 57 78 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,3-1 1 0 0,-3 3 26 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,-1-1 1 0 0,2 1-1 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 3-1 0 0,32 31 654 0 0,-25-20-421 0 0,1-1 1 0 0,-2 2-1 0 0,1-2 1 0 0,-2 2-1 0 0,0 0 1 0 0,6 22-1 0 0,21 105 626 0 0,-24-101-854 0 0,1 37-535 0 0,-10-72 114 0 0,0 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 0 1 0 0,-1 1 0 0 0,1 0-1 0 0,-3 9 1 0 0,3-15 12 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,0 1 0 0 0,1-1 0 0 0,-3 1 0 0 0,-10-8-4049 0 0,12 5 4080 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-4 1 0 0,2-4-411 0 0,-1 0 0 0 0,2 0 1 0 0,1 0-1 0 0,0 0 0 0 0,6-13 1 0 0,1 0-7 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink30.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-07-18T14:26:47.868"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">4 1247 132 0 0,'-3'13'2039'0'0,"5"-3"6636"0"0,9-6 137 0 0,1-2-6626 0 0,-3-2-3465 0 0,186 13 7325 0 0,0-12-5282 0 0,-119-2-1739 0 0,-23-4-1833 0 0,-22-5-3212 0 0,-32-10-350 0 0,-1 12 5227 0 0,-1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,-1 0 0 0 0,-6-9 0 0 0,-2-6-268 0 0,6 12 888 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="227.32">441 792 420 0 0,'-4'-9'4814'0'0,"-1"9"-1145"0"0,-2 20 1033 0 0,-1 33-1189 0 0,-26 369 1603 0 0,-48 207-5938 0 0,79-601 285 0 0,-13 68-1636 0 0,0-34-3530 0 0,16-61 4334 0 0,-11-10-2676 0 0,10 6 3709 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-7 0 0 0,2-39-1475 0 0,-1 44 1591 0 0,7-49-914 0 0,-2 26 751 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="509.98">319 1645 316 0 0,'11'-63'1755'0'0,"-7"47"438"0"0,-1-1 0 0 0,1-31-1 0 0,-3 46-1896 0 0,-1 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,-1 0-1 0 0,0 1-102 0 0,0 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,-1 1 0 0 0,-7 3-153 0 0,1 1 1 0 0,0 0-1 0 0,0 1 0 0 0,-10 11 1 0 0,-139 148-4130 0 0,140-150 3331 0 0,10-11 554 0 0,12-13 504 0 0,-1 5-122 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,1 1 0 0 0,-1-1-1 0 0,6 0 1 0 0,11 0 745 0 0,44 2 0 0 0,-52 0-653 0 0,150 17 1313 0 0,-34-3-3424 0 0,-123-14 1227 0 0,-1 0 0 0 0,1-1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,7-2 0 0 0,-9 1 171 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-2 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0-4 0 0 0,4-16-1818 0 0,3-32-1 0 0,-8 51 2155 0 0,2-16-404 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1004.54">726 1161 72 0 0,'0'-1'155'0'0,"1"1"0"0"0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1-1 0 0,0 0 1 0 0,9 23 5058 0 0,-8-21-3940 0 0,1 4-486 0 0,0 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,-2 9-1 0 0,-3 11-384 0 0,-10 27 0 0 0,7-27 62 0 0,-85 236-458 0 0,35-107-3534 0 0,56-148 2664 0 0,0-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,-7 11 0 0 0,8-19-2280 0 0,2-8 1997 0 0,1-9 267 0 0,15-53-1067 0 0,36-109-1 0 0,-27 103 1855 0 0,-5 20 986 0 0,2 0 1 0 0,38-73-1 0 0,-34 84 2074 0 0,42-57 1 0 0,-37 71-547 0 0,-28 30-2180 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,4-1 1 0 0,-6 1-153 0 0,0 0 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,2 36 1232 0 0,-2-36-1212 0 0,-2 32 469 0 0,-2 0-1 0 0,-2-1 0 0 0,-1 1 1 0 0,-20 55-1 0 0,7-20-311 0 0,16-56-237 0 0,-23 83 47 0 0,-24 161 1 0 0,50-243-90 0 0,-1 0 0 0 0,2-1 0 0 0,0 1 0 0 0,1 0 0 0 0,0-1-1 0 0,1 1 1 0 0,1 0 0 0 0,6 21 0 0 0,-5-27 53 0 0,0-1-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,1 0-1 0 0,1-1 1 0 0,12 6-1 0 0,-16-7-223 0 0,1-2-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,6-1-1 0 0,-8 0-234 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 0-1 0 0,3-3 1 0 0,5-10-2223 0 0,-1 0-1 0 0,-1-1 1 0 0,8-19 0 0 0,13-54-3267 0 0,-23 71 5163 0 0,3-7-44 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1223.3">1155 1276 292 0 0,'-1'17'13067'0'0,"1"-17"-12847"0"0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,13-4 7306 0 0,-2-2-6790 0 0,0 1-101 0 0,0 0 0 0 0,0 1 0 0 0,0 0 1 0 0,0 1-1 0 0,1 0 0 0 0,-1 1 1 0 0,24 0-1 0 0,-14 1-1483 0 0,0 2-1 0 0,-1 1 0 0 0,39 8 1 0 0,-16 2-5031 0 0,-18-2-3815 0 0,-14-21 2631 0 0,-9-5 5294 0 0,-3 6 1140 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1605.09">1410 807 76 0 0,'-2'-4'-184'0'0,"-10"-12"3773"0"0,8 18-585 0 0,0 12-884 0 0,-2 59 4295 0 0,4 1-3487 0 0,-1 5-1405 0 0,-60 634 1343 0 0,55-640-2854 0 0,2-15-11 0 0,-3-1 0 0 0,-16 59 1 0 0,24-115-9 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-5 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,0-1 1 0 0,-1 0-1 0 0,-1-2-50 0 0,0-1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-6 0 0 0,-45-317 163 0 0,46 321 52 0 0,0 0 0 0 0,0-1-1 0 0,1 1 1 0 0,0-1 0 0 0,0 1 0 0 0,2-7 0 0 0,-2 11-60 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,2-1-1 0 0,-1 2-13 0 0,28-10 667 0 0,1 1-1 0 0,0 2 1 0 0,0 2 0 0 0,56-4-1 0 0,-63 9-918 0 0,31 0-3170 0 0,-2 5-6524 0 0,-24-3 1056 0 0,-28-3 8472 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,1-3 0 0 0,6-6-313 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1813.22">1715 1285 28 0 0,'-1'-1'1435'0'0,"1"0"-956"0"0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1-4 4306 0 0,0 3-4307 0 0,12-7 6665 0 0,27-3-2559 0 0,-21 7-3166 0 0,-6 2-978 0 0,0-1 0 0 0,0 2 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,26 4-1 0 0,-25-2-1336 0 0,1-1 0 0 0,-1 0-1 0 0,0-1 1 0 0,0-1 0 0 0,26-4-1 0 0,-14 0-1982 0 0,-20 4 1349 0 0,0 1 1 0 0,-1-2 0 0 0,1 1 0 0 0,-1-1 0 0 0,8-2 0 0 0,-11 3 1054 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1-4-1 0 0,18-47-2712 0 0,-14 37 2753 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1940.1">2166 1003 512 0 0,'11'-36'3372'0'0,"-2"7"5072"0"0,-11 19-3649 0 0,-6 1-4448 0 0,-18-7-6166 0 0,7 4 2581 0 0,10 4 2160 0 0,1-2-1 0 0,0 1 1 0 0,0-1 0 0 0,1 0-1 0 0,1 0 1 0 0,-8-17-1 0 0,7 9 471 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2160.76">1953 492 124 0 0,'-3'13'1169'0'0,"1"0"1"0"0,0 0-1 0 0,1 1 0 0 0,1-1 1 0 0,0 1-1 0 0,1-1 0 0 0,3 17 1 0 0,0 20 1589 0 0,13 176 4793 0 0,32 111-4569 0 0,-20-187-2654 0 0,7-1-1 0 0,7-1 1 0 0,66 155-1 0 0,-106-297-391 0 0,4 13-649 0 0,2 0 1 0 0,0 0-1 0 0,1-1 1 0 0,21 29 0 0 0,-30-46 548 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,2 0-1 0 0,-2 0-41 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-2 0 0 0,1-7-1196 0 0,-2 0-1 0 0,1 0 0 0 0,-3-13 0 0 0,-32-116-4526 0 0,28 112 5413 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2387.95">1637 1640 508 0 0,'-7'10'60'0'0,"2"0"8411"0"0,5-10-8202 0 0,1 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0-1-1 0 0,1 1 1 0 0,95-27 6074 0 0,-70 18-6455 0 0,-1 1-1 0 0,1 2 0 0 0,28-4 1 0 0,-45 9-856 0 0,0 1 0 0 0,0 0 0 0 0,15 2 0 0 0,8 7-6276 0 0,-31-9 7066 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-6 2-941 0 0,-1-2 569 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2577.35">1808 1432 472 0 0,'0'0'749'0'0,"-7"16"3308"0"0,-16 103 6246 0 0,2-6-7825 0 0,7-43-2310 0 0,-3 31-1694 0 0,16-87 198 0 0,0-1 0 0 0,3 27-1 0 0,-2-40 1187 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 1 0 0,1 0-1 0 0,8-13-2319 0 0,5-26 717 0 0,9-29 92 0 0,-13 41 1292 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2728.84">1908 1456 504 0 0,'11'-14'2744'0'0,"-11"14"-2616"0"0,1-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,8 34 7682 0 0,-6-24-7530 0 0,4 34 1039 0 0,-3 0-1 0 0,-2 67 0 0 0,-1-1-1898 0 0,1-77-128 0 0,4 50-2694 0 0,-4-75 2264 0 0,0 0-1 0 0,1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,8 14 1 0 0,-11-22 992 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,2 0 0 0 0,0-1-50 0 0,0 0 1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,2-3-1 0 0,7-5-415 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2916.73">2315 1487 48 0 0,'1'-10'16135'0'0,"-12"26"-7478"0"0,5-6-10490 0 0,-72 161 3095 0 0,29-55-3726 0 0,16-37-1967 0 0,19-47-620 0 0,-23 36 0 0 0,26-56 3231 0 0,9-17-3312 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3590.6">2868 481 160 0 0,'-6'12'10567'0'0,"18"-8"-6842"0"0,84 8 1756 0 0,48-9-3487 0 0,-113-3-1644 0 0,-29-1-349 0 0,-1 1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 2 0 0 0,-1 7-174 0 0,-1 0-1 0 0,-1 0 1 0 0,0-1 0 0 0,-7 14 0 0 0,6-13-94 0 0,-5 11-527 0 0,-1-1 1 0 0,-1-1-1 0 0,-1 0 1 0 0,0 0-1 0 0,-26 26 1 0 0,34-41 775 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 1 0 0,-9 0-1 0 0,3-2 3320 0 0,29-3-883 0 0,-1 1-2712 0 0,-1-1 286 0 0,1-1 0 0 0,-1 0-1 0 0,21-11 1 0 0,-28 12-568 0 0,0 0 0 0 0,0 0 0 0 0,-1-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1-1 0 0 0,-1 0 0 0 0,7-7 0 0 0,-11 11 227 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,0-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 1 0 0,0 0-86 0 0,0-1 0 0 0,0 1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-6-1 1 0 0,1 1-123 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3798.46">2999 549 28 0 0,'0'0'120'0'0,"0"0"0"0"0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-2 10 2707 0 0,-9 11 1235 0 0,-58 80 2454 0 0,-21 58-5599 0 0,68-113-1320 0 0,-14 28-1499 0 0,31-69 1124 0 0,0 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-1-1 0 0 0,-8 6-1 0 0,13-10 462 0 0,0 0 1 0 0,0-1-1 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-3 0 0 0 0,3-1 228 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 0 0 0 0,0 0 0 0 0,3-8-322 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4197.35">2861 867 176 0 0,'3'0'237'0'0,"0"1"1"0"0,0-1-1 0 0,-1 0 0 0 0,1 1 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 1 0 0,1 3-1 0 0,2 5 763 0 0,0 1 0 0 0,-1-1 0 0 0,0 1-1 0 0,2 12 1 0 0,-2-8-404 0 0,0-1-181 0 0,-1 1 1 0 0,1 23-1 0 0,-3 7-2753 0 0,10-64-40 0 0,3-20 877 0 0,-8 20 1158 0 0,0 1-1 0 0,16-30 1 0 0,-20 43 505 0 0,0 1-1 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 1 0 0,6-1-1 0 0,-7 1-23 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 1 1 0 0,0 4 50 0 0,0-1 1 0 0,0 1 0 0 0,-1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,0 1 0 0 0,-1 6-1 0 0,-1-1-110 0 0,-1-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-2 0-1 0 0,1-1 1 0 0,-16 18-1 0 0,20-26 160 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,-4 1-1 0 0,5-2 237 0 0,9 0 3350 0 0,26 0-3899 0 0,-24 0-235 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,12-4-1 0 0,-13 2-581 0 0,0 0-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 0 1 0 0,7-7 0 0 0,-6 3-291 0 0,1-1 0 0 0,-1 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,9-21 0 0 0,25-51-1706 0 0,-29 55 2268 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4368.39">3530 316 200 0 0,'-9'0'19889'0'0,"0"21"-21274"0"0,4-11-881 0 0,0-1-1 0 0,-1 1 1 0 0,-1-1 0 0 0,0 0 0 0 0,-14 14-1 0 0,-1 1-1826 0 0,18-19 3452 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5086.54">3410 449 228 0 0,'-1'12'941'0'0,"2"-1"10084"0"0,5-10-5559 0 0,4-3-4777 0 0,4-1 611 0 0,35-9 434 0 0,1 1-4748 0 0,-67 25-7149 0 0,-17 8 8715 0 0,17-10 1166 0 0,2 1-1 0 0,0 0 1 0 0,0 1 0 0 0,-15 20 0 0 0,-9 8 1870 0 0,39-42-1544 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,15 3 780 0 0,18-1-499 0 0,-33-2-287 0 0,45 0 195 0 0,-14 1-194 0 0,45-4 0 0 0,-42 2 108 0 0,-34 1-108 0 0,-12 18 152 0 0,4-8-177 0 0,-1-1 0 0 0,0 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,0-2 0 0 0,-16 10 0 0 0,0 1-34 0 0,7-4 418 0 0,-1-1 1 0 0,0 0-1 0 0,-1-1 1 0 0,0-2 0 0 0,-1 0-1 0 0,-27 9 1 0 0,57-19 4411 0 0,84 11-1971 0 0,-53-6-2548 0 0,40 1-1020 0 0,-89 1-6720 0 0,-23 4 4843 0 0,32-11 2293 0 0,-67 19-3147 0 0,-69 24 5420 0 0,124-37-720 0 0,-12 4 4892 0 0,26-8-5880 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,1-1 0 0 0,3 3-1 0 0,32 21 660 0 0,-26-18-415 0 0,0 0-293 0 0,0-1 0 0 0,1 0 1 0 0,0-1-1 0 0,0 0 1 0 0,24 5-1 0 0,-28-8-615 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 0 0 0 0,8-3 0 0 0,-15 3 11 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,2-2 1 0 0,-1-1-290 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0-6 0 0 0,-1-6-937 0 0,0 0 0 0 0,-1-1 1 0 0,-5-19-1 0 0,4 22 1172 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5213.53">3457 841 412 0 0,'-9'69'6101'0'0,"9"-68"-5960"0"0,-15 128 6005 0 0,-2-66-7515 0 0,13-52 183 0 0,0 0-1 0 0,-1-1 1 0 0,-10 15 0 0 0,12-21 752 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,0-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,0-1 0 0 0,-7 2-1 0 0,2-2-62 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5669.47">3064 1269 76 0 0,'6'19'1329'0'0,"-1"0"-1"0"0,0 1 1 0 0,-1-1-1 0 0,-1 1 1 0 0,-1 0-1 0 0,-1-1 1 0 0,-1 1-1 0 0,0 0 1 0 0,-4 23-1 0 0,-5 14 837 0 0,-29 103 1 0 0,34-148-2206 0 0,-4 19-582 0 0,-1-1-1 0 0,-16 32 0 0 0,24-62 72 0 0,1-5-732 0 0,0-1 601 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,2-9 1 0 0,2-6-271 0 0,12-27-1 0 0,-7 21 320 0 0,81-210-1346 0 0,-33 88 2392 0 0,-1 17 2453 0 0,-12 49 4553 0 0,-45 82-7257 0 0,0 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 1 1 0 0,1-1-19 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,0 3 1 0 0,2 1 14 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,-1 0-1 0 0,3 7 1 0 0,-1 7 107 0 0,0 0 0 0 0,-1 0 0 0 0,-1 1 1 0 0,-1 27-1 0 0,-11 86 69 0 0,6-84-272 0 0,-5 266-1988 0 0,9-257-37 0 0,1-48 2986 0 0,1 0-4004 0 0,-1 0-5543 0 0,-7-27 3483 0 0,1-1 2516 0 0,-4-31 0 0 0,5 25 1649 0 0,0 3 328 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5993.89">3106 1401 216 0 0,'-2'-4'339'0'0,"-1"2"135"0"0,1 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1-5 1 0 0,4 8 319 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,3 0 1 0 0,4 1 264 0 0,0-1 1 0 0,0 2 0 0 0,17 3-1 0 0,-17-2-925 0 0,0-1 0 0 0,0 2 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 1 0 0 0,14 9 0 0 0,-21-14-242 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 2 1 0 0,-1-1-61 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 1 0 0,-2 2-1 0 0,-6 7-327 0 0,0-1 0 0 0,0-1 1 0 0,-15 12-1 0 0,13-12 381 0 0,2-2 470 0 0,0 0 0 0 0,-1 0 0 0 0,-14 6 1 0 0,-8 6 3624 0 0,32-15 80 0 0,8 0-2907 0 0,12 2-1529 0 0,-18-6 750 0 0,81 22-1263 0 0,-76-20 54 0 0,-1-1-1 0 0,1 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 0 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,7-5 1 0 0,-5 2 64 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,7-10-1 0 0,50-69-2750 0 0,-39 48 2856 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6483.07">4075 434 196 0 0,'-11'120'16423'0'0,"10"-52"-13837"0"0,4 130-2857 0 0,0-164-1129 0 0,0 8-1624 0 0,-3-13-6575 0 0,-6-58 5705 0 0,6 16 3237 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6723.17">4224 407 480 0 0,'9'-10'757'0'0,"-7"8"-182"0"0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,2 0 0 0 0,-1 1 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,4 0-1 0 0,72 4 7844 0 0,40 13-5475 0 0,-82-12-1942 0 0,-29-4-903 0 0,0 0 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 1 0 0,9 8 0 0 0,-11-7-107 0 0,1-1 1 0 0,0 1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 8 0 0 0,0 7-551 0 0,-2-1 0 0 0,-1 1 0 0 0,-1 0 0 0 0,-9 28 0 0 0,-33 78-6848 0 0,42-119 6589 0 0,-5 15-2331 0 0,-15 24 0 0 0,21-42 2504 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0-1 1 0 0,-1 1-1 0 0,-8 5 0 0 0,12-9 490 0 0,-1 1 0 0 0,1-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,0 0-1 0 0,-3-2 1 0 0,-3-2-366 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6916.5">4295 572 36 0 0,'-24'-18'1636'0'0,"-2"-2"1770"0"0,9 4 6123 0 0,33 21-5629 0 0,9 12-2817 0 0,-10-8-620 0 0,0 1-264 0 0,78 42 794 0 0,-76-45-2284 0 0,33 11-1 0 0,-49-18 1034 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 2 1 0 0,-1 2-357 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,-5 7 1 0 0,-27 31-2370 0 0,20-26 2216 0 0,1-1 149 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7115.2">4219 932 320 0 0,'-8'8'14578'0'0,"7"-6"-12703"0"0,3 0-1496 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 0 0 0,4 2 1 0 0,39 4 346 0 0,-40-5-448 0 0,24 1-289 0 0,31 0 0 0 0,-52-2-770 0 0,-1-1-1 0 0,1 1 1 0 0,-1-2-1 0 0,1 1 1 0 0,-1-1-1 0 0,0-1 1 0 0,0 1-1 0 0,14-7 1 0 0,-20 7 223 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,2-6-1 0 0,-1-3-527 0 0,0 0 0 0 0,-1-1 0 0 0,-1-16 0 0 0,0 18 718 0 0,-1-8-187 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7380.54">4508 92 500 0 0,'-1'-8'2973'0'0,"-2"20"964"0"0,-2 4-2686 0 0,-6 19 1824 0 0,-10 52-1 0 0,11-40-1986 0 0,-77 336 2479 0 0,23 4-2644 0 0,64-383-919 0 0,-11 133 101 0 0,11-120-97 0 0,0-1 0 0 0,1 0 0 0 0,1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,8 24 0 0 0,-10-36 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,7 3 0 0 0,-5-3-55 0 0,0-1 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,10-3 0 0 0,1-2-654 0 0,-1 0 1 0 0,0-1-1 0 0,0-1 0 0 0,0 0 1 0 0,-1-1-1 0 0,25-18 0 0 0,-18 9-1105 0 0,0-1 0 0 0,-1-1 0 0 0,-1-1 0 0 0,29-37 0 0 0,58-98-3026 0 0,-90 128 4361 0 0,7-11-109 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7537.21">5263 90 128 0 0,'-20'-45'7364'0'0,"20"45"-7151"0"0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-2 1 0 0 0,-14 9 1749 0 0,6 1-3346 0 0,-73 110-15135 0 0,77-112 15713 0 0,1 0 145 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7717.29">5061 429 256 0 0,'-3'16'2332'0'0,"0"-1"0"0"0,1 1 0 0 0,1 0 0 0 0,0-1-1 0 0,2 23 1 0 0,-1-34-1992 0 0,8 68-1021 0 0,-7-45-3433 0 0,0 0 0 0 0,-4 28 0 0 0,3-42 3439 0 0,0 0 118 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7859.04">5012 1067 440 0 0,'0'10'1240'0'0,"-1"-9"-953"0"0,1 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,5 6 8347 0 0,2-10-3841 0 0,8-8-3054 0 0,-5 0-1951 0 0,0 0-1 0 0,13-20 0 0 0,-10 10-1638 0 0,-1 0-1 0 0,12-32 1 0 0,32-115-7763 0 0,-55 167 9583 0 0,42-150-4246 0 0,-31 109 3586 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8114.41">5388 43 100 0 0,'-24'57'3642'0'0,"-7"-3"4132"0"0,28-40 2685 0 0,22-16-567 0 0,-7-1-11397 0 0,251-32 4277 0 0,-199 31-3488 0 0,-1 3 1 0 0,74 7-1 0 0,-134-6 1641 0 0,7 1-1191 0 0,4-1-6165 0 0,-20-11-4325 0 0,-37-19 3724 0 0,-19-17 1808 0 0,28 21 3626 0 0,14 11 1081 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8316.9">5406 112 268 0 0,'-12'56'3977'0'0,"-26"80"1"0"0,10-41 403 0 0,-26 116 3030 0 0,-17 108-5135 0 0,18-75-3224 0 0,49-225 549 0 0,3-11-120 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,-1-1 0 0 0,0 0 0 0 0,-5 12 0 0 0,7-19 379 0 0,1-1-1 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 0 0 0,-6-19-1830 0 0,3-2 736 0 0,1 0 0 0 0,1 0 0 0 0,1 0 0 0 0,5-26 0 0 0,21-87-1553 0 0,-27 131 2714 0 0,45-147-1709 0 0,-26 100 1400 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9048.85">5535 218 0 0 0,'15'-14'647'0'0,"24"-20"1577"0"0,-37 32-1805 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,4 1 1 0 0,-6-1-97 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 2 0 0 0,3 34 2839 0 0,-3-33-2967 0 0,-1 16 295 0 0,-1 0 0 0 0,-1 0-1 0 0,-8 32 1 0 0,-23 58-336 0 0,29-94-141 0 0,-12 36-195 0 0,4-9-359 0 0,-1-1-1 0 0,-3-1 1 0 0,-26 49-1 0 0,41-86 448 0 0,0-1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,-1 0 0 0 0,-3 2 0 0 0,6-5 79 0 0,0 0 1 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 9 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,1-6 84 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,2-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,8-12 0 0 0,3-3 488 0 0,35-37-1 0 0,-37 44-307 0 0,1 2-1 0 0,1-1 1 0 0,23-14-1 0 0,-32 23-170 0 0,1 1-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 1 0 0 0,0 0 0 0 0,10-1 1 0 0,-14 2-43 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,2 8 1 0 0,-2-8-69 0 0,0 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,-5 5 1 0 0,-2-2-268 0 0,0 0 1 0 0,0-1-1 0 0,0 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,-13 4 0 0 0,-5 0-511 0 0,-38 7-1 0 0,62-14 720 0 0,-41 5-471 0 0,42-7 531 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 1 0 0,-7-2-1 0 0,9 3 29 0 0,1 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1-1 1 0 0,8-6 259 0 0,11-1 138 0 0,-6 4-225 0 0,0 0 0 0 0,0 1 1 0 0,0 1-1 0 0,0 0 0 0 0,20 1 1 0 0,-28 0-152 0 0,0 1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 1 0 0,6 6-1 0 0,-8-6-19 0 0,-1 1 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,0 7-1 0 0,-1 5-5 0 0,-1 0 0 0 0,-6 31 0 0 0,1-22-73 0 0,-14 32 0 0 0,13-39 22 0 0,0 1 1 0 0,2 0-1 0 0,-5 26 0 0 0,3 17 44 0 0,1 81 0 0 0,7-140 30 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0-1 0 0 0,-3 5 0 0 0,3-6-13 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,-5-2 0 0 0,-3 1-31 0 0,0-1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-2 1 0 0,0 0 0 0 0,1 0 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1-1 0 0 0,2 0-1 0 0,-17-10 1 0 0,19 10 37 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-3-13 0 0 0,5 16 57 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,1-1-1 0 0,4-9 1 0 0,-2 8 66 0 0,0 0-1 0 0,1-1 0 0 0,0 2 1 0 0,0-1-1 0 0,0 0 1 0 0,1 1-1 0 0,12-10 0 0 0,-6 6 55 0 0,1 1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,30-6 0 0 0,-17 9-96 0 0,0 0-1 0 0,0 1 1 0 0,0 2-1 0 0,0 1 1 0 0,0 1-1 0 0,0 1 1 0 0,36 10 0 0 0,181 62-2948 0 0,-216-65 2132 0 0,43 15-1461 0 0,196 61-6744 0 0,-230-77 7526 0 0,1-2-1 0 0,-1-1 0 0 0,1-2 0 0 0,0-2 1 0 0,53-3-1 0 0,-49-3 363 0 0,-1-3 0 0 0,0-1 1 0 0,59-20-1 0 0,-21 1 275 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink31.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -2085,11 +3682,11 @@
     </inkml:brush>
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">2695 224 136 0 0,'-14'-9'5158'0'0,"-5"-3"3276"0"0,10 10-7485 0 0,1-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 0 0 0 0,-9-8 0 0 0,-17-7 619 0 0,-3 0-362 0 0,-1 2 0 0 0,-1 2 0 0 0,-1 2 0 0 0,-71-15 0 0 0,-43 11 444 0 0,-305 7 1 0 0,293 11-1446 0 0,135 1-190 0 0,0 1 0 0 0,-39 9-1 0 0,-27 3-11 0 0,66-12-7 0 0,0 2 0 0 0,0 1-1 0 0,0 1 1 0 0,0 1 0 0 0,-36 17 0 0 0,-42 17-40 0 0,101-39 41 0 0,-13 5-7 0 0,-1 1 1 0 0,1 1-1 0 0,-36 23 1 0 0,-74 48-43 0 0,76-43 33 0 0,37-27 12 0 0,2 0 0 0 0,-29 25 0 0 0,-53 50-37 0 0,92-80 40 0 0,1-1 0 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 0-1 0 0,-1 0 1 0 0,-10 6 0 0 0,-18 32-14 0 0,27-36 15 0 0,2-1 1 0 0,-1 1-1 0 0,1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,1 0-1 0 0,1 1 1 0 0,-4 7-1 0 0,-21 34-2 0 0,10-22 1 0 0,0 1-1 0 0,-19 44 1 0 0,-9 15-3 0 0,25-39 6 0 0,18-39 0 0 0,-1 0 0 0 0,1 0 0 0 0,-2-1 0 0 0,-8 15 0 0 0,7-13 0 0 0,-1 1 0 0 0,2 0 0 0 0,0 1 0 0 0,-7 21 0 0 0,-6 12 0 0 0,8-21-8 0 0,2 1 0 0 0,-8 29 0 0 0,8-22-8 0 0,3-17 4 0 0,1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,0 27 0 0 0,-2 24-16 0 0,3-52 26 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,5 21 1 0 0,1 3-14 0 0,-6-28-2 0 0,1-1 0 0 0,0 0 0 0 0,1 1 1 0 0,8 18-1 0 0,15 25-27 0 0,35 62 41 0 0,-46-94-4 0 0,0 0-1 0 0,1-2 1 0 0,1 0-1 0 0,1 0 1 0 0,1-2-1 0 0,33 26 1 0 0,6-1 6 0 0,106 58 0 0 0,-109-71 12 0 0,86 35 1 0 0,-109-53-9 0 0,26 11 11 0 0,1-3 0 0 0,1-2 1 0 0,81 12-1 0 0,239 29 72 0 0,-375-58-85 0 0,189 14 26 0 0,-162-14-23 0 0,-1-2 1 0 0,0-1-1 0 0,0-1 0 0 0,34-9 0 0 0,30-5 10 0 0,13-3 6 0 0,-24-1 12 0 0,-47 13-17 0 0,0-2-1 0 0,-1-1 0 0 0,40-18 1 0 0,-31 8 2 0 0,-23 11-7 0 0,-1 0 0 0 0,0-1 0 0 0,32-24 0 0 0,-20 10 4 0 0,39-34 7 0 0,-38 26-4 0 0,88-96 47 0 0,-85 79-14 0 0,-2-2 1 0 0,49-95-1 0 0,-70 114-26 0 0,-1 0 1 0 0,-2-1-1 0 0,-1 0 0 0 0,-2-1 1 0 0,6-58-1 0 0,-9 29 2 0 0,-4 0 0 0 0,-2 0-1 0 0,-18-117 1 0 0,-26-59-52 0 0,39 218 35 0 0,0 1 1 0 0,-1 0-1 0 0,-2 1 1 0 0,0-1-1 0 0,-1 2 1 0 0,-1-1-1 0 0,-16-21 1 0 0,5 6 8 0 0,-8-9 11 0 0,-50-57 0 0 0,17 23-29 0 0,49 59 1 0 0,9 11 0 0 0,-1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,-14-11 0 0 0,-42-34 0 0 0,46 36 0 0 0,-1 0 0 0 0,-1 2 0 0 0,-1 0 0 0 0,-22-11 0 0 0,-13-7 0 0 0,40 22 0 0 0,-1 1 0 0 0,0 0 0 0 0,-22-8 0 0 0,-49-20 0 0 0,-42-6 0 0 0,94 32 0 0 0,27 8 0 0 0,1 0 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,-8 2 0 0 0,10-2 0 0 0,1-3 0 0 0,0 3 0 0 0,-1 1 0 0 0,-54 2-1892 0 0,9 9-4718 0 0,46-9 5742 0 0,0 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 1 0 0 0,1 0 0 0 0,0-1 1 0 0,-3 8-1 0 0,-2 2-991 0 0,5-9 1180 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,-1 9 0 0 0,3-3-72 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="143.61">1655 315 232 0 0,'1'16'-73'0'0,"0"-15"493"0"0,-1 0-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 1 0 0 0,0-1-1 0 0,0 2 1 0 0,-16 1 559 0 0,5-1-3616 0 0,-2-3 1230 0 0,-31-6-7087 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="143.6">1655 315 232 0 0,'1'16'-73'0'0,"0"-15"493"0"0,-1 0-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 1 0 0 0,0-1-1 0 0,0 2 1 0 0,-16 1 559 0 0,5-1-3616 0 0,-2-3 1230 0 0,-31-6-7087 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink32.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -2128,7 +3725,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink33.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -2166,39 +3763,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink2.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
-          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
-          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2025-04-17T13:14:17.317"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.035" units="cm"/>
-      <inkml:brushProperty name="height" value="0.035" units="cm"/>
-      <inkml:brushProperty name="color" value="#E71224"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 328 0 0,'7'16'3826'0'0,"0"1"1"0"0,-1 0-1 0 0,-1 1 1 0 0,4 21-1 0 0,9 80 6008 0 0,5 26-6361 0 0,8-15-3473 0 0,23 207 0 0 0,-49-308-192 0 0,1 21 565 0 0,-5-47-620 0 0,-1-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 1 0 0,-3 2-1 0 0,3-3-168 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,-1-2 0 0 0,-27-30-7188 0 0,23 22 6181 0 0,1-1 0 0 0,0 1 0 0 0,-4-19 0 0 0,1 6 246 0 0,-1 2 499 0 0</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink34.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -2227,46 +3792,12 @@
     </inkml:brush>
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">503 283 496 0 0,'0'-3'498'0'0,"0"0"0"0"0,-1 0 0 0 0,1 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-3-3 0 0 0,0 2 317 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-12-2-1 0 0,7 2 80 0 0,0 0 0 0 0,0 1-1 0 0,0 0 1 0 0,0 1 0 0 0,-13 2-1 0 0,16-2-699 0 0,0 1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1 0 0 0 0,-7 6-1 0 0,-6 6 170 0 0,0 2 1 0 0,2 0-1 0 0,0 1 0 0 0,1 1 0 0 0,0 1 0 0 0,2 0 0 0 0,1 1 0 0 0,0 0 1 0 0,-16 36-1 0 0,12-16-70 0 0,1 1 1 0 0,2 1-1 0 0,2 1 0 0 0,-11 66 1 0 0,20-83-231 0 0,1-1 1 0 0,1 0 0 0 0,2 1-1 0 0,0 0 1 0 0,8 47-1 0 0,-5-56-58 0 0,1-1 0 0 0,1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,0 0 0 0 0,2 0 0 0 0,0-1 0 0 0,17 23 0 0 0,-23-34-69 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,1-1 1 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,7-5 0 0 0,10-7-1498 0 0,0 0 1 0 0,-1-2 0 0 0,-1 0 0 0 0,33-36 0 0 0,-41 41 398 0 0,3-7-654 0 0,-1-1-1 0 0,0 0 1 0 0,-1-1 0 0 0,-2 0 0 0 0,0-1-1 0 0,11-29 1 0 0,8-12-2276 0 0,-3-2 1473 0 0,-17 48 2136 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="258.28">931 187 544 0 0,'16'-37'21110'0'0,"-16"40"-17945"0"0,-1 16-1848 0 0,-8 16-84 0 0,-2-1 0 0 0,-21 46 0 0 0,3-6-578 0 0,-14 35-541 0 0,-87 160 0 0 0,71-183-1612 0 0,36-55 463 0 0,18-24 140 0 0,-2-1 1 0 0,1 1-1 0 0,0-1 1 0 0,-1-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,-13 7-1 0 0,19-12-805 0 0,-2-7-2156 0 0,2 3 3203 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0-1 0 0,1-1 1 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,0-9-1 0 0,8-48-2528 0 0,23-83 0 0 0,-17 107 2667 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="258.27">931 187 544 0 0,'16'-37'21110'0'0,"-16"40"-17945"0"0,-1 16-1848 0 0,-8 16-84 0 0,-2-1 0 0 0,-21 46 0 0 0,3-6-578 0 0,-14 35-541 0 0,-87 160 0 0 0,71-183-1612 0 0,36-55 463 0 0,18-24 140 0 0,-2-1 1 0 0,1 1-1 0 0,0-1 1 0 0,-1-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,-13 7-1 0 0,19-12-805 0 0,-2-7-2156 0 0,2 3 3203 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0-1 0 0,1-1 1 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,0-9-1 0 0,8-48-2528 0 0,23-83 0 0 0,-17 107 2667 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="500.35">801 134 172 0 0,'28'-33'1173'0'0,"-26"31"-697"0"0,0 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0-1 0 0 0,4 0-1 0 0,-4 2-2 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 4 0 0 0,12 14 1250 0 0,0 1-1 0 0,-2 0 0 0 0,-1 1 1 0 0,16 38-1 0 0,27 100 1703 0 0,-54-155-3341 0 0,45 170 1450 0 0,2 9-1246 0 0,-26-91-258 0 0,-2-41-87 0 0,-16-45-183 0 0,0 1 1 0 0,-1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 10 0 0 0,-2-17 118 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,-26 0-4557 0 0,-20-13-2779 0 0,32 7 5592 0 0,1-2 0 0 0,1 0 1 0 0,-18-13-1 0 0,-6-4-675 0 0,28 19 1944 0 0,0-1-1 0 0,1 0 1 0 0,-14-14-1 0 0,10 9 72 0 0,-9-9-108 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="697.93">752 656 200 0 0,'-7'0'1089'0'0,"7"0"-891"0"0,0 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-6 11 13534 0 0,29 0-8202 0 0,17-10-3028 0 0,-25 1-1813 0 0,-1-2 0 0 0,1 0 0 0 0,19-3 0 0 0,-13 0-431 0 0,1-1 0 0 0,-2-2 0 0 0,24-8 0 0 0,-36 11-648 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,8-10 1 0 0,1-4-3111 0 0,11-16-3949 0 0,-5 17-4342 0 0,-5 9 8629 0 0,-6 4 2467 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="917.53">1489 192 516 0 0,'0'0'514'0'0,"1"-1"-1"0"0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0-30 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0 1 1 0 0,-1 0-1 0 0,-23 70 5014 0 0,20-60-5682 0 0,-17 43 973 0 0,-69 170-162 0 0,62-163-3267 0 0,-56 90-1 0 0,69-131 1106 0 0,-7 11-1128 0 0,15-15-2140 0 0,7-50-2124 0 0,3-5 4962 0 0,2-1 1 0 0,2 0-1 0 0,19-63 0 0 0,-23 92 1747 0 0,7-32-403 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1169.22">1402 267 356 0 0,'21'-33'1063'0'0,"5"11"3282"0"0,-25 22-4021 0 0,0-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 1 0 0,1 0 0 0 0,0 0 214 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,2 5 1 0 0,6 12 1465 0 0,0 0 1 0 0,13 38-1 0 0,19 99 1910 0 0,-20-66-2303 0 0,-6-15-696 0 0,-10-45-436 0 0,16 50-1 0 0,11 59 112 0 0,-33-139-586 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,11-11 100 0 0,5-19-59 0 0,-15 29-47 0 0,11-27 1 0 0,-2 0 0 0 0,0-1 0 0 0,-2 0 0 0 0,6-41 0 0 0,3-13 0 0 0,37-167-404 0 0,-45 204-619 0 0,5-49 1 0 0,-9 2-6820 0 0,-11 124-7320 0 0,13 5 8960 0 0,-3-30 5478 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1600.68">2187 0 312 0 0,'-5'23'8946'0'0,"13"-6"2131"0"0,12-3-4546 0 0,41 6-2121 0 0,-9-3-3358 0 0,-44-13-1009 0 0,1 0 0 0 0,-1 1 1 0 0,0 0-1 0 0,-1 0 0 0 0,13 11 1 0 0,-17-13-41 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 7-1 0 0,-1 17 3 0 0,-2 1 0 0 0,0 0-1 0 0,-3-1 1 0 0,0 1 0 0 0,-19 49 0 0 0,1-16 9 0 0,-49 86 0 0 0,53-112 1 0 0,-1-1 1 0 0,-45 54-1 0 0,56-77-15 0 0,0-1-1 0 0,-1 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1-1-1 0 0,-2 0 1 0 0,1-1-1 0 0,-20 8 1 0 0,32-15-1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,65-31 0 0 0,102-34 0 0 0,-133 56 0 0 0,0 0 0 0 0,0 3 0 0 0,1 1 0 0 0,0 1 0 0 0,40 1 0 0 0,-36 5 1427 0 0,-9 1-5006 0 0,-24-1 559 0 0,-47 10-7861 0 0,25-8 8703 0 0,8-1 1299 0 0,-1 0-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0-1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,-7-4 0 0 0,-6-5 3 0 0</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink3.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
-          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
-          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2025-04-17T13:14:16.081"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.035" units="cm"/>
-      <inkml:brushProperty name="height" value="0.035" units="cm"/>
-      <inkml:brushProperty name="color" value="#E71224"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">423 62 328 0 0,'8'-30'2678'0'0,"-2"9"9263"0"0,-34 12-3443 0 0,-1 8-5824 0 0,-21 1 466 0 0,38 4-2985 0 0,0 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 2 0 0 0,1-1 0 0 0,0 1 0 0 0,0 1 0 0 0,1-1 0 0 0,-13 17-1 0 0,3-1-120 0 0,1 2-1 0 0,1-1 0 0 0,1 2 0 0 0,-15 35 0 0 0,26-54-31 0 0,-8 19 2 0 0,2-1 0 0 0,0 1-1 0 0,1 1 1 0 0,-9 56-1 0 0,11-19-17 0 0,3-46-1 0 0,2 1 0 0 0,0-1 0 0 0,1 1 0 0 0,1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,9 36 0 0 0,-5-40-2 0 0,0-1 0 0 0,1 0-1 0 0,1 0 1 0 0,0-1 0 0 0,1 0 0 0 0,1 0-1 0 0,0-1 1 0 0,0 0 0 0 0,1-1 0 0 0,1 0 0 0 0,16 14-1 0 0,-21-21-170 0 0,0 0-1 0 0,0-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 1 0 0,1-2-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 0 1 0 0,-1 0-1 0 0,10-4 0 0 0,-7 1-541 0 0,-1 0 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0-1 0 0 0,7-9 0 0 0,6-10-3748 0 0,26-48 0 0 0,-34 52 2147 0 0,1 2 0 0 0,0-1 0 0 0,32-33 0 0 0,-33 45 1682 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="586.76">1026 123 268 0 0,'-2'-2'872'0'0,"-1"-1"0"0"0,1 2 0 0 0,0-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-4 0 0 0 0,3 1-219 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 1 0 0 0,-1-1 0 0 0,-3 2 0 0 0,-9 6 98 0 0,0 1 1 0 0,1 0-1 0 0,-29 24 1 0 0,7-5 397 0 0,27-21-990 0 0,0 1 0 0 0,1 0 0 0 0,0 1 1 0 0,1 0-1 0 0,0 1 0 0 0,1 0 0 0 0,0 0 1 0 0,0 1-1 0 0,1-1 0 0 0,1 2 0 0 0,-8 21 1 0 0,3-6-54 0 0,3 0 0 0 0,0 0 0 0 0,2 1 0 0 0,-5 43 0 0 0,10-56-104 0 0,1-1 0 0 0,0 1 1 0 0,1 0-1 0 0,0-1 0 0 0,1 1 0 0 0,1-1 0 0 0,1 0 1 0 0,8 22-1 0 0,-9-28-27 0 0,1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,2 0 0 0 0,-1 0 0 0 0,1-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,0-1 0 0 0,9 6 0 0 0,-11-9-46 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,6-6 0 0 0,2 0-174 0 0,-1 0 0 0 0,0-2 1 0 0,-1 1-1 0 0,0-2 0 0 0,-1 0 1 0 0,18-23-1 0 0,-13 12-139 0 0,-1-2 0 0 0,-2 0 0 0 0,0-1 0 0 0,-2 0 0 0 0,0-1 0 0 0,11-47 0 0 0,-13 30-82 0 0,-2-1 0 0 0,-1 1-1 0 0,-1-69 1 0 0,-15 52 3230 0 0,9 63-2657 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,1 5 0 0 0,0 47 159 0 0,5 3-172 0 0,3 0 0 0 0,2 0-1 0 0,2-2 1 0 0,22 57 0 0 0,-34-108-136 0 0,26 57-255 0 0,-25-57 123 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 0 0 0,4 2 1 0 0,-5-4-86 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0-2-1 0 0,6-9-1126 0 0,-2 0 0 0 0,0 0 0 0 0,5-16 1 0 0,-8 20 850 0 0,31-121-4728 0 0,-24 102 4546 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="998.24">1469 72 564 0 0,'-2'5'913'0'0,"0"1"0"0"0,1-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1 0 0 0,3 8 0 0 0,8 41 3103 0 0,26 222 1249 0 0,-28-201-4840 0 0,-7-47-196 0 0,4 49 1 0 0,-8-76-214 0 0,2 0 4 0 0,6-7-10 0 0,4-13 0 0 0,0-26-55 0 0,16-43 0 0 0,4-9-65 0 0,-12 9 4 0 0,12-37-93 0 0,-5 64 121 0 0,-26 58 78 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,4-1 1 0 0,-4 3 26 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,1 3-1 0 0,32 32 654 0 0,-25-21-421 0 0,0-1 1 0 0,-1 2-1 0 0,0-1 1 0 0,-1 1-1 0 0,-1 0 1 0 0,7 23-1 0 0,22 106 626 0 0,-26-102-854 0 0,2 37-535 0 0,-11-73 114 0 0,0 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,-4 9 1 0 0,4-15 12 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,0 1 0 0 0,1-1 0 0 0,-3 1 0 0 0,-11-8-4049 0 0,13 5 4080 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-4 1 0 0,2-5-411 0 0,0 1 0 0 0,1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,7-14 1 0 0,0 1-7 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1600.67">2187 0 312 0 0,'-5'23'8946'0'0,"13"-6"2131"0"0,12-3-4546 0 0,41 6-2121 0 0,-9-3-3358 0 0,-44-13-1009 0 0,1 0 0 0 0,-1 1 1 0 0,0 0-1 0 0,-1 0 0 0 0,13 11 1 0 0,-17-13-41 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 7-1 0 0,-1 17 3 0 0,-2 1 0 0 0,0 0-1 0 0,-3-1 1 0 0,0 1 0 0 0,-19 49 0 0 0,1-16 9 0 0,-49 86 0 0 0,53-112 1 0 0,-1-1 1 0 0,-45 54-1 0 0,56-77-15 0 0,0-1-1 0 0,-1 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1-1-1 0 0,-2 0 1 0 0,1-1-1 0 0,-20 8 1 0 0,32-15-1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,65-31 0 0 0,102-34 0 0 0,-133 56 0 0 0,0 0 0 0 0,0 3 0 0 0,1 1 0 0 0,0 1 0 0 0,40 1 0 0 0,-36 5 1427 0 0,-9 1-5006 0 0,-24-1 559 0 0,-47 10-7861 0 0,25-8 8703 0 0,8-1 1299 0 0,-1 0-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0-1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,-7-4 0 0 0,-6-5 3 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -2298,10 +3829,10 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">382 126 0 0 0,'-4'-36'3640'0'0,"2"31"-2258"0"0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,-5-4 0 0 0,-14 5 2737 0 0,-16 11-2362 0 0,26 0-1501 0 0,0 1 0 0 0,0 0-1 0 0,1 1 1 0 0,0 0 0 0 0,0 1 0 0 0,2 0-1 0 0,-1 1 1 0 0,1 0 0 0 0,1 1 0 0 0,0 0-1 0 0,1 0 1 0 0,-8 19 0 0 0,-8 18 45 0 0,2 2 1 0 0,-15 58 0 0 0,26-73-282 0 0,1 0 0 0 0,1 1 0 0 0,3 0 0 0 0,1 0 1 0 0,1 1-1 0 0,3-1 0 0 0,4 58 0 0 0,-1-80-73 0 0,0 1-1 0 0,1-1 0 0 0,1 0 1 0 0,9 24-1 0 0,-12-37-128 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,5-1-1 0 0,1 0-584 0 0,1-1 0 0 0,-1 0 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,-1-1 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1-1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 0-1 0 0,8-8 1 0 0,9-10-1684 0 0,-2-1 0 0 0,-1-1 1 0 0,22-34-1 0 0,8-11 192 0 0,-33 48 1675 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="431.29">773 246 400 0 0,'14'-24'17532'0'0,"-54"37"-12776"0"0,21-8-3837 0 0,0 1 1 0 0,1 1 0 0 0,-28 14-1 0 0,29-11-681 0 0,0 1 0 0 0,1 0 0 0 0,1 1 0 0 0,0 1 0 0 0,1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,1 1 0 0 0,0 1-1 0 0,-14 25 1 0 0,14-18-206 0 0,1 0-1 0 0,1 2 1 0 0,0-1-1 0 0,2 1 0 0 0,1 0 1 0 0,2 1-1 0 0,-5 35 1 0 0,10-55-46 0 0,-1 0 1 0 0,1 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,0-1 1 0 0,7 2 0 0 0,-3-1-91 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-2 0 0 0,-1 1 0 0 0,1-2 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1-1 0 0 0,16-7 0 0 0,-12 3-117 0 0,1 0 0 0 0,-2-2 0 0 0,1 1 1 0 0,-1-2-1 0 0,0 1 0 0 0,-1-2 0 0 0,20-22 0 0 0,-1-9-369 0 0,-1 0 0 0 0,-2-2-1 0 0,-2-1 1 0 0,19-50 0 0 0,-14 7-20 0 0,-16 42 572 0 0,-17 54 1520 0 0,-1-1-1305 0 0,1 0 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 13 0 0 0,2 10-115 0 0,1 0 1 0 0,2 0-1 0 0,1 0 1 0 0,2 0-1 0 0,17 55 1 0 0,-11-44-232 0 0,-8-27 14 0 0,1-1 1 0 0,0 1-1 0 0,1-1 1 0 0,9 17-1 0 0,-1 3-1827 0 0,-8-14-2233 0 0,-1-42-4925 0 0,8-79 2721 0 0,-3 20 4422 0 0,-5 45 1524 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="797.68">1192 167 512 0 0,'7'10'1393'0'0,"-1"0"-1"0"0,0 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,3 21 1 0 0,3 7 1269 0 0,70 281 4152 0 0,-25-98-5823 0 0,-44-189-901 0 0,-4-20-48 0 0,-3-12-28 0 0,8-42-191 0 0,-2-1 1 0 0,-1 0 0 0 0,2-80 0 0 0,7-45-302 0 0,-7 87 254 0 0,5-24 20 0 0,-14 95 200 0 0,2 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,9-16 0 0 0,-11 24 12 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 0 0 0,1-1 0 0 0,0 2 19 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,3 1 0 0 0,3 6 150 0 0,1 0 1 0 0,-1 0-1 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,0 0 0 0 0,4 20 0 0 0,0 14 213 0 0,4 65 0 0 0,-9-74-359 0 0,1 12-1030 0 0,-2 0-1 0 0,-8 78 1 0 0,6-122 767 0 0,-11 50-3502 0 0,-4-25-2087 0 0,14-29 5649 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1-1 1 0 0,-14-25-2537 0 0,13 17 2158 0 0,0 0 0 0 0,0-1-1 0 0,2 1 1 0 0,-1 0 0 0 0,1-1 0 0 0,1-10-1 0 0,3-7 2 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1041.05">2063 1 104 0 0,'2'3'1870'0'0,"0"0"1"0"0,0 1-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 4 1 0 0,7 19 5652 0 0,-1-9-5565 0 0,-1 0 1 0 0,10 36 0 0 0,10 93-193 0 0,-20-100-1517 0 0,26 224-417 0 0,-29-152-4904 0 0,-4-119 4868 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 1-1 0 0,-22-7-6839 0 0,17 4 5841 0 0,1-1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-5-6 0 0 0,-5-27-2257 0 0,10 23 2736 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">368 125 0 0 0,'-4'-36'3640'0'0,"2"31"-2258"0"0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,-5-4 0 0 0,-13 5 2737 0 0,-15 11-2362 0 0,24 0-1501 0 0,1 1 0 0 0,-1 0-1 0 0,2 0 1 0 0,-1 1 0 0 0,0 1 0 0 0,3 0-1 0 0,-2 1 1 0 0,2 0 0 0 0,0 1 0 0 0,0 0-1 0 0,2 0 1 0 0,-9 18 0 0 0,-7 19 45 0 0,2 2 1 0 0,-15 57 0 0 0,26-72-282 0 0,0-1 0 0 0,1 2 0 0 0,4 0 0 0 0,0 0 1 0 0,1 0-1 0 0,3 0 0 0 0,4 57 0 0 0,-1-79-73 0 0,0 1-1 0 0,1-1 0 0 0,0 0 1 0 0,10 23-1 0 0,-12-36-128 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0-1 0 0,2 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-2-1 0 0 0,2 1 0 0 0,5-1-1 0 0,1 0-584 0 0,0-1 0 0 0,0 0 0 0 0,-1-1-1 0 0,1 0 1 0 0,0 0 0 0 0,-2-1 0 0 0,2 0-1 0 0,-1-1 1 0 0,0 0 0 0 0,0-1 0 0 0,0 0-1 0 0,-2 0 1 0 0,2-1 0 0 0,-1 0-1 0 0,7-8 1 0 0,9-9-1684 0 0,-2-2 0 0 0,-1-1 1 0 0,22-34-1 0 0,7-10 192 0 0,-32 47 1675 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="431.29">744 244 400 0 0,'14'-24'17532'0'0,"-53"37"-12776"0"0,21-8-3837 0 0,-1 1 1 0 0,2 1 0 0 0,-27 14-1 0 0,28-11-681 0 0,-1 1 0 0 0,2 0 0 0 0,0 1 0 0 0,1 1 0 0 0,0 0 0 0 0,1 1 0 0 0,0 0 0 0 0,2 1 0 0 0,-1 1-1 0 0,-13 25 1 0 0,14-18-206 0 0,0-1-1 0 0,2 3 1 0 0,-1-1-1 0 0,2 1 0 0 0,1 0 1 0 0,3 0-1 0 0,-6 36 1 0 0,10-55-46 0 0,-1 0 1 0 0,1 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,1-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,1 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,0-1-1 0 0,1-1 1 0 0,7 2 0 0 0,-4-1-91 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-2 0 0 0,-1 1 0 0 0,0-2 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0-1 0 0 0,15-7 0 0 0,-11 3-117 0 0,0 0 0 0 0,-1-2 0 0 0,0 1 1 0 0,0-2-1 0 0,-1 1 0 0 0,0-2 0 0 0,19-21 0 0 0,-2-10-369 0 0,0 0 0 0 0,-2-1-1 0 0,-2-2 1 0 0,19-49 0 0 0,-14 6-20 0 0,-16 43 572 0 0,-16 53 1520 0 0,-1-2-1305 0 0,2 1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 13 0 0 0,2 10-115 0 0,1-1 1 0 0,2 1-1 0 0,1 0 1 0 0,2 0-1 0 0,16 54 1 0 0,-11-43-232 0 0,-7-27 14 0 0,1-1 1 0 0,0 1-1 0 0,0-2 1 0 0,10 18-1 0 0,-2 3-1827 0 0,-7-14-2233 0 0,-1-42-4925 0 0,7-78 2721 0 0,-2 19 4422 0 0,-5 46 1524 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="797.68">1147 166 512 0 0,'7'10'1393'0'0,"-1"0"-1"0"0,0 1 0 0 0,-1-2 1 0 0,0 2-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,2 21 1 0 0,4 7 1269 0 0,67 278 4152 0 0,-24-97-5823 0 0,-42-187-901 0 0,-4-20-48 0 0,-4-12-28 0 0,9-42-191 0 0,-2 0 1 0 0,-2-1 0 0 0,3-79 0 0 0,6-45-302 0 0,-6 87 254 0 0,4-24 20 0 0,-13 94 200 0 0,2 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,9-16 0 0 0,-11 24 12 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 0 0 0,1-1 0 0 0,0 2 19 0 0,-2-1 0 0 0,1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-2 1 0 0 0,4 1 0 0 0,3 6 150 0 0,1 0 1 0 0,-1 0-1 0 0,-2 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 1 1 0 0,-1-2-1 0 0,0 2 0 0 0,0 0 0 0 0,4 20 0 0 0,0 14 213 0 0,3 64 0 0 0,-8-73-359 0 0,1 11-1030 0 0,-2 1-1 0 0,-8 77 1 0 0,6-121 767 0 0,-11 50-3502 0 0,-3-26-2087 0 0,13-28 5649 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,0 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1-1 1 0 0,-13-24-2537 0 0,12 16 2158 0 0,0 0 0 0 0,0-1-1 0 0,2 1 1 0 0,-1 0 0 0 0,1-1 0 0 0,1-10-1 0 0,3-7 2 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1041.05">1986 1 104 0 0,'2'3'1870'0'0,"0"0"1"0"0,0 1-1 0 0,-1 0 1 0 0,0-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 4 1 0 0,7 19 5652 0 0,-1-10-5565 0 0,-2 1 1 0 0,11 36 0 0 0,9 92-193 0 0,-20-100-1517 0 0,26 223-417 0 0,-28-151-4904 0 0,-4-118 4868 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 1-1 0 0,-21-7-6839 0 0,16 4 5841 0 0,2-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-4-6 0 0 0,-6-27-2257 0 0,11 23 2736 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -2333,10 +3864,10 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">684 163 64 0 0,'0'-5'660'0'0,"-1"0"0"0"0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0 0 1 0 0,-1-1-1 0 0,-4 0 0 0 0,-1-1 657 0 0,0 0 0 0 0,0 1 0 0 0,-1 0 0 0 0,-17-2 0 0 0,-38 4-106 0 0,48 4-1012 0 0,1 1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1 1 1 0 0,1 0-1 0 0,0 2 1 0 0,0 0-1 0 0,1 1 1 0 0,0 0-1 0 0,1 1 0 0 0,0 1 1 0 0,1 0-1 0 0,0 1 1 0 0,0 0-1 0 0,1 1 1 0 0,1 0-1 0 0,-14 22 1 0 0,0 3-148 0 0,1 1 0 0 0,3 2 1 0 0,1 0-1 0 0,2 1 1 0 0,-20 69-1 0 0,25-68-43 0 0,2 1 0 0 0,2 0 1 0 0,-4 52-1 0 0,12-80-66 0 0,0-1 1 0 0,1 0-1 0 0,1 0 0 0 0,0 1 1 0 0,1-1-1 0 0,1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,1-1 1 0 0,0 1-1 0 0,1-1 0 0 0,0 0 1 0 0,10 14-1 0 0,-14-24-47 0 0,1-1 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,8 1 0 0 0,-4-2-212 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,15-3 0 0 0,6-5-1208 0 0,0 0-1 0 0,-1-2 1 0 0,39-20 0 0 0,-61 28 1227 0 0,50-30-3047 0 0,-1-1 1 0 0,-2-4 0 0 0,-1-1-1 0 0,58-59 1 0 0,-73 65 2409 0 0,-14 11 443 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="438.8">976 372 272 0 0,'4'-13'602'0'0,"-2"8"41"0"0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,-2-10 1 0 0,1 12-58 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-5-1-1 0 0,2 1-141 0 0,0 0 0 0 0,1 1 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,0 1 1 0 0,1 1 0 0 0,-9 2 0 0 0,1 1-127 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 1 1 0 0,0 1-1 0 0,0 0 0 0 0,1 1 1 0 0,-12 12-1 0 0,8-4-146 0 0,0 0-1 0 0,2 1 1 0 0,0 1 0 0 0,1 0-1 0 0,1 0 1 0 0,1 1 0 0 0,1 0-1 0 0,-6 22 1 0 0,10-31-163 0 0,2 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,0 0 0 0 0,1-1 1 0 0,0 1-1 0 0,1 0 0 0 0,0 0 0 0 0,1-1 1 0 0,0 1-1 0 0,1-1 0 0 0,0 0 1 0 0,8 14-1 0 0,-10-20-69 0 0,1 1 0 0 0,1-2 0 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,10-4 0 0 0,0-3-280 0 0,0-1 0 0 0,-1-1 0 0 0,0 0 1 0 0,-1-1-1 0 0,0 0 0 0 0,-1-1 0 0 0,0-1 0 0 0,-1 0 0 0 0,20-26 0 0 0,4-14-842 0 0,40-80-1 0 0,-57 99 826 0 0,-11 18 281 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-2 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1-30 0 0 0,-8 30 831 0 0,-5 22 445 0 0,-5 26-177 0 0,10 1-884 0 0,1 0 0 0 0,2-1-1 0 0,1 1 1 0 0,1 0-1 0 0,2 0 1 0 0,9 36-1 0 0,-4-13-5 0 0,0-16-329 0 0,2 1 0 0 0,1-1 0 0 0,2-1 0 0 0,2-1 0 0 0,26 47 0 0 0,-42-83 90 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,2 1 0 0 0,-2-2-125 0 0,0 1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0-2 0 0 0,16-55-6572 0 0,-17 57 6808 0 0,17-131-7277 0 0,0-3 3371 0 0,-8 105 3351 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="796.89">1503 186 488 0 0,'5'7'1437'0'0,"-1"0"0"0"0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,0 2 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 10 0 0 0,5 17 2154 0 0,7 49 364 0 0,5 119 0 0 0,-15-159-3301 0 0,-2-2-206 0 0,11 91 464 0 0,-3-106-858 0 0,-10-27-56 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,0-1 1 0 0,21-50-254 0 0,-16 39 203 0 0,63-230-1038 0 0,-20 59 323 0 0,-43 166 702 0 0,1 0 1 0 0,0 0 0 0 0,1 1 0 0 0,10-17 0 0 0,-15 30 98 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,4 1 0 0 0,-2 1 103 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,2 7 1 0 0,2 6-43 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,5 32-1 0 0,-7-22-205 0 0,-1 0-1 0 0,-2 1 1 0 0,0 0-1 0 0,-2 0 1 0 0,-1-1-1 0 0,-2 1 1 0 0,-6 29 0 0 0,4-37-1641 0 0,-2 0 0 0 0,-13 30 1 0 0,16-43 181 0 0,1-1 0 0 0,-1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-8 9 1 0 0,5-23-6157 0 0,5 6 7405 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,2-4 1 0 0,15-40-1670 0 0,-8 19 1275 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1019.49">2342 1 128 0 0,'2'4'1285'0'0,"0"1"-1"0"0,1 0 1 0 0,-2 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 8 1 0 0,2 4 2699 0 0,27 152 8965 0 0,-6 0-7726 0 0,25 344-7799 0 0,-38-379 4074 0 0,-2-60-5405 0 0,-9-72 1649 0 0,0-23-8420 0 0,0 4 8675 0 0,2-29-3454 0 0,16-83 1 0 0,-6 49 3453 0 0,-6 25 1174 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">662 161 64 0 0,'0'-5'660'0'0,"-1"0"0"0"0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,-1 2 1 0 0,1-1-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,1 0 1 0 0,-2-1-1 0 0,-4 0 0 0 0,-1-1 657 0 0,1 0 0 0 0,-1 1 0 0 0,-1 0 0 0 0,-16-2 0 0 0,-37 5-106 0 0,47 2-1012 0 0,1 2 1 0 0,-1 1-1 0 0,2 0 0 0 0,-2 1 1 0 0,2 0-1 0 0,-1 2 1 0 0,1 0-1 0 0,0 1 1 0 0,1 0-1 0 0,0 1 0 0 0,1 0 1 0 0,0 1-1 0 0,1 1 1 0 0,-1 0-1 0 0,1 1 1 0 0,2 0-1 0 0,-14 21 1 0 0,-1 4-148 0 0,2 0 0 0 0,3 3 1 0 0,1-1-1 0 0,1 1 1 0 0,-19 69-1 0 0,25-68-43 0 0,1 2 0 0 0,3-1 1 0 0,-5 52-1 0 0,12-79-66 0 0,0-1 1 0 0,1-1-1 0 0,1 1 0 0 0,0 1 1 0 0,1-1-1 0 0,1 0 0 0 0,0-1 1 0 0,1 1-1 0 0,0-1 1 0 0,1 1-1 0 0,1-1 0 0 0,0-1 1 0 0,9 15-1 0 0,-13-24-47 0 0,1-1 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1-1 0 0,1-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,7 0 0 0 0,-3-1-212 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,-1-1 0 0 0,16-2 0 0 0,5-6-1208 0 0,0 0-1 0 0,-1-2 1 0 0,38-20 0 0 0,-60 28 1227 0 0,50-29-3047 0 0,-2-2 1 0 0,-2-3 0 0 0,-1-2-1 0 0,57-57 1 0 0,-72 63 2409 0 0,-12 11 443 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="438.8">944 367 272 0 0,'4'-13'602'0'0,"-2"8"41"0"0,0 0-1 0 0,0 1 0 0 0,0 0 1 0 0,-2-1-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,-2-10 1 0 0,1 12-58 0 0,0 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 2 1 0 0,1-1 0 0 0,-1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,0-1 1 0 0,0 1 0 0 0,-5-1-1 0 0,2 1-141 0 0,0 0 0 0 0,1 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,0 1 1 0 0,2 1 0 0 0,-10 2 0 0 0,1 1-127 0 0,1 1 1 0 0,-1 0-1 0 0,1-1 0 0 0,0 2 1 0 0,0 1-1 0 0,1 0 0 0 0,0 1 1 0 0,-11 12-1 0 0,7-4-146 0 0,1-1-1 0 0,1 2 1 0 0,0 1 0 0 0,2 0-1 0 0,0-1 1 0 0,1 2 0 0 0,2 0-1 0 0,-7 21 1 0 0,10-30-163 0 0,2 1 1 0 0,-1-1-1 0 0,2 1 0 0 0,0-1 0 0 0,0 1 1 0 0,1 0-1 0 0,0 0 0 0 0,1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,1-1 0 0 0,1 0 1 0 0,0 1-1 0 0,1-1 0 0 0,0 0 1 0 0,8 13-1 0 0,-11-19-69 0 0,2 1 0 0 0,1-2 0 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,2 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-2 0 0 0,0 2 0 0 0,1-1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,11-3 0 0 0,-1-4-280 0 0,1-1 0 0 0,-2-1 0 0 0,1 0 1 0 0,-2-1-1 0 0,1 0 0 0 0,-1-1 0 0 0,-1 0 0 0 0,0-1 0 0 0,19-26 0 0 0,3-13-842 0 0,40-79-1 0 0,-56 97 826 0 0,-10 18 281 0 0,-1 2 0 0 0,0-2 0 0 0,-1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,1-29 0 0 0,-8 29 831 0 0,-5 22 445 0 0,-5 25-177 0 0,11 2-884 0 0,0 0 0 0 0,2-2-1 0 0,1 2 1 0 0,0-1-1 0 0,3 1 1 0 0,9 35-1 0 0,-4-13-5 0 0,-1-15-329 0 0,3 0 0 0 0,1 0 0 0 0,1-2 0 0 0,3 0 0 0 0,24 46 0 0 0,-40-82 90 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,1 1 0 0 0,-1-2-125 0 0,0 1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0-2 0 0 0,15-54-6572 0 0,-16 56 6808 0 0,17-129-7277 0 0,-1-3 3371 0 0,-7 103 3351 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="796.89">1454 184 488 0 0,'4'6'1437'0'0,"0"1"0"0"0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,0 2 0 0 0,-1-1 0 0 0,0-1 0 0 0,1 11 0 0 0,5 17 2154 0 0,7 48 364 0 0,4 117 0 0 0,-14-157-3301 0 0,-2-1-206 0 0,10 89 464 0 0,-2-104-858 0 0,-10-27-56 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,0-1 1 0 0,20-50-254 0 0,-15 40 203 0 0,61-228-1038 0 0,-20 58 323 0 0,-41 164 702 0 0,1 1 1 0 0,-1-1 0 0 0,2 1 0 0 0,10-16 0 0 0,-15 29 98 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,2 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-2-1 0 0 0,2 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,4 1 0 0 0,-2 1 103 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1 0 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,2 7 1 0 0,1 6-43 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,4 31-1 0 0,-6-21-205 0 0,-1 0-1 0 0,-2 0 1 0 0,0 1-1 0 0,-2 0 1 0 0,-1-2-1 0 0,-2 2 1 0 0,-6 28 0 0 0,4-36-1641 0 0,-1-1 0 0 0,-14 31 1 0 0,17-43 181 0 0,0-1 0 0 0,-1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-8 9 1 0 0,6-23-6157 0 0,4 6 7405 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,-1 1 1 0 0,1-2-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,2-4 1 0 0,14-40-1670 0 0,-7 20 1275 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1019.49">2265 1 128 0 0,'2'4'1285'0'0,"0"1"-1"0"0,1 0 1 0 0,-2 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 1 0 0,0-1-1 0 0,0 9 1 0 0,2 4 2699 0 0,26 150 8965 0 0,-5 0-7726 0 0,23 339-7799 0 0,-36-374 4074 0 0,-3-59-5405 0 0,-8-71 1649 0 0,0-23-8420 0 0,0 5 8675 0 0,2-30-3454 0 0,16-81 1 0 0,-7 48 3453 0 0,-5 25 1174 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -2400,10 +3931,10 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">476 274 412 0 0,'18'-21'2238'0'0,"-16"19"-1799"0"0,0 0 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,4-9 13363 0 0,-43 20-8439 0 0,-12 1-2282 0 0,41-8-2762 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,-13 10 0 0 0,-17 15 69 0 0,27-20-388 0 0,0-1-1 0 0,1 2 1 0 0,-1 0-1 0 0,2 0 1 0 0,-17 21-1 0 0,-4 12 0 0 0,1 2 0 0 0,2 1 0 0 0,-24 57 0 0 0,41-77 0 0 0,2 0 0 0 0,1 1 0 0 0,1 0 0 0 0,1 0 0 0 0,-2 30 0 0 0,6-39 0 0 0,1-1 0 0 0,1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,2-1 0 0 0,0 0 0 0 0,0 0 0 0 0,2-1 0 0 0,9 24 0 0 0,-11-33 2 0 0,0 0 0 0 0,0 0 1 0 0,1-1-1 0 0,0 1 0 0 0,0-1 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 0 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,1-1-1 0 0,-1 0 0 0 0,13 2 0 0 0,-7-3-447 0 0,0 0 0 0 0,0-2 0 0 0,0 1 0 0 0,0-2 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0-1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,19-11 0 0 0,0-4-2671 0 0,0-2-1 0 0,-1-1 1 0 0,-2-1 0 0 0,0-1-1 0 0,-2-2 1 0 0,39-50-1 0 0,-47 55 1019 0 0,39-39-1 0 0,-38 47 1418 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="505.57">1206 251 40 0 0,'-2'-22'1438'0'0,"1"20"-983"0"0,1 1 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-3-2 0 0 0,2 2 177 0 0,0 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,1 1-1 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 1 0 0,-3 1-1 0 0,-11 4 279 0 0,1 0 0 0 0,0 1 0 0 0,0 1 1 0 0,1 0-1 0 0,0 1 0 0 0,-24 20 0 0 0,19-11-342 0 0,0 0-1 0 0,2 1 0 0 0,-30 41 0 0 0,25-26-383 0 0,1 1-1 0 0,2 1 0 0 0,2 1 0 0 0,1 0 1 0 0,-17 60-1 0 0,30-85-168 0 0,0 1 0 0 0,0-1-1 0 0,1 1 1 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,4 23 0 0 0,-3-29-23 0 0,-1-1 1 0 0,1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1-1 0 0 0,6 2 0 0 0,-4-1-60 0 0,0 0-1 0 0,1-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,1-1 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,10-5 1 0 0,-6 2-126 0 0,-1-1 1 0 0,0 0 0 0 0,0-1 0 0 0,0-1 0 0 0,-1 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,9-12 0 0 0,7-16-546 0 0,-2-1 0 0 0,-1-1 0 0 0,-2-1 0 0 0,18-49 0 0 0,-25 55 349 0 0,-1-1 0 0 0,-2 0 0 0 0,-1 0 0 0 0,-2-1 0 0 0,-2 0-1 0 0,3-60 1 0 0,-11 69 451 0 0,2 27-38 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 192 0 0,-22 23 1320 0 0,21-19-1481 0 0,1 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,1 9 1 0 0,12 55 136 0 0,-5-33-76 0 0,69 302 509 0 0,-55-253-614 0 0,-20-75-366 0 0,0 0-1 0 0,1 0 0 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,0-1 0 0 0,7 10 1 0 0,-10-18 136 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,1-2 0 0 0,15-16-3599 0 0,-5-7 1320 0 0,0 1 0 0 0,-1-2 0 0 0,10-40 0 0 0,13-29-126 0 0,-20 62 2044 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="887.91">1739 204 52 0 0,'2'3'20396'0'0,"3"8"-15493"0"0,1 10-6307 0 0,-5-14 3383 0 0,11 127 1771 0 0,-1 1-1999 0 0,-8-39-1081 0 0,17 118 0 0 0,-19-201-670 0 0,-1-10-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,2 0 1 0 0,1 3-1 0 0,-4-8-44 0 0,1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,2-5 0 0 0,3-9-136 0 0,55-315-2132 0 0,-27 136 1313 0 0,-17 138 781 0 0,-16 55 211 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,4-3 0 0 0,-4 5 14 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 1 1 0 0,3 5-1 0 0,6 6 95 0 0,-2 1 0 0 0,0 0 0 0 0,11 26-1 0 0,-9-13 15 0 0,-1 1-1 0 0,-1 0 1 0 0,9 55-1 0 0,2 95-639 0 0,-17-149 200 0 0,-3 55-1903 0 0,-9-30-2526 0 0,-2-32-1387 0 0,10-22 5911 0 0,1-1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1-1 0 0 0,-10-20-6623 0 0,9 0 7037 0 0,2 7-757 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1215.7">2568 0 512 0 0,'0'0'2207'0'0,"14"23"12839"0"0,-2 25-8127 0 0,-1-11-4904 0 0,25 156 2853 0 0,-11 3-3668 0 0,28 160-1200 0 0,-37-298 73 0 0,1 2-710 0 0,-13-21-3139 0 0,-4-38 3649 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-16-14-3725 0 0,16 13 3623 0 0,-8-7-1292 0 0,1 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 0-1 0 0,-6-13 1 0 0,-1-7-1512 0 0,-16-55 0 0 0,27 80 2860 0 0,-7-28-574 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">461 270 412 0 0,'18'-21'2238'0'0,"-16"19"-1799"0"0,0 0 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-2-1 1 0 0,5-8 13363 0 0,-42 18-8439 0 0,-11 2-2282 0 0,39-8-2762 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0 0 0 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0 0 0 0 0,-14 10 0 0 0,-15 14 69 0 0,25-19-388 0 0,0-1-1 0 0,2 2 1 0 0,-2 0-1 0 0,2 0 1 0 0,-16 20-1 0 0,-4 13 0 0 0,1 1 0 0 0,2 1 0 0 0,-24 57 0 0 0,41-77 0 0 0,1 1 0 0 0,1 0 0 0 0,1 1 0 0 0,2 0 0 0 0,-3 29 0 0 0,6-39 0 0 0,1 0 0 0 0,1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,2 0 0 0 0,0 0 0 0 0,0 0 0 0 0,2-2 0 0 0,8 25 0 0 0,-10-33 2 0 0,0 0 0 0 0,0-1 1 0 0,1 0-1 0 0,0 1 0 0 0,-1-1 0 0 0,2 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,0 0-1 0 0,1 0 0 0 0,0-2 0 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 1 0 0,1-1-1 0 0,-2 0 0 0 0,14 2 0 0 0,-8-3-447 0 0,1 0 0 0 0,0-2 0 0 0,-1 1 0 0 0,1-2 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,-1-1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,18-10 0 0 0,0-5-2671 0 0,0-2-1 0 0,-1 0 1 0 0,-1-2 0 0 0,-1-1-1 0 0,-2-1 1 0 0,38-50-1 0 0,-46 54 1019 0 0,39-38-1 0 0,-38 46 1418 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="505.57">1169 247 40 0 0,'-2'-21'1438'0'0,"1"19"-983"0"0,1 1 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-3-2 0 0 0,2 2 177 0 0,0 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,2 0 1 0 0,-2 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,1 1-1 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 1 0 0,-3 1-1 0 0,-10 4 279 0 0,0 0 0 0 0,1 1 0 0 0,-1 0 1 0 0,2 1-1 0 0,-1 1 0 0 0,-23 20 0 0 0,19-12-342 0 0,-1 1-1 0 0,3 1 0 0 0,-30 40 0 0 0,25-26-383 0 0,1 2-1 0 0,1 0 0 0 0,3 2 0 0 0,0-1 1 0 0,-16 60-1 0 0,29-84-168 0 0,0 0 0 0 0,0 0-1 0 0,1 1 1 0 0,2 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,3 23 0 0 0,-2-30-23 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1-1 0 0 0,5 2 0 0 0,-3-1-60 0 0,0 0-1 0 0,1-1 0 0 0,-2 0 1 0 0,1 0-1 0 0,1-1 1 0 0,-1 0-1 0 0,0-1 1 0 0,0 0-1 0 0,1 0 0 0 0,-2-1 1 0 0,1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,9-5 1 0 0,-5 2-126 0 0,-2-1 1 0 0,1 1 0 0 0,0-2 0 0 0,-1-1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,8-11 0 0 0,7-17-546 0 0,-1 0 0 0 0,-2-2 0 0 0,-2 0 0 0 0,18-49 0 0 0,-24 55 349 0 0,-2-2 0 0 0,-1 1 0 0 0,-1 0 0 0 0,-3-2 0 0 0,-1 1-1 0 0,3-60 1 0 0,-11 69 451 0 0,2 26-38 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 192 0 0,-21 22 1320 0 0,20-18-1481 0 0,1 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,1 9 1 0 0,12 54 136 0 0,-5-33-76 0 0,66 298 509 0 0,-53-249-614 0 0,-19-74-366 0 0,0-1-1 0 0,1 1 0 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,0-1 0 0 0,7 9 1 0 0,-11-17 136 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,1-2 0 0 0,14-16-3599 0 0,-4-7 1320 0 0,0 2 0 0 0,-2-3 0 0 0,11-39 0 0 0,12-29-126 0 0,-20 62 2044 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="887.91">1686 201 52 0 0,'2'3'20396'0'0,"3"8"-15493"0"0,1 9-6307 0 0,-5-13 3383 0 0,10 125 1771 0 0,0 1-1999 0 0,-8-38-1081 0 0,16 115 0 0 0,-18-197-670 0 0,-1-10-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,2 0 1 0 0,1 3-1 0 0,-4-8-44 0 0,1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,2-5 0 0 0,2-8-136 0 0,55-311-2132 0 0,-27 134 1313 0 0,-17 136 781 0 0,-15 54 211 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,4-3 0 0 0,-4 5 14 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,2 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 1-1 0 0,1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 1 1 0 0,3 5-1 0 0,5 5 95 0 0,-1 2 0 0 0,0 0 0 0 0,10 25-1 0 0,-8-12 15 0 0,-2 0-1 0 0,0 1 1 0 0,9 54-1 0 0,1 93-639 0 0,-16-146 200 0 0,-3 53-1903 0 0,-9-29-2526 0 0,-2-31-1387 0 0,10-22 5911 0 0,1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1-1 0 0 0,-10-20-6623 0 0,9 1 7037 0 0,2 6-757 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1215.7">2490 0 512 0 0,'0'0'2207'0'0,"13"23"12839"0"0,-1 24-8127 0 0,-1-11-4904 0 0,24 154 2853 0 0,-11 3-3668 0 0,27 158-1200 0 0,-35-294 73 0 0,0 2-710 0 0,-12-20-3139 0 0,-4-38 3649 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-15-14-3725 0 0,15 13 3623 0 0,-8-7-1292 0 0,1 0-1 0 0,2 0 1 0 0,-2-1 0 0 0,1 1-1 0 0,-6-14 1 0 0,0-7-1512 0 0,-16-53 0 0 0,26 78 2860 0 0,-7-28-574 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -2435,10 +3966,10 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">396 117 316 0 0,'0'-2'429'0'0,"0"1"-1"0"0,0 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-2 0 1 0 0,-1-1 360 0 0,1 0 0 0 0,-1 1 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-6 1 0 0 0,3 0-296 0 0,1 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 2 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0 0 1 0 0,0 1 0 0 0,-8 4-1 0 0,-3 7-303 0 0,1 0-1 0 0,0 1 1 0 0,1 1 0 0 0,1 0-1 0 0,1 2 1 0 0,0-1-1 0 0,1 1 1 0 0,-18 39 0 0 0,10-16-154 0 0,3 0 0 0 0,1 2 1 0 0,2 0-1 0 0,2 1 0 0 0,1 0 1 0 0,-7 81-1 0 0,17-111-97 0 0,1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,0-1 0 0 0,1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,12 16 0 0 0,-14-24-271 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0-1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1-1-1 0 0,1 0 1 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-2 0 0 0,0 1 0 0 0,0-1-1 0 0,11-2 1 0 0,1-1-847 0 0,0-1 0 0 0,0 0-1 0 0,0-2 1 0 0,0 0 0 0 0,-1-1-1 0 0,25-16 1 0 0,30-23-2751 0 0,118-101-1 0 0,-157 116 3415 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="397.59">1027 358 380 0 0,'34'-41'17058'0'0,"-43"36"-15028"0"0,-38 22 2999 0 0,38-14-4818 0 0,0-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,1 1 1 0 0,0 0-1 0 0,0 0 1 0 0,-14 11-1 0 0,10-4-86 0 0,0 0 0 0 0,1 1 1 0 0,0 0-1 0 0,0 1 0 0 0,2 0 0 0 0,-1 0 0 0 0,2 1 0 0 0,0 0 0 0 0,-11 27 1 0 0,12-19-107 0 0,0 0 0 0 0,2 0 0 0 0,1 0 0 0 0,0 0 0 0 0,2 1 1 0 0,0 32-1 0 0,3-46-51 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,0-1-1 0 0,1 1 0 0 0,0 0 1 0 0,0-1-1 0 0,1 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0-1-1 0 0,1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,1 0 0 0 0,0 0 1 0 0,11 8-1 0 0,-12-12-57 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,5-2 0 0 0,-1 0-92 0 0,0 0-1 0 0,0-1 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0-2 1 0 0,12-10-1 0 0,4-7-467 0 0,-1-1 1 0 0,-1-1-1 0 0,32-47 1 0 0,-30 36 147 0 0,-2 0 1 0 0,-1-2-1 0 0,-1-1 1 0 0,18-56 0 0 0,-33 86 1532 0 0,-7 24 966 0 0,0 6-1650 0 0,3 25-248 0 0,3 0 1 0 0,1 0 0 0 0,2-1 0 0 0,24 78-1 0 0,-24-100-439 0 0,1 0 0 0 0,13 24 0 0 0,-17-40-356 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,1 0 0 0 0,-1-1 0 0 0,1 0 1 0 0,0 0-1 0 0,10 7 0 0 0,-15-12 474 0 0,-1-1 1 0 0,1 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-2 1 0 0,12-22-3038 0 0,-3-30 868 0 0,-1 3 1014 0 0,-4 24 863 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="794.02">1583 186 480 0 0,'9'48'6929'0'0,"-8"-35"-5373"0"0,19 138 9192 0 0,1 78-6483 0 0,-16-164-3762 0 0,5 105 312 0 0,-10-169-810 0 0,-1 1-1 0 0,1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,1 2 0 0 0,-1-5-14 0 0,0 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-2 0 0 0,70-301-1330 0 0,-63 272 1226 0 0,1 0 0 0 0,1 1 0 0 0,1 0 1 0 0,26-52-1 0 0,-33 78 110 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,10-4 1 0 0,-11 6 39 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,4 2 0 0 0,3 4 198 0 0,0 0 1 0 0,-1 0-1 0 0,-1 1 0 0 0,1 0 0 0 0,-2 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,-1 0 0 0 0,0 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,6 24 0 0 0,-4-4 100 0 0,-1 0 0 0 0,-2 1-1 0 0,0 65 1 0 0,-4-79-670 0 0,-2 0 0 0 0,1 0 0 0 0,-6 20 1 0 0,-9 8-3407 0 0,-9-10-5867 0 0,20-37 3289 0 0,4 0 6174 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0-1 0 0 0,3-26-1352 0 0,-2 21 1068 0 0,0-11-221 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1011.53">2398 1 148 0 0,'1'5'1176'0'0,"0"0"0"0"0,0 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,6 8-1 0 0,6 17 3784 0 0,23 85 6034 0 0,-4 1-5181 0 0,6 49-3605 0 0,-18-57-2591 0 0,10 175 1 0 0,-23-193 466 0 0,0 21-2944 0 0,-12-38-4618 0 0,5-84-4558 0 0,-1-14 6175 0 0,4-98 2183 0 0,-3 69 2888 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">383 115 316 0 0,'0'-2'429'0'0,"0"1"-1"0"0,0 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-2 0 1 0 0,-1-1 360 0 0,1 0 0 0 0,-1 1 0 0 0,0 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,-6 1 0 0 0,3 0-296 0 0,2 0-1 0 0,-2 0 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 2 1 0 0,1-1-1 0 0,-2 1 1 0 0,1 0-1 0 0,0 0 1 0 0,0 1 0 0 0,-7 4-1 0 0,-4 6-303 0 0,2 1-1 0 0,-1 1 1 0 0,2 1 0 0 0,0 0-1 0 0,2 1 1 0 0,-1 0-1 0 0,2 1 1 0 0,-19 38 0 0 0,11-16-154 0 0,3 1 0 0 0,0 1 1 0 0,3 1-1 0 0,1 0 0 0 0,1 0 1 0 0,-6 81-1 0 0,16-111-97 0 0,1 2 0 0 0,1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,0-2 0 0 0,1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,2 0 0 0 0,0-1 0 0 0,1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,13 16 0 0 0,-14-25-271 0 0,0 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1-1 0 0,1 0 1 0 0,0 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-2 0 0 0,0 1 0 0 0,0-1-1 0 0,10-2 1 0 0,1-1-847 0 0,1-1 0 0 0,-1 0-1 0 0,0-2 1 0 0,1 0 0 0 0,-2-1-1 0 0,25-15 1 0 0,29-24-2751 0 0,113-99-1 0 0,-151 115 3415 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="397.59">994 353 380 0 0,'33'-40'17058'0'0,"-42"35"-15028"0"0,-36 21 2999 0 0,36-13-4818 0 0,0-1-1 0 0,2 1 1 0 0,-2 0-1 0 0,1 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-15 11-1 0 0,11-4-86 0 0,-1 0 0 0 0,1 0 1 0 0,1 1-1 0 0,-1 1 0 0 0,2 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1 0 0 0,-10 27 1 0 0,11-20-107 0 0,0 1 0 0 0,2 0 0 0 0,2-1 0 0 0,-1 1 0 0 0,2 1 1 0 0,0 31-1 0 0,3-45-51 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,1-1 1 0 0,0 0-1 0 0,0 1 0 0 0,1 0 1 0 0,0-1-1 0 0,1 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,1-1-1 0 0,1 1 0 0 0,0 0 1 0 0,10 8-1 0 0,-11-12-57 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,5-2 0 0 0,-2 0-92 0 0,1 0-1 0 0,0-1 0 0 0,-1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-2 1 0 0,11-9-1 0 0,4-8-467 0 0,0-1 1 0 0,-2 0-1 0 0,31-47 1 0 0,-29 35 147 0 0,-1 1 1 0 0,-2-3-1 0 0,-1 0 1 0 0,18-56 0 0 0,-32 85 1532 0 0,-7 24 966 0 0,0 6-1650 0 0,3 24-248 0 0,3 0 1 0 0,1 1 0 0 0,2-2 0 0 0,23 77-1 0 0,-24-98-439 0 0,2 0 0 0 0,12 23 0 0 0,-16-39-356 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 0 0 0,0 0 0 0 0,1 0 1 0 0,0 0-1 0 0,9 7 0 0 0,-14-12 474 0 0,-1-1 1 0 0,1 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-2 1 0 0,11-22-3038 0 0,-2-29 868 0 0,-1 3 1014 0 0,-4 23 863 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="794.02">1532 183 480 0 0,'9'48'6929'0'0,"-8"-35"-5373"0"0,18 135 9192 0 0,1 78-6483 0 0,-15-162-3762 0 0,5 104 312 0 0,-10-167-810 0 0,-1 1-1 0 0,1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,1 2 0 0 0,-1-5-14 0 0,0 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-2 0 0 0,68-297-1330 0 0,-61 269 1226 0 0,1-1 0 0 0,0 1 0 0 0,2 1 1 0 0,25-52-1 0 0,-32 77 110 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-2 1 0 0 0,2-1 0 0 0,0 2 0 0 0,0-1-1 0 0,0 0 1 0 0,1 0 0 0 0,0 1 0 0 0,-2 0 0 0 0,2 0 0 0 0,0 0-1 0 0,10-4 1 0 0,-11 6 39 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,2 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,4 2 0 0 0,2 4 198 0 0,1-1 1 0 0,-1 1-1 0 0,-1 1 0 0 0,0 0 0 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,-2-1 0 0 0,1 2 1 0 0,-1 0-1 0 0,0 0 0 0 0,6 23 0 0 0,-5-3 100 0 0,0-1 0 0 0,-2 2-1 0 0,0 64 1 0 0,-4-79-670 0 0,-2 1 0 0 0,1 0 0 0 0,-6 19 1 0 0,-8 9-3407 0 0,-10-11-5867 0 0,21-36 3289 0 0,3 0 6174 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0-1 0 0 0,3-25-1352 0 0,-2 20 1068 0 0,0-11-221 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1011.53">2321 1 148 0 0,'1'5'1176'0'0,"0"0"0"0"0,0 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1-1 1 0 0,7 9-1 0 0,6 17 3784 0 0,22 83 6034 0 0,-4 2-5181 0 0,5 47-3605 0 0,-16-55-2591 0 0,9 172 1 0 0,-23-190 466 0 0,1 20-2944 0 0,-12-37-4618 0 0,5-83-4558 0 0,-1-13 6175 0 0,4-98 2183 0 0,-3 69 2888 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -2462,7 +3993,7 @@
           <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2025-04-17T13:14:46.458"/>
+      <inkml:timestamp xml:id="ts0" timeString="2025-04-17T13:14:47.948"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -2470,18 +4001,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">35 125 56 0 0,'-11'7'758'0'0,"0"0"2317"0"0,1-3 3398 0 0,9-4-5815 0 0,10 9 371 0 0,21 5-1105 0 0,-14-9 50 0 0,-14-5 19 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,1-1 0 0 0,7-5-76 0 0,5-5-9 0 0,-13 10 90 0 0,-1-1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-2-4 0 0 0,1 3 8 0 0,-21-48 725 0 0,22 51-622 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 0-1 0 0,1 1 1 0 0,-3 0-1 0 0,1 1 60 0 0,0 0 0 0 0,-1 0-1 0 0,2 0 1 0 0,-1 0 0 0 0,0 1 0 0 0,0-1-1 0 0,1 1 1 0 0,0 0 0 0 0,-1 0 0 0 0,1-1-1 0 0,0 2 1 0 0,0-1 0 0 0,1 0 0 0 0,-1 0-1 0 0,-1 5 1 0 0,0 0-138 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,1 12 0 0 0,-1-16-42 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 1 0 0,0 1-1 0 0,1-1 0 0 0,0 0 0 0 0,4 2 1 0 0,-5-3 6 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,4-1 0 0 0,-2-1 4 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,2-6 0 0 0,0-3 18 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1-1 1 0 0,0-22-1 0 0,-1 34 18 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,-1 0 0 0 0,1 1 32 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 1 1 0 0,1-1 0 0 0,0 0 0 0 0,-2 4 0 0 0,-4 12 25 0 0,5-13-87 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 0 0 0,2 10 1 0 0,-2-13-8 0 0,-1-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,1 0 0 0 0,0-1 12 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,2-6 0 0 0,0 3 12 0 0,1-4 42 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1-13 0 0 0,-3 22-16 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1-1 0 0,0-1 1 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-2 0 0 0 0,-24 4 1015 0 0,22-3-949 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,-5 6 1 0 0,7-5-107 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 8 0 0 0,2-12-19 0 0,0 1 1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,3 3-1 0 0,-2-4 3 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,2-2-1 0 0,0 0 46 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1-6 0 0 0,-2 10 92 0 0,-11-4 2356 0 0,10 6-2449 0 0,-1-1 1 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 2 0 0 0,-1-2-72 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 1 0 0,3 3-1 0 0,-2-4 20 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0-2-1 0 0,3-2 40 0 0,-1 0-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,2-14-1 0 0,-3 18-2 0 0,-2-19 151 0 0,2 22-162 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,-2 2 16 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 1-1 0 0,-2 5 1 0 0,0 0-58 0 0,1 1 0 0 0,0-1 0 0 0,1 0 0 0 0,0 1 0 0 0,1 12 0 0 0,0-21 20 0 0,10-38 16 0 0,-10 37-9 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,-22 3-2057 0 0,17 0 996 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-5 5 1 0 0,5-2 14 0 0,0 0 1 0 0,1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,1 0 1 0 0,0 0-1 0 0,0 1 1 0 0,1-1-1 0 0,0 1 1 0 0,-1 8 0 0 0,-1 8-755 0 0,1-1 1 0 0,1 34 0 0 0,2-34 988 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1490.55">49 885 4 0 0,'-3'0'9418'0'0,"-5"5"-4424"0"0,6-4-4678 0 0,0 0-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,1-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 3 1 0 0,-12 51 2038 0 0,23-14-1955 0 0,-9-41-398 0 0,0 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1-1 1 0 0,4 2-1 0 0,-2-2 3 0 0,0-1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,2-6-1 0 0,3-11 30 0 0,0 1 0 0 0,4-29 0 0 0,-9 40-7 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,-4-11 0 0 0,5 17 20 0 0,1 1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,-2-1-1 0 0,1 2 2 0 0,0-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 1-1 0 0,-1 1 1 0 0,-4 8 3 0 0,0 0 1 0 0,1 1-1 0 0,0-1 1 0 0,1 1-1 0 0,0 0 0 0 0,0 1 1 0 0,2-1-1 0 0,-1 1 0 0 0,2-1 1 0 0,0 1-1 0 0,0 16 1 0 0,1-28-55 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,2 0 1 0 0,1-2 11 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1-1 0 0,7-7 1 0 0,-3 1 21 0 0,0-1-1 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,7-18 1 0 0,3-2 27 0 0,-16 30-41 0 0,1 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,1 1 1 0 0,-27 13 703 0 0,21-7-713 0 0,1 0-1 0 0,0 0 1 0 0,0 1-1 0 0,1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1 0 1 0 0,-1 0-1 0 0,2 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,1 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,5 9 1 0 0,-6-15-13 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 0-1 0 0,2 0 0 0 0,-2-1 8 0 0,1 1-1 0 0,-1-1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,2-3 1 0 0,1-5 21 0 0,1 0 1 0 0,-1-1-1 0 0,-1 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,0 1 0 0 0,1-19-1 0 0,-3 26-1 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-5-3 0 0 0,4 4 7 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,0 5 1 0 0,0 1-78 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,0 1-1 0 0,1-1 1 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,0 1 0 0 0,5 11 0 0 0,-7-20 29 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,1 0 1 0 0,15-20-162 0 0,6-35 254 0 0,-18 41-24 0 0,-1-1 0 0 0,-1 0 0 0 0,0 0 1 0 0,1-26-1 0 0,-4 39 278 0 0,-2 3-317 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,1 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,1 5-1 0 0,-1-5-85 0 0,5 7-863 0 0,10-20 823 0 0,12-12 156 0 0,-23 19 7 0 0,-3 4-31 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1 0 1 0 0,0-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-3-1 0 0,-1 4 346 0 0,-29 5 8 0 0,28-4-375 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1 0 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-2 2 0 0 0,-1-1-452 0 0,4-3 220 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,-4-35-6823 0 0,3 31 6468 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 1 1 0 0,2-9-1 0 0,2-19-1888 0 0,-5 28 2240 0 0,0 0 1 0 0,0 1-1 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 1 0 0,2 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,3-4-1 0 0,4-2-344 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2463.25">266 148 232 0 0,'-10'8'23916'0'0,"10"-7"-23213"0"0,5 14 1975 0 0,47 11-1021 0 0,-4-1-583 0 0,1-2 1 0 0,89 28 0 0 0,7-8-688 0 0,87 21-417 0 0,-196-57 30 0 0,488 123 0 0 0,-391-87 0 0 0,-121-37 0 0 0,-11-5 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,2-1 0 0 0,-25-5-3100 0 0,-1 0 0 0 0,1-1 0 0 0,0-1 0 0 0,1-1 0 0 0,-30-16 0 0 0,26 13-259 0 0,19 9 2763 0 0,0 1 1 0 0,-1-2-1 0 0,1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,2 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-5-8-1 0 0,4 0 51 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2746.88">1472 259 444 0 0,'16'13'14412'0'0,"30"12"-7370"0"0,-13-6-5194 0 0,27 14 357 0 0,-35-20-1492 0 0,-1 0 0 0 0,0 2 0 0 0,-1 1 1 0 0,36 32-1 0 0,-51-41-545 0 0,-1 0-1 0 0,0 1 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,8 15-1 0 0,-13-21-122 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-4 2 1 0 0,-40 34 36 0 0,34-26-434 0 0,-1-1 0 0 0,0-1 0 0 0,-1 1 0 0 0,-1-2-1 0 0,1 0 1 0 0,-18 7 0 0 0,-42 21-3623 0 0,31-19-353 0 0,27-11 1475 0 0,1 0 0 0 0,-1-1 0 0 0,-33 7-1 0 0,44-12 2375 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 1 0 0,-5-5-1 0 0,-5-6-156 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5819.81">2216 27 256 0 0,'0'0'291'0'0,"0"0"0"0"0,1 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 20 2975 0 0,-11 20-2759 0 0,11-38-197 0 0,-60 229 652 0 0,35-119-2568 0 0,22-99 995 0 0,-4 20-828 0 0,5-14-2907 0 0,-15-52 386 0 0,17 17 2977 0 0,0 1 0 0 0,3-32-1 0 0,2 28 509 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5984.26">2155 185 236 0 0,'0'-1'185'0'0,"0"0"0"0"0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,2 2 0 0 0,19 6 1105 0 0,-11-5-1072 0 0,-1 0 1 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,19-7 0 0 0,-5-1 59 0 0,-17 7-3649 0 0,-29 13-42 0 0,-69 39-2351 0 0,85-45 5412 0 0,-4 6-185 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6127.66">2263 254 216 0 0,'0'6'624'0'0,"1"-1"-1"0"0,0 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0-1 0 0,3 5 1 0 0,4 11 1368 0 0,1-5-1578 0 0,0-3-1574 0 0,-6-1-3576 0 0,6-16 3710 0 0,3 3 601 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6444.81">2673 92 184 0 0,'2'0'269'0'0,"-1"0"1"0"0,1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 2-1 0 0,0 13 225 0 0,0 0-1 0 0,-1 0 0 0 0,-7 26 1 0 0,3-17-410 0 0,-6 17 76 0 0,12-42-128 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0 0 0 0,-3 1 0 0 0,3-1 35 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 1-1 0 0,1-3 1 0 0,10-6 3 0 0,1 0 1 0 0,-1 1 0 0 0,1 1 0 0 0,1 0 0 0 0,16-7 0 0 0,12-7 17 0 0,118-59-2108 0 0,-185 79-8281 0 0,19 1 9841 0 0,0 1 0 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,-11 4 1 0 0,-17 17-1327 0 0,22-14 1408 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6595.22">2753 222 192 0 0,'0'0'867'0'0,"37"42"7540"0"0,35 78-4255 0 0,-71-118-4034 0 0,-2-2-254 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,-10-4 276 0 0,-103-20-7010 0 0,93 19 6380 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7240.15">2272 445 260 0 0,'1'1'224'0'0,"-1"0"0"0"0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1-1 0 0,1-1 1 0 0,1-1 0 0 0,43 3 2140 0 0,-41-2-1760 0 0,196-14 3200 0 0,-60 5-2991 0 0,-140 9-703 0 0,-44 10 61 0 0,18-3-156 0 0,0 1 0 0 0,0 1 0 0 0,-32 16-1 0 0,-8 4-25 0 0,26-12 2 0 0,1 1 0 0 0,-54 35 0 0 0,75-39 1 0 0,17-14 7 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,35-2-147 0 0,-8-1 184 0 0,10 0 60 0 0,0-1 1 0 0,59-15-1 0 0,-46 9 29 0 0,6 0 77 0 0,-55 10 128 0 0,-20 14-30 0 0,-132 107-72 0 0,133-105-224 0 0,0 0-1 0 0,-2-1 1 0 0,1-1-1 0 0,-32 16 1 0 0,50-30-2 0 0,1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0-1-1 0 0,-1 1 0 0 0,4-13 74 0 0,14-19 52 0 0,-15 30-110 0 0,4-8 31 0 0,1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,1 1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 1 1 0 0,1 0-1 0 0,-1 1 1 0 0,1 0-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,20 0-1 0 0,-15 1 26 0 0,-1 2 0 0 0,1-1 1 0 0,-1 2-1 0 0,1 0 0 0 0,-1 1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 1-1 0 0,-1 1 0 0 0,0 0 0 0 0,0 1 0 0 0,0 0 1 0 0,-1 1-1 0 0,21 16 0 0 0,-25-16-104 0 0,0 0 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,8 13-1 0 0,-13-21-109 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-3 3 0 0 0,0-1-318 0 0,0-1-1 0 0,1 0 1 0 0,-2 0-1 0 0,1 0 1 0 0,0-1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,-9 0 1 0 0,7-1 83 0 0,0 0 1 0 0,0-1 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,1 0 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0-1 1 0 0,-13-9 0 0 0,1-1-109 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7469.56">2465 217 124 0 0,'0'0'1117'0'0,"10"39"2866"0"0,-6-22-3013 0 0,-1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,-1 30-1 0 0,0 5 322 0 0,2-11-701 0 0,23 490 2185 0 0,-27-492-3140 0 0,-11 69 0 0 0,12-107 315 0 0,0-1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1-1-55 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,-24-49-3546 0 0,17 25 2609 0 0,2 0 1 0 0,0 0-1 0 0,2-1 1 0 0,1 0-1 0 0,1-47 1 0 0,1 70 992 0 0,0-21-351 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7614.21">2432 774 136 0 0,'1'-1'183'0'0,"-1"0"1"0"0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,-1-1 0 0 0,-1 1 202 0 0,1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,0-1-1 0 0,1 1 1 0 0,-3 1 0 0 0,-21 24 1565 0 0,-34 49 1 0 0,17-21-1507 0 0,10-23-158 0 0,-7-8-3637 0 0,37-24 3031 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-2-4 0 0 0,-15-17-2151 0 0,18 13 1903 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">46 868 4 0 0,'-3'0'9418'0'0,"-4"5"-4424"0"0,5-4-4678 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 1-1 0 0,1 0 1 0 0,0-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 3 1 0 0,-11 50 2038 0 0,21-14-1955 0 0,-8-40-398 0 0,0 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-2 0-1 0 0,2 0 0 0 0,-1-1 1 0 0,4 1-1 0 0,-2-1 3 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-2 0 0 0 0,2 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,2-5-1 0 0,3-12 30 0 0,-1 1 0 0 0,5-28 0 0 0,-9 39-7 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,-4-11 0 0 0,5 17 20 0 0,1 1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 1-1 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,0 2 2 0 0,0-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 1-1 0 0,0 1 1 0 0,-5 8 3 0 0,0 0 1 0 0,2 1-1 0 0,-1-2 1 0 0,1 2-1 0 0,0 0 0 0 0,0 1 1 0 0,3-2-1 0 0,-2 2 0 0 0,2-1 1 0 0,0 1-1 0 0,0 15 1 0 0,1-27-55 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,0-1 0 0 0,1 0 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,2 0 1 0 0,1-2 11 0 0,0 1 0 0 0,0-1 0 0 0,-1 2 0 0 0,1-2 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,7-7 1 0 0,-4 1 21 0 0,1-1-1 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,-1-1-1 0 0,6-17 1 0 0,3-3 27 0 0,-15 30-41 0 0,1 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,1 1 1 0 0,-26 13 703 0 0,20-7-713 0 0,2 0-1 0 0,-1 0 1 0 0,0 1-1 0 0,1-1 1 0 0,0 0-1 0 0,1 1 0 0 0,0 0 1 0 0,-1 0-1 0 0,2 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1-1-1 0 0,1 2 1 0 0,-1-1-1 0 0,1 0 0 0 0,1 0 1 0 0,-2 0-1 0 0,6 8 1 0 0,-6-14-13 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,2 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 0 1 0 0,-2 1-1 0 0,2-1 1 0 0,0 0-1 0 0,2 0 0 0 0,-2-1 8 0 0,1 1-1 0 0,-1-1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,-1 0 0 0 0,3-2 1 0 0,1-6 21 0 0,1 0 1 0 0,-1-1-1 0 0,-2 1 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,1-18-1 0 0,-3 25-1 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,-5-3 0 0 0,4 4 7 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,0 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,0 1 1 0 0,1-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0 0 0 0 0,2 0-1 0 0,-2 1 1 0 0,1-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,0 5 1 0 0,0 1-78 0 0,0 1 0 0 0,0-1 0 0 0,1-1 0 0 0,0 2-1 0 0,1-1 1 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1 0 0 0,5 10 0 0 0,-7-19 29 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,1 0 1 0 0,14-19-162 0 0,5-35 254 0 0,-16 40-24 0 0,-1-1 0 0 0,-1 1 0 0 0,0-1 1 0 0,0-25-1 0 0,-3 38 278 0 0,-1 3-317 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,1 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,1 5-1 0 0,-1-5-85 0 0,5 7-863 0 0,9-20 823 0 0,11-12 156 0 0,-21 19 7 0 0,-3 4-31 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-3-1 0 0,0 4 346 0 0,-29 5 8 0 0,27-4-375 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,0-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-2 1 0 0 0,-1 0-452 0 0,4-3 220 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,-4-35-6823 0 0,3 31 6468 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 1 1 0 0,2-8-1 0 0,2-20-1888 0 0,-5 28 2240 0 0,0 0 1 0 0,0 1-1 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 1 0 0,2 0-1 0 0,-1 1 0 0 0,-1-1 1 0 0,4-4-1 0 0,4-2-344 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -2749,47 +4269,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A66:J78"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
       <c r="D66" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
       <c r="G66" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
-      <c r="D67" s="1"/>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
     </row>
-    <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
       <c r="D68" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
       <c r="G68" s="2" t="s">
         <v>5</v>
       </c>
@@ -2797,40 +4317,40 @@
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
       <c r="D70" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A71" s="1"/>
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
     </row>
-    <row r="78" spans="1:10" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="C78" s="3"/>
+    <row r="78" spans="1:10" ht="25" x14ac:dyDescent="0.5">
+      <c r="C78" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2852,9 +4372,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7B3A893-A98A-42C4-8725-BE8AEC17811B}">
   <dimension ref="A46:H49"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="46" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>0</v>
       </c>
@@ -2868,7 +4388,7 @@
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -2878,22 +4398,22 @@
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
       <c r="D48" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
